--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Loyalty Program\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646D5A51-6C36-4BD2-8DEB-5E38F5904CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17ED9FA7-6F98-478F-A575-B59115CC1FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -8379,7 +8379,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="45">
+    <row r="22" spans="1:17" ht="30">
       <c r="A22" s="4" t="s">
         <v>1173</v>
       </c>
@@ -14481,7 +14481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="45">
+    <row r="78" spans="1:23" ht="30">
       <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="45">
+    <row r="79" spans="1:23" ht="30">
       <c r="A79" s="4" t="s">
         <v>10</v>
       </c>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17ED9FA7-6F98-478F-A575-B59115CC1FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0E5EAC-9517-4640-A34C-6226E976EC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -16,13 +16,14 @@
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
     <sheet name="Atributes" sheetId="2" r:id="rId2"/>
     <sheet name="Reference Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Relationships" sheetId="4" r:id="rId4"/>
-    <sheet name="Validation Rules" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
+    <sheet name="Relationships" sheetId="4" r:id="rId5"/>
+    <sheet name="Validation Rules" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atributes!$A$1:$W$396</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reference Data'!$A$1:$H$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Relationships!$A$1:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Relationships!$A$1:$K$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10209" uniqueCount="2225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10285" uniqueCount="2258">
   <si>
     <t>Domain</t>
   </si>
@@ -6709,6 +6710,105 @@
   </si>
   <si>
     <t>Store must belong to the Offer's Organization.</t>
+  </si>
+  <si>
+    <t>Entity Type Code</t>
+  </si>
+  <si>
+    <t>ORGANIZATION</t>
+  </si>
+  <si>
+    <t>ORGANIZATION_USER</t>
+  </si>
+  <si>
+    <t>MEMBERSHIP_PRODUCT</t>
+  </si>
+  <si>
+    <t>SUBSCRIPTION_PLAN</t>
+  </si>
+  <si>
+    <t>REDEMPTION</t>
+  </si>
+  <si>
+    <t>ORGANIZATION_BRANDING</t>
+  </si>
+  <si>
+    <t>NOTIFICATION_CONFIGURATION</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Statuses</t>
+  </si>
+  <si>
+    <t>PENDING, ACTIVE, INACTIVE, SUSPENDED, CLOSED</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>PENDING, ACTIVE, INACTIVE, SUSPENDED, LOCKED, CLOSED</t>
+  </si>
+  <si>
+    <t>ACTIVE, INACTIVE, RETIRED</t>
+  </si>
+  <si>
+    <t>ORGANIZATION_USER_ROLE</t>
+  </si>
+  <si>
+    <t>PENDING, ACTIVE, INACTIVE, REVOKED*</t>
+  </si>
+  <si>
+    <t>PRIVILEGE</t>
+  </si>
+  <si>
+    <t>Organization User / Platform User Role</t>
+  </si>
+  <si>
+    <t>PLATFORM_USER_ROLE</t>
+  </si>
+  <si>
+    <t>DRAFT, ACTIVE, INACTIVE, EXPIRED, RETIRED</t>
+  </si>
+  <si>
+    <t>PENDING, ACTIVE, INACTIVE, EXPIRED, CANCELLED</t>
+  </si>
+  <si>
+    <t>SUCCESS, FAILED, REVERSED</t>
+  </si>
+  <si>
+    <t>PENDING, ACTIVE, INACTIVE, CLOSED</t>
+  </si>
+  <si>
+    <t>PENDING, ACTIVE, INACTIVE, RELIEVED, RETIRED</t>
+  </si>
+  <si>
+    <t>STAFF_STORE_ASSIGNMENT</t>
+  </si>
+  <si>
+    <t>DRAFT, ACTIVE, INACTIVE</t>
+  </si>
+  <si>
+    <t>PENDING, SUCCESS, FAILED, REVERSED</t>
+  </si>
+  <si>
+    <t>DRAFT, ACTIVE, INACTIVE, SUSPENDED</t>
+  </si>
+  <si>
+    <t>ACTIVE, INACTIVE</t>
+  </si>
+  <si>
+    <t>TEMPLATE</t>
+  </si>
+  <si>
+    <t>DRAFT, ACTIVE, INACTIVE, RETIRED</t>
+  </si>
+  <si>
+    <t>TEMPLATE_TYPE</t>
+  </si>
+  <si>
+    <t>DRAFT, ACTIVE, INACTIVE, EXPIRED, CANCELLED</t>
   </si>
 </sst>
 </file>
@@ -6757,12 +6857,18 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -6778,7 +6884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6828,6 +6934,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8379,7 +8488,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="30">
+    <row r="22" spans="1:17" ht="45">
       <c r="A22" s="4" t="s">
         <v>1173</v>
       </c>
@@ -9237,6 +9346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W396"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9336,7 +9446,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="30">
+    <row r="2" spans="1:23" ht="30" hidden="1">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -9402,7 +9512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30">
+    <row r="3" spans="1:23" ht="30" hidden="1">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -9470,7 +9580,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30">
+    <row r="4" spans="1:23" ht="30" hidden="1">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -9538,7 +9648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="60">
+    <row r="5" spans="1:23" ht="60" hidden="1">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -9607,7 +9717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30">
+    <row r="6" spans="1:23" ht="30" hidden="1">
       <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
@@ -9675,7 +9785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -9811,7 +9921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -9879,7 +9989,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -9947,7 +10057,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
@@ -10015,7 +10125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30">
+    <row r="12" spans="1:23" ht="30" hidden="1">
       <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
@@ -10083,7 +10193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" hidden="1">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -10151,7 +10261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="30">
+    <row r="14" spans="1:23" ht="30" hidden="1">
       <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
@@ -10219,7 +10329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -10287,7 +10397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="30">
+    <row r="16" spans="1:23" ht="30" hidden="1">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -10355,7 +10465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" hidden="1">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -10423,7 +10533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="30">
+    <row r="18" spans="1:23" ht="30" hidden="1">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -10490,7 +10600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="30">
+    <row r="19" spans="1:23" ht="30" hidden="1">
       <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
@@ -10559,7 +10669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" hidden="1">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -10626,7 +10736,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" hidden="1">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -10693,7 +10803,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" hidden="1">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
@@ -10760,7 +10870,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="30">
+    <row r="23" spans="1:23" ht="30" hidden="1">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -10829,7 +10939,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="30">
+    <row r="24" spans="1:23" ht="30" hidden="1">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -10896,7 +11006,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="30">
+    <row r="25" spans="1:23" ht="30" hidden="1">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -10963,7 +11073,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="30">
+    <row r="26" spans="1:23" ht="30" hidden="1">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -11101,7 +11211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="30">
+    <row r="28" spans="1:23" ht="30" hidden="1">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
@@ -11168,7 +11278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" hidden="1">
       <c r="A29" s="3" t="s">
         <v>8</v>
       </c>
@@ -11237,7 +11347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="30">
+    <row r="30" spans="1:23" ht="30" hidden="1">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
@@ -11304,7 +11414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" hidden="1">
       <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
@@ -11373,7 +11483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="30">
+    <row r="32" spans="1:23" ht="30" hidden="1">
       <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
@@ -11440,7 +11550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" hidden="1">
       <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
@@ -11507,7 +11617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="30">
+    <row r="34" spans="1:23" ht="30" hidden="1">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -11578,7 +11688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="30">
+    <row r="35" spans="1:23" ht="30" hidden="1">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -11649,7 +11759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" hidden="1">
       <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
@@ -11720,7 +11830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45">
+    <row r="37" spans="1:23" ht="45" hidden="1">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -11862,7 +11972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="30">
+    <row r="39" spans="1:23" ht="30" hidden="1">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
@@ -11933,7 +12043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="30">
+    <row r="40" spans="1:23" ht="30" hidden="1">
       <c r="A40" s="3" t="s">
         <v>37</v>
       </c>
@@ -12004,7 +12114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" hidden="1">
       <c r="A41" s="3" t="s">
         <v>37</v>
       </c>
@@ -12075,7 +12185,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="30">
+    <row r="42" spans="1:23" ht="30" hidden="1">
       <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
@@ -12146,7 +12256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" hidden="1">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
@@ -12217,7 +12327,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" hidden="1">
       <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
@@ -12288,7 +12398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" hidden="1">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -12359,7 +12469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="30">
+    <row r="46" spans="1:23" ht="30" hidden="1">
       <c r="A46" s="3" t="s">
         <v>317</v>
       </c>
@@ -12406,7 +12516,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="30">
+    <row r="47" spans="1:23" ht="30" hidden="1">
       <c r="A47" s="3" t="s">
         <v>317</v>
       </c>
@@ -12453,7 +12563,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="45">
+    <row r="48" spans="1:23" ht="45" hidden="1">
       <c r="A48" s="3" t="s">
         <v>317</v>
       </c>
@@ -12500,7 +12610,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="30">
+    <row r="49" spans="1:23" ht="30" hidden="1">
       <c r="A49" s="3" t="s">
         <v>317</v>
       </c>
@@ -12594,7 +12704,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="30">
+    <row r="51" spans="1:23" ht="30" hidden="1">
       <c r="A51" s="4" t="s">
         <v>341</v>
       </c>
@@ -12662,7 +12772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="30">
+    <row r="52" spans="1:23" ht="30" hidden="1">
       <c r="A52" s="4" t="s">
         <v>341</v>
       </c>
@@ -12730,7 +12840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="30">
+    <row r="53" spans="1:23" ht="30" hidden="1">
       <c r="A53" s="4" t="s">
         <v>341</v>
       </c>
@@ -12866,7 +12976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="30">
+    <row r="55" spans="1:23" ht="30" hidden="1">
       <c r="A55" s="4" t="s">
         <v>341</v>
       </c>
@@ -12934,7 +13044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="30">
+    <row r="56" spans="1:23" ht="30" hidden="1">
       <c r="A56" s="4" t="s">
         <v>341</v>
       </c>
@@ -13002,7 +13112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="30">
+    <row r="57" spans="1:23" ht="30" hidden="1">
       <c r="A57" s="4" t="s">
         <v>341</v>
       </c>
@@ -13070,7 +13180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="30">
+    <row r="58" spans="1:23" ht="30" hidden="1">
       <c r="A58" s="4" t="s">
         <v>341</v>
       </c>
@@ -13138,7 +13248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="45">
+    <row r="59" spans="1:23" ht="45" hidden="1">
       <c r="A59" s="4" t="s">
         <v>341</v>
       </c>
@@ -13206,7 +13316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="30">
+    <row r="60" spans="1:23" ht="30" hidden="1">
       <c r="A60" s="4" t="s">
         <v>341</v>
       </c>
@@ -13274,7 +13384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="30">
+    <row r="61" spans="1:23" ht="30" hidden="1">
       <c r="A61" s="4" t="s">
         <v>370</v>
       </c>
@@ -13345,7 +13455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="30">
+    <row r="62" spans="1:23" ht="30" hidden="1">
       <c r="A62" s="4" t="s">
         <v>370</v>
       </c>
@@ -13416,7 +13526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="30">
+    <row r="63" spans="1:23" ht="30" hidden="1">
       <c r="A63" s="4" t="s">
         <v>370</v>
       </c>
@@ -13487,7 +13597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="30">
+    <row r="64" spans="1:23" ht="30" hidden="1">
       <c r="A64" s="4" t="s">
         <v>370</v>
       </c>
@@ -13629,7 +13739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="30">
+    <row r="66" spans="1:23" ht="30" hidden="1">
       <c r="A66" s="4" t="s">
         <v>377</v>
       </c>
@@ -13700,7 +13810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="30">
+    <row r="67" spans="1:23" ht="30" hidden="1">
       <c r="A67" s="4" t="s">
         <v>377</v>
       </c>
@@ -13771,7 +13881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="30">
+    <row r="68" spans="1:23" ht="30" hidden="1">
       <c r="A68" s="4" t="s">
         <v>377</v>
       </c>
@@ -13842,7 +13952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="30">
+    <row r="69" spans="1:23" ht="30" hidden="1">
       <c r="A69" s="4" t="s">
         <v>10</v>
       </c>
@@ -13913,7 +14023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="30">
+    <row r="70" spans="1:23" ht="30" hidden="1">
       <c r="A70" s="4" t="s">
         <v>10</v>
       </c>
@@ -13984,7 +14094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="45">
+    <row r="71" spans="1:23" ht="45" hidden="1">
       <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
@@ -14055,7 +14165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="45">
+    <row r="72" spans="1:23" ht="45" hidden="1">
       <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
@@ -14126,7 +14236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="30">
+    <row r="73" spans="1:23" ht="30" hidden="1">
       <c r="A73" s="4" t="s">
         <v>10</v>
       </c>
@@ -14197,7 +14307,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30">
+    <row r="74" spans="1:23" ht="30" hidden="1">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -14268,7 +14378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30">
+    <row r="75" spans="1:23" ht="30" hidden="1">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -14339,7 +14449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="30">
+    <row r="76" spans="1:23" ht="30" hidden="1">
       <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
@@ -14481,7 +14591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="30">
+    <row r="78" spans="1:23" ht="45" hidden="1">
       <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
@@ -14552,7 +14662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="30">
+    <row r="79" spans="1:23" ht="45" hidden="1">
       <c r="A79" s="4" t="s">
         <v>10</v>
       </c>
@@ -14623,7 +14733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="30">
+    <row r="80" spans="1:23" ht="30" hidden="1">
       <c r="A80" s="4" t="s">
         <v>10</v>
       </c>
@@ -14694,7 +14804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="30">
+    <row r="81" spans="1:23" ht="30" hidden="1">
       <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
@@ -14765,7 +14875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="30">
+    <row r="82" spans="1:23" ht="30" hidden="1">
       <c r="A82" s="4" t="s">
         <v>10</v>
       </c>
@@ -14836,7 +14946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="30">
+    <row r="83" spans="1:23" ht="30" hidden="1">
       <c r="A83" s="4" t="s">
         <v>10</v>
       </c>
@@ -14907,7 +15017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="45">
+    <row r="84" spans="1:23" ht="45" hidden="1">
       <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
@@ -14978,7 +15088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="30">
+    <row r="85" spans="1:23" ht="30" hidden="1">
       <c r="A85" s="4" t="s">
         <v>10</v>
       </c>
@@ -15049,7 +15159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="30">
+    <row r="86" spans="1:23" ht="30" hidden="1">
       <c r="A86" s="4" t="s">
         <v>490</v>
       </c>
@@ -15120,7 +15230,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="30">
+    <row r="87" spans="1:23" ht="30" hidden="1">
       <c r="A87" s="4" t="s">
         <v>490</v>
       </c>
@@ -15191,7 +15301,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30">
+    <row r="88" spans="1:23" ht="30" hidden="1">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -15262,7 +15372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30">
+    <row r="89" spans="1:23" ht="30" hidden="1">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -15333,7 +15443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" hidden="1">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -15404,7 +15514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" hidden="1">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -15475,7 +15585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="45">
+    <row r="92" spans="1:23" ht="45" hidden="1">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -15617,7 +15727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="30">
+    <row r="94" spans="1:23" ht="30" hidden="1">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -15688,7 +15798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30">
+    <row r="95" spans="1:23" ht="30" hidden="1">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -15759,7 +15869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30">
+    <row r="96" spans="1:23" ht="30" hidden="1">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -15830,7 +15940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="30">
+    <row r="97" spans="1:23" ht="30" hidden="1">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -15901,7 +16011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30">
+    <row r="98" spans="1:23" ht="30" hidden="1">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -15972,7 +16082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30">
+    <row r="99" spans="1:23" ht="30" hidden="1">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -16043,7 +16153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30">
+    <row r="100" spans="1:23" ht="30" hidden="1">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -16114,7 +16224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30">
+    <row r="101" spans="1:23" ht="30" hidden="1">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -16185,7 +16295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30">
+    <row r="102" spans="1:23" ht="30" hidden="1">
       <c r="A102" s="4" t="s">
         <v>548</v>
       </c>
@@ -16256,7 +16366,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30">
+    <row r="103" spans="1:23" ht="30" hidden="1">
       <c r="A103" s="4" t="s">
         <v>548</v>
       </c>
@@ -16327,7 +16437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30">
+    <row r="104" spans="1:23" ht="30" hidden="1">
       <c r="A104" s="4" t="s">
         <v>548</v>
       </c>
@@ -16398,7 +16508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30">
+    <row r="105" spans="1:23" ht="30" hidden="1">
       <c r="A105" s="4" t="s">
         <v>548</v>
       </c>
@@ -16469,7 +16579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30">
+    <row r="106" spans="1:23" ht="30" hidden="1">
       <c r="A106" s="4" t="s">
         <v>548</v>
       </c>
@@ -16540,7 +16650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" hidden="1">
       <c r="A107" s="4" t="s">
         <v>548</v>
       </c>
@@ -16611,7 +16721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" hidden="1">
       <c r="A108" s="4" t="s">
         <v>548</v>
       </c>
@@ -16682,7 +16792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" hidden="1">
       <c r="A109" s="4" t="s">
         <v>548</v>
       </c>
@@ -16753,7 +16863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30">
+    <row r="110" spans="1:23" ht="30" hidden="1">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -16895,7 +17005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="30">
+    <row r="112" spans="1:23" ht="30" hidden="1">
       <c r="A112" s="4" t="s">
         <v>548</v>
       </c>
@@ -16966,7 +17076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" hidden="1">
       <c r="A113" s="4" t="s">
         <v>548</v>
       </c>
@@ -17037,7 +17147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="30">
+    <row r="114" spans="1:23" ht="30" hidden="1">
       <c r="A114" s="4" t="s">
         <v>548</v>
       </c>
@@ -17108,7 +17218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:23">
+    <row r="115" spans="1:23" hidden="1">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
@@ -17179,7 +17289,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="30">
+    <row r="116" spans="1:23" ht="30" hidden="1">
       <c r="A116" s="4" t="s">
         <v>548</v>
       </c>
@@ -17250,7 +17360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:23">
+    <row r="117" spans="1:23" hidden="1">
       <c r="A117" s="4" t="s">
         <v>548</v>
       </c>
@@ -17321,7 +17431,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" hidden="1">
       <c r="A118" s="4" t="s">
         <v>548</v>
       </c>
@@ -17392,7 +17502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:23">
+    <row r="119" spans="1:23" hidden="1">
       <c r="A119" s="4" t="s">
         <v>548</v>
       </c>
@@ -17463,7 +17573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="30">
+    <row r="120" spans="1:23" ht="30" hidden="1">
       <c r="A120" s="4" t="s">
         <v>620</v>
       </c>
@@ -17534,7 +17644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="30">
+    <row r="121" spans="1:23" ht="30" hidden="1">
       <c r="A121" s="4" t="s">
         <v>620</v>
       </c>
@@ -17605,7 +17715,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" hidden="1">
       <c r="A122" s="4" t="s">
         <v>620</v>
       </c>
@@ -17676,7 +17786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="30">
+    <row r="123" spans="1:23" ht="30" hidden="1">
       <c r="A123" s="4" t="s">
         <v>620</v>
       </c>
@@ -17747,7 +17857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" hidden="1">
       <c r="A124" s="4" t="s">
         <v>620</v>
       </c>
@@ -17818,7 +17928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="30">
+    <row r="125" spans="1:23" ht="30" hidden="1">
       <c r="A125" s="4" t="s">
         <v>620</v>
       </c>
@@ -17889,7 +17999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:23" hidden="1">
       <c r="A126" s="4" t="s">
         <v>620</v>
       </c>
@@ -18031,7 +18141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="30">
+    <row r="128" spans="1:23" ht="30" hidden="1">
       <c r="A128" s="4" t="s">
         <v>620</v>
       </c>
@@ -18102,7 +18212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:23" ht="30">
+    <row r="129" spans="1:23" ht="30" hidden="1">
       <c r="A129" s="4" t="s">
         <v>620</v>
       </c>
@@ -18173,7 +18283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:23" hidden="1">
       <c r="A130" s="4" t="s">
         <v>620</v>
       </c>
@@ -18244,7 +18354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="30">
+    <row r="131" spans="1:23" ht="30" hidden="1">
       <c r="A131" s="4" t="s">
         <v>620</v>
       </c>
@@ -18315,7 +18425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" hidden="1">
       <c r="A132" s="4" t="s">
         <v>620</v>
       </c>
@@ -18386,7 +18496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:23" hidden="1">
       <c r="A133" s="4" t="s">
         <v>620</v>
       </c>
@@ -18457,7 +18567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:23" hidden="1">
       <c r="A134" s="4" t="s">
         <v>620</v>
       </c>
@@ -18528,7 +18638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:23" ht="30">
+    <row r="135" spans="1:23" ht="30" hidden="1">
       <c r="A135" s="4" t="s">
         <v>673</v>
       </c>
@@ -18599,7 +18709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="30">
+    <row r="136" spans="1:23" ht="30" hidden="1">
       <c r="A136" s="4" t="s">
         <v>673</v>
       </c>
@@ -18670,7 +18780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:23" ht="30">
+    <row r="137" spans="1:23" ht="30" hidden="1">
       <c r="A137" s="4" t="s">
         <v>673</v>
       </c>
@@ -18741,7 +18851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:23" ht="30">
+    <row r="138" spans="1:23" ht="30" hidden="1">
       <c r="A138" s="4" t="s">
         <v>673</v>
       </c>
@@ -18812,7 +18922,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:23" ht="30">
+    <row r="139" spans="1:23" ht="30" hidden="1">
       <c r="A139" s="4" t="s">
         <v>673</v>
       </c>
@@ -18883,7 +18993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="30">
+    <row r="140" spans="1:23" ht="30" hidden="1">
       <c r="A140" s="4" t="s">
         <v>673</v>
       </c>
@@ -18954,7 +19064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="30">
+    <row r="141" spans="1:23" ht="30" hidden="1">
       <c r="A141" s="4" t="s">
         <v>673</v>
       </c>
@@ -19025,7 +19135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:23">
+    <row r="142" spans="1:23" hidden="1">
       <c r="A142" s="4" t="s">
         <v>673</v>
       </c>
@@ -19167,7 +19277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="30">
+    <row r="144" spans="1:23" ht="30" hidden="1">
       <c r="A144" s="4" t="s">
         <v>673</v>
       </c>
@@ -19238,7 +19348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="30">
+    <row r="145" spans="1:23" ht="30" hidden="1">
       <c r="A145" s="4" t="s">
         <v>673</v>
       </c>
@@ -19309,7 +19419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="30">
+    <row r="146" spans="1:23" ht="30" hidden="1">
       <c r="A146" s="4" t="s">
         <v>673</v>
       </c>
@@ -19380,7 +19490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:23" ht="30">
+    <row r="147" spans="1:23" ht="30" hidden="1">
       <c r="A147" s="4" t="s">
         <v>673</v>
       </c>
@@ -19451,7 +19561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="30">
+    <row r="148" spans="1:23" ht="30" hidden="1">
       <c r="A148" s="4" t="s">
         <v>673</v>
       </c>
@@ -19522,7 +19632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:23" hidden="1">
       <c r="A149" s="4" t="s">
         <v>673</v>
       </c>
@@ -19593,7 +19703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="30">
+    <row r="150" spans="1:23" ht="30" hidden="1">
       <c r="A150" s="4" t="s">
         <v>34</v>
       </c>
@@ -19664,7 +19774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="30">
+    <row r="151" spans="1:23" ht="30" hidden="1">
       <c r="A151" s="4" t="s">
         <v>34</v>
       </c>
@@ -19735,7 +19845,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="30">
+    <row r="152" spans="1:23" ht="30" hidden="1">
       <c r="A152" s="4" t="s">
         <v>34</v>
       </c>
@@ -19806,7 +19916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="30">
+    <row r="153" spans="1:23" ht="30" hidden="1">
       <c r="A153" s="4" t="s">
         <v>34</v>
       </c>
@@ -19877,7 +19987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" hidden="1">
       <c r="A154" s="4" t="s">
         <v>34</v>
       </c>
@@ -19948,7 +20058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="30">
+    <row r="155" spans="1:23" ht="30" hidden="1">
       <c r="A155" s="4" t="s">
         <v>34</v>
       </c>
@@ -20019,7 +20129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="30">
+    <row r="156" spans="1:23" ht="30" hidden="1">
       <c r="A156" s="4" t="s">
         <v>34</v>
       </c>
@@ -20161,7 +20271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="30">
+    <row r="158" spans="1:23" ht="30" hidden="1">
       <c r="A158" s="4" t="s">
         <v>34</v>
       </c>
@@ -20232,7 +20342,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="30">
+    <row r="159" spans="1:23" ht="30" hidden="1">
       <c r="A159" s="4" t="s">
         <v>34</v>
       </c>
@@ -20303,7 +20413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="30">
+    <row r="160" spans="1:23" ht="30" hidden="1">
       <c r="A160" s="4" t="s">
         <v>34</v>
       </c>
@@ -20374,7 +20484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:23" hidden="1">
       <c r="A161" s="4" t="s">
         <v>34</v>
       </c>
@@ -20445,7 +20555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="30">
+    <row r="162" spans="1:23" ht="30" hidden="1">
       <c r="A162" s="4" t="s">
         <v>34</v>
       </c>
@@ -20516,7 +20626,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="30">
+    <row r="163" spans="1:23" ht="30" hidden="1">
       <c r="A163" s="4" t="s">
         <v>34</v>
       </c>
@@ -20587,7 +20697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="30">
+    <row r="164" spans="1:23" ht="30" hidden="1">
       <c r="A164" s="4" t="s">
         <v>34</v>
       </c>
@@ -20658,7 +20768,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="30">
+    <row r="165" spans="1:23" ht="30" hidden="1">
       <c r="A165" s="4" t="s">
         <v>34</v>
       </c>
@@ -20729,7 +20839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="30">
+    <row r="166" spans="1:23" ht="30" hidden="1">
       <c r="A166" s="4" t="s">
         <v>35</v>
       </c>
@@ -20800,7 +20910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="30">
+    <row r="167" spans="1:23" ht="30" hidden="1">
       <c r="A167" s="4" t="s">
         <v>35</v>
       </c>
@@ -20871,7 +20981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="30">
+    <row r="168" spans="1:23" ht="30" hidden="1">
       <c r="A168" s="4" t="s">
         <v>35</v>
       </c>
@@ -20942,7 +21052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="30">
+    <row r="169" spans="1:23" ht="30" hidden="1">
       <c r="A169" s="4" t="s">
         <v>35</v>
       </c>
@@ -21013,7 +21123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="30">
+    <row r="170" spans="1:23" ht="30" hidden="1">
       <c r="A170" s="4" t="s">
         <v>35</v>
       </c>
@@ -21084,7 +21194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="30">
+    <row r="171" spans="1:23" ht="30" hidden="1">
       <c r="A171" s="4" t="s">
         <v>35</v>
       </c>
@@ -21155,7 +21265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="30">
+    <row r="172" spans="1:23" ht="30" hidden="1">
       <c r="A172" s="4" t="s">
         <v>35</v>
       </c>
@@ -21226,7 +21336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:23" ht="30">
+    <row r="173" spans="1:23" ht="30" hidden="1">
       <c r="A173" s="4" t="s">
         <v>35</v>
       </c>
@@ -21368,7 +21478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="30">
+    <row r="175" spans="1:23" ht="30" hidden="1">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -21439,7 +21549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="30">
+    <row r="176" spans="1:23" ht="30" hidden="1">
       <c r="A176" s="4" t="s">
         <v>35</v>
       </c>
@@ -21510,7 +21620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="30">
+    <row r="177" spans="1:23" ht="30" hidden="1">
       <c r="A177" s="4" t="s">
         <v>35</v>
       </c>
@@ -21581,7 +21691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="30">
+    <row r="178" spans="1:23" ht="30" hidden="1">
       <c r="A178" s="4" t="s">
         <v>35</v>
       </c>
@@ -21652,7 +21762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="30">
+    <row r="179" spans="1:23" ht="30" hidden="1">
       <c r="A179" s="4" t="s">
         <v>35</v>
       </c>
@@ -21723,7 +21833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="30">
+    <row r="180" spans="1:23" ht="30" hidden="1">
       <c r="A180" s="4" t="s">
         <v>35</v>
       </c>
@@ -21794,7 +21904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="30">
+    <row r="181" spans="1:23" ht="30" hidden="1">
       <c r="A181" s="3" t="s">
         <v>94</v>
       </c>
@@ -21861,7 +21971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="30">
+    <row r="182" spans="1:23" ht="30" hidden="1">
       <c r="A182" s="3" t="s">
         <v>94</v>
       </c>
@@ -21930,7 +22040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:23" ht="30">
+    <row r="183" spans="1:23" ht="30" hidden="1">
       <c r="A183" s="3" t="s">
         <v>94</v>
       </c>
@@ -21999,7 +22109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:23" ht="30">
+    <row r="184" spans="1:23" ht="30" hidden="1">
       <c r="A184" s="3" t="s">
         <v>94</v>
       </c>
@@ -22068,7 +22178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="30">
+    <row r="185" spans="1:23" ht="30" hidden="1">
       <c r="A185" s="3" t="s">
         <v>94</v>
       </c>
@@ -22137,7 +22247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="30">
+    <row r="186" spans="1:23" ht="30" hidden="1">
       <c r="A186" s="3" t="s">
         <v>94</v>
       </c>
@@ -22206,7 +22316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:23">
+    <row r="187" spans="1:23" hidden="1">
       <c r="A187" s="3" t="s">
         <v>42</v>
       </c>
@@ -22273,7 +22383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:23">
+    <row r="188" spans="1:23" hidden="1">
       <c r="A188" s="3" t="s">
         <v>42</v>
       </c>
@@ -22342,7 +22452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:23">
+    <row r="189" spans="1:23" hidden="1">
       <c r="A189" s="3" t="s">
         <v>42</v>
       </c>
@@ -22411,7 +22521,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="30">
+    <row r="190" spans="1:23" ht="30" hidden="1">
       <c r="A190" s="3" t="s">
         <v>42</v>
       </c>
@@ -22480,7 +22590,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:23">
+    <row r="191" spans="1:23" hidden="1">
       <c r="A191" s="3" t="s">
         <v>42</v>
       </c>
@@ -22549,7 +22659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:23" ht="30">
+    <row r="192" spans="1:23" ht="30" hidden="1">
       <c r="A192" s="3" t="s">
         <v>42</v>
       </c>
@@ -22618,7 +22728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:23">
+    <row r="193" spans="1:23" hidden="1">
       <c r="A193" s="3" t="s">
         <v>129</v>
       </c>
@@ -22685,7 +22795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:23">
+    <row r="194" spans="1:23" hidden="1">
       <c r="A194" s="3" t="s">
         <v>129</v>
       </c>
@@ -22754,7 +22864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:23">
+    <row r="195" spans="1:23" hidden="1">
       <c r="A195" s="3" t="s">
         <v>129</v>
       </c>
@@ -22823,7 +22933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:23">
+    <row r="196" spans="1:23" hidden="1">
       <c r="A196" s="3" t="s">
         <v>129</v>
       </c>
@@ -22892,7 +23002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:23">
+    <row r="197" spans="1:23" hidden="1">
       <c r="A197" s="3" t="s">
         <v>129</v>
       </c>
@@ -22961,7 +23071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="30">
+    <row r="198" spans="1:23" ht="30" hidden="1">
       <c r="A198" s="3" t="s">
         <v>129</v>
       </c>
@@ -23030,7 +23140,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="30">
+    <row r="199" spans="1:23" ht="30" hidden="1">
       <c r="A199" s="3" t="s">
         <v>129</v>
       </c>
@@ -23099,7 +23209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:23">
+    <row r="200" spans="1:23" hidden="1">
       <c r="A200" s="3" t="s">
         <v>126</v>
       </c>
@@ -23166,7 +23276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:23">
+    <row r="201" spans="1:23" hidden="1">
       <c r="A201" s="3" t="s">
         <v>126</v>
       </c>
@@ -23235,7 +23345,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:23">
+    <row r="202" spans="1:23" hidden="1">
       <c r="A202" s="3" t="s">
         <v>126</v>
       </c>
@@ -23304,7 +23414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:23" ht="30">
+    <row r="203" spans="1:23" ht="30" hidden="1">
       <c r="A203" s="3" t="s">
         <v>126</v>
       </c>
@@ -23373,7 +23483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:23" ht="30">
+    <row r="204" spans="1:23" ht="30" hidden="1">
       <c r="A204" s="3" t="s">
         <v>126</v>
       </c>
@@ -23442,7 +23552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" hidden="1">
       <c r="A205" s="3" t="s">
         <v>126</v>
       </c>
@@ -23511,7 +23621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="30">
+    <row r="206" spans="1:23" ht="30" hidden="1">
       <c r="A206" s="3" t="s">
         <v>126</v>
       </c>
@@ -23580,7 +23690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="30">
+    <row r="207" spans="1:23" ht="30" hidden="1">
       <c r="A207" s="3" t="s">
         <v>126</v>
       </c>
@@ -23649,7 +23759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="30">
+    <row r="208" spans="1:23" ht="30" hidden="1">
       <c r="A208" s="3" t="s">
         <v>313</v>
       </c>
@@ -23716,7 +23826,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:23" ht="30">
+    <row r="209" spans="1:23" ht="30" hidden="1">
       <c r="A209" s="3" t="s">
         <v>313</v>
       </c>
@@ -23785,7 +23895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:23" ht="30">
+    <row r="210" spans="1:23" ht="30" hidden="1">
       <c r="A210" s="3" t="s">
         <v>313</v>
       </c>
@@ -23854,7 +23964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:23" ht="30">
+    <row r="211" spans="1:23" ht="30" hidden="1">
       <c r="A211" s="3" t="s">
         <v>313</v>
       </c>
@@ -23923,7 +24033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:23" ht="30">
+    <row r="212" spans="1:23" ht="30" hidden="1">
       <c r="A212" s="3" t="s">
         <v>313</v>
       </c>
@@ -23992,7 +24102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:23" ht="45">
+    <row r="213" spans="1:23" ht="45" hidden="1">
       <c r="A213" s="3" t="s">
         <v>313</v>
       </c>
@@ -24061,7 +24171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="30">
+    <row r="214" spans="1:23" ht="30" hidden="1">
       <c r="A214" s="3" t="s">
         <v>445</v>
       </c>
@@ -24128,7 +24238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="30">
+    <row r="215" spans="1:23" ht="30" hidden="1">
       <c r="A215" s="3" t="s">
         <v>445</v>
       </c>
@@ -24197,7 +24307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:23" ht="30">
+    <row r="216" spans="1:23" ht="30" hidden="1">
       <c r="A216" s="3" t="s">
         <v>445</v>
       </c>
@@ -24266,7 +24376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="30">
+    <row r="217" spans="1:23" ht="30" hidden="1">
       <c r="A217" s="3" t="s">
         <v>445</v>
       </c>
@@ -24335,7 +24445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:23" ht="30">
+    <row r="218" spans="1:23" ht="30" hidden="1">
       <c r="A218" s="3" t="s">
         <v>445</v>
       </c>
@@ -24404,7 +24514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="30">
+    <row r="219" spans="1:23" ht="30" hidden="1">
       <c r="A219" s="3" t="s">
         <v>445</v>
       </c>
@@ -24473,7 +24583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="30">
+    <row r="220" spans="1:23" ht="30" hidden="1">
       <c r="A220" s="3" t="s">
         <v>451</v>
       </c>
@@ -24540,7 +24650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:23">
+    <row r="221" spans="1:23" hidden="1">
       <c r="A221" s="3" t="s">
         <v>451</v>
       </c>
@@ -24609,7 +24719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:23">
+    <row r="222" spans="1:23" hidden="1">
       <c r="A222" s="3" t="s">
         <v>451</v>
       </c>
@@ -24678,7 +24788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="30">
+    <row r="223" spans="1:23" ht="30" hidden="1">
       <c r="A223" s="3" t="s">
         <v>451</v>
       </c>
@@ -24747,7 +24857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:23">
+    <row r="224" spans="1:23" hidden="1">
       <c r="A224" s="3" t="s">
         <v>451</v>
       </c>
@@ -24816,7 +24926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="30">
+    <row r="225" spans="1:23" ht="30" hidden="1">
       <c r="A225" s="3" t="s">
         <v>451</v>
       </c>
@@ -24885,7 +24995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="30">
+    <row r="226" spans="1:23" ht="30" hidden="1">
       <c r="A226" s="3" t="s">
         <v>512</v>
       </c>
@@ -24952,7 +25062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="30">
+    <row r="227" spans="1:23" ht="30" hidden="1">
       <c r="A227" s="3" t="s">
         <v>512</v>
       </c>
@@ -25021,7 +25131,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="30">
+    <row r="228" spans="1:23" ht="30" hidden="1">
       <c r="A228" s="3" t="s">
         <v>512</v>
       </c>
@@ -25090,7 +25200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="30">
+    <row r="229" spans="1:23" ht="30" hidden="1">
       <c r="A229" s="3" t="s">
         <v>512</v>
       </c>
@@ -25159,7 +25269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="30">
+    <row r="230" spans="1:23" ht="30" hidden="1">
       <c r="A230" s="3" t="s">
         <v>512</v>
       </c>
@@ -25228,7 +25338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="30">
+    <row r="231" spans="1:23" ht="30" hidden="1">
       <c r="A231" s="3" t="s">
         <v>512</v>
       </c>
@@ -25297,7 +25407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="30">
+    <row r="232" spans="1:23" ht="30" hidden="1">
       <c r="A232" s="3" t="s">
         <v>518</v>
       </c>
@@ -25364,7 +25474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:23">
+    <row r="233" spans="1:23" hidden="1">
       <c r="A233" s="3" t="s">
         <v>518</v>
       </c>
@@ -25433,7 +25543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:23">
+    <row r="234" spans="1:23" hidden="1">
       <c r="A234" s="3" t="s">
         <v>518</v>
       </c>
@@ -25502,7 +25612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="30">
+    <row r="235" spans="1:23" ht="30" hidden="1">
       <c r="A235" s="3" t="s">
         <v>518</v>
       </c>
@@ -25571,7 +25681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:23">
+    <row r="236" spans="1:23" hidden="1">
       <c r="A236" s="3" t="s">
         <v>518</v>
       </c>
@@ -25640,7 +25750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:23" ht="30">
+    <row r="237" spans="1:23" ht="30" hidden="1">
       <c r="A237" s="3" t="s">
         <v>518</v>
       </c>
@@ -25709,7 +25819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="30">
+    <row r="238" spans="1:23" ht="30" hidden="1">
       <c r="A238" s="3" t="s">
         <v>757</v>
       </c>
@@ -25776,7 +25886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:23">
+    <row r="239" spans="1:23" hidden="1">
       <c r="A239" s="3" t="s">
         <v>757</v>
       </c>
@@ -25845,7 +25955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:23">
+    <row r="240" spans="1:23" hidden="1">
       <c r="A240" s="3" t="s">
         <v>757</v>
       </c>
@@ -25914,7 +26024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:23">
+    <row r="241" spans="1:23" hidden="1">
       <c r="A241" s="3" t="s">
         <v>757</v>
       </c>
@@ -25983,7 +26093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:23">
+    <row r="242" spans="1:23" hidden="1">
       <c r="A242" s="3" t="s">
         <v>757</v>
       </c>
@@ -26052,7 +26162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="30">
+    <row r="243" spans="1:23" ht="30" hidden="1">
       <c r="A243" s="3" t="s">
         <v>757</v>
       </c>
@@ -26121,7 +26231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="30">
+    <row r="244" spans="1:23" ht="30" hidden="1">
       <c r="A244" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26188,7 +26298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="30">
+    <row r="245" spans="1:23" ht="30" hidden="1">
       <c r="A245" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26255,7 +26365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="30">
+    <row r="246" spans="1:23" ht="30" hidden="1">
       <c r="A246" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26324,7 +26434,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="247" spans="1:23" ht="30">
+    <row r="247" spans="1:23" ht="30" hidden="1">
       <c r="A247" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26393,7 +26503,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="248" spans="1:23">
+    <row r="248" spans="1:23" hidden="1">
       <c r="A248" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26462,7 +26572,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="30">
+    <row r="249" spans="1:23" ht="30" hidden="1">
       <c r="A249" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26531,7 +26641,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="250" spans="1:23">
+    <row r="250" spans="1:23" hidden="1">
       <c r="A250" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26600,7 +26710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:23">
+    <row r="251" spans="1:23" hidden="1">
       <c r="A251" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26669,7 +26779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:23">
+    <row r="252" spans="1:23" hidden="1">
       <c r="A252" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26738,7 +26848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:23">
+    <row r="253" spans="1:23" hidden="1">
       <c r="A253" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26807,7 +26917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:23">
+    <row r="254" spans="1:23" hidden="1">
       <c r="A254" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26876,7 +26986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:23">
+    <row r="255" spans="1:23" hidden="1">
       <c r="A255" s="3" t="s">
         <v>1517</v>
       </c>
@@ -26945,7 +27055,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="30">
+    <row r="256" spans="1:23" ht="30" hidden="1">
       <c r="A256" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27014,7 +27124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:23" ht="30">
+    <row r="257" spans="1:23" ht="30" hidden="1">
       <c r="A257" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27083,7 +27193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" hidden="1">
       <c r="A258" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27150,7 +27260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:23">
+    <row r="259" spans="1:23" hidden="1">
       <c r="A259" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27217,7 +27327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:23">
+    <row r="260" spans="1:23" hidden="1">
       <c r="A260" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27284,7 +27394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:23">
+    <row r="261" spans="1:23" hidden="1">
       <c r="A261" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27353,7 +27463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:23">
+    <row r="262" spans="1:23" hidden="1">
       <c r="A262" s="3" t="s">
         <v>1517</v>
       </c>
@@ -27422,7 +27532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30">
+    <row r="263" spans="1:23" ht="30" hidden="1">
       <c r="A263" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27489,7 +27599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="30">
+    <row r="264" spans="1:23" ht="30" hidden="1">
       <c r="A264" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27556,7 +27666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30">
+    <row r="265" spans="1:23" ht="30" hidden="1">
       <c r="A265" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27627,7 +27737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" hidden="1">
       <c r="A266" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27694,7 +27804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="30">
+    <row r="267" spans="1:23" ht="30" hidden="1">
       <c r="A267" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27763,7 +27873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" hidden="1">
       <c r="A268" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27832,7 +27942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" hidden="1">
       <c r="A269" s="3" t="s">
         <v>1518</v>
       </c>
@@ -27968,7 +28078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="30">
+    <row r="271" spans="1:23" ht="30" hidden="1">
       <c r="A271" s="3" t="s">
         <v>1518</v>
       </c>
@@ -28035,7 +28145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23">
+    <row r="272" spans="1:23" hidden="1">
       <c r="A272" s="3" t="s">
         <v>1518</v>
       </c>
@@ -28100,7 +28210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23">
+    <row r="273" spans="1:23" hidden="1">
       <c r="A273" s="3" t="s">
         <v>1518</v>
       </c>
@@ -28165,7 +28275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" hidden="1">
       <c r="A274" s="3" t="s">
         <v>1518</v>
       </c>
@@ -28230,7 +28340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" hidden="1">
       <c r="A275" s="3" t="s">
         <v>1518</v>
       </c>
@@ -28299,7 +28409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" hidden="1">
       <c r="A276" s="3" t="s">
         <v>1518</v>
       </c>
@@ -28368,7 +28478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:23" ht="30">
+    <row r="277" spans="1:23" ht="30" hidden="1">
       <c r="A277" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28435,7 +28545,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="30">
+    <row r="278" spans="1:23" ht="30" hidden="1">
       <c r="A278" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28502,7 +28612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="45">
+    <row r="279" spans="1:23" ht="45" hidden="1">
       <c r="A279" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28573,7 +28683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="30">
+    <row r="280" spans="1:23" ht="30" hidden="1">
       <c r="A280" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28642,7 +28752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="30">
+    <row r="281" spans="1:23" ht="30" hidden="1">
       <c r="A281" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28711,7 +28821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="30">
+    <row r="282" spans="1:23" ht="30" hidden="1">
       <c r="A282" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28780,7 +28890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="30">
+    <row r="283" spans="1:23" ht="30" hidden="1">
       <c r="A283" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28849,7 +28959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:23" ht="30">
+    <row r="284" spans="1:23" ht="30" hidden="1">
       <c r="A284" s="3" t="s">
         <v>1578</v>
       </c>
@@ -28985,7 +29095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="30">
+    <row r="286" spans="1:23" ht="30" hidden="1">
       <c r="A286" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29052,7 +29162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="30">
+    <row r="287" spans="1:23" ht="30" hidden="1">
       <c r="A287" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29117,7 +29227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="30">
+    <row r="288" spans="1:23" ht="30" hidden="1">
       <c r="A288" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29182,7 +29292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="30">
+    <row r="289" spans="1:23" ht="30" hidden="1">
       <c r="A289" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29247,7 +29357,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="30">
+    <row r="290" spans="1:23" ht="30" hidden="1">
       <c r="A290" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29316,7 +29426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="30">
+    <row r="291" spans="1:23" ht="30" hidden="1">
       <c r="A291" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29385,7 +29495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:23" ht="30">
+    <row r="292" spans="1:23" ht="30" hidden="1">
       <c r="A292" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29452,7 +29562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:23" ht="30">
+    <row r="293" spans="1:23" ht="30" hidden="1">
       <c r="A293" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29519,7 +29629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:23" ht="45">
+    <row r="294" spans="1:23" ht="45" hidden="1">
       <c r="A294" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29588,7 +29698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" hidden="1">
       <c r="A295" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29655,7 +29765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" hidden="1">
       <c r="A296" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29722,7 +29832,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="30">
+    <row r="297" spans="1:23" ht="30" hidden="1">
       <c r="A297" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29856,7 +29966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="45">
+    <row r="299" spans="1:23" ht="45" hidden="1">
       <c r="A299" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29925,7 +30035,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="30">
+    <row r="300" spans="1:23" ht="30" hidden="1">
       <c r="A300" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29990,7 +30100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="30">
+    <row r="301" spans="1:23" ht="30" hidden="1">
       <c r="A301" s="3" t="s">
         <v>1635</v>
       </c>
@@ -30059,7 +30169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="30">
+    <row r="302" spans="1:23" ht="30" hidden="1">
       <c r="A302" s="3" t="s">
         <v>1635</v>
       </c>
@@ -30126,7 +30236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="30">
+    <row r="303" spans="1:23" ht="30" hidden="1">
       <c r="A303" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30193,7 +30303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="30">
+    <row r="304" spans="1:23" ht="30" hidden="1">
       <c r="A304" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30260,7 +30370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="30">
+    <row r="305" spans="1:23" ht="30" hidden="1">
       <c r="A305" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30329,7 +30439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30">
+    <row r="306" spans="1:23" ht="30" hidden="1">
       <c r="A306" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30396,7 +30506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="30">
+    <row r="307" spans="1:23" ht="30" hidden="1">
       <c r="A307" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30534,7 +30644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="30">
+    <row r="309" spans="1:23" ht="30" hidden="1">
       <c r="A309" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30601,7 +30711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="30">
+    <row r="310" spans="1:23" ht="30" hidden="1">
       <c r="A310" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30668,7 +30778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="30">
+    <row r="311" spans="1:23" ht="30" hidden="1">
       <c r="A311" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30733,7 +30843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="30">
+    <row r="312" spans="1:23" ht="30" hidden="1">
       <c r="A312" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30800,7 +30910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="45">
+    <row r="313" spans="1:23" ht="45" hidden="1">
       <c r="A313" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30869,7 +30979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="30">
+    <row r="314" spans="1:23" ht="30" hidden="1">
       <c r="A314" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30938,7 +31048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:23" ht="30">
+    <row r="315" spans="1:23" ht="30" hidden="1">
       <c r="A315" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31005,7 +31115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:23" ht="30">
+    <row r="316" spans="1:23" ht="30" hidden="1">
       <c r="A316" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31074,7 +31184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:23">
+    <row r="317" spans="1:23" hidden="1">
       <c r="A317" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31143,7 +31253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="30">
+    <row r="318" spans="1:23" ht="30" hidden="1">
       <c r="A318" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31212,7 +31322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:23">
+    <row r="319" spans="1:23" hidden="1">
       <c r="A319" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31350,7 +31460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="30">
+    <row r="321" spans="1:23" ht="30" hidden="1">
       <c r="A321" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31417,7 +31527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:23" hidden="1">
       <c r="A322" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31482,7 +31592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="30">
+    <row r="323" spans="1:23" ht="30" hidden="1">
       <c r="A323" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31551,7 +31661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:23" hidden="1">
       <c r="A324" s="3" t="s">
         <v>1704</v>
       </c>
@@ -31620,7 +31730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="30">
+    <row r="325" spans="1:23" ht="30" hidden="1">
       <c r="A325" s="3" t="s">
         <v>1806</v>
       </c>
@@ -31687,7 +31797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="30">
+    <row r="326" spans="1:23" ht="30" hidden="1">
       <c r="A326" s="3" t="s">
         <v>1806</v>
       </c>
@@ -31754,7 +31864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="30">
+    <row r="327" spans="1:23" ht="30" hidden="1">
       <c r="A327" s="3" t="s">
         <v>1806</v>
       </c>
@@ -31821,7 +31931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="30">
+    <row r="328" spans="1:23" ht="30" hidden="1">
       <c r="A328" s="3" t="s">
         <v>1806</v>
       </c>
@@ -31890,7 +32000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="45">
+    <row r="329" spans="1:23" ht="45" hidden="1">
       <c r="A329" s="3" t="s">
         <v>1806</v>
       </c>
@@ -31959,7 +32069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="30">
+    <row r="330" spans="1:23" ht="30" hidden="1">
       <c r="A330" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32026,7 +32136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="30">
+    <row r="331" spans="1:23" ht="30" hidden="1">
       <c r="A331" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32162,7 +32272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="30">
+    <row r="333" spans="1:23" ht="30" hidden="1">
       <c r="A333" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32229,7 +32339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="30">
+    <row r="334" spans="1:23" ht="30" hidden="1">
       <c r="A334" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32296,7 +32406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="30">
+    <row r="335" spans="1:23" ht="30" hidden="1">
       <c r="A335" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32361,7 +32471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="30">
+    <row r="336" spans="1:23" ht="30" hidden="1">
       <c r="A336" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32428,7 +32538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="45">
+    <row r="337" spans="1:23" ht="45" hidden="1">
       <c r="A337" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32497,7 +32607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="30">
+    <row r="338" spans="1:23" ht="30" hidden="1">
       <c r="A338" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32566,7 +32676,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:23">
+    <row r="339" spans="1:23" hidden="1">
       <c r="A339" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32635,7 +32745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:23">
+    <row r="340" spans="1:23" hidden="1">
       <c r="A340" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32704,7 +32814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:23">
+    <row r="341" spans="1:23" hidden="1">
       <c r="A341" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32773,7 +32883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="30">
+    <row r="342" spans="1:23" ht="30" hidden="1">
       <c r="A342" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32842,7 +32952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="30">
+    <row r="343" spans="1:23" ht="30" hidden="1">
       <c r="A343" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32913,7 +33023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="30">
+    <row r="344" spans="1:23" ht="30" hidden="1">
       <c r="A344" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32982,7 +33092,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="345" spans="1:23">
+    <row r="345" spans="1:23" hidden="1">
       <c r="A345" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33124,7 +33234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="30">
+    <row r="347" spans="1:23" ht="30" hidden="1">
       <c r="A347" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33195,7 +33305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:23">
+    <row r="348" spans="1:23" hidden="1">
       <c r="A348" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33264,7 +33374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="30">
+    <row r="349" spans="1:23" ht="30" hidden="1">
       <c r="A349" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33335,7 +33445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="30">
+    <row r="350" spans="1:23" ht="30" hidden="1">
       <c r="A350" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33404,7 +33514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="30">
+    <row r="351" spans="1:23" ht="30" hidden="1">
       <c r="A351" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33475,7 +33585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="30">
+    <row r="352" spans="1:23" ht="30" hidden="1">
       <c r="A352" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33546,7 +33656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="30">
+    <row r="353" spans="1:23" ht="30" hidden="1">
       <c r="A353" s="3" t="s">
         <v>1922</v>
       </c>
@@ -33615,7 +33725,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="30">
+    <row r="354" spans="1:23" ht="30" hidden="1">
       <c r="A354" s="3" t="s">
         <v>1922</v>
       </c>
@@ -33684,7 +33794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:23">
+    <row r="355" spans="1:23" hidden="1">
       <c r="A355" s="3" t="s">
         <v>1922</v>
       </c>
@@ -33753,7 +33863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="45">
+    <row r="356" spans="1:23" ht="45" hidden="1">
       <c r="A356" s="3" t="s">
         <v>1922</v>
       </c>
@@ -33893,7 +34003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="30">
+    <row r="358" spans="1:23" ht="30" hidden="1">
       <c r="A358" s="4" t="s">
         <v>2018</v>
       </c>
@@ -33964,7 +34074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="30">
+    <row r="359" spans="1:23" ht="30" hidden="1">
       <c r="A359" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34035,7 +34145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:23" ht="30">
+    <row r="360" spans="1:23" ht="30" hidden="1">
       <c r="A360" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34177,7 +34287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:23" ht="30">
+    <row r="362" spans="1:23" ht="30" hidden="1">
       <c r="A362" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34248,7 +34358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="30">
+    <row r="363" spans="1:23" ht="30" hidden="1">
       <c r="A363" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34319,7 +34429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="30">
+    <row r="364" spans="1:23" ht="30" hidden="1">
       <c r="A364" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34390,7 +34500,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="30">
+    <row r="365" spans="1:23" ht="30" hidden="1">
       <c r="A365" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34461,7 +34571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="30">
+    <row r="366" spans="1:23" ht="30" hidden="1">
       <c r="A366" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34532,7 +34642,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="30">
+    <row r="367" spans="1:23" ht="30" hidden="1">
       <c r="A367" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34603,7 +34713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="30">
+    <row r="368" spans="1:23" ht="30" hidden="1">
       <c r="A368" s="4" t="s">
         <v>2062</v>
       </c>
@@ -34674,7 +34784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="30">
+    <row r="369" spans="1:23" ht="30" hidden="1">
       <c r="A369" s="4" t="s">
         <v>2062</v>
       </c>
@@ -34745,7 +34855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:23" ht="30">
+    <row r="370" spans="1:23" ht="30" hidden="1">
       <c r="A370" s="4" t="s">
         <v>2062</v>
       </c>
@@ -34887,7 +34997,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="30">
+    <row r="372" spans="1:23" ht="30" hidden="1">
       <c r="A372" s="4" t="s">
         <v>2062</v>
       </c>
@@ -34958,7 +35068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="45">
+    <row r="373" spans="1:23" ht="45" hidden="1">
       <c r="A373" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35029,7 +35139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:23" ht="30">
+    <row r="374" spans="1:23" ht="30" hidden="1">
       <c r="A374" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35100,7 +35210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="30">
+    <row r="375" spans="1:23" ht="30" hidden="1">
       <c r="A375" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35171,7 +35281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="30">
+    <row r="376" spans="1:23" ht="30" hidden="1">
       <c r="A376" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35242,7 +35352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:23" ht="30">
+    <row r="377" spans="1:23" ht="30" hidden="1">
       <c r="A377" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35313,7 +35423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:23" ht="30">
+    <row r="378" spans="1:23" ht="30" hidden="1">
       <c r="A378" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35384,7 +35494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:23" ht="30">
+    <row r="379" spans="1:23" ht="30" hidden="1">
       <c r="A379" s="4" t="s">
         <v>2062</v>
       </c>
@@ -35455,7 +35565,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:23">
+    <row r="380" spans="1:23" hidden="1">
       <c r="A380" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35526,7 +35636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="30">
+    <row r="381" spans="1:23" ht="30" hidden="1">
       <c r="A381" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35597,7 +35707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:23" ht="30">
+    <row r="382" spans="1:23" ht="30" hidden="1">
       <c r="A382" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35668,7 +35778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="45">
+    <row r="383" spans="1:23" ht="45" hidden="1">
       <c r="A383" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35736,7 +35846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:23" ht="30">
+    <row r="384" spans="1:23" ht="30" hidden="1">
       <c r="A384" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35804,7 +35914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:23" ht="45">
+    <row r="385" spans="1:23" ht="45" hidden="1">
       <c r="A385" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35875,7 +35985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="30">
+    <row r="386" spans="1:23" ht="30" hidden="1">
       <c r="A386" s="4" t="s">
         <v>2110</v>
       </c>
@@ -35946,7 +36056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:23" ht="30">
+    <row r="387" spans="1:23" ht="30" hidden="1">
       <c r="A387" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36014,7 +36124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:23" ht="30">
+    <row r="388" spans="1:23" ht="30" hidden="1">
       <c r="A388" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36082,7 +36192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="30">
+    <row r="389" spans="1:23" ht="30" hidden="1">
       <c r="A389" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36221,7 +36331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:23" ht="30">
+    <row r="391" spans="1:23" ht="30" hidden="1">
       <c r="A391" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36292,7 +36402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:23" ht="30">
+    <row r="392" spans="1:23" ht="30" hidden="1">
       <c r="A392" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36363,7 +36473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="30">
+    <row r="393" spans="1:23" ht="30" hidden="1">
       <c r="A393" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36434,7 +36544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:23" ht="30">
+    <row r="394" spans="1:23" ht="30" hidden="1">
       <c r="A394" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36505,7 +36615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:23" ht="30">
+    <row r="395" spans="1:23" ht="30" hidden="1">
       <c r="A395" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36576,7 +36686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:23" ht="30">
+    <row r="396" spans="1:23" ht="30" hidden="1">
       <c r="A396" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36648,7 +36758,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}"/>
+  <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Status"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="Q9" r:id="rId1" display="mailto:admin@memgine.com" xr:uid="{93170BB8-77D4-4002-829B-D89928109808}"/>
     <hyperlink ref="Q11" r:id="rId2" display="https://memgine.com/" xr:uid="{F8EB4105-6CCB-4B06-B657-948DB365F556}"/>
@@ -38981,6 +39097,373 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7B29B1-81FD-48F8-9727-C5470F35164D}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="18" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>964</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
   <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -41211,7 +41694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0E5EAC-9517-4640-A34C-6226E976EC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2482C28D-D177-4072-94BA-F6C6E384582F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -16,14 +16,15 @@
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
     <sheet name="Atributes" sheetId="2" r:id="rId2"/>
     <sheet name="Reference Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
-    <sheet name="Relationships" sheetId="4" r:id="rId5"/>
-    <sheet name="Validation Rules" sheetId="5" r:id="rId6"/>
+    <sheet name="Status Ref Data" sheetId="6" r:id="rId4"/>
+    <sheet name="Entity Ref Data" sheetId="7" r:id="rId5"/>
+    <sheet name="Relationships" sheetId="4" r:id="rId6"/>
+    <sheet name="Validation Rules" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atributes!$A$1:$W$396</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reference Data'!$A$1:$H$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Relationships!$A$1:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Relationships!$A$1:$K$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10285" uniqueCount="2258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10694" uniqueCount="2298">
   <si>
     <t>Domain</t>
   </si>
@@ -6809,6 +6810,126 @@
   </si>
   <si>
     <t>DRAFT, ACTIVE, INACTIVE, EXPIRED, CANCELLED</t>
+  </si>
+  <si>
+    <t>Company-owned physical branch</t>
+  </si>
+  <si>
+    <t>Canadian Dollar</t>
+  </si>
+  <si>
+    <t>Coffee chain</t>
+  </si>
+  <si>
+    <t>Fitness centre</t>
+  </si>
+  <si>
+    <t>Yoga studio</t>
+  </si>
+  <si>
+    <t>Retail store</t>
+  </si>
+  <si>
+    <t>Educational institute</t>
+  </si>
+  <si>
+    <t>Theme park</t>
+  </si>
+  <si>
+    <t>Coworking space</t>
+  </si>
+  <si>
+    <t>Automobile service centre</t>
+  </si>
+  <si>
+    <t>External payment gateway or payment service integration</t>
+  </si>
+  <si>
+    <t>Point of Sale system integration</t>
+  </si>
+  <si>
+    <t>ERP system integration</t>
+  </si>
+  <si>
+    <t>CRM platform integration</t>
+  </si>
+  <si>
+    <t>SMS gateway integration</t>
+  </si>
+  <si>
+    <t>Cloud file storage integration</t>
+  </si>
+  <si>
+    <t>Needs final catalogue</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>ISO 3166-1 alpha-2</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>Region / State / Province</t>
+  </si>
+  <si>
+    <t>First-level administrative region within a country</t>
+  </si>
+  <si>
+    <t>Country-dependent; use ISO/official administrative codes where available</t>
+  </si>
+  <si>
+    <t>City/locality within a country and region</t>
+  </si>
+  <si>
+    <t>Country + Region dependent</t>
+  </si>
+  <si>
+    <t>Accounting/bookkeeping integration</t>
+  </si>
+  <si>
+    <t>Loyalty/rewards integration</t>
+  </si>
+  <si>
+    <t>Online commerce integration</t>
+  </si>
+  <si>
+    <t>Authentication/SSO integration</t>
+  </si>
+  <si>
+    <t>Email provider integration</t>
+  </si>
+  <si>
+    <t>WhatsApp messaging integration</t>
+  </si>
+  <si>
+    <t>Push notification integration</t>
+  </si>
+  <si>
+    <t>Reporting/analytics integration</t>
+  </si>
+  <si>
+    <t>Inbound/outbound webhook integration</t>
+  </si>
+  <si>
+    <t>Generic API integration</t>
+  </si>
+  <si>
+    <t>Proprietary external integration</t>
+  </si>
+  <si>
+    <t>Platform presentation template</t>
   </si>
 </sst>
 </file>
@@ -6884,7 +7005,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6937,6 +7058,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9785,7 +9909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1">
+    <row r="7" spans="1:23">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -9853,7 +9977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" hidden="1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -11142,7 +11266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="30">
+    <row r="27" spans="1:23" ht="30" hidden="1">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -11830,7 +11954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45" hidden="1">
+    <row r="37" spans="1:23" ht="45">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -11901,7 +12025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="30">
+    <row r="38" spans="1:23" ht="30" hidden="1">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -12657,7 +12781,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="30">
+    <row r="50" spans="1:23" ht="30" hidden="1">
       <c r="A50" s="3" t="s">
         <v>317</v>
       </c>
@@ -12908,7 +13032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="30">
+    <row r="54" spans="1:23" ht="30" hidden="1">
       <c r="A54" s="4" t="s">
         <v>341</v>
       </c>
@@ -13668,7 +13792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="30">
+    <row r="65" spans="1:23" ht="30" hidden="1">
       <c r="A65" s="4" t="s">
         <v>370</v>
       </c>
@@ -14307,7 +14431,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30" hidden="1">
+    <row r="74" spans="1:23" ht="30">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -14378,7 +14502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30" hidden="1">
+    <row r="75" spans="1:23" ht="30">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -14520,7 +14644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="30">
+    <row r="77" spans="1:23" ht="30" hidden="1">
       <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
@@ -15443,7 +15567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23" hidden="1">
+    <row r="90" spans="1:23">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -15514,7 +15638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23" hidden="1">
+    <row r="91" spans="1:23">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -15656,7 +15780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="30">
+    <row r="93" spans="1:23" ht="30" hidden="1">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -16863,7 +16987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30" hidden="1">
+    <row r="110" spans="1:23" ht="30">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -16934,7 +17058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" hidden="1">
       <c r="A111" s="4" t="s">
         <v>548</v>
       </c>
@@ -18070,7 +18194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" hidden="1">
       <c r="A127" s="4" t="s">
         <v>620</v>
       </c>
@@ -19206,7 +19330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="30">
+    <row r="143" spans="1:23" ht="30" hidden="1">
       <c r="A143" s="4" t="s">
         <v>673</v>
       </c>
@@ -19987,7 +20111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23" hidden="1">
+    <row r="154" spans="1:23">
       <c r="A154" s="4" t="s">
         <v>34</v>
       </c>
@@ -20200,7 +20324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="30">
+    <row r="157" spans="1:23" ht="30" hidden="1">
       <c r="A157" s="4" t="s">
         <v>34</v>
       </c>
@@ -21407,7 +21531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="30">
+    <row r="174" spans="1:23" ht="30" hidden="1">
       <c r="A174" s="4" t="s">
         <v>35</v>
       </c>
@@ -28011,7 +28135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="30">
+    <row r="270" spans="1:23" ht="30" hidden="1">
       <c r="A270" s="3" t="s">
         <v>1518</v>
       </c>
@@ -29028,7 +29152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:23" ht="30">
+    <row r="285" spans="1:23" ht="30" hidden="1">
       <c r="A285" s="3" t="s">
         <v>1578</v>
       </c>
@@ -29765,7 +29889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23" hidden="1">
+    <row r="296" spans="1:23">
       <c r="A296" s="3" t="s">
         <v>1635</v>
       </c>
@@ -29899,7 +30023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:23">
+    <row r="298" spans="1:23" hidden="1">
       <c r="A298" s="3" t="s">
         <v>1635</v>
       </c>
@@ -30439,7 +30563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30" hidden="1">
+    <row r="306" spans="1:23" ht="30">
       <c r="A306" s="3" t="s">
         <v>1689</v>
       </c>
@@ -30575,7 +30699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="30">
+    <row r="308" spans="1:23" ht="30" hidden="1">
       <c r="A308" s="3" t="s">
         <v>1689</v>
       </c>
@@ -31391,7 +31515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="30">
+    <row r="320" spans="1:23" ht="30" hidden="1">
       <c r="A320" s="3" t="s">
         <v>1704</v>
       </c>
@@ -32203,7 +32327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="30">
+    <row r="332" spans="1:23" ht="30" hidden="1">
       <c r="A332" s="3" t="s">
         <v>1806</v>
       </c>
@@ -32745,7 +32869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:23" hidden="1">
+    <row r="340" spans="1:23">
       <c r="A340" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33163,7 +33287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="30">
+    <row r="346" spans="1:23" ht="30" hidden="1">
       <c r="A346" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33932,7 +34056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="30">
+    <row r="357" spans="1:23" ht="30" hidden="1">
       <c r="A357" s="3" t="s">
         <v>1922</v>
       </c>
@@ -34216,7 +34340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:23" ht="45">
+    <row r="361" spans="1:23" ht="45" hidden="1">
       <c r="A361" s="4" t="s">
         <v>2018</v>
       </c>
@@ -34926,7 +35050,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="30">
+    <row r="371" spans="1:23" ht="30" hidden="1">
       <c r="A371" s="4" t="s">
         <v>2062</v>
       </c>
@@ -36260,7 +36384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:23" ht="30">
+    <row r="390" spans="1:23" ht="30" hidden="1">
       <c r="A390" s="4" t="s">
         <v>2110</v>
       </c>
@@ -36761,7 +36885,16 @@
   <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
     <filterColumn colId="10">
       <filters>
-        <filter val="Status"/>
+        <filter val="Benefit Category"/>
+        <filter val="Benefit Type"/>
+        <filter val="Currency"/>
+        <filter val="Integration Type"/>
+        <filter val="Organization Type"/>
+        <filter val="Organization User Type"/>
+        <filter val="Product Category"/>
+        <filter val="Product Type"/>
+        <filter val="Store Type"/>
+        <filter val="Template Type"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -39464,6 +39597,1689 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCF67D5-27CE-4C3A-997A-96A77E128378}">
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21" style="4" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>853</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45">
+      <c r="A5" s="13" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30">
+      <c r="A6" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30">
+      <c r="A9" s="13" t="s">
+        <v>757</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" ht="30">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" ht="30">
+      <c r="A12" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="E14" s="5">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="E15" s="5">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="E18" s="5">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" ht="30">
+      <c r="A19" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" ht="30">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="E24" s="5">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="E25" s="5">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" ht="30">
+      <c r="A26" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" ht="30">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" ht="30">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="E28" s="5">
+        <v>3</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="30">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="E29" s="5">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E32" s="5">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E33" s="5">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E34" s="5">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E36" s="5">
+        <v>2</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E37" s="5">
+        <v>3</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E39" s="5">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="5">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E41" s="5">
+        <v>7</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E42" s="5">
+        <v>8</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E43" s="5">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E44" s="5">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E45" s="5">
+        <v>11</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E46" s="5">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E47" s="5">
+        <v>13</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E48" s="5">
+        <v>14</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E49" s="5">
+        <v>15</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E50" s="5">
+        <v>16</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E51" s="5">
+        <v>17</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E52" s="5">
+        <v>18</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" ht="30">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E53" s="5">
+        <v>19</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" ht="45">
+      <c r="A54" s="13" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="30">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="30">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E56" s="5">
+        <v>3</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="45">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>2271</v>
+      </c>
+      <c r="E57" s="5">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="30">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E58" s="5">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E59" s="5">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="30">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E60" s="5">
+        <v>7</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="30">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E61" s="5">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="30">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E62" s="5">
+        <v>9</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="30">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E63" s="5">
+        <v>10</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="30">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E64" s="5">
+        <v>11</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="30">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E65" s="5">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="30">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E66" s="5">
+        <v>13</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="30">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E67" s="5">
+        <v>14</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="30">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E68" s="5">
+        <v>15</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="30">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E69" s="5">
+        <v>16</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="30">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E70" s="5">
+        <v>17</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="30">
+      <c r="A71" s="13" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
   <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -41694,7 +43510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,23 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2482C28D-D177-4072-94BA-F6C6E384582F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646BDD4-2FDE-4846-A818-98AC9DF4AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
     <sheet name="Atributes" sheetId="2" r:id="rId2"/>
-    <sheet name="Reference Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Status Ref Data" sheetId="6" r:id="rId4"/>
-    <sheet name="Entity Ref Data" sheetId="7" r:id="rId5"/>
-    <sheet name="Relationships" sheetId="4" r:id="rId6"/>
-    <sheet name="Validation Rules" sheetId="5" r:id="rId7"/>
+    <sheet name="Template Default Content" sheetId="10" r:id="rId3"/>
+    <sheet name="Organization Type Template" sheetId="11" r:id="rId4"/>
+    <sheet name="Reference Data" sheetId="3" r:id="rId5"/>
+    <sheet name="Country-State-City Ref data" sheetId="8" r:id="rId6"/>
+    <sheet name="Template Ref Data" sheetId="9" r:id="rId7"/>
+    <sheet name="Status Ref Data" sheetId="6" r:id="rId8"/>
+    <sheet name="Entity Ref Data" sheetId="7" r:id="rId9"/>
+    <sheet name="Relationships" sheetId="4" r:id="rId10"/>
+    <sheet name="Validation Rules" sheetId="5" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atributes!$A$1:$W$396</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reference Data'!$A$1:$H$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Relationships!$A$1:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reference Data'!$A$1:$H$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Relationships!$A$1:$K$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10694" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10892" uniqueCount="2399">
   <si>
     <t>Domain</t>
   </si>
@@ -6930,6 +6934,309 @@
   </si>
   <si>
     <t>Platform presentation template</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Initial cities</t>
+  </si>
+  <si>
+    <t>Ontario</t>
+  </si>
+  <si>
+    <t>Toronto, Ottawa, Mississauga, Brampton, Hamilton, London, Markham, Vaughan</t>
+  </si>
+  <si>
+    <t>British Columbia</t>
+  </si>
+  <si>
+    <t>Vancouver, Victoria, Surrey, Burnaby, Richmond</t>
+  </si>
+  <si>
+    <t>Quebec</t>
+  </si>
+  <si>
+    <t>Montreal, Quebec City, Laval, Gatineau</t>
+  </si>
+  <si>
+    <t>Alberta</t>
+  </si>
+  <si>
+    <t>Calgary, Edmonton, Red Deer</t>
+  </si>
+  <si>
+    <t>Manitoba</t>
+  </si>
+  <si>
+    <t>Winnipeg</t>
+  </si>
+  <si>
+    <t>Saskatchewan</t>
+  </si>
+  <si>
+    <t>Saskatoon, Regina</t>
+  </si>
+  <si>
+    <t>Nova Scotia</t>
+  </si>
+  <si>
+    <t>Halifax</t>
+  </si>
+  <si>
+    <t>New Brunswick</t>
+  </si>
+  <si>
+    <t>Moncton, Saint John, Fredericton</t>
+  </si>
+  <si>
+    <t>Newfoundland and Labrador</t>
+  </si>
+  <si>
+    <t>St. John's</t>
+  </si>
+  <si>
+    <t>Prince Edward Island</t>
+  </si>
+  <si>
+    <t>Charlottetown</t>
+  </si>
+  <si>
+    <t>Yukon</t>
+  </si>
+  <si>
+    <t>Whitehorse</t>
+  </si>
+  <si>
+    <t>Northwest Territories</t>
+  </si>
+  <si>
+    <t>Yellowknife</t>
+  </si>
+  <si>
+    <t>Nunavut</t>
+  </si>
+  <si>
+    <t>Iqaluit</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Los Angeles, San Diego, San Jose, San Francisco, Sacramento</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>New York City, Buffalo, Rochester, Albany</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Houston, San Antonio, Dallas, Austin, Fort Worth</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Seattle, Spokane, Tacoma</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Miami, Orlando, Tampa, Jacksonville</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Chicago, Aurora, Naperville</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Boston, Worcester, Springfield</t>
+  </si>
+  <si>
+    <t>Mumbai, Pune, Nagpur, Nashik, Thane, Navi Mumbai</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Bengaluru, Mysuru, Mangaluru</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Kolkata, Howrah, Siliguri</t>
+  </si>
+  <si>
+    <t>Tamil Nadu</t>
+  </si>
+  <si>
+    <t>Chennai, Coimbatore, Madurai</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Hyderabad, Warangal</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Ahmedabad, Surat, Vadodara, Rajkot</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>Jaipur, Jodhpur, Udaipur, Jaisalmer</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>Lucknow, Kanpur, Varanasi, Agra, Prayagraj</t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>Thiruvananthapuram, Kochi, Kozhikode</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>Amritsar, Ludhiana, Jalandhar</t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t>Gurugram, Faridabad, Panipat</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Patna, Gaya</t>
+  </si>
+  <si>
+    <t>Odisha</t>
+  </si>
+  <si>
+    <t>Bhubaneswar, Cuttack</t>
+  </si>
+  <si>
+    <t>Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>Bhopal, Indore, Gwalior, Jabalpur</t>
+  </si>
+  <si>
+    <t>Template Code</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>F_AND_B_BAKERY_V1</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage — Café / Bakery</t>
+  </si>
+  <si>
+    <t>FOOD_AND_BEVERAGE</t>
+  </si>
+  <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
+    <t>SALON_V1</t>
+  </si>
+  <si>
+    <t>BEAUTY_AND_WELLNESS</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Template Default Content ID</t>
+  </si>
+  <si>
+    <t>template_default_content_id</t>
+  </si>
+  <si>
+    <t>FK → Template</t>
+  </si>
+  <si>
+    <t>Content Format</t>
+  </si>
+  <si>
+    <t>content_format</t>
+  </si>
+  <si>
+    <t>Content Definition</t>
+  </si>
+  <si>
+    <t>content_definition</t>
+  </si>
+  <si>
+    <t>Starter configuration/content</t>
+  </si>
+  <si>
+    <t>Content Version</t>
+  </si>
+  <si>
+    <t>content_version</t>
+  </si>
+  <si>
+    <t>Version the starter pack</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>Soft delete</t>
+  </si>
+  <si>
+    <t>Organization Type Template ID</t>
+  </si>
+  <si>
+    <t>organization_type_template_id</t>
+  </si>
+  <si>
+    <t>FK → Organization Type</t>
+  </si>
+  <si>
+    <t>is_default</t>
+  </si>
+  <si>
+    <t>Identifies default template</t>
+  </si>
+  <si>
+    <t>Mapping availability</t>
+  </si>
+  <si>
+    <t>Ordering</t>
   </si>
 </sst>
 </file>
@@ -9468,6 +9775,3193 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
+  <dimension ref="A1:K63"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="58.140625" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="14" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="4" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>2211</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="4" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="4" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="4" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F28" t="s">
+        <v>774</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F31" t="s">
+        <v>839</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F36" t="s">
+        <v>713</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="4" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="4" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="4" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="4" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1717</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="4" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="4" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="4" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="30">
+      <c r="A49" s="4" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="4" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="30">
+      <c r="A51" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="30">
+      <c r="A52" s="4" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="4" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="4" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="4" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="4" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="4" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="45">
+      <c r="A58" s="4" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="30">
+      <c r="A59" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="4" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="4" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="4" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="4" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K63" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="12" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1388</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+      <c r="C6" t="s">
+        <v>587</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B7" t="s">
+        <v>620</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H8" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>826</v>
+      </c>
+      <c r="D9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H9" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B10" t="s">
+        <v>673</v>
+      </c>
+      <c r="C10" t="s">
+        <v>707</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H10" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H11" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B13" t="s">
+        <v>548</v>
+      </c>
+      <c r="C13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H13" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H14" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C15" t="s">
+        <v>317</v>
+      </c>
+      <c r="D15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H15" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="30">
+      <c r="A16" s="3" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30">
+      <c r="A17" s="3" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1882</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30">
+      <c r="A18" s="3" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30">
+      <c r="A19" s="3" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30">
+      <c r="A20" s="3" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30">
+      <c r="A21" s="3" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30">
+      <c r="A22" s="3" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="30">
+      <c r="A23" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30">
+      <c r="A24" s="3" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30">
+      <c r="A25" s="3" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F26" t="s">
+        <v>2212</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2187</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2214</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D29" t="s">
+        <v>291</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2216</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2217</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2218</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2196</v>
+      </c>
+      <c r="F31" t="s">
+        <v>2188</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="3" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2219</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D33" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2199</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2221</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2222</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2201</v>
+      </c>
+      <c r="F35" t="s">
+        <v>2223</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2224</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
   <sheetPr filterMode="1"/>
@@ -9909,7 +13403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -11954,7 +15448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45">
+    <row r="37" spans="1:23" ht="45" hidden="1">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -14431,7 +17925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30">
+    <row r="74" spans="1:23" ht="30" hidden="1">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -14502,7 +17996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30">
+    <row r="75" spans="1:23" ht="30" hidden="1">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -15567,7 +19061,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" hidden="1">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -15638,7 +19132,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" hidden="1">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -16987,7 +20481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30">
+    <row r="110" spans="1:23" ht="30" hidden="1">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -20111,7 +23605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" hidden="1">
       <c r="A154" s="4" t="s">
         <v>34</v>
       </c>
@@ -29889,7 +33383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" hidden="1">
       <c r="A296" s="3" t="s">
         <v>1635</v>
       </c>
@@ -30563,7 +34057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30">
+    <row r="306" spans="1:23" ht="30" hidden="1">
       <c r="A306" s="3" t="s">
         <v>1689</v>
       </c>
@@ -32800,7 +36294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:23" hidden="1">
+    <row r="339" spans="1:23">
       <c r="A339" s="3" t="s">
         <v>1914</v>
       </c>
@@ -32938,7 +36432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:23" hidden="1">
+    <row r="341" spans="1:23">
       <c r="A341" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33007,7 +36501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="30" hidden="1">
+    <row r="342" spans="1:23" ht="30">
       <c r="A342" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33076,7 +36570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="30" hidden="1">
+    <row r="343" spans="1:23" ht="30">
       <c r="A343" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33147,7 +36641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="30" hidden="1">
+    <row r="344" spans="1:23" ht="30">
       <c r="A344" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33216,7 +36710,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="345" spans="1:23" hidden="1">
+    <row r="345" spans="1:23">
       <c r="A345" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33287,7 +36781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="30" hidden="1">
+    <row r="346" spans="1:23" ht="30">
       <c r="A346" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33358,7 +36852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="30" hidden="1">
+    <row r="347" spans="1:23" ht="30">
       <c r="A347" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33429,7 +36923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:23" hidden="1">
+    <row r="348" spans="1:23">
       <c r="A348" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33498,7 +36992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="30" hidden="1">
+    <row r="349" spans="1:23" ht="30">
       <c r="A349" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33569,7 +37063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="30" hidden="1">
+    <row r="350" spans="1:23" ht="30">
       <c r="A350" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33638,7 +37132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="30" hidden="1">
+    <row r="351" spans="1:23" ht="30">
       <c r="A351" s="3" t="s">
         <v>1914</v>
       </c>
@@ -33709,7 +37203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="30" hidden="1">
+    <row r="352" spans="1:23" ht="30">
       <c r="A352" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36883,18 +40377,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-    <filterColumn colId="10">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Benefit Category"/>
-        <filter val="Benefit Type"/>
-        <filter val="Currency"/>
-        <filter val="Integration Type"/>
-        <filter val="Organization Type"/>
-        <filter val="Organization User Type"/>
-        <filter val="Product Category"/>
-        <filter val="Product Type"/>
-        <filter val="Store Type"/>
-        <filter val="Template Type"/>
+        <filter val="Template"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -36910,6 +40395,328 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB69E303-A7E6-4340-BB09-24AE7640CD38}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30">
+      <c r="A2" s="3" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30">
+      <c r="A5" s="3" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB6A490-4722-4D86-89A3-00192739A23A}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="41.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FF8F3C-B975-44A1-AEC1-A0B924B73AFA}">
   <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -39229,7 +43036,488 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC977184-2C78-4F4B-925B-1B78E6658C38}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="35.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="73.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA9DE7E5-F033-4EE0-B5C6-8E739555A5CA}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23" style="4" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30">
+      <c r="A2" s="3" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7B29B1-81FD-48F8-9727-C5470F35164D}">
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -39596,7 +43884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCF67D5-27CE-4C3A-997A-96A77E128378}">
   <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -41277,3191 +45565,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="58.140625" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="14" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>1295</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>1296</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>1297</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>1298</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="4" t="s">
-        <v>1299</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>1300</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="3" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="4" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="4" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>1313</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="4" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="4" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="4" t="s">
-        <v>1319</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>1320</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="4" t="s">
-        <v>1322</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="4" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="4" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="4" t="s">
-        <v>1328</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>1329</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="4" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="4" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="4" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>2211</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="4" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="4" t="s">
-        <v>1338</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="4" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="4" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>1337</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="4" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="4" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>1348</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="4" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>1350</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="4" t="s">
-        <v>1349</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="4" t="s">
-        <v>1352</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="4" t="s">
-        <v>1355</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="4" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="4" t="s">
-        <v>1359</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F28" t="s">
-        <v>774</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="4" t="s">
-        <v>1360</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>1364</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="4" t="s">
-        <v>1361</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="4" t="s">
-        <v>1363</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F31" t="s">
-        <v>839</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="4" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="4" t="s">
-        <v>1369</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="4" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="4" t="s">
-        <v>1373</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="4" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F36" t="s">
-        <v>713</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="4" t="s">
-        <v>1379</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>1806</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>1845</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="4" t="s">
-        <v>1381</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>1806</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>1848</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="4" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>1806</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>1851</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>1852</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="4" t="s">
-        <v>1847</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>1635</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>2180</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="4" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>1635</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>1858</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="4" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>1635</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>1630</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>1668</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="4" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>1862</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>1520</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="4" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>1704</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>1704</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>1705</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="4" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>1716</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1717</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>1337</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="4" t="s">
-        <v>1861</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>1518</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>1337</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="4" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F48" t="s">
-        <v>1565</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="30">
-      <c r="A49" s="4" t="s">
-        <v>1866</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>1875</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>1365</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>1337</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="4" t="s">
-        <v>1868</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>1578</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>1877</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F50" t="s">
-        <v>1620</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="30">
-      <c r="A51" s="4" t="s">
-        <v>1870</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>2018</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="30">
-      <c r="A52" s="4" t="s">
-        <v>1872</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>2018</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="4" t="s">
-        <v>1874</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>2018</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>2208</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F53" s="16" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>2209</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="4" t="s">
-        <v>2057</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>2062</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>2098</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="4" t="s">
-        <v>2058</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>2062</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>2100</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="4" t="s">
-        <v>2059</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>2062</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>2102</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="4" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>2168</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="45">
-      <c r="A58" s="4" t="s">
-        <v>2105</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>2170</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="30">
-      <c r="A59" s="4" t="s">
-        <v>2106</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>2172</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" s="4" t="s">
-        <v>2176</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" s="4" t="s">
-        <v>2177</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>1922</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>1914</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>2181</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>1925</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="A62" s="4" t="s">
-        <v>2178</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>1914</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>1966</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F62" t="s">
-        <v>1967</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>2183</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="4" t="s">
-        <v>2179</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>2184</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K63" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
-        <v>1382</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>1383</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>1385</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>1386</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>1387</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>1388</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>1389</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1390</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1391</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>1394</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1396</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>1397</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1390</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1403</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>1404</v>
-      </c>
-      <c r="B6" t="s">
-        <v>548</v>
-      </c>
-      <c r="C6" t="s">
-        <v>587</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1406</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1407</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>1408</v>
-      </c>
-      <c r="B7" t="s">
-        <v>620</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D7" t="s">
-        <v>291</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1410</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1411</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>1413</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1414</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1415</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H8" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>1416</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>826</v>
-      </c>
-      <c r="D9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H9" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>1419</v>
-      </c>
-      <c r="B10" t="s">
-        <v>673</v>
-      </c>
-      <c r="C10" t="s">
-        <v>707</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1420</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1421</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H10" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>1422</v>
-      </c>
-      <c r="B11" t="s">
-        <v>673</v>
-      </c>
-      <c r="C11" t="s">
-        <v>620</v>
-      </c>
-      <c r="D11" t="s">
-        <v>175</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1423</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1424</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H11" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>1425</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B13" t="s">
-        <v>548</v>
-      </c>
-      <c r="C13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1430</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1431</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H13" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1434</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H14" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>1435</v>
-      </c>
-      <c r="B15" t="s">
-        <v>341</v>
-      </c>
-      <c r="C15" t="s">
-        <v>317</v>
-      </c>
-      <c r="D15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1437</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H15" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30">
-      <c r="A16" s="3" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1806</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>1880</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>1412</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30">
-      <c r="A17" s="3" t="s">
-        <v>1881</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>1806</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>1882</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>1883</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30">
-      <c r="A18" s="3" t="s">
-        <v>1884</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1806</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>1885</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>1887</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="30">
-      <c r="A19" s="3" t="s">
-        <v>1888</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>1640</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>1889</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>1890</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30">
-      <c r="A20" s="3" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>1892</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>1893</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="30">
-      <c r="A21" s="3" t="s">
-        <v>1894</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>1704</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>1896</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>1897</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="30">
-      <c r="A22" s="3" t="s">
-        <v>1895</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>1899</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1900</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>1901</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="30">
-      <c r="A23" s="3" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>1518</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1903</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>1904</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30">
-      <c r="A24" s="3" t="s">
-        <v>1902</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>1907</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="30">
-      <c r="A25" s="3" t="s">
-        <v>1905</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1909</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>1910</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="3" t="s">
-        <v>1908</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2186</v>
-      </c>
-      <c r="F26" t="s">
-        <v>2212</v>
-      </c>
-      <c r="G26" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H26" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>2190</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2187</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H27" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="3" t="s">
-        <v>2191</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2213</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E28" t="s">
-        <v>2214</v>
-      </c>
-      <c r="F28" t="s">
-        <v>2214</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H28" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="3" t="s">
-        <v>2192</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C29" t="s">
-        <v>2215</v>
-      </c>
-      <c r="D29" t="s">
-        <v>291</v>
-      </c>
-      <c r="E29" t="s">
-        <v>2189</v>
-      </c>
-      <c r="F29" t="s">
-        <v>2216</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H29" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="3" t="s">
-        <v>2193</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2062</v>
-      </c>
-      <c r="C30" t="s">
-        <v>2213</v>
-      </c>
-      <c r="D30" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2217</v>
-      </c>
-      <c r="F30" t="s">
-        <v>2218</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H30" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="3" t="s">
-        <v>2197</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>2194</v>
-      </c>
-      <c r="D31" t="s">
-        <v>2195</v>
-      </c>
-      <c r="E31" t="s">
-        <v>2196</v>
-      </c>
-      <c r="F31" t="s">
-        <v>2188</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="3" t="s">
-        <v>2203</v>
-      </c>
-      <c r="B32" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C32" t="s">
-        <v>2126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" t="s">
-        <v>2198</v>
-      </c>
-      <c r="F32" t="s">
-        <v>2219</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="3" t="s">
-        <v>2204</v>
-      </c>
-      <c r="B33" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2220</v>
-      </c>
-      <c r="D33" t="s">
-        <v>291</v>
-      </c>
-      <c r="E33" t="s">
-        <v>2199</v>
-      </c>
-      <c r="F33" t="s">
-        <v>2221</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H33" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="3" t="s">
-        <v>2205</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2146</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2200</v>
-      </c>
-      <c r="F34" t="s">
-        <v>2222</v>
-      </c>
-      <c r="G34" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H34" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="3" t="s">
-        <v>2206</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C35" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E35" t="s">
-        <v>2201</v>
-      </c>
-      <c r="F35" t="s">
-        <v>2223</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H35" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="3" t="s">
-        <v>2207</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E36" t="s">
-        <v>2202</v>
-      </c>
-      <c r="F36" t="s">
-        <v>2224</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1392</v>
-      </c>
-      <c r="H36" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646BDD4-2FDE-4846-A818-98AC9DF4AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F57A97-FD42-4D5F-B918-433EC83B7732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10892" uniqueCount="2399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11202" uniqueCount="2463">
   <si>
     <t>Domain</t>
   </si>
@@ -7237,6 +7237,198 @@
   </si>
   <si>
     <t>Ordering</t>
+  </si>
+  <si>
+    <t>Customer Experience</t>
+  </si>
+  <si>
+    <t>customer_experience</t>
+  </si>
+  <si>
+    <t>Represents the organization-specific customer-facing experience configuration derived from a Memgine platform template. Controls the presentation, branding, sections and configurable customer-facing content while the underlying business data remains in its respective domain entities.</t>
+  </si>
+  <si>
+    <t>customer_experience_id</t>
+  </si>
+  <si>
+    <t>Experience Name</t>
+  </si>
+  <si>
+    <t>One customer experience configuration belongs to an organization. The selected Template controls the supported experience structure and capabilities. Actual transactional/domain content such as Offers remains in its respective entity and is not duplicated here.</t>
+  </si>
+  <si>
+    <t>Customer Experience ID</t>
+  </si>
+  <si>
+    <t>Uniquely identify a customer experience</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the organization customer experience configuration</t>
+  </si>
+  <si>
+    <t>Primary identifier for the customer experience configuration</t>
+  </si>
+  <si>
+    <t>ce-1001</t>
+  </si>
+  <si>
+    <t>Identify the owning organization</t>
+  </si>
+  <si>
+    <t>Identifies the organization that owns this customer experience</t>
+  </si>
+  <si>
+    <t>Tenant ownership and isolation key</t>
+  </si>
+  <si>
+    <t>org-1001</t>
+  </si>
+  <si>
+    <t>Identify the governing platform template</t>
+  </si>
+  <si>
+    <t>References the Memgine platform template that defines the structure and capabilities of the experience</t>
+  </si>
+  <si>
+    <t>Determines which sections and presentation capabilities are supported</t>
+  </si>
+  <si>
+    <t>tpl-f-and-b-bakery-v1</t>
+  </si>
+  <si>
+    <t>experience_name</t>
+  </si>
+  <si>
+    <t>Identify the customer experience configuration</t>
+  </si>
+  <si>
+    <t>Human-readable name for the organization's customer experience configuration</t>
+  </si>
+  <si>
+    <t>Administrative name used to identify the configuration</t>
+  </si>
+  <si>
+    <t>Sunrise Bakery Customer Experience</t>
+  </si>
+  <si>
+    <t>Experience Definition</t>
+  </si>
+  <si>
+    <t>experience_definition</t>
+  </si>
+  <si>
+    <t>Store configurable customer experience content and presentation</t>
+  </si>
+  <si>
+    <t>Stores flexible section configuration and customer-facing content governed by the selected template</t>
+  </si>
+  <si>
+    <t>{"hero":{"enabled":true}}</t>
+  </si>
+  <si>
+    <t>Template default</t>
+  </si>
+  <si>
+    <t>Experience Status ID</t>
+  </si>
+  <si>
+    <t>experience_status_id</t>
+  </si>
+  <si>
+    <t>Control the lifecycle of the customer experience</t>
+  </si>
+  <si>
+    <t>References the canonical Status entity controlling the lifecycle of the experience</t>
+  </si>
+  <si>
+    <t>Determines whether the experience is draft, active, inactive, etc.</t>
+  </si>
+  <si>
+    <t>status-active</t>
+  </si>
+  <si>
+    <t>Published At</t>
+  </si>
+  <si>
+    <t>published_at</t>
+  </si>
+  <si>
+    <t>Record when the current customer experience was published</t>
+  </si>
+  <si>
+    <t>Timestamp of the most recent successful publication</t>
+  </si>
+  <si>
+    <t>Publication audit timestamp</t>
+  </si>
+  <si>
+    <t>2026-08-25T10:30:00Z</t>
+  </si>
+  <si>
+    <t>Published By</t>
+  </si>
+  <si>
+    <t>published_by</t>
+  </si>
+  <si>
+    <t>Identify who published the experience</t>
+  </si>
+  <si>
+    <t>User responsible for the most recent publication</t>
+  </si>
+  <si>
+    <t>Publication audit user</t>
+  </si>
+  <si>
+    <t>user-1001</t>
+  </si>
+  <si>
+    <t>Timestamp when the customer experience record was created</t>
+  </si>
+  <si>
+    <t>Creation timestamp</t>
+  </si>
+  <si>
+    <t>2026-08-25T09:00:00Z</t>
+  </si>
+  <si>
+    <t>User that created the customer experience record</t>
+  </si>
+  <si>
+    <t>Creation audit user</t>
+  </si>
+  <si>
+    <t>Timestamp when the customer experience record was last modified</t>
+  </si>
+  <si>
+    <t>Last modification timestamp</t>
+  </si>
+  <si>
+    <t>2026-08-25T10:15:00Z</t>
+  </si>
+  <si>
+    <t>User that last modified the customer experience record</t>
+  </si>
+  <si>
+    <t>Last modification audit user</t>
+  </si>
+  <si>
+    <t>Indicates whether the customer experience record has been logically deleted</t>
+  </si>
+  <si>
+    <t>Prevents physical deletion while removing the record from normal application use</t>
+  </si>
+  <si>
+    <t>Version number used to prevent conflicting updates</t>
+  </si>
+  <si>
+    <t>Incremented whenever the record is modified</t>
+  </si>
+  <si>
+    <t>JSON/XML representation of configurable experience sections and content</t>
+  </si>
+  <si>
+    <t>customer-experience-status-draft</t>
   </si>
 </sst>
 </file>
@@ -7462,7 +7654,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q37" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q38" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -7783,20 +7975,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="4" customWidth="1"/>
     <col min="5" max="5" width="30" style="4" customWidth="1"/>
     <col min="6" max="6" width="48.5703125" style="4" customWidth="1"/>
     <col min="7" max="7" width="14.140625" style="4" customWidth="1"/>
     <col min="8" max="8" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="4" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27.42578125" style="4" customWidth="1"/>
@@ -9765,6 +9957,50 @@
       </c>
       <c r="Q37" s="4" t="s">
         <v>2116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="105">
+      <c r="A38" s="4" t="s">
+        <v>2399</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>2400</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>2401</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>2402</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>2403</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>2404</v>
       </c>
     </row>
   </sheetData>
@@ -12964,8 +13200,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:W396"/>
+  <dimension ref="A1:W410"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -13064,7 +13299,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="30" hidden="1">
+    <row r="2" spans="1:23" ht="30">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -13130,7 +13365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30" hidden="1">
+    <row r="3" spans="1:23" ht="30">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -13198,7 +13433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30" hidden="1">
+    <row r="4" spans="1:23" ht="30">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -13266,7 +13501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="60" hidden="1">
+    <row r="5" spans="1:23" ht="60">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -13335,7 +13570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30" hidden="1">
+    <row r="6" spans="1:23" ht="30">
       <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
@@ -13403,7 +13638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1">
+    <row r="7" spans="1:23">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -13471,7 +13706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1">
+    <row r="8" spans="1:23">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -13539,7 +13774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1">
+    <row r="9" spans="1:23">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -13607,7 +13842,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1">
+    <row r="10" spans="1:23">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -13675,7 +13910,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1">
+    <row r="11" spans="1:23">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
@@ -13743,7 +13978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30" hidden="1">
+    <row r="12" spans="1:23" ht="30">
       <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
@@ -13811,7 +14046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1">
+    <row r="13" spans="1:23">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -13879,7 +14114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="30" hidden="1">
+    <row r="14" spans="1:23" ht="30">
       <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
@@ -13947,7 +14182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1">
+    <row r="15" spans="1:23">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -14015,7 +14250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="30" hidden="1">
+    <row r="16" spans="1:23" ht="30">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -14083,7 +14318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1">
+    <row r="17" spans="1:23">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -14151,7 +14386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="30" hidden="1">
+    <row r="18" spans="1:23" ht="30">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -14218,7 +14453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="30" hidden="1">
+    <row r="19" spans="1:23" ht="30">
       <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
@@ -14287,7 +14522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1">
+    <row r="20" spans="1:23">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -14354,7 +14589,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1">
+    <row r="21" spans="1:23">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -14421,7 +14656,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1">
+    <row r="22" spans="1:23">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
@@ -14488,7 +14723,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="30" hidden="1">
+    <row r="23" spans="1:23" ht="30">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -14557,7 +14792,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="30" hidden="1">
+    <row r="24" spans="1:23" ht="30">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -14624,7 +14859,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="30" hidden="1">
+    <row r="25" spans="1:23" ht="30">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -14691,7 +14926,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="30" hidden="1">
+    <row r="26" spans="1:23" ht="30">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -14760,7 +14995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="30" hidden="1">
+    <row r="27" spans="1:23" ht="30">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -14829,7 +15064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="30" hidden="1">
+    <row r="28" spans="1:23" ht="30">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
@@ -14896,7 +15131,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1">
+    <row r="29" spans="1:23">
       <c r="A29" s="3" t="s">
         <v>8</v>
       </c>
@@ -14965,7 +15200,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="30" hidden="1">
+    <row r="30" spans="1:23" ht="30">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
@@ -15032,7 +15267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1">
+    <row r="31" spans="1:23">
       <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
@@ -15101,7 +15336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="30" hidden="1">
+    <row r="32" spans="1:23" ht="30">
       <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
@@ -15168,7 +15403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:23" hidden="1">
+    <row r="33" spans="1:23">
       <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
@@ -15235,7 +15470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="30" hidden="1">
+    <row r="34" spans="1:23" ht="30">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -15306,7 +15541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="30" hidden="1">
+    <row r="35" spans="1:23" ht="30">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -15377,7 +15612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:23" hidden="1">
+    <row r="36" spans="1:23">
       <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
@@ -15448,7 +15683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45" hidden="1">
+    <row r="37" spans="1:23" ht="45">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -15519,7 +15754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="30" hidden="1">
+    <row r="38" spans="1:23" ht="30">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -15590,7 +15825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="30" hidden="1">
+    <row r="39" spans="1:23" ht="30">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
@@ -15661,7 +15896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="30" hidden="1">
+    <row r="40" spans="1:23" ht="30">
       <c r="A40" s="3" t="s">
         <v>37</v>
       </c>
@@ -15732,7 +15967,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:23" hidden="1">
+    <row r="41" spans="1:23">
       <c r="A41" s="3" t="s">
         <v>37</v>
       </c>
@@ -15803,7 +16038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="30" hidden="1">
+    <row r="42" spans="1:23" ht="30">
       <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
@@ -15874,7 +16109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1">
+    <row r="43" spans="1:23">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
@@ -15945,7 +16180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1">
+    <row r="44" spans="1:23">
       <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
@@ -16016,7 +16251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:23" hidden="1">
+    <row r="45" spans="1:23">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -16087,7 +16322,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="30" hidden="1">
+    <row r="46" spans="1:23" ht="30">
       <c r="A46" s="3" t="s">
         <v>317</v>
       </c>
@@ -16134,7 +16369,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="30" hidden="1">
+    <row r="47" spans="1:23" ht="30">
       <c r="A47" s="3" t="s">
         <v>317</v>
       </c>
@@ -16181,7 +16416,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="45" hidden="1">
+    <row r="48" spans="1:23" ht="45">
       <c r="A48" s="3" t="s">
         <v>317</v>
       </c>
@@ -16228,7 +16463,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="30" hidden="1">
+    <row r="49" spans="1:23" ht="30">
       <c r="A49" s="3" t="s">
         <v>317</v>
       </c>
@@ -16275,7 +16510,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="30" hidden="1">
+    <row r="50" spans="1:23" ht="30">
       <c r="A50" s="3" t="s">
         <v>317</v>
       </c>
@@ -16322,7 +16557,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="30" hidden="1">
+    <row r="51" spans="1:23" ht="30">
       <c r="A51" s="4" t="s">
         <v>341</v>
       </c>
@@ -16390,7 +16625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="30" hidden="1">
+    <row r="52" spans="1:23" ht="30">
       <c r="A52" s="4" t="s">
         <v>341</v>
       </c>
@@ -16458,7 +16693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="30" hidden="1">
+    <row r="53" spans="1:23" ht="30">
       <c r="A53" s="4" t="s">
         <v>341</v>
       </c>
@@ -16526,7 +16761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="30" hidden="1">
+    <row r="54" spans="1:23" ht="30">
       <c r="A54" s="4" t="s">
         <v>341</v>
       </c>
@@ -16594,7 +16829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="30" hidden="1">
+    <row r="55" spans="1:23" ht="30">
       <c r="A55" s="4" t="s">
         <v>341</v>
       </c>
@@ -16662,7 +16897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="30" hidden="1">
+    <row r="56" spans="1:23" ht="30">
       <c r="A56" s="4" t="s">
         <v>341</v>
       </c>
@@ -16730,7 +16965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="30" hidden="1">
+    <row r="57" spans="1:23" ht="30">
       <c r="A57" s="4" t="s">
         <v>341</v>
       </c>
@@ -16798,7 +17033,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="30" hidden="1">
+    <row r="58" spans="1:23" ht="30">
       <c r="A58" s="4" t="s">
         <v>341</v>
       </c>
@@ -16866,7 +17101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="45" hidden="1">
+    <row r="59" spans="1:23" ht="45">
       <c r="A59" s="4" t="s">
         <v>341</v>
       </c>
@@ -16934,7 +17169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="30" hidden="1">
+    <row r="60" spans="1:23" ht="30">
       <c r="A60" s="4" t="s">
         <v>341</v>
       </c>
@@ -17002,7 +17237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="30" hidden="1">
+    <row r="61" spans="1:23" ht="30">
       <c r="A61" s="4" t="s">
         <v>370</v>
       </c>
@@ -17073,7 +17308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="30" hidden="1">
+    <row r="62" spans="1:23" ht="30">
       <c r="A62" s="4" t="s">
         <v>370</v>
       </c>
@@ -17144,7 +17379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="30" hidden="1">
+    <row r="63" spans="1:23" ht="30">
       <c r="A63" s="4" t="s">
         <v>370</v>
       </c>
@@ -17215,7 +17450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="30" hidden="1">
+    <row r="64" spans="1:23" ht="30">
       <c r="A64" s="4" t="s">
         <v>370</v>
       </c>
@@ -17286,7 +17521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="30" hidden="1">
+    <row r="65" spans="1:23" ht="30">
       <c r="A65" s="4" t="s">
         <v>370</v>
       </c>
@@ -17357,7 +17592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="30" hidden="1">
+    <row r="66" spans="1:23" ht="30">
       <c r="A66" s="4" t="s">
         <v>377</v>
       </c>
@@ -17428,7 +17663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="30" hidden="1">
+    <row r="67" spans="1:23" ht="30">
       <c r="A67" s="4" t="s">
         <v>377</v>
       </c>
@@ -17499,7 +17734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="30" hidden="1">
+    <row r="68" spans="1:23" ht="30">
       <c r="A68" s="4" t="s">
         <v>377</v>
       </c>
@@ -17570,7 +17805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="30" hidden="1">
+    <row r="69" spans="1:23" ht="30">
       <c r="A69" s="4" t="s">
         <v>10</v>
       </c>
@@ -17641,7 +17876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="30" hidden="1">
+    <row r="70" spans="1:23" ht="30">
       <c r="A70" s="4" t="s">
         <v>10</v>
       </c>
@@ -17712,7 +17947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="45" hidden="1">
+    <row r="71" spans="1:23" ht="45">
       <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
@@ -17783,7 +18018,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="45" hidden="1">
+    <row r="72" spans="1:23" ht="45">
       <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
@@ -17854,7 +18089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="30" hidden="1">
+    <row r="73" spans="1:23" ht="30">
       <c r="A73" s="4" t="s">
         <v>10</v>
       </c>
@@ -17925,7 +18160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30" hidden="1">
+    <row r="74" spans="1:23" ht="30">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -17996,7 +18231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30" hidden="1">
+    <row r="75" spans="1:23" ht="30">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -18067,7 +18302,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="30" hidden="1">
+    <row r="76" spans="1:23" ht="30">
       <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
@@ -18138,7 +18373,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="30" hidden="1">
+    <row r="77" spans="1:23" ht="30">
       <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
@@ -18209,7 +18444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="45" hidden="1">
+    <row r="78" spans="1:23" ht="45">
       <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
@@ -18280,7 +18515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="45" hidden="1">
+    <row r="79" spans="1:23" ht="45">
       <c r="A79" s="4" t="s">
         <v>10</v>
       </c>
@@ -18351,7 +18586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="30" hidden="1">
+    <row r="80" spans="1:23" ht="30">
       <c r="A80" s="4" t="s">
         <v>10</v>
       </c>
@@ -18422,7 +18657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="30" hidden="1">
+    <row r="81" spans="1:23" ht="30">
       <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
@@ -18493,7 +18728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="30" hidden="1">
+    <row r="82" spans="1:23" ht="30">
       <c r="A82" s="4" t="s">
         <v>10</v>
       </c>
@@ -18564,7 +18799,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="30" hidden="1">
+    <row r="83" spans="1:23" ht="30">
       <c r="A83" s="4" t="s">
         <v>10</v>
       </c>
@@ -18635,7 +18870,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="45" hidden="1">
+    <row r="84" spans="1:23" ht="45">
       <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
@@ -18706,7 +18941,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="30" hidden="1">
+    <row r="85" spans="1:23" ht="30">
       <c r="A85" s="4" t="s">
         <v>10</v>
       </c>
@@ -18777,7 +19012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="30" hidden="1">
+    <row r="86" spans="1:23" ht="30">
       <c r="A86" s="4" t="s">
         <v>490</v>
       </c>
@@ -18848,7 +19083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="30" hidden="1">
+    <row r="87" spans="1:23" ht="30">
       <c r="A87" s="4" t="s">
         <v>490</v>
       </c>
@@ -18919,7 +19154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30" hidden="1">
+    <row r="88" spans="1:23" ht="30">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -18990,7 +19225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30" hidden="1">
+    <row r="89" spans="1:23" ht="30">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -19061,7 +19296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23" hidden="1">
+    <row r="90" spans="1:23">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -19132,7 +19367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23" hidden="1">
+    <row r="91" spans="1:23">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -19203,7 +19438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="45" hidden="1">
+    <row r="92" spans="1:23" ht="45">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -19274,7 +19509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="30" hidden="1">
+    <row r="93" spans="1:23" ht="30">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -19345,7 +19580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="30" hidden="1">
+    <row r="94" spans="1:23" ht="30">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -19416,7 +19651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30" hidden="1">
+    <row r="95" spans="1:23" ht="30">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -19487,7 +19722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30" hidden="1">
+    <row r="96" spans="1:23" ht="30">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -19558,7 +19793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="30" hidden="1">
+    <row r="97" spans="1:23" ht="30">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -19629,7 +19864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30" hidden="1">
+    <row r="98" spans="1:23" ht="30">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -19700,7 +19935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30" hidden="1">
+    <row r="99" spans="1:23" ht="30">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -19771,7 +20006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30" hidden="1">
+    <row r="100" spans="1:23" ht="30">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -19842,7 +20077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30" hidden="1">
+    <row r="101" spans="1:23" ht="30">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -19913,7 +20148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30" hidden="1">
+    <row r="102" spans="1:23" ht="30">
       <c r="A102" s="4" t="s">
         <v>548</v>
       </c>
@@ -19984,7 +20219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30" hidden="1">
+    <row r="103" spans="1:23" ht="30">
       <c r="A103" s="4" t="s">
         <v>548</v>
       </c>
@@ -20055,7 +20290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30" hidden="1">
+    <row r="104" spans="1:23" ht="30">
       <c r="A104" s="4" t="s">
         <v>548</v>
       </c>
@@ -20126,7 +20361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30" hidden="1">
+    <row r="105" spans="1:23" ht="30">
       <c r="A105" s="4" t="s">
         <v>548</v>
       </c>
@@ -20197,7 +20432,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30" hidden="1">
+    <row r="106" spans="1:23" ht="30">
       <c r="A106" s="4" t="s">
         <v>548</v>
       </c>
@@ -20268,7 +20503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:23" hidden="1">
+    <row r="107" spans="1:23">
       <c r="A107" s="4" t="s">
         <v>548</v>
       </c>
@@ -20339,7 +20574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:23" hidden="1">
+    <row r="108" spans="1:23">
       <c r="A108" s="4" t="s">
         <v>548</v>
       </c>
@@ -20410,7 +20645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:23" hidden="1">
+    <row r="109" spans="1:23">
       <c r="A109" s="4" t="s">
         <v>548</v>
       </c>
@@ -20481,7 +20716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30" hidden="1">
+    <row r="110" spans="1:23" ht="30">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -20552,7 +20787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:23" hidden="1">
+    <row r="111" spans="1:23">
       <c r="A111" s="4" t="s">
         <v>548</v>
       </c>
@@ -20623,7 +20858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="30" hidden="1">
+    <row r="112" spans="1:23" ht="30">
       <c r="A112" s="4" t="s">
         <v>548</v>
       </c>
@@ -20694,7 +20929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:23" hidden="1">
+    <row r="113" spans="1:23">
       <c r="A113" s="4" t="s">
         <v>548</v>
       </c>
@@ -20765,7 +21000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="30" hidden="1">
+    <row r="114" spans="1:23" ht="30">
       <c r="A114" s="4" t="s">
         <v>548</v>
       </c>
@@ -20836,7 +21071,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:23" hidden="1">
+    <row r="115" spans="1:23">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
@@ -20907,7 +21142,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="30" hidden="1">
+    <row r="116" spans="1:23" ht="30">
       <c r="A116" s="4" t="s">
         <v>548</v>
       </c>
@@ -20978,7 +21213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:23" hidden="1">
+    <row r="117" spans="1:23">
       <c r="A117" s="4" t="s">
         <v>548</v>
       </c>
@@ -21049,7 +21284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:23" hidden="1">
+    <row r="118" spans="1:23">
       <c r="A118" s="4" t="s">
         <v>548</v>
       </c>
@@ -21120,7 +21355,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:23" hidden="1">
+    <row r="119" spans="1:23">
       <c r="A119" s="4" t="s">
         <v>548</v>
       </c>
@@ -21191,7 +21426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="30" hidden="1">
+    <row r="120" spans="1:23" ht="30">
       <c r="A120" s="4" t="s">
         <v>620</v>
       </c>
@@ -21262,7 +21497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="30" hidden="1">
+    <row r="121" spans="1:23" ht="30">
       <c r="A121" s="4" t="s">
         <v>620</v>
       </c>
@@ -21333,7 +21568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:23" hidden="1">
+    <row r="122" spans="1:23">
       <c r="A122" s="4" t="s">
         <v>620</v>
       </c>
@@ -21404,7 +21639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="30" hidden="1">
+    <row r="123" spans="1:23" ht="30">
       <c r="A123" s="4" t="s">
         <v>620</v>
       </c>
@@ -21475,7 +21710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:23" hidden="1">
+    <row r="124" spans="1:23">
       <c r="A124" s="4" t="s">
         <v>620</v>
       </c>
@@ -21546,7 +21781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="30" hidden="1">
+    <row r="125" spans="1:23" ht="30">
       <c r="A125" s="4" t="s">
         <v>620</v>
       </c>
@@ -21617,7 +21852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:23" hidden="1">
+    <row r="126" spans="1:23">
       <c r="A126" s="4" t="s">
         <v>620</v>
       </c>
@@ -21688,7 +21923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:23" hidden="1">
+    <row r="127" spans="1:23">
       <c r="A127" s="4" t="s">
         <v>620</v>
       </c>
@@ -21759,7 +21994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="30" hidden="1">
+    <row r="128" spans="1:23" ht="30">
       <c r="A128" s="4" t="s">
         <v>620</v>
       </c>
@@ -21830,7 +22065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:23" ht="30" hidden="1">
+    <row r="129" spans="1:23" ht="30">
       <c r="A129" s="4" t="s">
         <v>620</v>
       </c>
@@ -21901,7 +22136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:23" hidden="1">
+    <row r="130" spans="1:23">
       <c r="A130" s="4" t="s">
         <v>620</v>
       </c>
@@ -21972,7 +22207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="30" hidden="1">
+    <row r="131" spans="1:23" ht="30">
       <c r="A131" s="4" t="s">
         <v>620</v>
       </c>
@@ -22043,7 +22278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:23" hidden="1">
+    <row r="132" spans="1:23">
       <c r="A132" s="4" t="s">
         <v>620</v>
       </c>
@@ -22114,7 +22349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:23" hidden="1">
+    <row r="133" spans="1:23">
       <c r="A133" s="4" t="s">
         <v>620</v>
       </c>
@@ -22185,7 +22420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:23" hidden="1">
+    <row r="134" spans="1:23">
       <c r="A134" s="4" t="s">
         <v>620</v>
       </c>
@@ -22256,7 +22491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:23" ht="30" hidden="1">
+    <row r="135" spans="1:23" ht="30">
       <c r="A135" s="4" t="s">
         <v>673</v>
       </c>
@@ -22327,7 +22562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="30" hidden="1">
+    <row r="136" spans="1:23" ht="30">
       <c r="A136" s="4" t="s">
         <v>673</v>
       </c>
@@ -22398,7 +22633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:23" ht="30" hidden="1">
+    <row r="137" spans="1:23" ht="30">
       <c r="A137" s="4" t="s">
         <v>673</v>
       </c>
@@ -22469,7 +22704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:23" ht="30" hidden="1">
+    <row r="138" spans="1:23" ht="30">
       <c r="A138" s="4" t="s">
         <v>673</v>
       </c>
@@ -22540,7 +22775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:23" ht="30" hidden="1">
+    <row r="139" spans="1:23" ht="30">
       <c r="A139" s="4" t="s">
         <v>673</v>
       </c>
@@ -22611,7 +22846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="30" hidden="1">
+    <row r="140" spans="1:23" ht="30">
       <c r="A140" s="4" t="s">
         <v>673</v>
       </c>
@@ -22682,7 +22917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="30" hidden="1">
+    <row r="141" spans="1:23" ht="30">
       <c r="A141" s="4" t="s">
         <v>673</v>
       </c>
@@ -22753,7 +22988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:23" hidden="1">
+    <row r="142" spans="1:23">
       <c r="A142" s="4" t="s">
         <v>673</v>
       </c>
@@ -22824,7 +23059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="30" hidden="1">
+    <row r="143" spans="1:23" ht="30">
       <c r="A143" s="4" t="s">
         <v>673</v>
       </c>
@@ -22895,7 +23130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="30" hidden="1">
+    <row r="144" spans="1:23" ht="30">
       <c r="A144" s="4" t="s">
         <v>673</v>
       </c>
@@ -22966,7 +23201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="30" hidden="1">
+    <row r="145" spans="1:23" ht="30">
       <c r="A145" s="4" t="s">
         <v>673</v>
       </c>
@@ -23037,7 +23272,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="30" hidden="1">
+    <row r="146" spans="1:23" ht="30">
       <c r="A146" s="4" t="s">
         <v>673</v>
       </c>
@@ -23108,7 +23343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:23" ht="30" hidden="1">
+    <row r="147" spans="1:23" ht="30">
       <c r="A147" s="4" t="s">
         <v>673</v>
       </c>
@@ -23179,7 +23414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="30" hidden="1">
+    <row r="148" spans="1:23" ht="30">
       <c r="A148" s="4" t="s">
         <v>673</v>
       </c>
@@ -23250,7 +23485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:23" hidden="1">
+    <row r="149" spans="1:23">
       <c r="A149" s="4" t="s">
         <v>673</v>
       </c>
@@ -23321,7 +23556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="30" hidden="1">
+    <row r="150" spans="1:23" ht="30">
       <c r="A150" s="4" t="s">
         <v>34</v>
       </c>
@@ -23392,7 +23627,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="30" hidden="1">
+    <row r="151" spans="1:23" ht="30">
       <c r="A151" s="4" t="s">
         <v>34</v>
       </c>
@@ -23463,7 +23698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="30" hidden="1">
+    <row r="152" spans="1:23" ht="30">
       <c r="A152" s="4" t="s">
         <v>34</v>
       </c>
@@ -23534,7 +23769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="30" hidden="1">
+    <row r="153" spans="1:23" ht="30">
       <c r="A153" s="4" t="s">
         <v>34</v>
       </c>
@@ -23605,7 +23840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23" hidden="1">
+    <row r="154" spans="1:23">
       <c r="A154" s="4" t="s">
         <v>34</v>
       </c>
@@ -23676,7 +23911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="30" hidden="1">
+    <row r="155" spans="1:23" ht="30">
       <c r="A155" s="4" t="s">
         <v>34</v>
       </c>
@@ -23747,7 +23982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="30" hidden="1">
+    <row r="156" spans="1:23" ht="30">
       <c r="A156" s="4" t="s">
         <v>34</v>
       </c>
@@ -23818,7 +24053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="30" hidden="1">
+    <row r="157" spans="1:23" ht="30">
       <c r="A157" s="4" t="s">
         <v>34</v>
       </c>
@@ -23889,7 +24124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="30" hidden="1">
+    <row r="158" spans="1:23" ht="30">
       <c r="A158" s="4" t="s">
         <v>34</v>
       </c>
@@ -23960,7 +24195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="30" hidden="1">
+    <row r="159" spans="1:23" ht="30">
       <c r="A159" s="4" t="s">
         <v>34</v>
       </c>
@@ -24031,7 +24266,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="30" hidden="1">
+    <row r="160" spans="1:23" ht="30">
       <c r="A160" s="4" t="s">
         <v>34</v>
       </c>
@@ -24102,7 +24337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:23" hidden="1">
+    <row r="161" spans="1:23">
       <c r="A161" s="4" t="s">
         <v>34</v>
       </c>
@@ -24173,7 +24408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="30" hidden="1">
+    <row r="162" spans="1:23" ht="30">
       <c r="A162" s="4" t="s">
         <v>34</v>
       </c>
@@ -24244,7 +24479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="30" hidden="1">
+    <row r="163" spans="1:23" ht="30">
       <c r="A163" s="4" t="s">
         <v>34</v>
       </c>
@@ -24315,7 +24550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="30" hidden="1">
+    <row r="164" spans="1:23" ht="30">
       <c r="A164" s="4" t="s">
         <v>34</v>
       </c>
@@ -24386,7 +24621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="30" hidden="1">
+    <row r="165" spans="1:23" ht="30">
       <c r="A165" s="4" t="s">
         <v>34</v>
       </c>
@@ -24457,7 +24692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="30" hidden="1">
+    <row r="166" spans="1:23" ht="30">
       <c r="A166" s="4" t="s">
         <v>35</v>
       </c>
@@ -24528,7 +24763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="30" hidden="1">
+    <row r="167" spans="1:23" ht="30">
       <c r="A167" s="4" t="s">
         <v>35</v>
       </c>
@@ -24599,7 +24834,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="30" hidden="1">
+    <row r="168" spans="1:23" ht="30">
       <c r="A168" s="4" t="s">
         <v>35</v>
       </c>
@@ -24670,7 +24905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="30" hidden="1">
+    <row r="169" spans="1:23" ht="30">
       <c r="A169" s="4" t="s">
         <v>35</v>
       </c>
@@ -24741,7 +24976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="30" hidden="1">
+    <row r="170" spans="1:23" ht="30">
       <c r="A170" s="4" t="s">
         <v>35</v>
       </c>
@@ -24812,7 +25047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="30" hidden="1">
+    <row r="171" spans="1:23" ht="30">
       <c r="A171" s="4" t="s">
         <v>35</v>
       </c>
@@ -24883,7 +25118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="30" hidden="1">
+    <row r="172" spans="1:23" ht="30">
       <c r="A172" s="4" t="s">
         <v>35</v>
       </c>
@@ -24954,7 +25189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:23" ht="30" hidden="1">
+    <row r="173" spans="1:23" ht="30">
       <c r="A173" s="4" t="s">
         <v>35</v>
       </c>
@@ -25025,7 +25260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="30" hidden="1">
+    <row r="174" spans="1:23" ht="30">
       <c r="A174" s="4" t="s">
         <v>35</v>
       </c>
@@ -25096,7 +25331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="30" hidden="1">
+    <row r="175" spans="1:23" ht="30">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -25167,7 +25402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="30" hidden="1">
+    <row r="176" spans="1:23" ht="30">
       <c r="A176" s="4" t="s">
         <v>35</v>
       </c>
@@ -25238,7 +25473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="30" hidden="1">
+    <row r="177" spans="1:23" ht="30">
       <c r="A177" s="4" t="s">
         <v>35</v>
       </c>
@@ -25309,7 +25544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="30" hidden="1">
+    <row r="178" spans="1:23" ht="30">
       <c r="A178" s="4" t="s">
         <v>35</v>
       </c>
@@ -25380,7 +25615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="30" hidden="1">
+    <row r="179" spans="1:23" ht="30">
       <c r="A179" s="4" t="s">
         <v>35</v>
       </c>
@@ -25451,7 +25686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="30" hidden="1">
+    <row r="180" spans="1:23" ht="30">
       <c r="A180" s="4" t="s">
         <v>35</v>
       </c>
@@ -25522,7 +25757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="30" hidden="1">
+    <row r="181" spans="1:23" ht="30">
       <c r="A181" s="3" t="s">
         <v>94</v>
       </c>
@@ -25589,7 +25824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="30" hidden="1">
+    <row r="182" spans="1:23" ht="30">
       <c r="A182" s="3" t="s">
         <v>94</v>
       </c>
@@ -25658,7 +25893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:23" ht="30" hidden="1">
+    <row r="183" spans="1:23" ht="30">
       <c r="A183" s="3" t="s">
         <v>94</v>
       </c>
@@ -25727,7 +25962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:23" ht="30" hidden="1">
+    <row r="184" spans="1:23" ht="30">
       <c r="A184" s="3" t="s">
         <v>94</v>
       </c>
@@ -25796,7 +26031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="30" hidden="1">
+    <row r="185" spans="1:23" ht="30">
       <c r="A185" s="3" t="s">
         <v>94</v>
       </c>
@@ -25865,7 +26100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="30" hidden="1">
+    <row r="186" spans="1:23" ht="30">
       <c r="A186" s="3" t="s">
         <v>94</v>
       </c>
@@ -25934,7 +26169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:23" hidden="1">
+    <row r="187" spans="1:23">
       <c r="A187" s="3" t="s">
         <v>42</v>
       </c>
@@ -26001,7 +26236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:23" hidden="1">
+    <row r="188" spans="1:23">
       <c r="A188" s="3" t="s">
         <v>42</v>
       </c>
@@ -26070,7 +26305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:23" hidden="1">
+    <row r="189" spans="1:23">
       <c r="A189" s="3" t="s">
         <v>42</v>
       </c>
@@ -26139,7 +26374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="30" hidden="1">
+    <row r="190" spans="1:23" ht="30">
       <c r="A190" s="3" t="s">
         <v>42</v>
       </c>
@@ -26208,7 +26443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:23" hidden="1">
+    <row r="191" spans="1:23">
       <c r="A191" s="3" t="s">
         <v>42</v>
       </c>
@@ -26277,7 +26512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:23" ht="30" hidden="1">
+    <row r="192" spans="1:23" ht="30">
       <c r="A192" s="3" t="s">
         <v>42</v>
       </c>
@@ -26346,7 +26581,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:23" hidden="1">
+    <row r="193" spans="1:23">
       <c r="A193" s="3" t="s">
         <v>129</v>
       </c>
@@ -26413,7 +26648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:23" hidden="1">
+    <row r="194" spans="1:23">
       <c r="A194" s="3" t="s">
         <v>129</v>
       </c>
@@ -26482,7 +26717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:23" hidden="1">
+    <row r="195" spans="1:23">
       <c r="A195" s="3" t="s">
         <v>129</v>
       </c>
@@ -26551,7 +26786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:23" hidden="1">
+    <row r="196" spans="1:23">
       <c r="A196" s="3" t="s">
         <v>129</v>
       </c>
@@ -26620,7 +26855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:23" hidden="1">
+    <row r="197" spans="1:23">
       <c r="A197" s="3" t="s">
         <v>129</v>
       </c>
@@ -26689,7 +26924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="30" hidden="1">
+    <row r="198" spans="1:23" ht="30">
       <c r="A198" s="3" t="s">
         <v>129</v>
       </c>
@@ -26758,7 +26993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="30" hidden="1">
+    <row r="199" spans="1:23" ht="30">
       <c r="A199" s="3" t="s">
         <v>129</v>
       </c>
@@ -26827,7 +27062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:23" hidden="1">
+    <row r="200" spans="1:23">
       <c r="A200" s="3" t="s">
         <v>126</v>
       </c>
@@ -26894,7 +27129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:23" hidden="1">
+    <row r="201" spans="1:23">
       <c r="A201" s="3" t="s">
         <v>126</v>
       </c>
@@ -26963,7 +27198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:23" hidden="1">
+    <row r="202" spans="1:23">
       <c r="A202" s="3" t="s">
         <v>126</v>
       </c>
@@ -27032,7 +27267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:23" ht="30" hidden="1">
+    <row r="203" spans="1:23" ht="30">
       <c r="A203" s="3" t="s">
         <v>126</v>
       </c>
@@ -27101,7 +27336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:23" ht="30" hidden="1">
+    <row r="204" spans="1:23" ht="30">
       <c r="A204" s="3" t="s">
         <v>126</v>
       </c>
@@ -27170,7 +27405,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:23" hidden="1">
+    <row r="205" spans="1:23">
       <c r="A205" s="3" t="s">
         <v>126</v>
       </c>
@@ -27239,7 +27474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="30" hidden="1">
+    <row r="206" spans="1:23" ht="30">
       <c r="A206" s="3" t="s">
         <v>126</v>
       </c>
@@ -27308,7 +27543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="30" hidden="1">
+    <row r="207" spans="1:23" ht="30">
       <c r="A207" s="3" t="s">
         <v>126</v>
       </c>
@@ -27377,7 +27612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="30" hidden="1">
+    <row r="208" spans="1:23" ht="30">
       <c r="A208" s="3" t="s">
         <v>313</v>
       </c>
@@ -27444,7 +27679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:23" ht="30" hidden="1">
+    <row r="209" spans="1:23" ht="30">
       <c r="A209" s="3" t="s">
         <v>313</v>
       </c>
@@ -27513,7 +27748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:23" ht="30" hidden="1">
+    <row r="210" spans="1:23" ht="30">
       <c r="A210" s="3" t="s">
         <v>313</v>
       </c>
@@ -27582,7 +27817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:23" ht="30" hidden="1">
+    <row r="211" spans="1:23" ht="30">
       <c r="A211" s="3" t="s">
         <v>313</v>
       </c>
@@ -27651,7 +27886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:23" ht="30" hidden="1">
+    <row r="212" spans="1:23" ht="30">
       <c r="A212" s="3" t="s">
         <v>313</v>
       </c>
@@ -27720,7 +27955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:23" ht="45" hidden="1">
+    <row r="213" spans="1:23" ht="45">
       <c r="A213" s="3" t="s">
         <v>313</v>
       </c>
@@ -27789,7 +28024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="30" hidden="1">
+    <row r="214" spans="1:23" ht="30">
       <c r="A214" s="3" t="s">
         <v>445</v>
       </c>
@@ -27856,7 +28091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="30" hidden="1">
+    <row r="215" spans="1:23" ht="30">
       <c r="A215" s="3" t="s">
         <v>445</v>
       </c>
@@ -27925,7 +28160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:23" ht="30" hidden="1">
+    <row r="216" spans="1:23" ht="30">
       <c r="A216" s="3" t="s">
         <v>445</v>
       </c>
@@ -27994,7 +28229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="30" hidden="1">
+    <row r="217" spans="1:23" ht="30">
       <c r="A217" s="3" t="s">
         <v>445</v>
       </c>
@@ -28063,7 +28298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:23" ht="30" hidden="1">
+    <row r="218" spans="1:23" ht="30">
       <c r="A218" s="3" t="s">
         <v>445</v>
       </c>
@@ -28132,7 +28367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="30" hidden="1">
+    <row r="219" spans="1:23" ht="30">
       <c r="A219" s="3" t="s">
         <v>445</v>
       </c>
@@ -28201,7 +28436,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="30" hidden="1">
+    <row r="220" spans="1:23" ht="30">
       <c r="A220" s="3" t="s">
         <v>451</v>
       </c>
@@ -28268,7 +28503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:23" hidden="1">
+    <row r="221" spans="1:23">
       <c r="A221" s="3" t="s">
         <v>451</v>
       </c>
@@ -28337,7 +28572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:23" hidden="1">
+    <row r="222" spans="1:23">
       <c r="A222" s="3" t="s">
         <v>451</v>
       </c>
@@ -28406,7 +28641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="30" hidden="1">
+    <row r="223" spans="1:23" ht="30">
       <c r="A223" s="3" t="s">
         <v>451</v>
       </c>
@@ -28475,7 +28710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:23" hidden="1">
+    <row r="224" spans="1:23">
       <c r="A224" s="3" t="s">
         <v>451</v>
       </c>
@@ -28544,7 +28779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="30" hidden="1">
+    <row r="225" spans="1:23" ht="30">
       <c r="A225" s="3" t="s">
         <v>451</v>
       </c>
@@ -28613,7 +28848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="30" hidden="1">
+    <row r="226" spans="1:23" ht="30">
       <c r="A226" s="3" t="s">
         <v>512</v>
       </c>
@@ -28680,7 +28915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="30" hidden="1">
+    <row r="227" spans="1:23" ht="30">
       <c r="A227" s="3" t="s">
         <v>512</v>
       </c>
@@ -28749,7 +28984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="30" hidden="1">
+    <row r="228" spans="1:23" ht="30">
       <c r="A228" s="3" t="s">
         <v>512</v>
       </c>
@@ -28818,7 +29053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="30" hidden="1">
+    <row r="229" spans="1:23" ht="30">
       <c r="A229" s="3" t="s">
         <v>512</v>
       </c>
@@ -28887,7 +29122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="30" hidden="1">
+    <row r="230" spans="1:23" ht="30">
       <c r="A230" s="3" t="s">
         <v>512</v>
       </c>
@@ -28956,7 +29191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="30" hidden="1">
+    <row r="231" spans="1:23" ht="30">
       <c r="A231" s="3" t="s">
         <v>512</v>
       </c>
@@ -29025,7 +29260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="30" hidden="1">
+    <row r="232" spans="1:23" ht="30">
       <c r="A232" s="3" t="s">
         <v>518</v>
       </c>
@@ -29092,7 +29327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:23" hidden="1">
+    <row r="233" spans="1:23">
       <c r="A233" s="3" t="s">
         <v>518</v>
       </c>
@@ -29161,7 +29396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:23" hidden="1">
+    <row r="234" spans="1:23">
       <c r="A234" s="3" t="s">
         <v>518</v>
       </c>
@@ -29230,7 +29465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="30" hidden="1">
+    <row r="235" spans="1:23" ht="30">
       <c r="A235" s="3" t="s">
         <v>518</v>
       </c>
@@ -29299,7 +29534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:23" hidden="1">
+    <row r="236" spans="1:23">
       <c r="A236" s="3" t="s">
         <v>518</v>
       </c>
@@ -29368,7 +29603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:23" ht="30" hidden="1">
+    <row r="237" spans="1:23" ht="30">
       <c r="A237" s="3" t="s">
         <v>518</v>
       </c>
@@ -29437,7 +29672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="30" hidden="1">
+    <row r="238" spans="1:23" ht="30">
       <c r="A238" s="3" t="s">
         <v>757</v>
       </c>
@@ -29504,7 +29739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:23" hidden="1">
+    <row r="239" spans="1:23">
       <c r="A239" s="3" t="s">
         <v>757</v>
       </c>
@@ -29573,7 +29808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:23" hidden="1">
+    <row r="240" spans="1:23">
       <c r="A240" s="3" t="s">
         <v>757</v>
       </c>
@@ -29642,7 +29877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:23" hidden="1">
+    <row r="241" spans="1:23">
       <c r="A241" s="3" t="s">
         <v>757</v>
       </c>
@@ -29711,7 +29946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:23" hidden="1">
+    <row r="242" spans="1:23">
       <c r="A242" s="3" t="s">
         <v>757</v>
       </c>
@@ -29780,7 +30015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="30" hidden="1">
+    <row r="243" spans="1:23" ht="30">
       <c r="A243" s="3" t="s">
         <v>757</v>
       </c>
@@ -29849,7 +30084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="30" hidden="1">
+    <row r="244" spans="1:23" ht="30">
       <c r="A244" s="3" t="s">
         <v>1517</v>
       </c>
@@ -29916,7 +30151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="30" hidden="1">
+    <row r="245" spans="1:23" ht="30">
       <c r="A245" s="3" t="s">
         <v>1517</v>
       </c>
@@ -29983,7 +30218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="30" hidden="1">
+    <row r="246" spans="1:23" ht="30">
       <c r="A246" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30052,7 +30287,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="247" spans="1:23" ht="30" hidden="1">
+    <row r="247" spans="1:23" ht="30">
       <c r="A247" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30121,7 +30356,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="248" spans="1:23" hidden="1">
+    <row r="248" spans="1:23">
       <c r="A248" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30190,7 +30425,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="30" hidden="1">
+    <row r="249" spans="1:23" ht="30">
       <c r="A249" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30259,7 +30494,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="250" spans="1:23" hidden="1">
+    <row r="250" spans="1:23">
       <c r="A250" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30328,7 +30563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:23" hidden="1">
+    <row r="251" spans="1:23">
       <c r="A251" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30397,7 +30632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:23" hidden="1">
+    <row r="252" spans="1:23">
       <c r="A252" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30466,7 +30701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:23" hidden="1">
+    <row r="253" spans="1:23">
       <c r="A253" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30535,7 +30770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:23" hidden="1">
+    <row r="254" spans="1:23">
       <c r="A254" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30604,7 +30839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:23" hidden="1">
+    <row r="255" spans="1:23">
       <c r="A255" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30673,7 +30908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="30" hidden="1">
+    <row r="256" spans="1:23" ht="30">
       <c r="A256" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30742,7 +30977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:23" ht="30" hidden="1">
+    <row r="257" spans="1:23" ht="30">
       <c r="A257" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30811,7 +31046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:23" hidden="1">
+    <row r="258" spans="1:23">
       <c r="A258" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30878,7 +31113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:23" hidden="1">
+    <row r="259" spans="1:23">
       <c r="A259" s="3" t="s">
         <v>1517</v>
       </c>
@@ -30945,7 +31180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:23" hidden="1">
+    <row r="260" spans="1:23">
       <c r="A260" s="3" t="s">
         <v>1517</v>
       </c>
@@ -31012,7 +31247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:23" hidden="1">
+    <row r="261" spans="1:23">
       <c r="A261" s="3" t="s">
         <v>1517</v>
       </c>
@@ -31081,7 +31316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:23" hidden="1">
+    <row r="262" spans="1:23">
       <c r="A262" s="3" t="s">
         <v>1517</v>
       </c>
@@ -31150,7 +31385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30" hidden="1">
+    <row r="263" spans="1:23" ht="30">
       <c r="A263" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31217,7 +31452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="30" hidden="1">
+    <row r="264" spans="1:23" ht="30">
       <c r="A264" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31284,7 +31519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30" hidden="1">
+    <row r="265" spans="1:23" ht="30">
       <c r="A265" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31355,7 +31590,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:23" hidden="1">
+    <row r="266" spans="1:23">
       <c r="A266" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31422,7 +31657,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="30" hidden="1">
+    <row r="267" spans="1:23" ht="30">
       <c r="A267" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31491,7 +31726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23" hidden="1">
+    <row r="268" spans="1:23">
       <c r="A268" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31560,7 +31795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23" hidden="1">
+    <row r="269" spans="1:23">
       <c r="A269" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31629,7 +31864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="30" hidden="1">
+    <row r="270" spans="1:23" ht="30">
       <c r="A270" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31696,7 +31931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="30" hidden="1">
+    <row r="271" spans="1:23" ht="30">
       <c r="A271" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31763,7 +31998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23" hidden="1">
+    <row r="272" spans="1:23">
       <c r="A272" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31828,7 +32063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23" hidden="1">
+    <row r="273" spans="1:23">
       <c r="A273" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31893,7 +32128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23" hidden="1">
+    <row r="274" spans="1:23">
       <c r="A274" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31958,7 +32193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23" hidden="1">
+    <row r="275" spans="1:23">
       <c r="A275" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32027,7 +32262,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23" hidden="1">
+    <row r="276" spans="1:23">
       <c r="A276" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32096,7 +32331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:23" ht="30" hidden="1">
+    <row r="277" spans="1:23" ht="30">
       <c r="A277" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32163,7 +32398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="30" hidden="1">
+    <row r="278" spans="1:23" ht="30">
       <c r="A278" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32230,7 +32465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="45" hidden="1">
+    <row r="279" spans="1:23" ht="45">
       <c r="A279" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32301,7 +32536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="30" hidden="1">
+    <row r="280" spans="1:23" ht="30">
       <c r="A280" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32370,7 +32605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="30" hidden="1">
+    <row r="281" spans="1:23" ht="30">
       <c r="A281" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32439,7 +32674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="30" hidden="1">
+    <row r="282" spans="1:23" ht="30">
       <c r="A282" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32508,7 +32743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="30" hidden="1">
+    <row r="283" spans="1:23" ht="30">
       <c r="A283" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32577,7 +32812,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:23" ht="30" hidden="1">
+    <row r="284" spans="1:23" ht="30">
       <c r="A284" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32646,7 +32881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:23" ht="30" hidden="1">
+    <row r="285" spans="1:23" ht="30">
       <c r="A285" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32713,7 +32948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="30" hidden="1">
+    <row r="286" spans="1:23" ht="30">
       <c r="A286" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32780,7 +33015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="30" hidden="1">
+    <row r="287" spans="1:23" ht="30">
       <c r="A287" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32845,7 +33080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="30" hidden="1">
+    <row r="288" spans="1:23" ht="30">
       <c r="A288" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32910,7 +33145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="30" hidden="1">
+    <row r="289" spans="1:23" ht="30">
       <c r="A289" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32975,7 +33210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="30" hidden="1">
+    <row r="290" spans="1:23" ht="30">
       <c r="A290" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33044,7 +33279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="30" hidden="1">
+    <row r="291" spans="1:23" ht="30">
       <c r="A291" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33113,7 +33348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:23" ht="30" hidden="1">
+    <row r="292" spans="1:23" ht="30">
       <c r="A292" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33180,7 +33415,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:23" ht="30" hidden="1">
+    <row r="293" spans="1:23" ht="30">
       <c r="A293" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33247,7 +33482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:23" ht="45" hidden="1">
+    <row r="294" spans="1:23" ht="45">
       <c r="A294" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33316,7 +33551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:23" hidden="1">
+    <row r="295" spans="1:23">
       <c r="A295" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33383,7 +33618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23" hidden="1">
+    <row r="296" spans="1:23">
       <c r="A296" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33450,7 +33685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="30" hidden="1">
+    <row r="297" spans="1:23" ht="30">
       <c r="A297" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33517,7 +33752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:23" hidden="1">
+    <row r="298" spans="1:23">
       <c r="A298" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33584,7 +33819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="45" hidden="1">
+    <row r="299" spans="1:23" ht="45">
       <c r="A299" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33653,7 +33888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="30" hidden="1">
+    <row r="300" spans="1:23" ht="30">
       <c r="A300" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33718,7 +33953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="30" hidden="1">
+    <row r="301" spans="1:23" ht="30">
       <c r="A301" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33787,7 +34022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="30" hidden="1">
+    <row r="302" spans="1:23" ht="30">
       <c r="A302" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33854,7 +34089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="30" hidden="1">
+    <row r="303" spans="1:23" ht="30">
       <c r="A303" s="3" t="s">
         <v>1689</v>
       </c>
@@ -33921,7 +34156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="30" hidden="1">
+    <row r="304" spans="1:23" ht="30">
       <c r="A304" s="3" t="s">
         <v>1689</v>
       </c>
@@ -33988,7 +34223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="30" hidden="1">
+    <row r="305" spans="1:23" ht="30">
       <c r="A305" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34057,7 +34292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30" hidden="1">
+    <row r="306" spans="1:23" ht="30">
       <c r="A306" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34124,7 +34359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="30" hidden="1">
+    <row r="307" spans="1:23" ht="30">
       <c r="A307" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34193,7 +34428,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="30" hidden="1">
+    <row r="308" spans="1:23" ht="30">
       <c r="A308" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34262,7 +34497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="30" hidden="1">
+    <row r="309" spans="1:23" ht="30">
       <c r="A309" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34329,7 +34564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="30" hidden="1">
+    <row r="310" spans="1:23" ht="30">
       <c r="A310" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34396,7 +34631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="30" hidden="1">
+    <row r="311" spans="1:23" ht="30">
       <c r="A311" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34461,7 +34696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="30" hidden="1">
+    <row r="312" spans="1:23" ht="30">
       <c r="A312" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34528,7 +34763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="45" hidden="1">
+    <row r="313" spans="1:23" ht="45">
       <c r="A313" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34597,7 +34832,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="30" hidden="1">
+    <row r="314" spans="1:23" ht="30">
       <c r="A314" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34666,7 +34901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:23" ht="30" hidden="1">
+    <row r="315" spans="1:23" ht="30">
       <c r="A315" s="3" t="s">
         <v>1704</v>
       </c>
@@ -34733,7 +34968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:23" ht="30" hidden="1">
+    <row r="316" spans="1:23" ht="30">
       <c r="A316" s="3" t="s">
         <v>1704</v>
       </c>
@@ -34802,7 +35037,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:23" hidden="1">
+    <row r="317" spans="1:23">
       <c r="A317" s="3" t="s">
         <v>1704</v>
       </c>
@@ -34871,7 +35106,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="30" hidden="1">
+    <row r="318" spans="1:23" ht="30">
       <c r="A318" s="3" t="s">
         <v>1704</v>
       </c>
@@ -34940,7 +35175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:23" hidden="1">
+    <row r="319" spans="1:23">
       <c r="A319" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35009,7 +35244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="30" hidden="1">
+    <row r="320" spans="1:23" ht="30">
       <c r="A320" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35078,7 +35313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="30" hidden="1">
+    <row r="321" spans="1:23" ht="30">
       <c r="A321" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35145,7 +35380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:23" hidden="1">
+    <row r="322" spans="1:23">
       <c r="A322" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35210,7 +35445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="30" hidden="1">
+    <row r="323" spans="1:23" ht="30">
       <c r="A323" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35279,7 +35514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:23" hidden="1">
+    <row r="324" spans="1:23">
       <c r="A324" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35348,7 +35583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="30" hidden="1">
+    <row r="325" spans="1:23" ht="30">
       <c r="A325" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35415,7 +35650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="30" hidden="1">
+    <row r="326" spans="1:23" ht="30">
       <c r="A326" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35482,7 +35717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="30" hidden="1">
+    <row r="327" spans="1:23" ht="30">
       <c r="A327" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35549,7 +35784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="30" hidden="1">
+    <row r="328" spans="1:23" ht="30">
       <c r="A328" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35618,7 +35853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="45" hidden="1">
+    <row r="329" spans="1:23" ht="45">
       <c r="A329" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35687,7 +35922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="30" hidden="1">
+    <row r="330" spans="1:23" ht="30">
       <c r="A330" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35754,7 +35989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="30" hidden="1">
+    <row r="331" spans="1:23" ht="30">
       <c r="A331" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35821,7 +36056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="30" hidden="1">
+    <row r="332" spans="1:23" ht="30">
       <c r="A332" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35890,7 +36125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="30" hidden="1">
+    <row r="333" spans="1:23" ht="30">
       <c r="A333" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35957,7 +36192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="30" hidden="1">
+    <row r="334" spans="1:23" ht="30">
       <c r="A334" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36024,7 +36259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="30" hidden="1">
+    <row r="335" spans="1:23" ht="30">
       <c r="A335" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36089,7 +36324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="30" hidden="1">
+    <row r="336" spans="1:23" ht="30">
       <c r="A336" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36156,7 +36391,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="45" hidden="1">
+    <row r="337" spans="1:23" ht="45">
       <c r="A337" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36225,7 +36460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="30" hidden="1">
+    <row r="338" spans="1:23" ht="30">
       <c r="A338" s="3" t="s">
         <v>1806</v>
       </c>
@@ -37274,7 +37509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="30" hidden="1">
+    <row r="353" spans="1:23" ht="30">
       <c r="A353" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37343,7 +37578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="30" hidden="1">
+    <row r="354" spans="1:23" ht="30">
       <c r="A354" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37412,7 +37647,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:23" hidden="1">
+    <row r="355" spans="1:23">
       <c r="A355" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37481,7 +37716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="45" hidden="1">
+    <row r="356" spans="1:23" ht="45">
       <c r="A356" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37550,7 +37785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="30" hidden="1">
+    <row r="357" spans="1:23" ht="30">
       <c r="A357" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37621,7 +37856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="30" hidden="1">
+    <row r="358" spans="1:23" ht="30">
       <c r="A358" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37692,7 +37927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="30" hidden="1">
+    <row r="359" spans="1:23" ht="30">
       <c r="A359" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37763,7 +37998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:23" ht="30" hidden="1">
+    <row r="360" spans="1:23" ht="30">
       <c r="A360" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37834,7 +38069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:23" ht="45" hidden="1">
+    <row r="361" spans="1:23" ht="45">
       <c r="A361" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37905,7 +38140,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:23" ht="30" hidden="1">
+    <row r="362" spans="1:23" ht="30">
       <c r="A362" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37976,7 +38211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="30" hidden="1">
+    <row r="363" spans="1:23" ht="30">
       <c r="A363" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38047,7 +38282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="30" hidden="1">
+    <row r="364" spans="1:23" ht="30">
       <c r="A364" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38118,7 +38353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="30" hidden="1">
+    <row r="365" spans="1:23" ht="30">
       <c r="A365" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38189,7 +38424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="30" hidden="1">
+    <row r="366" spans="1:23" ht="30">
       <c r="A366" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38260,7 +38495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="30" hidden="1">
+    <row r="367" spans="1:23" ht="30">
       <c r="A367" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38331,7 +38566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="30" hidden="1">
+    <row r="368" spans="1:23" ht="30">
       <c r="A368" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38402,7 +38637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="30" hidden="1">
+    <row r="369" spans="1:23" ht="30">
       <c r="A369" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38473,7 +38708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:23" ht="30" hidden="1">
+    <row r="370" spans="1:23" ht="30">
       <c r="A370" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38544,7 +38779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="30" hidden="1">
+    <row r="371" spans="1:23" ht="30">
       <c r="A371" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38615,7 +38850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="30" hidden="1">
+    <row r="372" spans="1:23" ht="30">
       <c r="A372" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38686,7 +38921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="45" hidden="1">
+    <row r="373" spans="1:23" ht="45">
       <c r="A373" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38757,7 +38992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:23" ht="30" hidden="1">
+    <row r="374" spans="1:23" ht="30">
       <c r="A374" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38828,7 +39063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="30" hidden="1">
+    <row r="375" spans="1:23" ht="30">
       <c r="A375" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38899,7 +39134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="30" hidden="1">
+    <row r="376" spans="1:23" ht="30">
       <c r="A376" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38970,7 +39205,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:23" ht="30" hidden="1">
+    <row r="377" spans="1:23" ht="30">
       <c r="A377" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39041,7 +39276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:23" ht="30" hidden="1">
+    <row r="378" spans="1:23" ht="30">
       <c r="A378" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39112,7 +39347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:23" ht="30" hidden="1">
+    <row r="379" spans="1:23" ht="30">
       <c r="A379" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39183,7 +39418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:23" hidden="1">
+    <row r="380" spans="1:23">
       <c r="A380" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39254,7 +39489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="30" hidden="1">
+    <row r="381" spans="1:23" ht="30">
       <c r="A381" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39325,7 +39560,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:23" ht="30" hidden="1">
+    <row r="382" spans="1:23" ht="30">
       <c r="A382" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39396,7 +39631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="45" hidden="1">
+    <row r="383" spans="1:23" ht="45">
       <c r="A383" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39464,7 +39699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:23" ht="30" hidden="1">
+    <row r="384" spans="1:23" ht="30">
       <c r="A384" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39532,7 +39767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:23" ht="45" hidden="1">
+    <row r="385" spans="1:23" ht="45">
       <c r="A385" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39603,7 +39838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="30" hidden="1">
+    <row r="386" spans="1:23" ht="30">
       <c r="A386" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39674,7 +39909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:23" ht="30" hidden="1">
+    <row r="387" spans="1:23" ht="30">
       <c r="A387" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39742,7 +39977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:23" ht="30" hidden="1">
+    <row r="388" spans="1:23" ht="30">
       <c r="A388" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39810,7 +40045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="30" hidden="1">
+    <row r="389" spans="1:23" ht="30">
       <c r="A389" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39878,7 +40113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:23" ht="30" hidden="1">
+    <row r="390" spans="1:23" ht="30">
       <c r="A390" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39949,7 +40184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:23" ht="30" hidden="1">
+    <row r="391" spans="1:23" ht="30">
       <c r="A391" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40020,7 +40255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:23" ht="30" hidden="1">
+    <row r="392" spans="1:23" ht="30">
       <c r="A392" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40091,7 +40326,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="30" hidden="1">
+    <row r="393" spans="1:23" ht="30">
       <c r="A393" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40162,7 +40397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:23" ht="30" hidden="1">
+    <row r="394" spans="1:23" ht="30">
       <c r="A394" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40233,7 +40468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:23" ht="30" hidden="1">
+    <row r="395" spans="1:23" ht="30">
       <c r="A395" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40304,7 +40539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:23" ht="30" hidden="1">
+    <row r="396" spans="1:23" ht="30">
       <c r="A396" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40375,14 +40610,1002 @@
         <v>21</v>
       </c>
     </row>
+    <row r="397" spans="1:23" ht="45">
+      <c r="A397" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B397" s="5">
+        <v>1</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D397" s="3" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E397" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F397" s="5">
+        <v>36</v>
+      </c>
+      <c r="G397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H397" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J397" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K397" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M397" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N397" s="3" t="s">
+        <v>2406</v>
+      </c>
+      <c r="O397" s="3" t="s">
+        <v>2407</v>
+      </c>
+      <c r="P397" s="3" t="s">
+        <v>2408</v>
+      </c>
+      <c r="Q397" s="3" t="s">
+        <v>2409</v>
+      </c>
+      <c r="R397" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T397" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="U397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V397" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W397" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="398" spans="1:23" ht="30">
+      <c r="A398" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B398" s="5">
+        <v>2</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D398" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E398" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F398" s="5">
+        <v>36</v>
+      </c>
+      <c r="G398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K398" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N398" s="3" t="s">
+        <v>2410</v>
+      </c>
+      <c r="O398" s="3" t="s">
+        <v>2411</v>
+      </c>
+      <c r="P398" s="3" t="s">
+        <v>2412</v>
+      </c>
+      <c r="Q398" s="3" t="s">
+        <v>2413</v>
+      </c>
+      <c r="R398" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W398" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="399" spans="1:23" ht="45">
+      <c r="A399" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B399" s="5">
+        <v>3</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E399" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F399" s="5">
+        <v>36</v>
+      </c>
+      <c r="G399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H399" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I399" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K399" s="3" t="s">
+        <v>1914</v>
+      </c>
+      <c r="L399" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M399" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N399" s="3" t="s">
+        <v>2414</v>
+      </c>
+      <c r="O399" s="3" t="s">
+        <v>2415</v>
+      </c>
+      <c r="P399" s="3" t="s">
+        <v>2416</v>
+      </c>
+      <c r="Q399" s="3" t="s">
+        <v>2417</v>
+      </c>
+      <c r="R399" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W399" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="400" spans="1:23" ht="30">
+      <c r="A400" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B400" s="5">
+        <v>4</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D400" s="3" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E400" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F400" s="5">
+        <v>150</v>
+      </c>
+      <c r="G400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H400" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I400" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J400" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K400" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L400" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M400" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N400" s="3" t="s">
+        <v>2419</v>
+      </c>
+      <c r="O400" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="P400" s="3" t="s">
+        <v>2421</v>
+      </c>
+      <c r="Q400" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="R400" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W400" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="401" spans="1:23" ht="45">
+      <c r="A401" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B401" s="5">
+        <v>5</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D401" s="3" t="s">
+        <v>2424</v>
+      </c>
+      <c r="E401" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F401" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G401" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K401" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N401" s="3" t="s">
+        <v>2425</v>
+      </c>
+      <c r="O401" s="3" t="s">
+        <v>2426</v>
+      </c>
+      <c r="P401" s="3" t="s">
+        <v>2461</v>
+      </c>
+      <c r="Q401" s="3" t="s">
+        <v>2427</v>
+      </c>
+      <c r="R401" s="3" t="s">
+        <v>2428</v>
+      </c>
+      <c r="S401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="U401" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="V401" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W401" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="402" spans="1:23" ht="45">
+      <c r="A402" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B402" s="5">
+        <v>6</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D402" s="3" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E402" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F402" s="5">
+        <v>36</v>
+      </c>
+      <c r="G402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H402" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I402" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K402" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L402" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M402" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N402" s="3" t="s">
+        <v>2431</v>
+      </c>
+      <c r="O402" s="3" t="s">
+        <v>2432</v>
+      </c>
+      <c r="P402" s="3" t="s">
+        <v>2433</v>
+      </c>
+      <c r="Q402" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="R402" s="3" t="s">
+        <v>2462</v>
+      </c>
+      <c r="S402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W402" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="403" spans="1:23" ht="45">
+      <c r="A403" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B403" s="5">
+        <v>7</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>2435</v>
+      </c>
+      <c r="D403" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E403" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F403" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H403" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K403" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M403" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N403" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="O403" s="3" t="s">
+        <v>2438</v>
+      </c>
+      <c r="P403" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="Q403" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="R403" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T403" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U403" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W403" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="404" spans="1:23" ht="30">
+      <c r="A404" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B404" s="5">
+        <v>8</v>
+      </c>
+      <c r="C404" s="3" t="s">
+        <v>2441</v>
+      </c>
+      <c r="D404" s="3" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E404" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F404" s="5">
+        <v>36</v>
+      </c>
+      <c r="G404" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I404" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K404" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L404" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M404" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N404" s="3" t="s">
+        <v>2443</v>
+      </c>
+      <c r="O404" s="3" t="s">
+        <v>2444</v>
+      </c>
+      <c r="P404" s="3" t="s">
+        <v>2445</v>
+      </c>
+      <c r="Q404" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="R404" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V404" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W404" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="405" spans="1:23" ht="30">
+      <c r="A405" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B405" s="5">
+        <v>9</v>
+      </c>
+      <c r="C405" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D405" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E405" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F405" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G405" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H405" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I405" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J405" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K405" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L405" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M405" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N405" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="O405" s="3" t="s">
+        <v>2447</v>
+      </c>
+      <c r="P405" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="Q405" s="3" t="s">
+        <v>2449</v>
+      </c>
+      <c r="R405" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S405" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T405" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U405" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V405" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W405" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="406" spans="1:23" ht="30">
+      <c r="A406" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B406" s="5">
+        <v>10</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D406" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E406" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F406" s="5">
+        <v>36</v>
+      </c>
+      <c r="G406" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J406" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K406" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M406" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N406" s="3" t="s">
+        <v>1974</v>
+      </c>
+      <c r="O406" s="3" t="s">
+        <v>2450</v>
+      </c>
+      <c r="P406" s="3" t="s">
+        <v>2451</v>
+      </c>
+      <c r="Q406" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="R406" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S406" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T406" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U406" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W406" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="407" spans="1:23" ht="30">
+      <c r="A407" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B407" s="5">
+        <v>11</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D407" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E407" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F407" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G407" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H407" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I407" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J407" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K407" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L407" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M407" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N407" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="O407" s="3" t="s">
+        <v>2452</v>
+      </c>
+      <c r="P407" s="3" t="s">
+        <v>2453</v>
+      </c>
+      <c r="Q407" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="R407" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S407" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T407" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U407" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V407" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W407" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="408" spans="1:23" ht="30">
+      <c r="A408" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B408" s="5">
+        <v>12</v>
+      </c>
+      <c r="C408" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D408" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E408" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F408" s="5">
+        <v>36</v>
+      </c>
+      <c r="G408" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H408" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I408" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J408" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K408" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L408" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M408" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N408" s="3" t="s">
+        <v>1979</v>
+      </c>
+      <c r="O408" s="3" t="s">
+        <v>2455</v>
+      </c>
+      <c r="P408" s="3" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q408" s="3" t="s">
+        <v>2446</v>
+      </c>
+      <c r="R408" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S408" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T408" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U408" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V408" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W408" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="409" spans="1:23" ht="30">
+      <c r="A409" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B409" s="5">
+        <v>13</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D409" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E409" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F409" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G409" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K409" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M409" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N409" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="O409" s="3" t="s">
+        <v>2457</v>
+      </c>
+      <c r="P409" s="3" t="s">
+        <v>2458</v>
+      </c>
+      <c r="Q409" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R409" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T409" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="V409" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W409" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="410" spans="1:23" ht="30">
+      <c r="A410" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B410" s="5">
+        <v>14</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D410" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E410" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F410" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G410" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K410" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M410" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N410" s="3" t="s">
+        <v>1985</v>
+      </c>
+      <c r="O410" s="3" t="s">
+        <v>2459</v>
+      </c>
+      <c r="P410" s="3" t="s">
+        <v>2460</v>
+      </c>
+      <c r="Q410" s="3">
+        <v>1</v>
+      </c>
+      <c r="R410" s="3">
+        <v>1</v>
+      </c>
+      <c r="S410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="U410" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W410" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Template"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}"/>
   <hyperlinks>
     <hyperlink ref="Q9" r:id="rId1" display="mailto:admin@memgine.com" xr:uid="{93170BB8-77D4-4002-829B-D89928109808}"/>
     <hyperlink ref="Q11" r:id="rId2" display="https://memgine.com/" xr:uid="{F8EB4105-6CCB-4B06-B657-948DB365F556}"/>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F57A97-FD42-4D5F-B918-433EC83B7732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331967AC-A866-4C7C-8443-77689366D5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -9376,7 +9376,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="45">
+    <row r="27" spans="1:17" ht="30">
       <c r="A27" s="4" t="s">
         <v>1576</v>
       </c>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331967AC-A866-4C7C-8443-77689366D5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8006DC-09FC-43CC-91DF-5BF59D768099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
     <sheet name="Atributes" sheetId="2" r:id="rId2"/>
-    <sheet name="Template Default Content" sheetId="10" r:id="rId3"/>
-    <sheet name="Organization Type Template" sheetId="11" r:id="rId4"/>
-    <sheet name="Reference Data" sheetId="3" r:id="rId5"/>
-    <sheet name="Country-State-City Ref data" sheetId="8" r:id="rId6"/>
-    <sheet name="Template Ref Data" sheetId="9" r:id="rId7"/>
-    <sheet name="Status Ref Data" sheetId="6" r:id="rId8"/>
-    <sheet name="Entity Ref Data" sheetId="7" r:id="rId9"/>
-    <sheet name="Relationships" sheetId="4" r:id="rId10"/>
-    <sheet name="Validation Rules" sheetId="5" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId3"/>
+    <sheet name="Template Default Content" sheetId="10" r:id="rId4"/>
+    <sheet name="Organization Type Template" sheetId="11" r:id="rId5"/>
+    <sheet name="Reference Data" sheetId="3" r:id="rId6"/>
+    <sheet name="Country-State-City Ref data" sheetId="8" r:id="rId7"/>
+    <sheet name="Template Ref Data" sheetId="9" r:id="rId8"/>
+    <sheet name="Status Ref Data" sheetId="6" r:id="rId9"/>
+    <sheet name="Entity Ref Data" sheetId="7" r:id="rId10"/>
+    <sheet name="Relationships" sheetId="4" r:id="rId11"/>
+    <sheet name="Validation Rules" sheetId="5" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atributes!$A$1:$W$396</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reference Data'!$A$1:$H$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Relationships!$A$1:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atributes!$A$1:$W$410</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Reference Data'!$A$1:$H$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Relationships!$A$1:$K$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11202" uniqueCount="2463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11262" uniqueCount="2476">
   <si>
     <t>Domain</t>
   </si>
@@ -7429,6 +7430,45 @@
   </si>
   <si>
     <t>customer-experience-status-draft</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Template should seed it?</t>
+  </si>
+  <si>
+    <t>Editable?</t>
+  </si>
+  <si>
+    <t>Business Name</t>
+  </si>
+  <si>
+    <t>Business Type</t>
+  </si>
+  <si>
+    <t>No — selected during onboarding</t>
+  </si>
+  <si>
+    <t>Probably no here</t>
+  </si>
+  <si>
+    <t>No — system/admin controlled</t>
+  </si>
+  <si>
+    <t>Registration Number</t>
+  </si>
+  <si>
+    <t>OrganizationDetails</t>
+  </si>
+  <si>
+    <t>GST / Tax Number</t>
+  </si>
+  <si>
+    <t>Possibly starter</t>
+  </si>
+  <si>
+    <t>Address</t>
   </si>
 </sst>
 </file>
@@ -10012,6 +10052,1689 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCF67D5-27CE-4C3A-997A-96A77E128378}">
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21" style="4" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>853</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45">
+      <c r="A5" s="13" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30">
+      <c r="A6" s="13" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30">
+      <c r="A9" s="13" t="s">
+        <v>757</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" ht="30">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" ht="30">
+      <c r="A12" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="E14" s="5">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="E15" s="5">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="E18" s="5">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" ht="30">
+      <c r="A19" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" ht="30">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="E24" s="5">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="E25" s="5">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" ht="30">
+      <c r="A26" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" ht="30">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" ht="30">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="E28" s="5">
+        <v>3</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="30">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="E29" s="5">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E32" s="5">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E33" s="5">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E34" s="5">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E36" s="5">
+        <v>2</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E37" s="5">
+        <v>3</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E39" s="5">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="5">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E41" s="5">
+        <v>7</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E42" s="5">
+        <v>8</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E43" s="5">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E44" s="5">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E45" s="5">
+        <v>11</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E46" s="5">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E47" s="5">
+        <v>13</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E48" s="5">
+        <v>14</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E49" s="5">
+        <v>15</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E50" s="5">
+        <v>16</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E51" s="5">
+        <v>17</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E52" s="5">
+        <v>18</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" ht="30">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E53" s="5">
+        <v>19</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" ht="45">
+      <c r="A54" s="13" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="30">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="30">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E56" s="5">
+        <v>3</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="45">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>2271</v>
+      </c>
+      <c r="E57" s="5">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="30">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E58" s="5">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E59" s="5">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="30">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E60" s="5">
+        <v>7</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="30">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E61" s="5">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="30">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E62" s="5">
+        <v>9</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="30">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E63" s="5">
+        <v>10</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="30">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E64" s="5">
+        <v>11</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="30">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E65" s="5">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="30">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E66" s="5">
+        <v>13</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="30">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E67" s="5">
+        <v>14</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="30">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E68" s="5">
+        <v>15</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="30">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E69" s="5">
+        <v>16</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="30">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E70" s="5">
+        <v>17</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="30">
+      <c r="A71" s="13" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
   <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12242,7 +13965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13200,6 +14923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W410"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14386,7 +16110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="30">
+    <row r="18" spans="1:23" ht="30" hidden="1">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -14453,7 +16177,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="30">
+    <row r="19" spans="1:23" ht="30" hidden="1">
       <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
@@ -14522,7 +16246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" hidden="1">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -14589,7 +16313,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" hidden="1">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -14656,7 +16380,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" hidden="1">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
@@ -14723,7 +16447,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="30">
+    <row r="23" spans="1:23" ht="30" hidden="1">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -14792,7 +16516,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="30">
+    <row r="24" spans="1:23" ht="30" hidden="1">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -14859,7 +16583,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="30">
+    <row r="25" spans="1:23" ht="30" hidden="1">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -14926,7 +16650,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="30">
+    <row r="26" spans="1:23" ht="30" hidden="1">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -14995,7 +16719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="30">
+    <row r="27" spans="1:23" ht="30" hidden="1">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -15064,7 +16788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="30">
+    <row r="28" spans="1:23" ht="30" hidden="1">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
@@ -15131,7 +16855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" hidden="1">
       <c r="A29" s="3" t="s">
         <v>8</v>
       </c>
@@ -15200,7 +16924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="30">
+    <row r="30" spans="1:23" ht="30" hidden="1">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
@@ -15267,7 +16991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" hidden="1">
       <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
@@ -15336,7 +17060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="30">
+    <row r="32" spans="1:23" ht="30" hidden="1">
       <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
@@ -15403,7 +17127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" hidden="1">
       <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
@@ -15470,7 +17194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="30">
+    <row r="34" spans="1:23" ht="30" hidden="1">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -15541,7 +17265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="30">
+    <row r="35" spans="1:23" ht="30" hidden="1">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -15612,7 +17336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" hidden="1">
       <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
@@ -15683,7 +17407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45">
+    <row r="37" spans="1:23" ht="45" hidden="1">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -15754,7 +17478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="30">
+    <row r="38" spans="1:23" ht="30" hidden="1">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -15825,7 +17549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="30">
+    <row r="39" spans="1:23" ht="30" hidden="1">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
@@ -15896,7 +17620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="30">
+    <row r="40" spans="1:23" ht="30" hidden="1">
       <c r="A40" s="3" t="s">
         <v>37</v>
       </c>
@@ -15967,7 +17691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" hidden="1">
       <c r="A41" s="3" t="s">
         <v>37</v>
       </c>
@@ -16038,7 +17762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="30">
+    <row r="42" spans="1:23" ht="30" hidden="1">
       <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
@@ -16109,7 +17833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" hidden="1">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
@@ -16180,7 +17904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" hidden="1">
       <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
@@ -16251,7 +17975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" hidden="1">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -16322,7 +18046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="30">
+    <row r="46" spans="1:23" ht="30" hidden="1">
       <c r="A46" s="3" t="s">
         <v>317</v>
       </c>
@@ -16369,7 +18093,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="30">
+    <row r="47" spans="1:23" ht="30" hidden="1">
       <c r="A47" s="3" t="s">
         <v>317</v>
       </c>
@@ -16416,7 +18140,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="45">
+    <row r="48" spans="1:23" ht="45" hidden="1">
       <c r="A48" s="3" t="s">
         <v>317</v>
       </c>
@@ -16463,7 +18187,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="30">
+    <row r="49" spans="1:23" ht="30" hidden="1">
       <c r="A49" s="3" t="s">
         <v>317</v>
       </c>
@@ -16510,7 +18234,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="30">
+    <row r="50" spans="1:23" ht="30" hidden="1">
       <c r="A50" s="3" t="s">
         <v>317</v>
       </c>
@@ -16557,7 +18281,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="30">
+    <row r="51" spans="1:23" ht="30" hidden="1">
       <c r="A51" s="4" t="s">
         <v>341</v>
       </c>
@@ -16625,7 +18349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="30">
+    <row r="52" spans="1:23" ht="30" hidden="1">
       <c r="A52" s="4" t="s">
         <v>341</v>
       </c>
@@ -16693,7 +18417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="30">
+    <row r="53" spans="1:23" ht="30" hidden="1">
       <c r="A53" s="4" t="s">
         <v>341</v>
       </c>
@@ -16761,7 +18485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="30">
+    <row r="54" spans="1:23" ht="30" hidden="1">
       <c r="A54" s="4" t="s">
         <v>341</v>
       </c>
@@ -16829,7 +18553,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="30">
+    <row r="55" spans="1:23" ht="30" hidden="1">
       <c r="A55" s="4" t="s">
         <v>341</v>
       </c>
@@ -16897,7 +18621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="30">
+    <row r="56" spans="1:23" ht="30" hidden="1">
       <c r="A56" s="4" t="s">
         <v>341</v>
       </c>
@@ -16965,7 +18689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="30">
+    <row r="57" spans="1:23" ht="30" hidden="1">
       <c r="A57" s="4" t="s">
         <v>341</v>
       </c>
@@ -17033,7 +18757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="30">
+    <row r="58" spans="1:23" ht="30" hidden="1">
       <c r="A58" s="4" t="s">
         <v>341</v>
       </c>
@@ -17101,7 +18825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="45">
+    <row r="59" spans="1:23" ht="45" hidden="1">
       <c r="A59" s="4" t="s">
         <v>341</v>
       </c>
@@ -17169,7 +18893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="30">
+    <row r="60" spans="1:23" ht="30" hidden="1">
       <c r="A60" s="4" t="s">
         <v>341</v>
       </c>
@@ -17237,7 +18961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="30">
+    <row r="61" spans="1:23" ht="30" hidden="1">
       <c r="A61" s="4" t="s">
         <v>370</v>
       </c>
@@ -17308,7 +19032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="30">
+    <row r="62" spans="1:23" ht="30" hidden="1">
       <c r="A62" s="4" t="s">
         <v>370</v>
       </c>
@@ -17379,7 +19103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="30">
+    <row r="63" spans="1:23" ht="30" hidden="1">
       <c r="A63" s="4" t="s">
         <v>370</v>
       </c>
@@ -17450,7 +19174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="30">
+    <row r="64" spans="1:23" ht="30" hidden="1">
       <c r="A64" s="4" t="s">
         <v>370</v>
       </c>
@@ -17521,7 +19245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="30">
+    <row r="65" spans="1:23" ht="30" hidden="1">
       <c r="A65" s="4" t="s">
         <v>370</v>
       </c>
@@ -17592,7 +19316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="30">
+    <row r="66" spans="1:23" ht="30" hidden="1">
       <c r="A66" s="4" t="s">
         <v>377</v>
       </c>
@@ -17663,7 +19387,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="30">
+    <row r="67" spans="1:23" ht="30" hidden="1">
       <c r="A67" s="4" t="s">
         <v>377</v>
       </c>
@@ -17734,7 +19458,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="30">
+    <row r="68" spans="1:23" ht="30" hidden="1">
       <c r="A68" s="4" t="s">
         <v>377</v>
       </c>
@@ -17805,7 +19529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="30">
+    <row r="69" spans="1:23" ht="30" hidden="1">
       <c r="A69" s="4" t="s">
         <v>10</v>
       </c>
@@ -17876,7 +19600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="30">
+    <row r="70" spans="1:23" ht="30" hidden="1">
       <c r="A70" s="4" t="s">
         <v>10</v>
       </c>
@@ -17947,7 +19671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="45">
+    <row r="71" spans="1:23" ht="45" hidden="1">
       <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
@@ -18018,7 +19742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="45">
+    <row r="72" spans="1:23" ht="45" hidden="1">
       <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
@@ -18089,7 +19813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="30">
+    <row r="73" spans="1:23" ht="30" hidden="1">
       <c r="A73" s="4" t="s">
         <v>10</v>
       </c>
@@ -18160,7 +19884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30">
+    <row r="74" spans="1:23" ht="30" hidden="1">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -18231,7 +19955,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30">
+    <row r="75" spans="1:23" ht="30" hidden="1">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -18302,7 +20026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="30">
+    <row r="76" spans="1:23" ht="30" hidden="1">
       <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
@@ -18373,7 +20097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="30">
+    <row r="77" spans="1:23" ht="30" hidden="1">
       <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
@@ -18444,7 +20168,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="45">
+    <row r="78" spans="1:23" ht="45" hidden="1">
       <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
@@ -18515,7 +20239,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="45">
+    <row r="79" spans="1:23" ht="45" hidden="1">
       <c r="A79" s="4" t="s">
         <v>10</v>
       </c>
@@ -18586,7 +20310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="30">
+    <row r="80" spans="1:23" ht="30" hidden="1">
       <c r="A80" s="4" t="s">
         <v>10</v>
       </c>
@@ -18657,7 +20381,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="30">
+    <row r="81" spans="1:23" ht="30" hidden="1">
       <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
@@ -18728,7 +20452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="30">
+    <row r="82" spans="1:23" ht="30" hidden="1">
       <c r="A82" s="4" t="s">
         <v>10</v>
       </c>
@@ -18799,7 +20523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="30">
+    <row r="83" spans="1:23" ht="30" hidden="1">
       <c r="A83" s="4" t="s">
         <v>10</v>
       </c>
@@ -18870,7 +20594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="45">
+    <row r="84" spans="1:23" ht="45" hidden="1">
       <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
@@ -18941,7 +20665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="30">
+    <row r="85" spans="1:23" ht="30" hidden="1">
       <c r="A85" s="4" t="s">
         <v>10</v>
       </c>
@@ -19012,7 +20736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="30">
+    <row r="86" spans="1:23" ht="30" hidden="1">
       <c r="A86" s="4" t="s">
         <v>490</v>
       </c>
@@ -19083,7 +20807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="30">
+    <row r="87" spans="1:23" ht="30" hidden="1">
       <c r="A87" s="4" t="s">
         <v>490</v>
       </c>
@@ -19154,7 +20878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30">
+    <row r="88" spans="1:23" ht="30" hidden="1">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -19225,7 +20949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30">
+    <row r="89" spans="1:23" ht="30" hidden="1">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -19296,7 +21020,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" hidden="1">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -19367,7 +21091,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" hidden="1">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -19438,7 +21162,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="45">
+    <row r="92" spans="1:23" ht="45" hidden="1">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -19509,7 +21233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="30">
+    <row r="93" spans="1:23" ht="30" hidden="1">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -19580,7 +21304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="30">
+    <row r="94" spans="1:23" ht="30" hidden="1">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -19651,7 +21375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30">
+    <row r="95" spans="1:23" ht="30" hidden="1">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -19722,7 +21446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30">
+    <row r="96" spans="1:23" ht="30" hidden="1">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -19793,7 +21517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="30">
+    <row r="97" spans="1:23" ht="30" hidden="1">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -19864,7 +21588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30">
+    <row r="98" spans="1:23" ht="30" hidden="1">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -19935,7 +21659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30">
+    <row r="99" spans="1:23" ht="30" hidden="1">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -20006,7 +21730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30">
+    <row r="100" spans="1:23" ht="30" hidden="1">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -20077,7 +21801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30">
+    <row r="101" spans="1:23" ht="30" hidden="1">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -20148,7 +21872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30">
+    <row r="102" spans="1:23" ht="30" hidden="1">
       <c r="A102" s="4" t="s">
         <v>548</v>
       </c>
@@ -20219,7 +21943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30">
+    <row r="103" spans="1:23" ht="30" hidden="1">
       <c r="A103" s="4" t="s">
         <v>548</v>
       </c>
@@ -20290,7 +22014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30">
+    <row r="104" spans="1:23" ht="30" hidden="1">
       <c r="A104" s="4" t="s">
         <v>548</v>
       </c>
@@ -20361,7 +22085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30">
+    <row r="105" spans="1:23" ht="30" hidden="1">
       <c r="A105" s="4" t="s">
         <v>548</v>
       </c>
@@ -20432,7 +22156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30">
+    <row r="106" spans="1:23" ht="30" hidden="1">
       <c r="A106" s="4" t="s">
         <v>548</v>
       </c>
@@ -20503,7 +22227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" hidden="1">
       <c r="A107" s="4" t="s">
         <v>548</v>
       </c>
@@ -20574,7 +22298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" hidden="1">
       <c r="A108" s="4" t="s">
         <v>548</v>
       </c>
@@ -20645,7 +22369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" hidden="1">
       <c r="A109" s="4" t="s">
         <v>548</v>
       </c>
@@ -20716,7 +22440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30">
+    <row r="110" spans="1:23" ht="30" hidden="1">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -20787,7 +22511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" hidden="1">
       <c r="A111" s="4" t="s">
         <v>548</v>
       </c>
@@ -20858,7 +22582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="30">
+    <row r="112" spans="1:23" ht="30" hidden="1">
       <c r="A112" s="4" t="s">
         <v>548</v>
       </c>
@@ -20929,7 +22653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" hidden="1">
       <c r="A113" s="4" t="s">
         <v>548</v>
       </c>
@@ -21000,7 +22724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="30">
+    <row r="114" spans="1:23" ht="30" hidden="1">
       <c r="A114" s="4" t="s">
         <v>548</v>
       </c>
@@ -21071,7 +22795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:23">
+    <row r="115" spans="1:23" hidden="1">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
@@ -21142,7 +22866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="30">
+    <row r="116" spans="1:23" ht="30" hidden="1">
       <c r="A116" s="4" t="s">
         <v>548</v>
       </c>
@@ -21213,7 +22937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:23">
+    <row r="117" spans="1:23" hidden="1">
       <c r="A117" s="4" t="s">
         <v>548</v>
       </c>
@@ -21284,7 +23008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" hidden="1">
       <c r="A118" s="4" t="s">
         <v>548</v>
       </c>
@@ -21355,7 +23079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:23">
+    <row r="119" spans="1:23" hidden="1">
       <c r="A119" s="4" t="s">
         <v>548</v>
       </c>
@@ -21426,7 +23150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="30">
+    <row r="120" spans="1:23" ht="30" hidden="1">
       <c r="A120" s="4" t="s">
         <v>620</v>
       </c>
@@ -21497,7 +23221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="30">
+    <row r="121" spans="1:23" ht="30" hidden="1">
       <c r="A121" s="4" t="s">
         <v>620</v>
       </c>
@@ -21568,7 +23292,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" hidden="1">
       <c r="A122" s="4" t="s">
         <v>620</v>
       </c>
@@ -21639,7 +23363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="30">
+    <row r="123" spans="1:23" ht="30" hidden="1">
       <c r="A123" s="4" t="s">
         <v>620</v>
       </c>
@@ -21710,7 +23434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" hidden="1">
       <c r="A124" s="4" t="s">
         <v>620</v>
       </c>
@@ -21781,7 +23505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="30">
+    <row r="125" spans="1:23" ht="30" hidden="1">
       <c r="A125" s="4" t="s">
         <v>620</v>
       </c>
@@ -21852,7 +23576,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:23" hidden="1">
       <c r="A126" s="4" t="s">
         <v>620</v>
       </c>
@@ -21923,7 +23647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" hidden="1">
       <c r="A127" s="4" t="s">
         <v>620</v>
       </c>
@@ -21994,7 +23718,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="30">
+    <row r="128" spans="1:23" ht="30" hidden="1">
       <c r="A128" s="4" t="s">
         <v>620</v>
       </c>
@@ -22065,7 +23789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:23" ht="30">
+    <row r="129" spans="1:23" ht="30" hidden="1">
       <c r="A129" s="4" t="s">
         <v>620</v>
       </c>
@@ -22136,7 +23860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:23" hidden="1">
       <c r="A130" s="4" t="s">
         <v>620</v>
       </c>
@@ -22207,7 +23931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="30">
+    <row r="131" spans="1:23" ht="30" hidden="1">
       <c r="A131" s="4" t="s">
         <v>620</v>
       </c>
@@ -22278,7 +24002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" hidden="1">
       <c r="A132" s="4" t="s">
         <v>620</v>
       </c>
@@ -22349,7 +24073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:23" hidden="1">
       <c r="A133" s="4" t="s">
         <v>620</v>
       </c>
@@ -22420,7 +24144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:23" hidden="1">
       <c r="A134" s="4" t="s">
         <v>620</v>
       </c>
@@ -22491,7 +24215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:23" ht="30">
+    <row r="135" spans="1:23" ht="30" hidden="1">
       <c r="A135" s="4" t="s">
         <v>673</v>
       </c>
@@ -22562,7 +24286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="30">
+    <row r="136" spans="1:23" ht="30" hidden="1">
       <c r="A136" s="4" t="s">
         <v>673</v>
       </c>
@@ -22633,7 +24357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:23" ht="30">
+    <row r="137" spans="1:23" ht="30" hidden="1">
       <c r="A137" s="4" t="s">
         <v>673</v>
       </c>
@@ -22704,7 +24428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:23" ht="30">
+    <row r="138" spans="1:23" ht="30" hidden="1">
       <c r="A138" s="4" t="s">
         <v>673</v>
       </c>
@@ -22775,7 +24499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:23" ht="30">
+    <row r="139" spans="1:23" ht="30" hidden="1">
       <c r="A139" s="4" t="s">
         <v>673</v>
       </c>
@@ -22846,7 +24570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="30">
+    <row r="140" spans="1:23" ht="30" hidden="1">
       <c r="A140" s="4" t="s">
         <v>673</v>
       </c>
@@ -22917,7 +24641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="30">
+    <row r="141" spans="1:23" ht="30" hidden="1">
       <c r="A141" s="4" t="s">
         <v>673</v>
       </c>
@@ -22988,7 +24712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:23">
+    <row r="142" spans="1:23" hidden="1">
       <c r="A142" s="4" t="s">
         <v>673</v>
       </c>
@@ -23059,7 +24783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="30">
+    <row r="143" spans="1:23" ht="30" hidden="1">
       <c r="A143" s="4" t="s">
         <v>673</v>
       </c>
@@ -23130,7 +24854,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="30">
+    <row r="144" spans="1:23" ht="30" hidden="1">
       <c r="A144" s="4" t="s">
         <v>673</v>
       </c>
@@ -23201,7 +24925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="30">
+    <row r="145" spans="1:23" ht="30" hidden="1">
       <c r="A145" s="4" t="s">
         <v>673</v>
       </c>
@@ -23272,7 +24996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="30">
+    <row r="146" spans="1:23" ht="30" hidden="1">
       <c r="A146" s="4" t="s">
         <v>673</v>
       </c>
@@ -23343,7 +25067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:23" ht="30">
+    <row r="147" spans="1:23" ht="30" hidden="1">
       <c r="A147" s="4" t="s">
         <v>673</v>
       </c>
@@ -23414,7 +25138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="30">
+    <row r="148" spans="1:23" ht="30" hidden="1">
       <c r="A148" s="4" t="s">
         <v>673</v>
       </c>
@@ -23485,7 +25209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:23" hidden="1">
       <c r="A149" s="4" t="s">
         <v>673</v>
       </c>
@@ -23556,7 +25280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="30">
+    <row r="150" spans="1:23" ht="30" hidden="1">
       <c r="A150" s="4" t="s">
         <v>34</v>
       </c>
@@ -23627,7 +25351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="30">
+    <row r="151" spans="1:23" ht="30" hidden="1">
       <c r="A151" s="4" t="s">
         <v>34</v>
       </c>
@@ -23698,7 +25422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="30">
+    <row r="152" spans="1:23" ht="30" hidden="1">
       <c r="A152" s="4" t="s">
         <v>34</v>
       </c>
@@ -23769,7 +25493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="30">
+    <row r="153" spans="1:23" ht="30" hidden="1">
       <c r="A153" s="4" t="s">
         <v>34</v>
       </c>
@@ -23840,7 +25564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" hidden="1">
       <c r="A154" s="4" t="s">
         <v>34</v>
       </c>
@@ -23911,7 +25635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="30">
+    <row r="155" spans="1:23" ht="30" hidden="1">
       <c r="A155" s="4" t="s">
         <v>34</v>
       </c>
@@ -23982,7 +25706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="30">
+    <row r="156" spans="1:23" ht="30" hidden="1">
       <c r="A156" s="4" t="s">
         <v>34</v>
       </c>
@@ -24053,7 +25777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="30">
+    <row r="157" spans="1:23" ht="30" hidden="1">
       <c r="A157" s="4" t="s">
         <v>34</v>
       </c>
@@ -24124,7 +25848,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="30">
+    <row r="158" spans="1:23" ht="30" hidden="1">
       <c r="A158" s="4" t="s">
         <v>34</v>
       </c>
@@ -24195,7 +25919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="30">
+    <row r="159" spans="1:23" ht="30" hidden="1">
       <c r="A159" s="4" t="s">
         <v>34</v>
       </c>
@@ -24266,7 +25990,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="30">
+    <row r="160" spans="1:23" ht="30" hidden="1">
       <c r="A160" s="4" t="s">
         <v>34</v>
       </c>
@@ -24337,7 +26061,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:23" hidden="1">
       <c r="A161" s="4" t="s">
         <v>34</v>
       </c>
@@ -24408,7 +26132,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="30">
+    <row r="162" spans="1:23" ht="30" hidden="1">
       <c r="A162" s="4" t="s">
         <v>34</v>
       </c>
@@ -24479,7 +26203,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="30">
+    <row r="163" spans="1:23" ht="30" hidden="1">
       <c r="A163" s="4" t="s">
         <v>34</v>
       </c>
@@ -24550,7 +26274,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="30">
+    <row r="164" spans="1:23" ht="30" hidden="1">
       <c r="A164" s="4" t="s">
         <v>34</v>
       </c>
@@ -24621,7 +26345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="30">
+    <row r="165" spans="1:23" ht="30" hidden="1">
       <c r="A165" s="4" t="s">
         <v>34</v>
       </c>
@@ -24692,7 +26416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="30">
+    <row r="166" spans="1:23" ht="30" hidden="1">
       <c r="A166" s="4" t="s">
         <v>35</v>
       </c>
@@ -24763,7 +26487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="30">
+    <row r="167" spans="1:23" ht="30" hidden="1">
       <c r="A167" s="4" t="s">
         <v>35</v>
       </c>
@@ -24834,7 +26558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="30">
+    <row r="168" spans="1:23" ht="30" hidden="1">
       <c r="A168" s="4" t="s">
         <v>35</v>
       </c>
@@ -24905,7 +26629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="30">
+    <row r="169" spans="1:23" ht="30" hidden="1">
       <c r="A169" s="4" t="s">
         <v>35</v>
       </c>
@@ -24976,7 +26700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="30">
+    <row r="170" spans="1:23" ht="30" hidden="1">
       <c r="A170" s="4" t="s">
         <v>35</v>
       </c>
@@ -25047,7 +26771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="30">
+    <row r="171" spans="1:23" ht="30" hidden="1">
       <c r="A171" s="4" t="s">
         <v>35</v>
       </c>
@@ -25118,7 +26842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="30">
+    <row r="172" spans="1:23" ht="30" hidden="1">
       <c r="A172" s="4" t="s">
         <v>35</v>
       </c>
@@ -25189,7 +26913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:23" ht="30">
+    <row r="173" spans="1:23" ht="30" hidden="1">
       <c r="A173" s="4" t="s">
         <v>35</v>
       </c>
@@ -25260,7 +26984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="30">
+    <row r="174" spans="1:23" ht="30" hidden="1">
       <c r="A174" s="4" t="s">
         <v>35</v>
       </c>
@@ -25331,7 +27055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="30">
+    <row r="175" spans="1:23" ht="30" hidden="1">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -25402,7 +27126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="30">
+    <row r="176" spans="1:23" ht="30" hidden="1">
       <c r="A176" s="4" t="s">
         <v>35</v>
       </c>
@@ -25473,7 +27197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="30">
+    <row r="177" spans="1:23" ht="30" hidden="1">
       <c r="A177" s="4" t="s">
         <v>35</v>
       </c>
@@ -25544,7 +27268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="30">
+    <row r="178" spans="1:23" ht="30" hidden="1">
       <c r="A178" s="4" t="s">
         <v>35</v>
       </c>
@@ -25615,7 +27339,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="30">
+    <row r="179" spans="1:23" ht="30" hidden="1">
       <c r="A179" s="4" t="s">
         <v>35</v>
       </c>
@@ -25686,7 +27410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="30">
+    <row r="180" spans="1:23" ht="30" hidden="1">
       <c r="A180" s="4" t="s">
         <v>35</v>
       </c>
@@ -25757,7 +27481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="30">
+    <row r="181" spans="1:23" ht="30" hidden="1">
       <c r="A181" s="3" t="s">
         <v>94</v>
       </c>
@@ -25824,7 +27548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="30">
+    <row r="182" spans="1:23" ht="30" hidden="1">
       <c r="A182" s="3" t="s">
         <v>94</v>
       </c>
@@ -25893,7 +27617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:23" ht="30">
+    <row r="183" spans="1:23" ht="30" hidden="1">
       <c r="A183" s="3" t="s">
         <v>94</v>
       </c>
@@ -25962,7 +27686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:23" ht="30">
+    <row r="184" spans="1:23" ht="30" hidden="1">
       <c r="A184" s="3" t="s">
         <v>94</v>
       </c>
@@ -26031,7 +27755,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="30">
+    <row r="185" spans="1:23" ht="30" hidden="1">
       <c r="A185" s="3" t="s">
         <v>94</v>
       </c>
@@ -26100,7 +27824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="30">
+    <row r="186" spans="1:23" ht="30" hidden="1">
       <c r="A186" s="3" t="s">
         <v>94</v>
       </c>
@@ -26169,7 +27893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:23">
+    <row r="187" spans="1:23" hidden="1">
       <c r="A187" s="3" t="s">
         <v>42</v>
       </c>
@@ -26236,7 +27960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:23">
+    <row r="188" spans="1:23" hidden="1">
       <c r="A188" s="3" t="s">
         <v>42</v>
       </c>
@@ -26305,7 +28029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:23">
+    <row r="189" spans="1:23" hidden="1">
       <c r="A189" s="3" t="s">
         <v>42</v>
       </c>
@@ -26374,7 +28098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="30">
+    <row r="190" spans="1:23" ht="30" hidden="1">
       <c r="A190" s="3" t="s">
         <v>42</v>
       </c>
@@ -26443,7 +28167,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:23">
+    <row r="191" spans="1:23" hidden="1">
       <c r="A191" s="3" t="s">
         <v>42</v>
       </c>
@@ -26512,7 +28236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:23" ht="30">
+    <row r="192" spans="1:23" ht="30" hidden="1">
       <c r="A192" s="3" t="s">
         <v>42</v>
       </c>
@@ -26581,7 +28305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:23">
+    <row r="193" spans="1:23" hidden="1">
       <c r="A193" s="3" t="s">
         <v>129</v>
       </c>
@@ -26648,7 +28372,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:23">
+    <row r="194" spans="1:23" hidden="1">
       <c r="A194" s="3" t="s">
         <v>129</v>
       </c>
@@ -26717,7 +28441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:23">
+    <row r="195" spans="1:23" hidden="1">
       <c r="A195" s="3" t="s">
         <v>129</v>
       </c>
@@ -26786,7 +28510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:23">
+    <row r="196" spans="1:23" hidden="1">
       <c r="A196" s="3" t="s">
         <v>129</v>
       </c>
@@ -26855,7 +28579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:23">
+    <row r="197" spans="1:23" hidden="1">
       <c r="A197" s="3" t="s">
         <v>129</v>
       </c>
@@ -26924,7 +28648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="30">
+    <row r="198" spans="1:23" ht="30" hidden="1">
       <c r="A198" s="3" t="s">
         <v>129</v>
       </c>
@@ -26993,7 +28717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="30">
+    <row r="199" spans="1:23" ht="30" hidden="1">
       <c r="A199" s="3" t="s">
         <v>129</v>
       </c>
@@ -27062,7 +28786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:23">
+    <row r="200" spans="1:23" hidden="1">
       <c r="A200" s="3" t="s">
         <v>126</v>
       </c>
@@ -27129,7 +28853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:23">
+    <row r="201" spans="1:23" hidden="1">
       <c r="A201" s="3" t="s">
         <v>126</v>
       </c>
@@ -27198,7 +28922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:23">
+    <row r="202" spans="1:23" hidden="1">
       <c r="A202" s="3" t="s">
         <v>126</v>
       </c>
@@ -27267,7 +28991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:23" ht="30">
+    <row r="203" spans="1:23" ht="30" hidden="1">
       <c r="A203" s="3" t="s">
         <v>126</v>
       </c>
@@ -27336,7 +29060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:23" ht="30">
+    <row r="204" spans="1:23" ht="30" hidden="1">
       <c r="A204" s="3" t="s">
         <v>126</v>
       </c>
@@ -27405,7 +29129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" hidden="1">
       <c r="A205" s="3" t="s">
         <v>126</v>
       </c>
@@ -27474,7 +29198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="30">
+    <row r="206" spans="1:23" ht="30" hidden="1">
       <c r="A206" s="3" t="s">
         <v>126</v>
       </c>
@@ -27543,7 +29267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="30">
+    <row r="207" spans="1:23" ht="30" hidden="1">
       <c r="A207" s="3" t="s">
         <v>126</v>
       </c>
@@ -27612,7 +29336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="30">
+    <row r="208" spans="1:23" ht="30" hidden="1">
       <c r="A208" s="3" t="s">
         <v>313</v>
       </c>
@@ -27679,7 +29403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:23" ht="30">
+    <row r="209" spans="1:23" ht="30" hidden="1">
       <c r="A209" s="3" t="s">
         <v>313</v>
       </c>
@@ -27748,7 +29472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:23" ht="30">
+    <row r="210" spans="1:23" ht="30" hidden="1">
       <c r="A210" s="3" t="s">
         <v>313</v>
       </c>
@@ -27817,7 +29541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:23" ht="30">
+    <row r="211" spans="1:23" ht="30" hidden="1">
       <c r="A211" s="3" t="s">
         <v>313</v>
       </c>
@@ -27886,7 +29610,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:23" ht="30">
+    <row r="212" spans="1:23" ht="30" hidden="1">
       <c r="A212" s="3" t="s">
         <v>313</v>
       </c>
@@ -27955,7 +29679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:23" ht="45">
+    <row r="213" spans="1:23" ht="45" hidden="1">
       <c r="A213" s="3" t="s">
         <v>313</v>
       </c>
@@ -28024,7 +29748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="30">
+    <row r="214" spans="1:23" ht="30" hidden="1">
       <c r="A214" s="3" t="s">
         <v>445</v>
       </c>
@@ -28091,7 +29815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="30">
+    <row r="215" spans="1:23" ht="30" hidden="1">
       <c r="A215" s="3" t="s">
         <v>445</v>
       </c>
@@ -28160,7 +29884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:23" ht="30">
+    <row r="216" spans="1:23" ht="30" hidden="1">
       <c r="A216" s="3" t="s">
         <v>445</v>
       </c>
@@ -28229,7 +29953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="30">
+    <row r="217" spans="1:23" ht="30" hidden="1">
       <c r="A217" s="3" t="s">
         <v>445</v>
       </c>
@@ -28298,7 +30022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:23" ht="30">
+    <row r="218" spans="1:23" ht="30" hidden="1">
       <c r="A218" s="3" t="s">
         <v>445</v>
       </c>
@@ -28367,7 +30091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="30">
+    <row r="219" spans="1:23" ht="30" hidden="1">
       <c r="A219" s="3" t="s">
         <v>445</v>
       </c>
@@ -28436,7 +30160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="30">
+    <row r="220" spans="1:23" ht="30" hidden="1">
       <c r="A220" s="3" t="s">
         <v>451</v>
       </c>
@@ -28503,7 +30227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:23">
+    <row r="221" spans="1:23" hidden="1">
       <c r="A221" s="3" t="s">
         <v>451</v>
       </c>
@@ -28572,7 +30296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:23">
+    <row r="222" spans="1:23" hidden="1">
       <c r="A222" s="3" t="s">
         <v>451</v>
       </c>
@@ -28641,7 +30365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="30">
+    <row r="223" spans="1:23" ht="30" hidden="1">
       <c r="A223" s="3" t="s">
         <v>451</v>
       </c>
@@ -28710,7 +30434,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:23">
+    <row r="224" spans="1:23" hidden="1">
       <c r="A224" s="3" t="s">
         <v>451</v>
       </c>
@@ -28779,7 +30503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="30">
+    <row r="225" spans="1:23" ht="30" hidden="1">
       <c r="A225" s="3" t="s">
         <v>451</v>
       </c>
@@ -28848,7 +30572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="30">
+    <row r="226" spans="1:23" ht="30" hidden="1">
       <c r="A226" s="3" t="s">
         <v>512</v>
       </c>
@@ -28915,7 +30639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="30">
+    <row r="227" spans="1:23" ht="30" hidden="1">
       <c r="A227" s="3" t="s">
         <v>512</v>
       </c>
@@ -28984,7 +30708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="30">
+    <row r="228" spans="1:23" ht="30" hidden="1">
       <c r="A228" s="3" t="s">
         <v>512</v>
       </c>
@@ -29053,7 +30777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="30">
+    <row r="229" spans="1:23" ht="30" hidden="1">
       <c r="A229" s="3" t="s">
         <v>512</v>
       </c>
@@ -29122,7 +30846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="30">
+    <row r="230" spans="1:23" ht="30" hidden="1">
       <c r="A230" s="3" t="s">
         <v>512</v>
       </c>
@@ -29191,7 +30915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="30">
+    <row r="231" spans="1:23" ht="30" hidden="1">
       <c r="A231" s="3" t="s">
         <v>512</v>
       </c>
@@ -29260,7 +30984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="30">
+    <row r="232" spans="1:23" ht="30" hidden="1">
       <c r="A232" s="3" t="s">
         <v>518</v>
       </c>
@@ -29327,7 +31051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:23">
+    <row r="233" spans="1:23" hidden="1">
       <c r="A233" s="3" t="s">
         <v>518</v>
       </c>
@@ -29396,7 +31120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:23">
+    <row r="234" spans="1:23" hidden="1">
       <c r="A234" s="3" t="s">
         <v>518</v>
       </c>
@@ -29465,7 +31189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="30">
+    <row r="235" spans="1:23" ht="30" hidden="1">
       <c r="A235" s="3" t="s">
         <v>518</v>
       </c>
@@ -29534,7 +31258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:23">
+    <row r="236" spans="1:23" hidden="1">
       <c r="A236" s="3" t="s">
         <v>518</v>
       </c>
@@ -29603,7 +31327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:23" ht="30">
+    <row r="237" spans="1:23" ht="30" hidden="1">
       <c r="A237" s="3" t="s">
         <v>518</v>
       </c>
@@ -29672,7 +31396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="30">
+    <row r="238" spans="1:23" ht="30" hidden="1">
       <c r="A238" s="3" t="s">
         <v>757</v>
       </c>
@@ -29739,7 +31463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:23">
+    <row r="239" spans="1:23" hidden="1">
       <c r="A239" s="3" t="s">
         <v>757</v>
       </c>
@@ -29808,7 +31532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:23">
+    <row r="240" spans="1:23" hidden="1">
       <c r="A240" s="3" t="s">
         <v>757</v>
       </c>
@@ -29877,7 +31601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:23">
+    <row r="241" spans="1:23" hidden="1">
       <c r="A241" s="3" t="s">
         <v>757</v>
       </c>
@@ -29946,7 +31670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:23">
+    <row r="242" spans="1:23" hidden="1">
       <c r="A242" s="3" t="s">
         <v>757</v>
       </c>
@@ -30015,7 +31739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="30">
+    <row r="243" spans="1:23" ht="30" hidden="1">
       <c r="A243" s="3" t="s">
         <v>757</v>
       </c>
@@ -31385,7 +33109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30">
+    <row r="263" spans="1:23" ht="30" hidden="1">
       <c r="A263" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31452,7 +33176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="30">
+    <row r="264" spans="1:23" ht="30" hidden="1">
       <c r="A264" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31519,7 +33243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30">
+    <row r="265" spans="1:23" ht="30" hidden="1">
       <c r="A265" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31590,7 +33314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" hidden="1">
       <c r="A266" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31657,7 +33381,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="30">
+    <row r="267" spans="1:23" ht="30" hidden="1">
       <c r="A267" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31726,7 +33450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" hidden="1">
       <c r="A268" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31795,7 +33519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" hidden="1">
       <c r="A269" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31864,7 +33588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="30">
+    <row r="270" spans="1:23" ht="30" hidden="1">
       <c r="A270" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31931,7 +33655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="30">
+    <row r="271" spans="1:23" ht="30" hidden="1">
       <c r="A271" s="3" t="s">
         <v>1518</v>
       </c>
@@ -31998,7 +33722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23">
+    <row r="272" spans="1:23" hidden="1">
       <c r="A272" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32063,7 +33787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23">
+    <row r="273" spans="1:23" hidden="1">
       <c r="A273" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32128,7 +33852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" hidden="1">
       <c r="A274" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32193,7 +33917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" hidden="1">
       <c r="A275" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32262,7 +33986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" hidden="1">
       <c r="A276" s="3" t="s">
         <v>1518</v>
       </c>
@@ -32331,7 +34055,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:23" ht="30">
+    <row r="277" spans="1:23" ht="30" hidden="1">
       <c r="A277" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32398,7 +34122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="30">
+    <row r="278" spans="1:23" ht="30" hidden="1">
       <c r="A278" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32465,7 +34189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="45">
+    <row r="279" spans="1:23" ht="45" hidden="1">
       <c r="A279" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32536,7 +34260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="30">
+    <row r="280" spans="1:23" ht="30" hidden="1">
       <c r="A280" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32605,7 +34329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="30">
+    <row r="281" spans="1:23" ht="30" hidden="1">
       <c r="A281" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32674,7 +34398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="30">
+    <row r="282" spans="1:23" ht="30" hidden="1">
       <c r="A282" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32743,7 +34467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="30">
+    <row r="283" spans="1:23" ht="30" hidden="1">
       <c r="A283" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32812,7 +34536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:23" ht="30">
+    <row r="284" spans="1:23" ht="30" hidden="1">
       <c r="A284" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32881,7 +34605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:23" ht="30">
+    <row r="285" spans="1:23" ht="30" hidden="1">
       <c r="A285" s="3" t="s">
         <v>1578</v>
       </c>
@@ -32948,7 +34672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="30">
+    <row r="286" spans="1:23" ht="30" hidden="1">
       <c r="A286" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33015,7 +34739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="30">
+    <row r="287" spans="1:23" ht="30" hidden="1">
       <c r="A287" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33080,7 +34804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="30">
+    <row r="288" spans="1:23" ht="30" hidden="1">
       <c r="A288" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33145,7 +34869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="30">
+    <row r="289" spans="1:23" ht="30" hidden="1">
       <c r="A289" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33210,7 +34934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="30">
+    <row r="290" spans="1:23" ht="30" hidden="1">
       <c r="A290" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33279,7 +35003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="30">
+    <row r="291" spans="1:23" ht="30" hidden="1">
       <c r="A291" s="3" t="s">
         <v>1578</v>
       </c>
@@ -33348,7 +35072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:23" ht="30">
+    <row r="292" spans="1:23" ht="30" hidden="1">
       <c r="A292" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33415,7 +35139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:23" ht="30">
+    <row r="293" spans="1:23" ht="30" hidden="1">
       <c r="A293" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33482,7 +35206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:23" ht="45">
+    <row r="294" spans="1:23" ht="45" hidden="1">
       <c r="A294" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33551,7 +35275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" hidden="1">
       <c r="A295" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33618,7 +35342,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" hidden="1">
       <c r="A296" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33685,7 +35409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="30">
+    <row r="297" spans="1:23" ht="30" hidden="1">
       <c r="A297" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33752,7 +35476,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:23">
+    <row r="298" spans="1:23" hidden="1">
       <c r="A298" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33819,7 +35543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="45">
+    <row r="299" spans="1:23" ht="45" hidden="1">
       <c r="A299" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33888,7 +35612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="30">
+    <row r="300" spans="1:23" ht="30" hidden="1">
       <c r="A300" s="3" t="s">
         <v>1635</v>
       </c>
@@ -33953,7 +35677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="30">
+    <row r="301" spans="1:23" ht="30" hidden="1">
       <c r="A301" s="3" t="s">
         <v>1635</v>
       </c>
@@ -34022,7 +35746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="30">
+    <row r="302" spans="1:23" ht="30" hidden="1">
       <c r="A302" s="3" t="s">
         <v>1635</v>
       </c>
@@ -34089,7 +35813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="30">
+    <row r="303" spans="1:23" ht="30" hidden="1">
       <c r="A303" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34156,7 +35880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="30">
+    <row r="304" spans="1:23" ht="30" hidden="1">
       <c r="A304" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34223,7 +35947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="30">
+    <row r="305" spans="1:23" ht="30" hidden="1">
       <c r="A305" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34292,7 +36016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30">
+    <row r="306" spans="1:23" ht="30" hidden="1">
       <c r="A306" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34359,7 +36083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="30">
+    <row r="307" spans="1:23" ht="30" hidden="1">
       <c r="A307" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34428,7 +36152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="30">
+    <row r="308" spans="1:23" ht="30" hidden="1">
       <c r="A308" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34497,7 +36221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="30">
+    <row r="309" spans="1:23" ht="30" hidden="1">
       <c r="A309" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34564,7 +36288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="30">
+    <row r="310" spans="1:23" ht="30" hidden="1">
       <c r="A310" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34631,7 +36355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="30">
+    <row r="311" spans="1:23" ht="30" hidden="1">
       <c r="A311" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34696,7 +36420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="30">
+    <row r="312" spans="1:23" ht="30" hidden="1">
       <c r="A312" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34763,7 +36487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="45">
+    <row r="313" spans="1:23" ht="45" hidden="1">
       <c r="A313" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34832,7 +36556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="30">
+    <row r="314" spans="1:23" ht="30" hidden="1">
       <c r="A314" s="3" t="s">
         <v>1689</v>
       </c>
@@ -34901,7 +36625,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:23" ht="30">
+    <row r="315" spans="1:23" ht="30" hidden="1">
       <c r="A315" s="3" t="s">
         <v>1704</v>
       </c>
@@ -34968,7 +36692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:23" ht="30">
+    <row r="316" spans="1:23" ht="30" hidden="1">
       <c r="A316" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35037,7 +36761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:23">
+    <row r="317" spans="1:23" hidden="1">
       <c r="A317" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35106,7 +36830,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="30">
+    <row r="318" spans="1:23" ht="30" hidden="1">
       <c r="A318" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35175,7 +36899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:23">
+    <row r="319" spans="1:23" hidden="1">
       <c r="A319" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35244,7 +36968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="30">
+    <row r="320" spans="1:23" ht="30" hidden="1">
       <c r="A320" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35313,7 +37037,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="30">
+    <row r="321" spans="1:23" ht="30" hidden="1">
       <c r="A321" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35380,7 +37104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:23" hidden="1">
       <c r="A322" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35445,7 +37169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="30">
+    <row r="323" spans="1:23" ht="30" hidden="1">
       <c r="A323" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35514,7 +37238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:23" hidden="1">
       <c r="A324" s="3" t="s">
         <v>1704</v>
       </c>
@@ -35583,7 +37307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="30">
+    <row r="325" spans="1:23" ht="30" hidden="1">
       <c r="A325" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35650,7 +37374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="30">
+    <row r="326" spans="1:23" ht="30" hidden="1">
       <c r="A326" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35717,7 +37441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="30">
+    <row r="327" spans="1:23" ht="30" hidden="1">
       <c r="A327" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35784,7 +37508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="30">
+    <row r="328" spans="1:23" ht="30" hidden="1">
       <c r="A328" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35853,7 +37577,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="45">
+    <row r="329" spans="1:23" ht="45" hidden="1">
       <c r="A329" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35922,7 +37646,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="30">
+    <row r="330" spans="1:23" ht="30" hidden="1">
       <c r="A330" s="3" t="s">
         <v>1806</v>
       </c>
@@ -35989,7 +37713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="30">
+    <row r="331" spans="1:23" ht="30" hidden="1">
       <c r="A331" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36056,7 +37780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="30">
+    <row r="332" spans="1:23" ht="30" hidden="1">
       <c r="A332" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36125,7 +37849,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="30">
+    <row r="333" spans="1:23" ht="30" hidden="1">
       <c r="A333" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36192,7 +37916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="30">
+    <row r="334" spans="1:23" ht="30" hidden="1">
       <c r="A334" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36259,7 +37983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="30">
+    <row r="335" spans="1:23" ht="30" hidden="1">
       <c r="A335" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36324,7 +38048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="30">
+    <row r="336" spans="1:23" ht="30" hidden="1">
       <c r="A336" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36391,7 +38115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="45">
+    <row r="337" spans="1:23" ht="45" hidden="1">
       <c r="A337" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36460,7 +38184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="30">
+    <row r="338" spans="1:23" ht="30" hidden="1">
       <c r="A338" s="3" t="s">
         <v>1806</v>
       </c>
@@ -36529,7 +38253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:23">
+    <row r="339" spans="1:23" hidden="1">
       <c r="A339" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36598,7 +38322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:23">
+    <row r="340" spans="1:23" hidden="1">
       <c r="A340" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36667,7 +38391,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:23">
+    <row r="341" spans="1:23" hidden="1">
       <c r="A341" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36736,7 +38460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="30">
+    <row r="342" spans="1:23" ht="30" hidden="1">
       <c r="A342" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36805,7 +38529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="30">
+    <row r="343" spans="1:23" ht="30" hidden="1">
       <c r="A343" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36876,7 +38600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="30">
+    <row r="344" spans="1:23" ht="30" hidden="1">
       <c r="A344" s="3" t="s">
         <v>1914</v>
       </c>
@@ -36945,7 +38669,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="345" spans="1:23">
+    <row r="345" spans="1:23" hidden="1">
       <c r="A345" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37016,7 +38740,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="30">
+    <row r="346" spans="1:23" ht="30" hidden="1">
       <c r="A346" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37087,7 +38811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="30">
+    <row r="347" spans="1:23" ht="30" hidden="1">
       <c r="A347" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37158,7 +38882,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:23">
+    <row r="348" spans="1:23" hidden="1">
       <c r="A348" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37227,7 +38951,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="30">
+    <row r="349" spans="1:23" ht="30" hidden="1">
       <c r="A349" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37298,7 +39022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="30">
+    <row r="350" spans="1:23" ht="30" hidden="1">
       <c r="A350" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37367,7 +39091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="30">
+    <row r="351" spans="1:23" ht="30" hidden="1">
       <c r="A351" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37438,7 +39162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="30">
+    <row r="352" spans="1:23" ht="30" hidden="1">
       <c r="A352" s="3" t="s">
         <v>1914</v>
       </c>
@@ -37509,7 +39233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="30">
+    <row r="353" spans="1:23" ht="30" hidden="1">
       <c r="A353" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37578,7 +39302,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="30">
+    <row r="354" spans="1:23" ht="30" hidden="1">
       <c r="A354" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37647,7 +39371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:23">
+    <row r="355" spans="1:23" hidden="1">
       <c r="A355" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37716,7 +39440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="45">
+    <row r="356" spans="1:23" ht="45" hidden="1">
       <c r="A356" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37785,7 +39509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="30">
+    <row r="357" spans="1:23" ht="30" hidden="1">
       <c r="A357" s="3" t="s">
         <v>1922</v>
       </c>
@@ -37856,7 +39580,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="30">
+    <row r="358" spans="1:23" ht="30" hidden="1">
       <c r="A358" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37927,7 +39651,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="30">
+    <row r="359" spans="1:23" ht="30" hidden="1">
       <c r="A359" s="4" t="s">
         <v>2018</v>
       </c>
@@ -37998,7 +39722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:23" ht="30">
+    <row r="360" spans="1:23" ht="30" hidden="1">
       <c r="A360" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38069,7 +39793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:23" ht="45">
+    <row r="361" spans="1:23" ht="45" hidden="1">
       <c r="A361" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38140,7 +39864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:23" ht="30">
+    <row r="362" spans="1:23" ht="30" hidden="1">
       <c r="A362" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38211,7 +39935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="30">
+    <row r="363" spans="1:23" ht="30" hidden="1">
       <c r="A363" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38282,7 +40006,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="30">
+    <row r="364" spans="1:23" ht="30" hidden="1">
       <c r="A364" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38353,7 +40077,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="30">
+    <row r="365" spans="1:23" ht="30" hidden="1">
       <c r="A365" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38424,7 +40148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="30">
+    <row r="366" spans="1:23" ht="30" hidden="1">
       <c r="A366" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38495,7 +40219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="30">
+    <row r="367" spans="1:23" ht="30" hidden="1">
       <c r="A367" s="4" t="s">
         <v>2018</v>
       </c>
@@ -38566,7 +40290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="30">
+    <row r="368" spans="1:23" ht="30" hidden="1">
       <c r="A368" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38637,7 +40361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="30">
+    <row r="369" spans="1:23" ht="30" hidden="1">
       <c r="A369" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38708,7 +40432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:23" ht="30">
+    <row r="370" spans="1:23" ht="30" hidden="1">
       <c r="A370" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38779,7 +40503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="30">
+    <row r="371" spans="1:23" ht="30" hidden="1">
       <c r="A371" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38850,7 +40574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="30">
+    <row r="372" spans="1:23" ht="30" hidden="1">
       <c r="A372" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38921,7 +40645,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="45">
+    <row r="373" spans="1:23" ht="45" hidden="1">
       <c r="A373" s="4" t="s">
         <v>2062</v>
       </c>
@@ -38992,7 +40716,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:23" ht="30">
+    <row r="374" spans="1:23" ht="30" hidden="1">
       <c r="A374" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39063,7 +40787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="30">
+    <row r="375" spans="1:23" ht="30" hidden="1">
       <c r="A375" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39134,7 +40858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="30">
+    <row r="376" spans="1:23" ht="30" hidden="1">
       <c r="A376" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39205,7 +40929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:23" ht="30">
+    <row r="377" spans="1:23" ht="30" hidden="1">
       <c r="A377" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39276,7 +41000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:23" ht="30">
+    <row r="378" spans="1:23" ht="30" hidden="1">
       <c r="A378" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39347,7 +41071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:23" ht="30">
+    <row r="379" spans="1:23" ht="30" hidden="1">
       <c r="A379" s="4" t="s">
         <v>2062</v>
       </c>
@@ -39418,7 +41142,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:23">
+    <row r="380" spans="1:23" hidden="1">
       <c r="A380" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39489,7 +41213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="30">
+    <row r="381" spans="1:23" ht="30" hidden="1">
       <c r="A381" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39560,7 +41284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:23" ht="30">
+    <row r="382" spans="1:23" ht="30" hidden="1">
       <c r="A382" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39631,7 +41355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="45">
+    <row r="383" spans="1:23" ht="45" hidden="1">
       <c r="A383" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39699,7 +41423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:23" ht="30">
+    <row r="384" spans="1:23" ht="30" hidden="1">
       <c r="A384" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39767,7 +41491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:23" ht="45">
+    <row r="385" spans="1:23" ht="45" hidden="1">
       <c r="A385" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39838,7 +41562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="30">
+    <row r="386" spans="1:23" ht="30" hidden="1">
       <c r="A386" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39909,7 +41633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:23" ht="30">
+    <row r="387" spans="1:23" ht="30" hidden="1">
       <c r="A387" s="4" t="s">
         <v>2110</v>
       </c>
@@ -39977,7 +41701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:23" ht="30">
+    <row r="388" spans="1:23" ht="30" hidden="1">
       <c r="A388" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40045,7 +41769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="30">
+    <row r="389" spans="1:23" ht="30" hidden="1">
       <c r="A389" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40113,7 +41837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:23" ht="30">
+    <row r="390" spans="1:23" ht="30" hidden="1">
       <c r="A390" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40184,7 +41908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:23" ht="30">
+    <row r="391" spans="1:23" ht="30" hidden="1">
       <c r="A391" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40255,7 +41979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:23" ht="30">
+    <row r="392" spans="1:23" ht="30" hidden="1">
       <c r="A392" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40326,7 +42050,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="30">
+    <row r="393" spans="1:23" ht="30" hidden="1">
       <c r="A393" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40397,7 +42121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:23" ht="30">
+    <row r="394" spans="1:23" ht="30" hidden="1">
       <c r="A394" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40468,7 +42192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:23" ht="30">
+    <row r="395" spans="1:23" ht="30" hidden="1">
       <c r="A395" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40539,7 +42263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:23" ht="30">
+    <row r="396" spans="1:23" ht="30" hidden="1">
       <c r="A396" s="4" t="s">
         <v>2110</v>
       </c>
@@ -40610,7 +42334,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:23" ht="45">
+    <row r="397" spans="1:23" ht="45" hidden="1">
       <c r="A397" s="3" t="s">
         <v>2399</v>
       </c>
@@ -40681,7 +42405,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="398" spans="1:23" ht="30">
+    <row r="398" spans="1:23" ht="30" hidden="1">
       <c r="A398" s="3" t="s">
         <v>2399</v>
       </c>
@@ -40752,7 +42476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="399" spans="1:23" ht="45">
+    <row r="399" spans="1:23" ht="45" hidden="1">
       <c r="A399" s="3" t="s">
         <v>2399</v>
       </c>
@@ -40823,7 +42547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="400" spans="1:23" ht="30">
+    <row r="400" spans="1:23" ht="30" hidden="1">
       <c r="A400" s="3" t="s">
         <v>2399</v>
       </c>
@@ -40894,7 +42618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="401" spans="1:23" ht="45">
+    <row r="401" spans="1:23" ht="45" hidden="1">
       <c r="A401" s="3" t="s">
         <v>2399</v>
       </c>
@@ -40965,7 +42689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:23" ht="45">
+    <row r="402" spans="1:23" ht="45" hidden="1">
       <c r="A402" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41036,7 +42760,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="403" spans="1:23" ht="45">
+    <row r="403" spans="1:23" ht="45" hidden="1">
       <c r="A403" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41107,7 +42831,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="404" spans="1:23" ht="30">
+    <row r="404" spans="1:23" ht="30" hidden="1">
       <c r="A404" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41178,7 +42902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="405" spans="1:23" ht="30">
+    <row r="405" spans="1:23" ht="30" hidden="1">
       <c r="A405" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41249,7 +42973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="406" spans="1:23" ht="30">
+    <row r="406" spans="1:23" ht="30" hidden="1">
       <c r="A406" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41320,7 +43044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="407" spans="1:23" ht="30">
+    <row r="407" spans="1:23" ht="30" hidden="1">
       <c r="A407" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41391,7 +43115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="408" spans="1:23" ht="30">
+    <row r="408" spans="1:23" ht="30" hidden="1">
       <c r="A408" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41462,7 +43186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:23" ht="30">
+    <row r="409" spans="1:23" ht="30" hidden="1">
       <c r="A409" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41533,7 +43257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="410" spans="1:23" ht="30">
+    <row r="410" spans="1:23" ht="30" hidden="1">
       <c r="A410" s="3" t="s">
         <v>2399</v>
       </c>
@@ -41605,7 +43329,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W396" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}"/>
+  <autoFilter ref="A1:W410" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Organization"/>
+        <filter val="Organization Details"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="Q9" r:id="rId1" display="mailto:admin@memgine.com" xr:uid="{93170BB8-77D4-4002-829B-D89928109808}"/>
     <hyperlink ref="Q11" r:id="rId2" display="https://memgine.com/" xr:uid="{F8EB4105-6CCB-4B06-B657-948DB365F556}"/>
@@ -41618,6 +43349,232 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F1139C-59DB-4F0D-B7DD-DF0185DF3E48}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="45">
+      <c r="A1" s="2" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30">
+      <c r="A2" s="3" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30">
+      <c r="A3" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30">
+      <c r="A4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75">
+      <c r="A5" s="3" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="75">
+      <c r="A7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30">
+      <c r="A8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30">
+      <c r="A10" s="3" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30">
+      <c r="A11" s="3" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2474</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>2474</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30">
+      <c r="A15" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>2474</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB69E303-A7E6-4340-BB09-24AE7640CD38}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -41780,7 +43737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB6A490-4722-4D86-89A3-00192739A23A}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -41939,7 +43896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FF8F3C-B975-44A1-AEC1-A0B924B73AFA}">
   <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -44259,7 +46216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC977184-2C78-4F4B-925B-1B78E6658C38}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -44671,7 +46628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA9DE7E5-F033-4EE0-B5C6-8E739555A5CA}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -44740,7 +46697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7B29B1-81FD-48F8-9727-C5470F35164D}">
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -45105,1687 +47062,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCF67D5-27CE-4C3A-997A-96A77E128378}">
-  <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="24.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20" style="4" customWidth="1"/>
-    <col min="6" max="6" width="21" style="4" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2275</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2276</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" s="5">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
-        <v>2278</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2279</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="5">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>2280</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="5">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45">
-      <c r="A5" s="13" t="s">
-        <v>2281</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>2282</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30">
-      <c r="A6" s="13" t="s">
-        <v>1480</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>2284</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>2285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>902</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="E8" s="5">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30">
-      <c r="A9" s="13" t="s">
-        <v>757</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>2258</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="30">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="E11" s="5">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="30">
-      <c r="A12" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>928</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>930</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>932</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="E14" s="5">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="E15" s="5">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>959</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>960</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3" t="s">
-        <v>961</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
-        <v>964</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="E18" s="5">
-        <v>3</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="30">
-      <c r="A19" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>969</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="E20" s="5">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="30">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3" t="s">
-        <v>971</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>973</v>
-      </c>
-      <c r="E21" s="5">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>976</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3" t="s">
-        <v>977</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="E23" s="5">
-        <v>2</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="E24" s="5">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="E25" s="5">
-        <v>4</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="30">
-      <c r="A26" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" ht="30">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>990</v>
-      </c>
-      <c r="E27" s="5">
-        <v>2</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="30">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>992</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="E28" s="5">
-        <v>3</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="30">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>994</v>
-      </c>
-      <c r="E29" s="5">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="E30" s="5">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="E31" s="5">
-        <v>2</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E32" s="5">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E33" s="5">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>2259</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>2259</v>
-      </c>
-      <c r="E34" s="5">
-        <v>5</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>2260</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E36" s="5">
-        <v>2</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E37" s="5">
-        <v>3</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E38" s="5">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>1270</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>1270</v>
-      </c>
-      <c r="E39" s="5">
-        <v>5</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E40" s="5">
-        <v>6</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>2261</v>
-      </c>
-      <c r="E41" s="5">
-        <v>7</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>1275</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>2262</v>
-      </c>
-      <c r="E42" s="5">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>1277</v>
-      </c>
-      <c r="E43" s="5">
-        <v>9</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="E44" s="5">
-        <v>10</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>2263</v>
-      </c>
-      <c r="E45" s="5">
-        <v>11</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E46" s="5">
-        <v>12</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>1283</v>
-      </c>
-      <c r="E47" s="5">
-        <v>13</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E48" s="5">
-        <v>14</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>1287</v>
-      </c>
-      <c r="E49" s="5">
-        <v>15</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>2264</v>
-      </c>
-      <c r="E50" s="5">
-        <v>16</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>2265</v>
-      </c>
-      <c r="E51" s="5">
-        <v>17</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>2266</v>
-      </c>
-      <c r="E52" s="5">
-        <v>18</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" ht="30">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>2267</v>
-      </c>
-      <c r="E53" s="5">
-        <v>19</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" ht="45">
-      <c r="A54" s="13" t="s">
-        <v>1704</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>2268</v>
-      </c>
-      <c r="E54" s="5">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="30">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3" t="s">
-        <v>1709</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>2269</v>
-      </c>
-      <c r="E55" s="5">
-        <v>2</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="30">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>2270</v>
-      </c>
-      <c r="E56" s="5">
-        <v>3</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="45">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>2271</v>
-      </c>
-      <c r="E57" s="5">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="30">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3" t="s">
-        <v>1768</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>1769</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>2286</v>
-      </c>
-      <c r="E58" s="5">
-        <v>5</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="30">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3" t="s">
-        <v>961</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>2287</v>
-      </c>
-      <c r="E59" s="5">
-        <v>6</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="30">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3" t="s">
-        <v>1772</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>2288</v>
-      </c>
-      <c r="E60" s="5">
-        <v>7</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="30">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3" t="s">
-        <v>1775</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>2289</v>
-      </c>
-      <c r="E61" s="5">
-        <v>8</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="30">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>1779</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>2290</v>
-      </c>
-      <c r="E62" s="5">
-        <v>9</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="30">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3" t="s">
-        <v>1781</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>1782</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>2272</v>
-      </c>
-      <c r="E63" s="5">
-        <v>10</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="30">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>2291</v>
-      </c>
-      <c r="E64" s="5">
-        <v>11</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="30">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>1788</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>2292</v>
-      </c>
-      <c r="E65" s="5">
-        <v>12</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="30">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3" t="s">
-        <v>1790</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>1791</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>2273</v>
-      </c>
-      <c r="E66" s="5">
-        <v>13</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="30">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3" t="s">
-        <v>1793</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>1794</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>2293</v>
-      </c>
-      <c r="E67" s="5">
-        <v>14</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="30">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>1797</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>2294</v>
-      </c>
-      <c r="E68" s="5">
-        <v>15</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="30">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3" t="s">
-        <v>1799</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>1800</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>2295</v>
-      </c>
-      <c r="E69" s="5">
-        <v>16</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="30">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3" t="s">
-        <v>1802</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>1803</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>2296</v>
-      </c>
-      <c r="E70" s="5">
-        <v>17</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="30">
-      <c r="A71" s="13" t="s">
-        <v>1546</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>2297</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>2274</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8006DC-09FC-43CC-91DF-5BF59D768099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A0013F-1C4F-4BB1-AE68-0CE70620AE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -15023,7 +15023,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="30">
+    <row r="2" spans="1:23" ht="30" hidden="1">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -15089,7 +15089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30">
+    <row r="3" spans="1:23" ht="30" hidden="1">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30">
+    <row r="4" spans="1:23" ht="30" hidden="1">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -15225,7 +15225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="60">
+    <row r="5" spans="1:23" ht="60" hidden="1">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30">
+    <row r="6" spans="1:23" ht="30" hidden="1">
       <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
@@ -15362,7 +15362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -15430,7 +15430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" hidden="1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -15498,7 +15498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -15566,7 +15566,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30">
+    <row r="12" spans="1:23" ht="30" hidden="1">
       <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
@@ -15770,7 +15770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" hidden="1">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -15838,7 +15838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="30">
+    <row r="14" spans="1:23" ht="30" hidden="1">
       <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="30">
+    <row r="16" spans="1:23" ht="30" hidden="1">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" hidden="1">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -31808,7 +31808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="30">
+    <row r="244" spans="1:23" ht="30" hidden="1">
       <c r="A244" s="3" t="s">
         <v>1517</v>
       </c>
@@ -31875,7 +31875,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="30">
+    <row r="245" spans="1:23" ht="30" hidden="1">
       <c r="A245" s="3" t="s">
         <v>1517</v>
       </c>
@@ -31942,7 +31942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="30">
+    <row r="246" spans="1:23" ht="30" hidden="1">
       <c r="A246" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32011,7 +32011,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="247" spans="1:23" ht="30">
+    <row r="247" spans="1:23" ht="30" hidden="1">
       <c r="A247" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32080,7 +32080,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="248" spans="1:23">
+    <row r="248" spans="1:23" hidden="1">
       <c r="A248" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32149,7 +32149,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="30">
+    <row r="249" spans="1:23" ht="30" hidden="1">
       <c r="A249" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32218,7 +32218,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="250" spans="1:23">
+    <row r="250" spans="1:23" hidden="1">
       <c r="A250" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32287,7 +32287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:23">
+    <row r="251" spans="1:23" hidden="1">
       <c r="A251" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32356,7 +32356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:23">
+    <row r="252" spans="1:23" hidden="1">
       <c r="A252" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32425,7 +32425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:23">
+    <row r="253" spans="1:23" hidden="1">
       <c r="A253" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32494,7 +32494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:23">
+    <row r="254" spans="1:23" hidden="1">
       <c r="A254" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32563,7 +32563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:23">
+    <row r="255" spans="1:23" hidden="1">
       <c r="A255" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32632,7 +32632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="30">
+    <row r="256" spans="1:23" ht="30" hidden="1">
       <c r="A256" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32701,7 +32701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:23" ht="30">
+    <row r="257" spans="1:23" ht="30" hidden="1">
       <c r="A257" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32770,7 +32770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" hidden="1">
       <c r="A258" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32837,7 +32837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:23">
+    <row r="259" spans="1:23" hidden="1">
       <c r="A259" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32904,7 +32904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:23">
+    <row r="260" spans="1:23" hidden="1">
       <c r="A260" s="3" t="s">
         <v>1517</v>
       </c>
@@ -32971,7 +32971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:23">
+    <row r="261" spans="1:23" hidden="1">
       <c r="A261" s="3" t="s">
         <v>1517</v>
       </c>
@@ -33040,7 +33040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:23">
+    <row r="262" spans="1:23" hidden="1">
       <c r="A262" s="3" t="s">
         <v>1517</v>
       </c>
@@ -33109,7 +33109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30" hidden="1">
+    <row r="263" spans="1:23" ht="30">
       <c r="A263" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33176,7 +33176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="30" hidden="1">
+    <row r="264" spans="1:23" ht="30">
       <c r="A264" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33243,7 +33243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30" hidden="1">
+    <row r="265" spans="1:23" ht="30">
       <c r="A265" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33314,7 +33314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:23" hidden="1">
+    <row r="266" spans="1:23">
       <c r="A266" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33381,7 +33381,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="30" hidden="1">
+    <row r="267" spans="1:23" ht="30">
       <c r="A267" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33450,7 +33450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23" hidden="1">
+    <row r="268" spans="1:23">
       <c r="A268" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33519,7 +33519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23" hidden="1">
+    <row r="269" spans="1:23">
       <c r="A269" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33588,7 +33588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="30" hidden="1">
+    <row r="270" spans="1:23" ht="30">
       <c r="A270" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33655,7 +33655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="30" hidden="1">
+    <row r="271" spans="1:23" ht="30">
       <c r="A271" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33722,7 +33722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23" hidden="1">
+    <row r="272" spans="1:23">
       <c r="A272" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33787,7 +33787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23" hidden="1">
+    <row r="273" spans="1:23">
       <c r="A273" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33852,7 +33852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23" hidden="1">
+    <row r="274" spans="1:23">
       <c r="A274" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33917,7 +33917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23" hidden="1">
+    <row r="275" spans="1:23">
       <c r="A275" s="3" t="s">
         <v>1518</v>
       </c>
@@ -33986,7 +33986,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23" hidden="1">
+    <row r="276" spans="1:23">
       <c r="A276" s="3" t="s">
         <v>1518</v>
       </c>
@@ -43332,8 +43332,7 @@
   <autoFilter ref="A1:W410" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Organization"/>
-        <filter val="Organization Details"/>
+        <filter val="Organization Branding"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -43359,7 +43358,7 @@
     <col min="4" max="4" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="45">
+    <row r="1" spans="1:4" ht="30">
       <c r="A1" s="2" t="s">
         <v>2463</v>
       </c>
@@ -43373,7 +43372,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>2466</v>
       </c>
@@ -43387,7 +43386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>195</v>
       </c>
@@ -43401,7 +43400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>88</v>
       </c>
@@ -43415,7 +43414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="75">
+    <row r="5" spans="1:4" ht="30">
       <c r="A5" s="3" t="s">
         <v>2467</v>
       </c>
@@ -43429,7 +43428,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -43443,7 +43442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="75">
+    <row r="7" spans="1:4" ht="30">
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
@@ -43457,7 +43456,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>112</v>
       </c>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D40B066-C1C8-41D3-8BB0-AC1B2BFCB954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC82217B-53E9-40B5-B787-178C7AA3B44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="11" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11467" uniqueCount="2552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11807" uniqueCount="2624">
   <si>
     <t>Domain</t>
   </si>
@@ -7510,18 +7510,6 @@
     <t>product</t>
   </si>
   <si>
-    <t>Identify the product or service associated with the benefit.</t>
-  </si>
-  <si>
-    <t>Product or service that the benefit provides, discounts or otherwise relates to.</t>
-  </si>
-  <si>
-    <t>Represents the business product or service associated with the benefit.</t>
-  </si>
-  <si>
-    <t>Cappuccino</t>
-  </si>
-  <si>
     <t>Retail Price</t>
   </si>
   <si>
@@ -7697,6 +7685,234 @@
   </si>
   <si>
     <t>Unable to calculate upgraded subscription period.</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>Commerce</t>
+  </si>
+  <si>
+    <t>Product Management</t>
+  </si>
+  <si>
+    <t>Represents an organization-owned catalogue item or service that can be associated with Memgine Benefits.</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>Lightweight product catalogue used by Memgine for benefit association. Product does not represent inventory or stock management. Products may be maintained manually or populated from an external POS, menu, inventory or other business system in the future.</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Uniquely identify a Product.</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the Product.</t>
+  </si>
+  <si>
+    <t>Primary identifier for an organization-owned Product record.</t>
+  </si>
+  <si>
+    <t>PROD-1001</t>
+  </si>
+  <si>
+    <t>Identify the Organization that owns the Product.</t>
+  </si>
+  <si>
+    <t>References the Organization that owns and manages the Product.</t>
+  </si>
+  <si>
+    <t>Establishes tenant ownership and isolation of the Product.</t>
+  </si>
+  <si>
+    <t>Product Code</t>
+  </si>
+  <si>
+    <t>product_code</t>
+  </si>
+  <si>
+    <t>Provide a unique business identifier for the Product.</t>
+  </si>
+  <si>
+    <t>Business-defined code used to identify the Product.</t>
+  </si>
+  <si>
+    <t>Represents the organization's internal or external product/SKU code.</t>
+  </si>
+  <si>
+    <t>FC001</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>Identify the Product for business and customer-facing use.</t>
+  </si>
+  <si>
+    <t>Human-readable name of the Product or service.</t>
+  </si>
+  <si>
+    <t>Primary display name of the Product.</t>
+  </si>
+  <si>
+    <t>Filter Coffee</t>
+  </si>
+  <si>
+    <t>Describe the Product or service.</t>
+  </si>
+  <si>
+    <t>Additional business description of the Product.</t>
+  </si>
+  <si>
+    <t>Provides optional contextual information about the Product.</t>
+  </si>
+  <si>
+    <t>Hot brewed filter coffee</t>
+  </si>
+  <si>
+    <t>Control whether the Product is available for association with Benefits.</t>
+  </si>
+  <si>
+    <t>References the lifecycle status of the Product.</t>
+  </si>
+  <si>
+    <t>Determines whether the Product is active and available for business use.</t>
+  </si>
+  <si>
+    <t>Record Product creation time.</t>
+  </si>
+  <si>
+    <t>System-generated creation timestamp.</t>
+  </si>
+  <si>
+    <t>Audit timestamp recording when the Product was created.</t>
+  </si>
+  <si>
+    <t>2026-08-31T10:00:00</t>
+  </si>
+  <si>
+    <t>Identify who created the Product.</t>
+  </si>
+  <si>
+    <t>References the User who created the Product.</t>
+  </si>
+  <si>
+    <t>Audit reference identifying the creator of the Product.</t>
+  </si>
+  <si>
+    <t>Record the last Product modification time.</t>
+  </si>
+  <si>
+    <t>System-generated update timestamp.</t>
+  </si>
+  <si>
+    <t>Audit timestamp recording the latest Product modification.</t>
+  </si>
+  <si>
+    <t>Identify who last modified the Product.</t>
+  </si>
+  <si>
+    <t>References the User who last modified the Product.</t>
+  </si>
+  <si>
+    <t>Audit reference identifying the latest modifier.</t>
+  </si>
+  <si>
+    <t>Support logical deletion of Products.</t>
+  </si>
+  <si>
+    <t>Indicates whether the Product has been logically deleted.</t>
+  </si>
+  <si>
+    <t>Soft-delete flag; deleted Products are not available for new Benefit associations.</t>
+  </si>
+  <si>
+    <t>Support optimistic concurrency for Product updates.</t>
+  </si>
+  <si>
+    <t>System-managed version number.</t>
+  </si>
+  <si>
+    <t>Used to detect conflicting updates to the same Product.</t>
+  </si>
+  <si>
+    <t>Associate the Benefit with an organization Product.</t>
+  </si>
+  <si>
+    <t>References the Product or service associated with the Benefit.</t>
+  </si>
+  <si>
+    <t>Identifies the Product to which the Benefit applies.</t>
+  </si>
+  <si>
+    <t>Organization owns Product</t>
+  </si>
+  <si>
+    <t>Each Product belongs to exactly one Organization.</t>
+  </si>
+  <si>
+    <t>Product associated with Benefit</t>
+  </si>
+  <si>
+    <t>A Product may be associated with zero or more Benefits, while a Benefit may optionally reference one Product.</t>
+  </si>
+  <si>
+    <t>REL063</t>
+  </si>
+  <si>
+    <t>REL064</t>
+  </si>
+  <si>
+    <t>Must be unique within the Organization.</t>
+  </si>
+  <si>
+    <t>Duplicate Product Code within the Organization.</t>
+  </si>
+  <si>
+    <t>Product Code may correspond to an organization's internal SKU or an external product code.</t>
+  </si>
+  <si>
+    <t>VAL049</t>
+  </si>
+  <si>
+    <t>Organization must exist.</t>
+  </si>
+  <si>
+    <t>VAL050</t>
+  </si>
+  <si>
+    <t>Status must exist in Status reference data.</t>
+  </si>
+  <si>
+    <t>Invalid Product Status.</t>
+  </si>
+  <si>
+    <t>VAL051</t>
+  </si>
+  <si>
+    <t>If Product is specified, it must exist.</t>
+  </si>
+  <si>
+    <t>Invalid Product.</t>
+  </si>
+  <si>
+    <t>VAL052</t>
+  </si>
+  <si>
+    <t>If Product is specified, it must belong to the same Organization as the Benefit.</t>
+  </si>
+  <si>
+    <t>Product must belong to the Benefit's Organization.</t>
+  </si>
+  <si>
+    <t>VAL053</t>
+  </si>
+  <si>
+    <t>VAL054</t>
   </si>
 </sst>
 </file>
@@ -7925,7 +8141,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q38" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q39" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -8246,7 +8462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -10272,6 +10488,59 @@
       </c>
       <c r="Q38" s="4" t="s">
         <v>2404</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="105">
+      <c r="A39" s="4" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>2553</v>
       </c>
     </row>
   </sheetData>
@@ -11967,7 +12236,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -14189,6 +14458,76 @@
         <v>2185</v>
       </c>
     </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="4" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>2602</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="30">
+      <c r="A65" s="4" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>2605</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K63" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}"/>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -14199,7 +14538,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -15149,22 +15488,22 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="3" t="s">
-        <v>2503</v>
+        <v>2499</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>2504</v>
+        <v>2500</v>
       </c>
       <c r="D37" t="s">
         <v>2188</v>
       </c>
       <c r="E37" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
       <c r="F37" t="s">
-        <v>2506</v>
+        <v>2502</v>
       </c>
       <c r="G37" t="s">
         <v>1392</v>
@@ -15173,27 +15512,27 @@
         <v>1393</v>
       </c>
       <c r="I37" t="s">
-        <v>2507</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="3" t="s">
-        <v>2508</v>
+        <v>2504</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="D38" t="s">
         <v>1405</v>
       </c>
       <c r="E38" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
       <c r="F38" t="s">
-        <v>2511</v>
+        <v>2507</v>
       </c>
       <c r="G38" t="s">
         <v>1392</v>
@@ -15202,27 +15541,27 @@
         <v>1393</v>
       </c>
       <c r="I38" t="s">
-        <v>2512</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="3" t="s">
-        <v>2513</v>
+        <v>2509</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="D39" t="s">
         <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>2514</v>
+        <v>2510</v>
       </c>
       <c r="F39" t="s">
-        <v>2515</v>
+        <v>2511</v>
       </c>
       <c r="G39" t="s">
         <v>1392</v>
@@ -15231,27 +15570,27 @@
         <v>1393</v>
       </c>
       <c r="I39" t="s">
-        <v>2516</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="3" t="s">
-        <v>2517</v>
+        <v>2513</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>2518</v>
+        <v>2514</v>
       </c>
       <c r="D40" t="s">
         <v>2188</v>
       </c>
       <c r="E40" t="s">
-        <v>2519</v>
+        <v>2515</v>
       </c>
       <c r="F40" t="s">
-        <v>2520</v>
+        <v>2516</v>
       </c>
       <c r="G40" t="s">
         <v>1392</v>
@@ -15260,27 +15599,27 @@
         <v>1393</v>
       </c>
       <c r="I40" t="s">
-        <v>2521</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="3" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
       <c r="B41" t="s">
         <v>490</v>
       </c>
       <c r="C41" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="D41" t="s">
         <v>1405</v>
       </c>
       <c r="E41" t="s">
-        <v>2523</v>
+        <v>2519</v>
       </c>
       <c r="F41" t="s">
-        <v>2524</v>
+        <v>2520</v>
       </c>
       <c r="G41" t="s">
         <v>1392</v>
@@ -15291,22 +15630,22 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="3" t="s">
-        <v>2525</v>
+        <v>2521</v>
       </c>
       <c r="B42" t="s">
         <v>490</v>
       </c>
       <c r="C42" t="s">
-        <v>2498</v>
+        <v>2494</v>
       </c>
       <c r="D42" t="s">
         <v>1405</v>
       </c>
       <c r="E42" t="s">
-        <v>2526</v>
+        <v>2522</v>
       </c>
       <c r="F42" t="s">
-        <v>2527</v>
+        <v>2523</v>
       </c>
       <c r="G42" t="s">
         <v>1392</v>
@@ -15317,140 +15656,140 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="3" t="s">
-        <v>2528</v>
+        <v>2524</v>
       </c>
       <c r="B43" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="C43" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="D43" t="s">
         <v>2188</v>
       </c>
       <c r="E43" t="s">
-        <v>2536</v>
+        <v>2532</v>
       </c>
       <c r="F43" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="G43" t="s">
         <v>1392</v>
       </c>
       <c r="H43" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="3" t="s">
-        <v>2529</v>
+        <v>2525</v>
       </c>
       <c r="B44" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="C44" t="s">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="D44" t="s">
         <v>2188</v>
       </c>
       <c r="E44" t="s">
-        <v>2539</v>
+        <v>2535</v>
       </c>
       <c r="F44" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="G44" t="s">
         <v>1392</v>
       </c>
       <c r="H44" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="3" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B45" t="s">
         <v>2530</v>
       </c>
-      <c r="B45" t="s">
-        <v>2534</v>
-      </c>
       <c r="C45" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="D45" t="s">
         <v>175</v>
       </c>
       <c r="E45" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="F45" t="s">
-        <v>2543</v>
+        <v>2539</v>
       </c>
       <c r="G45" t="s">
         <v>1392</v>
       </c>
       <c r="H45" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="3" t="s">
-        <v>2531</v>
+        <v>2527</v>
       </c>
       <c r="B46" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="C46" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="D46" t="s">
         <v>175</v>
       </c>
       <c r="E46" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="F46" t="s">
-        <v>2546</v>
+        <v>2542</v>
       </c>
       <c r="G46" t="s">
         <v>1392</v>
       </c>
       <c r="H46" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="3" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="B47" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="C47" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="D47" t="s">
         <v>2188</v>
       </c>
       <c r="E47" t="s">
-        <v>2548</v>
+        <v>2544</v>
       </c>
       <c r="F47" t="s">
-        <v>2549</v>
+        <v>2545</v>
       </c>
       <c r="G47" t="s">
         <v>1392</v>
       </c>
       <c r="H47" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="3" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B48" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="C48" t="s">
         <v>576</v>
@@ -15459,16 +15798,175 @@
         <v>2188</v>
       </c>
       <c r="E48" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="F48" t="s">
-        <v>2551</v>
+        <v>2547</v>
       </c>
       <c r="G48" t="s">
         <v>1392</v>
       </c>
       <c r="H48" t="s">
-        <v>2538</v>
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="3" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F49" t="s">
+        <v>2609</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1393</v>
+      </c>
+      <c r="I49" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="3" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>175</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H51" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="3" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C52" t="s">
+        <v>42</v>
+      </c>
+      <c r="D52" t="s">
+        <v>175</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F52" t="s">
+        <v>2615</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="3" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B53" t="s">
+        <v>490</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F53" t="s">
+        <v>2618</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="3" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B54" t="s">
+        <v>490</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2620</v>
+      </c>
+      <c r="F54" t="s">
+        <v>2621</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1393</v>
       </c>
     </row>
   </sheetData>
@@ -15480,7 +15978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W427"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -22002,7 +22500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30">
+    <row r="96" spans="1:23">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -22013,13 +22511,13 @@
         <v>2476</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2488</v>
+        <v>2552</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F96" s="5">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>6</v>
@@ -22031,10 +22529,10 @@
         <v>6</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>269</v>
+        <v>2476</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>6</v>
@@ -22043,19 +22541,19 @@
         <v>6</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>2489</v>
+        <v>2599</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>2490</v>
+        <v>2600</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>2491</v>
+        <v>2601</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>2492</v>
+        <v>2558</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>269</v>
+        <v>72</v>
       </c>
       <c r="S96" s="1" t="s">
         <v>7</v>
@@ -22070,7 +22568,7 @@
         <v>7</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:23" ht="45">
@@ -22081,10 +22579,10 @@
         <v>10</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>2494</v>
+        <v>2490</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>173</v>
@@ -22114,13 +22612,13 @@
         <v>6</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>2495</v>
+        <v>2491</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>2496</v>
+        <v>2492</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="Q97" s="3">
         <v>5.5</v>
@@ -22152,10 +22650,10 @@
         <v>11</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>2498</v>
+        <v>2494</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2499</v>
+        <v>2495</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>173</v>
@@ -22185,13 +22683,13 @@
         <v>6</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>2500</v>
+        <v>2496</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>2501</v>
+        <v>2497</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>2502</v>
+        <v>2498</v>
       </c>
       <c r="Q98" s="3">
         <v>1.8</v>
@@ -44237,6 +44735,858 @@
       </c>
       <c r="W415" s="3" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="416" spans="1:23">
+      <c r="A416" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B416" s="4">
+        <v>1</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E416" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F416" s="4">
+        <v>36</v>
+      </c>
+      <c r="G416" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H416" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I416" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J416" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K416" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L416" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M416" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N416" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="O416" s="4" t="s">
+        <v>2556</v>
+      </c>
+      <c r="P416" s="4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="Q416" s="4" t="s">
+        <v>2558</v>
+      </c>
+      <c r="R416" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S416" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T416" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U416" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V416" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W416" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="417" spans="1:23">
+      <c r="A417" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B417" s="4">
+        <v>2</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E417" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F417" s="4">
+        <v>36</v>
+      </c>
+      <c r="G417" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H417" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I417" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J417" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K417" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L417" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M417" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N417" s="4" t="s">
+        <v>2559</v>
+      </c>
+      <c r="O417" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="P417" s="4" t="s">
+        <v>2561</v>
+      </c>
+      <c r="Q417" s="4" t="s">
+        <v>2125</v>
+      </c>
+      <c r="R417" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S417" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T417" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U417" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V417" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W417" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="418" spans="1:23">
+      <c r="A418" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B418" s="4">
+        <v>3</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E418" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F418" s="4">
+        <v>50</v>
+      </c>
+      <c r="G418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H418" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I418" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J418" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K418" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M418" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N418" s="4" t="s">
+        <v>2564</v>
+      </c>
+      <c r="O418" s="4" t="s">
+        <v>2565</v>
+      </c>
+      <c r="P418" s="4" t="s">
+        <v>2566</v>
+      </c>
+      <c r="Q418" s="4" t="s">
+        <v>2567</v>
+      </c>
+      <c r="R418" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W418" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="419" spans="1:23">
+      <c r="A419" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B419" s="4">
+        <v>4</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E419" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F419" s="4">
+        <v>150</v>
+      </c>
+      <c r="G419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K419" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M419" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N419" s="4" t="s">
+        <v>2569</v>
+      </c>
+      <c r="O419" s="4" t="s">
+        <v>2570</v>
+      </c>
+      <c r="P419" s="4" t="s">
+        <v>2571</v>
+      </c>
+      <c r="Q419" s="4" t="s">
+        <v>2572</v>
+      </c>
+      <c r="R419" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W419" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="420" spans="1:23">
+      <c r="A420" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B420" s="4">
+        <v>5</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E420" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F420" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H420" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K420" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M420" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N420" s="4" t="s">
+        <v>2573</v>
+      </c>
+      <c r="O420" s="4" t="s">
+        <v>2574</v>
+      </c>
+      <c r="P420" s="4" t="s">
+        <v>2575</v>
+      </c>
+      <c r="Q420" s="4" t="s">
+        <v>2576</v>
+      </c>
+      <c r="R420" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S420" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V420" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W420" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="421" spans="1:23">
+      <c r="A421" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B421" s="4">
+        <v>6</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E421" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F421" s="4">
+        <v>36</v>
+      </c>
+      <c r="G421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K421" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M421" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N421" s="4" t="s">
+        <v>2577</v>
+      </c>
+      <c r="O421" s="4" t="s">
+        <v>2578</v>
+      </c>
+      <c r="P421" s="4" t="s">
+        <v>2579</v>
+      </c>
+      <c r="Q421" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="R421" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W421" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="422" spans="1:23">
+      <c r="A422" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B422" s="4">
+        <v>7</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E422" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K422" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M422" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N422" s="4" t="s">
+        <v>2580</v>
+      </c>
+      <c r="O422" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="P422" s="4" t="s">
+        <v>2582</v>
+      </c>
+      <c r="Q422" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="R422" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="S422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U422" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W422" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="423" spans="1:23">
+      <c r="A423" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B423" s="4">
+        <v>8</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F423" s="4">
+        <v>36</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J423" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K423" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M423" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N423" s="4" t="s">
+        <v>2584</v>
+      </c>
+      <c r="O423" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="P423" s="4" t="s">
+        <v>2586</v>
+      </c>
+      <c r="Q423" s="4" t="s">
+        <v>2031</v>
+      </c>
+      <c r="R423" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T423" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W423" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="424" spans="1:23">
+      <c r="A424" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B424" s="4">
+        <v>9</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E424" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G424" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K424" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M424" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N424" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="O424" s="4" t="s">
+        <v>2588</v>
+      </c>
+      <c r="P424" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="Q424" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="R424" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="S424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U424" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W424" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="425" spans="1:23">
+      <c r="A425" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B425" s="4">
+        <v>10</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E425" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F425" s="4">
+        <v>36</v>
+      </c>
+      <c r="G425" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H425" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I425" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J425" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K425" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L425" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M425" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N425" s="4" t="s">
+        <v>2590</v>
+      </c>
+      <c r="O425" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="P425" s="4" t="s">
+        <v>2592</v>
+      </c>
+      <c r="Q425" s="4" t="s">
+        <v>2031</v>
+      </c>
+      <c r="R425" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S425" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T425" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U425" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V425" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W425" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="426" spans="1:23">
+      <c r="A426" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B426" s="4">
+        <v>11</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E426" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F426" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G426" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K426" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M426" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N426" s="4" t="s">
+        <v>2593</v>
+      </c>
+      <c r="O426" s="4" t="s">
+        <v>2594</v>
+      </c>
+      <c r="P426" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="Q426" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R426" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T426" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V426" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W426" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="427" spans="1:23">
+      <c r="A427" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B427" s="4">
+        <v>12</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E427" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F427" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G427" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K427" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M427" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N427" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="O427" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="P427" s="4" t="s">
+        <v>2598</v>
+      </c>
+      <c r="Q427" s="4">
+        <v>1</v>
+      </c>
+      <c r="R427" s="4">
+        <v>1</v>
+      </c>
+      <c r="S427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U427" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V427" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W427" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C5276E-8617-4EB0-8674-509D980D0BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5918DCBF-6558-4BBE-9C7F-EE824680324A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0AE8E6-1572-4E24-B2C8-D51913AE8AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAD9F30-F3EB-4E5D-BF24-1D07780EB6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -11872,7 +11872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11932,7 +11932,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -26966,13 +26965,12 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="21" customWidth="1"/>
-    <col min="2" max="2" width="37.42578125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="55.28515625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="30" style="21" customWidth="1"/>
-    <col min="6" max="6" width="26" style="21" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="21"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="55.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -62811,7 +62809,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30">
+    <row r="83" spans="1:9">
       <c r="A83" s="3" t="s">
         <v>1703</v>
       </c>
@@ -62840,7 +62838,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="30">
+    <row r="84" spans="1:9">
       <c r="A84" s="3" t="s">
         <v>1703</v>
       </c>
@@ -62956,7 +62954,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="30">
+    <row r="88" spans="1:9">
       <c r="A88" s="3" t="s">
         <v>1703</v>
       </c>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF80174B-274F-463E-BD86-95924B7AC6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1DC0D6-60E0-458B-8148-9DBF91DAF8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -24722,7 +24722,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="30">
+    <row r="2" spans="1:23" ht="30" hidden="1">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -24788,7 +24788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30">
+    <row r="3" spans="1:23" ht="30" hidden="1">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -24856,7 +24856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30">
+    <row r="4" spans="1:23" ht="30" hidden="1">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -24924,7 +24924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="60">
+    <row r="5" spans="1:23" ht="60" hidden="1">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -24993,7 +24993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30">
+    <row r="6" spans="1:23" ht="30" hidden="1">
       <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
@@ -25061,7 +25061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -25129,7 +25129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" hidden="1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -25197,7 +25197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -25265,7 +25265,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -25333,7 +25333,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
@@ -25401,7 +25401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30">
+    <row r="12" spans="1:23" ht="30" hidden="1">
       <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
@@ -25469,7 +25469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" hidden="1">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -25537,7 +25537,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="30">
+    <row r="14" spans="1:23" ht="30" hidden="1">
       <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
@@ -25605,7 +25605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -25673,7 +25673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="30">
+    <row r="16" spans="1:23" ht="30" hidden="1">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -25741,7 +25741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" hidden="1">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -30577,7 +30577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30" hidden="1">
+    <row r="88" spans="1:23" ht="30">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -30648,7 +30648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30" hidden="1">
+    <row r="89" spans="1:23" ht="30">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -30719,7 +30719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="30" hidden="1">
+    <row r="90" spans="1:23" ht="30">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -30790,7 +30790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="30" hidden="1">
+    <row r="91" spans="1:23" ht="30">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -30861,7 +30861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23" hidden="1">
+    <row r="92" spans="1:23">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -30932,7 +30932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23" hidden="1">
+    <row r="93" spans="1:23">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -31003,7 +31003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="45" hidden="1">
+    <row r="94" spans="1:23" ht="45">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -31074,7 +31074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30" hidden="1">
+    <row r="95" spans="1:23" ht="30">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -31145,7 +31145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30" hidden="1">
+    <row r="96" spans="1:23" ht="30">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -31216,7 +31216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="45" hidden="1">
+    <row r="97" spans="1:23" ht="45">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -31287,7 +31287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30" hidden="1">
+    <row r="98" spans="1:23" ht="30">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -31358,7 +31358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30" hidden="1">
+    <row r="99" spans="1:23" ht="30">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -31429,7 +31429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30" hidden="1">
+    <row r="100" spans="1:23" ht="30">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -31500,7 +31500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30" hidden="1">
+    <row r="101" spans="1:23" ht="30">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -31571,7 +31571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30" hidden="1">
+    <row r="102" spans="1:23" ht="30">
       <c r="A102" s="4" t="s">
         <v>490</v>
       </c>
@@ -31642,7 +31642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30" hidden="1">
+    <row r="103" spans="1:23" ht="30">
       <c r="A103" s="4" t="s">
         <v>490</v>
       </c>
@@ -31713,7 +31713,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30" hidden="1">
+    <row r="104" spans="1:23" ht="30">
       <c r="A104" s="4" t="s">
         <v>490</v>
       </c>
@@ -31784,7 +31784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30" hidden="1">
+    <row r="105" spans="1:23" ht="30">
       <c r="A105" s="4" t="s">
         <v>490</v>
       </c>
@@ -31855,7 +31855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30" hidden="1">
+    <row r="106" spans="1:23" ht="30">
       <c r="A106" s="4" t="s">
         <v>490</v>
       </c>
@@ -42601,7 +42601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:23" ht="30">
+    <row r="260" spans="1:23" ht="30" hidden="1">
       <c r="A260" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42668,7 +42668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:23" ht="30">
+    <row r="261" spans="1:23" ht="30" hidden="1">
       <c r="A261" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42735,7 +42735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="30">
+    <row r="262" spans="1:23" ht="30" hidden="1">
       <c r="A262" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42804,7 +42804,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30">
+    <row r="263" spans="1:23" ht="30" hidden="1">
       <c r="A263" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42873,7 +42873,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="264" spans="1:23">
+    <row r="264" spans="1:23" hidden="1">
       <c r="A264" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42942,7 +42942,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30">
+    <row r="265" spans="1:23" ht="30" hidden="1">
       <c r="A265" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43011,7 +43011,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" hidden="1">
       <c r="A266" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43080,7 +43080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23">
+    <row r="267" spans="1:23" hidden="1">
       <c r="A267" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43149,7 +43149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" hidden="1">
       <c r="A268" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43218,7 +43218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" hidden="1">
       <c r="A269" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43287,7 +43287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23">
+    <row r="270" spans="1:23" hidden="1">
       <c r="A270" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43356,7 +43356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23">
+    <row r="271" spans="1:23" hidden="1">
       <c r="A271" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43425,7 +43425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="30">
+    <row r="272" spans="1:23" ht="30" hidden="1">
       <c r="A272" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43494,7 +43494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="30">
+    <row r="273" spans="1:23" ht="30" hidden="1">
       <c r="A273" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43563,7 +43563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" hidden="1">
       <c r="A274" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43630,7 +43630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" hidden="1">
       <c r="A275" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43697,7 +43697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" hidden="1">
       <c r="A276" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43764,7 +43764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:23">
+    <row r="277" spans="1:23" hidden="1">
       <c r="A277" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43833,7 +43833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:23">
+    <row r="278" spans="1:23" hidden="1">
       <c r="A278" s="3" t="s">
         <v>1514</v>
       </c>
@@ -56209,8 +56209,7 @@
   <autoFilter ref="A1:W456" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Organization"/>
-        <filter val="Organization Details"/>
+        <filter val="Benefit"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1DC0D6-60E0-458B-8148-9DBF91DAF8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89E67E2-721B-4B8A-9324-DEC75EC7BB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -29408,7 +29408,7 @@
         <v>7</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>432</v>
@@ -29435,7 +29435,7 @@
         <v>7</v>
       </c>
       <c r="V71" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W71" s="1" t="s">
         <v>6</v>
@@ -30577,7 +30577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30">
+    <row r="88" spans="1:23" ht="30" hidden="1">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -30648,7 +30648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30">
+    <row r="89" spans="1:23" ht="30" hidden="1">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -30719,7 +30719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="30">
+    <row r="90" spans="1:23" ht="30" hidden="1">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -30790,7 +30790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="30">
+    <row r="91" spans="1:23" ht="30" hidden="1">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -30861,7 +30861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:23" hidden="1">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -30932,7 +30932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:23" hidden="1">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -31003,7 +31003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="45">
+    <row r="94" spans="1:23" ht="45" hidden="1">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -31074,7 +31074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30">
+    <row r="95" spans="1:23" ht="30" hidden="1">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -31145,7 +31145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30">
+    <row r="96" spans="1:23" ht="30" hidden="1">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -31216,7 +31216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="45">
+    <row r="97" spans="1:23" ht="45" hidden="1">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -31287,7 +31287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30">
+    <row r="98" spans="1:23" ht="30" hidden="1">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -31358,7 +31358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30">
+    <row r="99" spans="1:23" ht="30" hidden="1">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -31429,7 +31429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30">
+    <row r="100" spans="1:23" ht="30" hidden="1">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -31500,7 +31500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30">
+    <row r="101" spans="1:23" ht="30" hidden="1">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -31571,7 +31571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30">
+    <row r="102" spans="1:23" ht="30" hidden="1">
       <c r="A102" s="4" t="s">
         <v>490</v>
       </c>
@@ -31642,7 +31642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30">
+    <row r="103" spans="1:23" ht="30" hidden="1">
       <c r="A103" s="4" t="s">
         <v>490</v>
       </c>
@@ -31713,7 +31713,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30">
+    <row r="104" spans="1:23" ht="30" hidden="1">
       <c r="A104" s="4" t="s">
         <v>490</v>
       </c>
@@ -31784,7 +31784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30">
+    <row r="105" spans="1:23" ht="30" hidden="1">
       <c r="A105" s="4" t="s">
         <v>490</v>
       </c>
@@ -31855,7 +31855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30">
+    <row r="106" spans="1:23" ht="30" hidden="1">
       <c r="A106" s="4" t="s">
         <v>490</v>
       </c>
@@ -31926,7 +31926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="30" hidden="1">
+    <row r="107" spans="1:23" ht="30">
       <c r="A107" s="4" t="s">
         <v>548</v>
       </c>
@@ -31997,7 +31997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="30" hidden="1">
+    <row r="108" spans="1:23" ht="30">
       <c r="A108" s="4" t="s">
         <v>548</v>
       </c>
@@ -32068,7 +32068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:23" ht="30" hidden="1">
+    <row r="109" spans="1:23" ht="30">
       <c r="A109" s="4" t="s">
         <v>548</v>
       </c>
@@ -32106,7 +32106,7 @@
         <v>7</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N109" s="3" t="s">
         <v>563</v>
@@ -32133,13 +32133,13 @@
         <v>7</v>
       </c>
       <c r="V109" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W109" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30" hidden="1">
+    <row r="110" spans="1:23" ht="30">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -32210,7 +32210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="30" hidden="1">
+    <row r="111" spans="1:23" ht="30">
       <c r="A111" s="4" t="s">
         <v>548</v>
       </c>
@@ -32281,7 +32281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:23" hidden="1">
+    <row r="112" spans="1:23">
       <c r="A112" s="4" t="s">
         <v>548</v>
       </c>
@@ -32352,7 +32352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:23" hidden="1">
+    <row r="113" spans="1:23">
       <c r="A113" s="4" t="s">
         <v>548</v>
       </c>
@@ -32423,7 +32423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:23" hidden="1">
+    <row r="114" spans="1:23">
       <c r="A114" s="4" t="s">
         <v>548</v>
       </c>
@@ -32494,7 +32494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="30" hidden="1">
+    <row r="115" spans="1:23" ht="30">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
@@ -32565,7 +32565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:23" hidden="1">
+    <row r="116" spans="1:23">
       <c r="A116" s="4" t="s">
         <v>548</v>
       </c>
@@ -32636,7 +32636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="30" hidden="1">
+    <row r="117" spans="1:23" ht="30">
       <c r="A117" s="4" t="s">
         <v>548</v>
       </c>
@@ -32707,7 +32707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:23" hidden="1">
+    <row r="118" spans="1:23">
       <c r="A118" s="4" t="s">
         <v>548</v>
       </c>
@@ -32778,7 +32778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="30" hidden="1">
+    <row r="119" spans="1:23" ht="30">
       <c r="A119" s="4" t="s">
         <v>548</v>
       </c>
@@ -32849,7 +32849,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:23" hidden="1">
+    <row r="120" spans="1:23">
       <c r="A120" s="4" t="s">
         <v>548</v>
       </c>
@@ -32920,7 +32920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="30" hidden="1">
+    <row r="121" spans="1:23" ht="30">
       <c r="A121" s="4" t="s">
         <v>548</v>
       </c>
@@ -32991,7 +32991,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:23" hidden="1">
+    <row r="122" spans="1:23">
       <c r="A122" s="4" t="s">
         <v>548</v>
       </c>
@@ -33062,7 +33062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:23" hidden="1">
+    <row r="123" spans="1:23">
       <c r="A123" s="4" t="s">
         <v>548</v>
       </c>
@@ -33133,7 +33133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:23" hidden="1">
+    <row r="124" spans="1:23">
       <c r="A124" s="4" t="s">
         <v>548</v>
       </c>
@@ -56209,7 +56209,7 @@
   <autoFilter ref="A1:W456" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Benefit"/>
+        <filter val="Subscription Plan"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89E67E2-721B-4B8A-9324-DEC75EC7BB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0694C604-9124-46E7-B720-E703D626DD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <sheet name="Validation Rules" sheetId="5" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Atributes!$A$1:$W$456</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Atributes!$A$1:$W$462</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Reference Data'!$A$1:$I$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Relationships!$A$1:$K$63</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14910" uniqueCount="3979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15086" uniqueCount="4031">
   <si>
     <t>Domain</t>
   </si>
@@ -11981,6 +11981,162 @@
   </si>
   <si>
     <t>Records when the store ceased operations and system managed</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Promotion Image URL</t>
+  </si>
+  <si>
+    <t>promotion_image_url</t>
+  </si>
+  <si>
+    <t>Provides the promotional image associated with the Offer.</t>
+  </si>
+  <si>
+    <t>Stores the image reference used for the Offer's customer-facing promotional card.</t>
+  </si>
+  <si>
+    <t>Customer-facing promotional image displayed with the Offer.</t>
+  </si>
+  <si>
+    <t>local://offers/croissant.jpg</t>
+  </si>
+  <si>
+    <t>Badge Text</t>
+  </si>
+  <si>
+    <t>badge_text</t>
+  </si>
+  <si>
+    <t>Provides a short promotional badge for the Offer.</t>
+  </si>
+  <si>
+    <t>Displays a short label such as LIMITED TIME or MEMBER PERK.</t>
+  </si>
+  <si>
+    <t>Short customer-facing promotional badge displayed on the Offer card.</t>
+  </si>
+  <si>
+    <t>LIMITED TIME</t>
+  </si>
+  <si>
+    <t>Availability Text</t>
+  </si>
+  <si>
+    <t>availability_text</t>
+  </si>
+  <si>
+    <t>Provides customer-facing information about Offer availability.</t>
+  </si>
+  <si>
+    <t>Displays information such as This weekend only or Available every Tuesday.</t>
+  </si>
+  <si>
+    <t>Customer-facing text describing when or how the Offer is available.</t>
+  </si>
+  <si>
+    <t>This weekend only</t>
+  </si>
+  <si>
+    <t>CTA Label</t>
+  </si>
+  <si>
+    <t>cta_label</t>
+  </si>
+  <si>
+    <t>Defines the call-to-action label displayed for the Offer.</t>
+  </si>
+  <si>
+    <t>Specifies the text shown on the Offer action button.</t>
+  </si>
+  <si>
+    <t>Customer-facing action label such as Redeem Now or Shop Now.</t>
+  </si>
+  <si>
+    <t>Redeem Now</t>
+  </si>
+  <si>
+    <t>CTA Type</t>
+  </si>
+  <si>
+    <t>cta_type</t>
+  </si>
+  <si>
+    <t>Defines the action performed when the customer selects the Offer CTA.</t>
+  </si>
+  <si>
+    <t>Determines the business action initiated by the Offer call-to-action button.</t>
+  </si>
+  <si>
+    <t>Supported Offer action type such as REDEEM_OFFER or SHOP.</t>
+  </si>
+  <si>
+    <t>REDEEM_OFFER</t>
+  </si>
+  <si>
+    <t>CTA Target</t>
+  </si>
+  <si>
+    <t>cta_target</t>
+  </si>
+  <si>
+    <t>Provides an optional target for the Offer CTA action.</t>
+  </si>
+  <si>
+    <t>Identifies the business object or destination associated with the CTA action.</t>
+  </si>
+  <si>
+    <t>Target reference used by the application when processing the selected CTA action.</t>
+  </si>
+  <si>
+    <t>offer-1001</t>
+  </si>
+  <si>
+    <t>Promotion Image</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Every Offer must have a Promotion Image.</t>
+  </si>
+  <si>
+    <t>Promotion Image is required.</t>
+  </si>
+  <si>
+    <t>Every Offer must have a CTA Label.</t>
+  </si>
+  <si>
+    <t>CTA Label is required.</t>
+  </si>
+  <si>
+    <t>Allowed Values</t>
+  </si>
+  <si>
+    <t>CTA Type must be one of the supported Offer action types: REDEEM_OFFER, SHOP.</t>
+  </si>
+  <si>
+    <t>Invalid Offer CTA Type.</t>
+  </si>
+  <si>
+    <t>CTA Target is required when the selected CTA Type requires a target.</t>
+  </si>
+  <si>
+    <t>CTA Target is required for this CTA Type.</t>
+  </si>
+  <si>
+    <t>VAL055</t>
+  </si>
+  <si>
+    <t>VAL056</t>
+  </si>
+  <si>
+    <t>VAL057</t>
+  </si>
+  <si>
+    <t>VAL058</t>
   </si>
 </sst>
 </file>
@@ -20685,7 +20841,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E5E88D-7637-4195-842B-FF426225AADB}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -22115,6 +22271,114 @@
       <c r="H54" t="s">
         <v>1390</v>
       </c>
+    </row>
+    <row r="55" spans="1:9" ht="30">
+      <c r="A55" s="3" t="s">
+        <v>4027</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>4016</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>4017</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>4018</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>4019</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="3" t="s">
+        <v>4028</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>3998</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>4017</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>4020</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>4021</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="1:9" ht="45">
+      <c r="A57" s="3" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>4004</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>4022</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4023</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4024</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" ht="30">
+      <c r="A58" s="3" t="s">
+        <v>4030</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>4010</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4025</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4026</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I58" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -24622,8 +24886,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:W456"/>
+  <dimension ref="A1:W462"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -24722,7 +24985,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="30" hidden="1">
+    <row r="2" spans="1:23" ht="30">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -24788,7 +25051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30" hidden="1">
+    <row r="3" spans="1:23" ht="30">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -24856,7 +25119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30" hidden="1">
+    <row r="4" spans="1:23" ht="30">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -24924,7 +25187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="60" hidden="1">
+    <row r="5" spans="1:23" ht="60">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -24993,7 +25256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30" hidden="1">
+    <row r="6" spans="1:23" ht="30">
       <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
@@ -25061,7 +25324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1">
+    <row r="7" spans="1:23">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -25129,7 +25392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1">
+    <row r="8" spans="1:23">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -25197,7 +25460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1">
+    <row r="9" spans="1:23">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -25265,7 +25528,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1">
+    <row r="10" spans="1:23">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -25333,7 +25596,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1">
+    <row r="11" spans="1:23">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
@@ -25401,7 +25664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30" hidden="1">
+    <row r="12" spans="1:23" ht="30">
       <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
@@ -25469,7 +25732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1">
+    <row r="13" spans="1:23">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -25537,7 +25800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="30" hidden="1">
+    <row r="14" spans="1:23" ht="30">
       <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
@@ -25605,7 +25868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1">
+    <row r="15" spans="1:23">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -25673,7 +25936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="30" hidden="1">
+    <row r="16" spans="1:23" ht="30">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -25741,7 +26004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1">
+    <row r="17" spans="1:23">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -25809,7 +26072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="30" hidden="1">
+    <row r="18" spans="1:23" ht="30">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -25876,7 +26139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="30" hidden="1">
+    <row r="19" spans="1:23" ht="30">
       <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
@@ -25945,7 +26208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1">
+    <row r="20" spans="1:23">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -26012,7 +26275,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1">
+    <row r="21" spans="1:23">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -26079,7 +26342,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1">
+    <row r="22" spans="1:23">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
@@ -26146,7 +26409,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="30" hidden="1">
+    <row r="23" spans="1:23" ht="30">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -26215,7 +26478,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="30" hidden="1">
+    <row r="24" spans="1:23" ht="30">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -26282,7 +26545,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="30" hidden="1">
+    <row r="25" spans="1:23" ht="30">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -26349,7 +26612,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="30" hidden="1">
+    <row r="26" spans="1:23" ht="30">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -26418,7 +26681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="30" hidden="1">
+    <row r="27" spans="1:23" ht="30">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -26487,7 +26750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="30" hidden="1">
+    <row r="28" spans="1:23" ht="30">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
@@ -26554,7 +26817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1">
+    <row r="29" spans="1:23">
       <c r="A29" s="3" t="s">
         <v>8</v>
       </c>
@@ -26623,7 +26886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="30" hidden="1">
+    <row r="30" spans="1:23" ht="30">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
@@ -26690,7 +26953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1">
+    <row r="31" spans="1:23">
       <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
@@ -26759,7 +27022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="30" hidden="1">
+    <row r="32" spans="1:23" ht="30">
       <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
@@ -26826,7 +27089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:23" hidden="1">
+    <row r="33" spans="1:23">
       <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
@@ -26893,7 +27156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="30" hidden="1">
+    <row r="34" spans="1:23" ht="30">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -26964,7 +27227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="30" hidden="1">
+    <row r="35" spans="1:23" ht="30">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -27035,7 +27298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:23" hidden="1">
+    <row r="36" spans="1:23">
       <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
@@ -27106,7 +27369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45" hidden="1">
+    <row r="37" spans="1:23" ht="45">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -27177,7 +27440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="30" hidden="1">
+    <row r="38" spans="1:23" ht="30">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -27248,7 +27511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="30" hidden="1">
+    <row r="39" spans="1:23" ht="30">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
@@ -27319,7 +27582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="30" hidden="1">
+    <row r="40" spans="1:23" ht="30">
       <c r="A40" s="3" t="s">
         <v>37</v>
       </c>
@@ -27390,7 +27653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:23" hidden="1">
+    <row r="41" spans="1:23">
       <c r="A41" s="3" t="s">
         <v>37</v>
       </c>
@@ -27461,7 +27724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="30" hidden="1">
+    <row r="42" spans="1:23" ht="30">
       <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
@@ -27532,7 +27795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1">
+    <row r="43" spans="1:23">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
@@ -27603,7 +27866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1">
+    <row r="44" spans="1:23">
       <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
@@ -27674,7 +27937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:23" hidden="1">
+    <row r="45" spans="1:23">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -27745,7 +28008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="30" hidden="1">
+    <row r="46" spans="1:23" ht="30">
       <c r="A46" s="3" t="s">
         <v>317</v>
       </c>
@@ -27792,7 +28055,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="30" hidden="1">
+    <row r="47" spans="1:23" ht="30">
       <c r="A47" s="3" t="s">
         <v>317</v>
       </c>
@@ -27839,7 +28102,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="45" hidden="1">
+    <row r="48" spans="1:23" ht="45">
       <c r="A48" s="3" t="s">
         <v>317</v>
       </c>
@@ -27886,7 +28149,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="30" hidden="1">
+    <row r="49" spans="1:23" ht="30">
       <c r="A49" s="3" t="s">
         <v>317</v>
       </c>
@@ -27933,7 +28196,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="30" hidden="1">
+    <row r="50" spans="1:23" ht="30">
       <c r="A50" s="3" t="s">
         <v>317</v>
       </c>
@@ -27980,7 +28243,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="30" hidden="1">
+    <row r="51" spans="1:23" ht="30">
       <c r="A51" s="4" t="s">
         <v>341</v>
       </c>
@@ -28048,7 +28311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="30" hidden="1">
+    <row r="52" spans="1:23" ht="30">
       <c r="A52" s="4" t="s">
         <v>341</v>
       </c>
@@ -28116,7 +28379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="30" hidden="1">
+    <row r="53" spans="1:23" ht="30">
       <c r="A53" s="4" t="s">
         <v>341</v>
       </c>
@@ -28184,7 +28447,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="30" hidden="1">
+    <row r="54" spans="1:23" ht="30">
       <c r="A54" s="4" t="s">
         <v>341</v>
       </c>
@@ -28252,7 +28515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="30" hidden="1">
+    <row r="55" spans="1:23" ht="30">
       <c r="A55" s="4" t="s">
         <v>341</v>
       </c>
@@ -28320,7 +28583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="30" hidden="1">
+    <row r="56" spans="1:23" ht="30">
       <c r="A56" s="4" t="s">
         <v>341</v>
       </c>
@@ -28388,7 +28651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="30" hidden="1">
+    <row r="57" spans="1:23" ht="30">
       <c r="A57" s="4" t="s">
         <v>341</v>
       </c>
@@ -28456,7 +28719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="30" hidden="1">
+    <row r="58" spans="1:23" ht="30">
       <c r="A58" s="4" t="s">
         <v>341</v>
       </c>
@@ -28524,7 +28787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="45" hidden="1">
+    <row r="59" spans="1:23" ht="45">
       <c r="A59" s="4" t="s">
         <v>341</v>
       </c>
@@ -28592,7 +28855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="30" hidden="1">
+    <row r="60" spans="1:23" ht="30">
       <c r="A60" s="4" t="s">
         <v>341</v>
       </c>
@@ -28660,7 +28923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="30" hidden="1">
+    <row r="61" spans="1:23" ht="30">
       <c r="A61" s="4" t="s">
         <v>370</v>
       </c>
@@ -28731,7 +28994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="30" hidden="1">
+    <row r="62" spans="1:23" ht="30">
       <c r="A62" s="4" t="s">
         <v>370</v>
       </c>
@@ -28802,7 +29065,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="30" hidden="1">
+    <row r="63" spans="1:23" ht="30">
       <c r="A63" s="4" t="s">
         <v>370</v>
       </c>
@@ -28873,7 +29136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="30" hidden="1">
+    <row r="64" spans="1:23" ht="30">
       <c r="A64" s="4" t="s">
         <v>370</v>
       </c>
@@ -28944,7 +29207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="30" hidden="1">
+    <row r="65" spans="1:23" ht="30">
       <c r="A65" s="4" t="s">
         <v>370</v>
       </c>
@@ -29015,7 +29278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="30" hidden="1">
+    <row r="66" spans="1:23" ht="30">
       <c r="A66" s="4" t="s">
         <v>377</v>
       </c>
@@ -29086,7 +29349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="30" hidden="1">
+    <row r="67" spans="1:23" ht="30">
       <c r="A67" s="4" t="s">
         <v>377</v>
       </c>
@@ -29157,7 +29420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="30" hidden="1">
+    <row r="68" spans="1:23" ht="30">
       <c r="A68" s="4" t="s">
         <v>377</v>
       </c>
@@ -29228,7 +29491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="30" hidden="1">
+    <row r="69" spans="1:23" ht="30">
       <c r="A69" s="4" t="s">
         <v>10</v>
       </c>
@@ -29299,7 +29562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="30" hidden="1">
+    <row r="70" spans="1:23" ht="30">
       <c r="A70" s="4" t="s">
         <v>10</v>
       </c>
@@ -29370,7 +29633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="45" hidden="1">
+    <row r="71" spans="1:23" ht="45">
       <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
@@ -29441,7 +29704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="45" hidden="1">
+    <row r="72" spans="1:23" ht="45">
       <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
@@ -29512,7 +29775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="30" hidden="1">
+    <row r="73" spans="1:23" ht="30">
       <c r="A73" s="4" t="s">
         <v>10</v>
       </c>
@@ -29583,7 +29846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30" hidden="1">
+    <row r="74" spans="1:23" ht="30">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -29654,7 +29917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30" hidden="1">
+    <row r="75" spans="1:23" ht="30">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -29725,7 +29988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="30" hidden="1">
+    <row r="76" spans="1:23" ht="30">
       <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
@@ -29796,7 +30059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="30" hidden="1">
+    <row r="77" spans="1:23" ht="30">
       <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
@@ -29867,7 +30130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="30" hidden="1">
+    <row r="78" spans="1:23" ht="30">
       <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
@@ -29938,7 +30201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="30" hidden="1">
+    <row r="79" spans="1:23" ht="30">
       <c r="A79" s="4" t="s">
         <v>10</v>
       </c>
@@ -30009,7 +30272,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="45" hidden="1">
+    <row r="80" spans="1:23" ht="45">
       <c r="A80" s="4" t="s">
         <v>10</v>
       </c>
@@ -30080,7 +30343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="45" hidden="1">
+    <row r="81" spans="1:23" ht="45">
       <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
@@ -30151,7 +30414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="30" hidden="1">
+    <row r="82" spans="1:23" ht="30">
       <c r="A82" s="4" t="s">
         <v>10</v>
       </c>
@@ -30222,7 +30485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="30" hidden="1">
+    <row r="83" spans="1:23" ht="30">
       <c r="A83" s="4" t="s">
         <v>10</v>
       </c>
@@ -30293,7 +30556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="30" hidden="1">
+    <row r="84" spans="1:23" ht="30">
       <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
@@ -30364,7 +30627,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="30" hidden="1">
+    <row r="85" spans="1:23" ht="30">
       <c r="A85" s="4" t="s">
         <v>10</v>
       </c>
@@ -30435,7 +30698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="45" hidden="1">
+    <row r="86" spans="1:23" ht="45">
       <c r="A86" s="4" t="s">
         <v>10</v>
       </c>
@@ -30506,7 +30769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="30" hidden="1">
+    <row r="87" spans="1:23" ht="30">
       <c r="A87" s="4" t="s">
         <v>10</v>
       </c>
@@ -30577,7 +30840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30" hidden="1">
+    <row r="88" spans="1:23" ht="30">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -30648,7 +30911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30" hidden="1">
+    <row r="89" spans="1:23" ht="30">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -30719,7 +30982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="30" hidden="1">
+    <row r="90" spans="1:23" ht="30">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -30790,7 +31053,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="30" hidden="1">
+    <row r="91" spans="1:23" ht="30">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -30861,7 +31124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23" hidden="1">
+    <row r="92" spans="1:23">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -30932,7 +31195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23" hidden="1">
+    <row r="93" spans="1:23">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -31003,7 +31266,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="45" hidden="1">
+    <row r="94" spans="1:23" ht="45">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -31074,7 +31337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30" hidden="1">
+    <row r="95" spans="1:23" ht="30">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -31145,7 +31408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30" hidden="1">
+    <row r="96" spans="1:23" ht="30">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -31216,7 +31479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="45" hidden="1">
+    <row r="97" spans="1:23" ht="45">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -31287,7 +31550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30" hidden="1">
+    <row r="98" spans="1:23" ht="30">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -31358,7 +31621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30" hidden="1">
+    <row r="99" spans="1:23" ht="30">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -31429,7 +31692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30" hidden="1">
+    <row r="100" spans="1:23" ht="30">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -31500,7 +31763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30" hidden="1">
+    <row r="101" spans="1:23" ht="30">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -31571,7 +31834,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30" hidden="1">
+    <row r="102" spans="1:23" ht="30">
       <c r="A102" s="4" t="s">
         <v>490</v>
       </c>
@@ -31642,7 +31905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30" hidden="1">
+    <row r="103" spans="1:23" ht="30">
       <c r="A103" s="4" t="s">
         <v>490</v>
       </c>
@@ -31713,7 +31976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30" hidden="1">
+    <row r="104" spans="1:23" ht="30">
       <c r="A104" s="4" t="s">
         <v>490</v>
       </c>
@@ -31784,7 +32047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30" hidden="1">
+    <row r="105" spans="1:23" ht="30">
       <c r="A105" s="4" t="s">
         <v>490</v>
       </c>
@@ -31855,7 +32118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30" hidden="1">
+    <row r="106" spans="1:23" ht="30">
       <c r="A106" s="4" t="s">
         <v>490</v>
       </c>
@@ -33204,7 +33467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="30" hidden="1">
+    <row r="125" spans="1:23" ht="30">
       <c r="A125" s="4" t="s">
         <v>620</v>
       </c>
@@ -33275,7 +33538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:23" ht="30" hidden="1">
+    <row r="126" spans="1:23" ht="30">
       <c r="A126" s="4" t="s">
         <v>620</v>
       </c>
@@ -33346,7 +33609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:23" hidden="1">
+    <row r="127" spans="1:23">
       <c r="A127" s="4" t="s">
         <v>620</v>
       </c>
@@ -33417,7 +33680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="30" hidden="1">
+    <row r="128" spans="1:23" ht="30">
       <c r="A128" s="4" t="s">
         <v>620</v>
       </c>
@@ -33488,7 +33751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:23" hidden="1">
+    <row r="129" spans="1:23">
       <c r="A129" s="4" t="s">
         <v>620</v>
       </c>
@@ -33559,7 +33822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:23" ht="30" hidden="1">
+    <row r="130" spans="1:23" ht="30">
       <c r="A130" s="4" t="s">
         <v>620</v>
       </c>
@@ -33630,7 +33893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:23" hidden="1">
+    <row r="131" spans="1:23">
       <c r="A131" s="4" t="s">
         <v>620</v>
       </c>
@@ -33701,7 +33964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:23" hidden="1">
+    <row r="132" spans="1:23">
       <c r="A132" s="4" t="s">
         <v>620</v>
       </c>
@@ -33772,7 +34035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:23" ht="30" hidden="1">
+    <row r="133" spans="1:23" ht="30">
       <c r="A133" s="4" t="s">
         <v>620</v>
       </c>
@@ -33843,7 +34106,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:23" ht="30" hidden="1">
+    <row r="134" spans="1:23" ht="30">
       <c r="A134" s="4" t="s">
         <v>620</v>
       </c>
@@ -33914,7 +34177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:23" hidden="1">
+    <row r="135" spans="1:23">
       <c r="A135" s="4" t="s">
         <v>620</v>
       </c>
@@ -33985,7 +34248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="30" hidden="1">
+    <row r="136" spans="1:23" ht="30">
       <c r="A136" s="4" t="s">
         <v>620</v>
       </c>
@@ -34056,7 +34319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:23" hidden="1">
+    <row r="137" spans="1:23">
       <c r="A137" s="4" t="s">
         <v>620</v>
       </c>
@@ -34127,7 +34390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:23" hidden="1">
+    <row r="138" spans="1:23">
       <c r="A138" s="4" t="s">
         <v>620</v>
       </c>
@@ -34198,7 +34461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:23" hidden="1">
+    <row r="139" spans="1:23">
       <c r="A139" s="4" t="s">
         <v>620</v>
       </c>
@@ -34269,7 +34532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="30" hidden="1">
+    <row r="140" spans="1:23" ht="30">
       <c r="A140" s="4" t="s">
         <v>673</v>
       </c>
@@ -34340,7 +34603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="30" hidden="1">
+    <row r="141" spans="1:23" ht="30">
       <c r="A141" s="4" t="s">
         <v>673</v>
       </c>
@@ -34411,7 +34674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:23" ht="30" hidden="1">
+    <row r="142" spans="1:23" ht="30">
       <c r="A142" s="4" t="s">
         <v>673</v>
       </c>
@@ -34482,7 +34745,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="30" hidden="1">
+    <row r="143" spans="1:23" ht="30">
       <c r="A143" s="4" t="s">
         <v>673</v>
       </c>
@@ -34553,7 +34816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="30" hidden="1">
+    <row r="144" spans="1:23" ht="30">
       <c r="A144" s="4" t="s">
         <v>673</v>
       </c>
@@ -34624,7 +34887,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="30" hidden="1">
+    <row r="145" spans="1:23" ht="30">
       <c r="A145" s="4" t="s">
         <v>673</v>
       </c>
@@ -34695,7 +34958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="30" hidden="1">
+    <row r="146" spans="1:23" ht="30">
       <c r="A146" s="4" t="s">
         <v>673</v>
       </c>
@@ -34766,7 +35029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:23" hidden="1">
+    <row r="147" spans="1:23">
       <c r="A147" s="4" t="s">
         <v>673</v>
       </c>
@@ -34837,7 +35100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="30" hidden="1">
+    <row r="148" spans="1:23" ht="30">
       <c r="A148" s="4" t="s">
         <v>673</v>
       </c>
@@ -34908,7 +35171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:23" ht="30" hidden="1">
+    <row r="149" spans="1:23" ht="30">
       <c r="A149" s="4" t="s">
         <v>673</v>
       </c>
@@ -34979,7 +35242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="30" hidden="1">
+    <row r="150" spans="1:23" ht="30">
       <c r="A150" s="4" t="s">
         <v>673</v>
       </c>
@@ -35050,7 +35313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="30" hidden="1">
+    <row r="151" spans="1:23" ht="30">
       <c r="A151" s="4" t="s">
         <v>673</v>
       </c>
@@ -35121,7 +35384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="30" hidden="1">
+    <row r="152" spans="1:23" ht="30">
       <c r="A152" s="4" t="s">
         <v>673</v>
       </c>
@@ -35192,7 +35455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="30" hidden="1">
+    <row r="153" spans="1:23" ht="30">
       <c r="A153" s="4" t="s">
         <v>673</v>
       </c>
@@ -35263,7 +35526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23" hidden="1">
+    <row r="154" spans="1:23">
       <c r="A154" s="4" t="s">
         <v>673</v>
       </c>
@@ -35334,7 +35597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="30" hidden="1">
+    <row r="155" spans="1:23" ht="30">
       <c r="A155" s="4" t="s">
         <v>34</v>
       </c>
@@ -35405,7 +35668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="30" hidden="1">
+    <row r="156" spans="1:23" ht="30">
       <c r="A156" s="4" t="s">
         <v>34</v>
       </c>
@@ -35476,7 +35739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="30" hidden="1">
+    <row r="157" spans="1:23" ht="30">
       <c r="A157" s="4" t="s">
         <v>34</v>
       </c>
@@ -35547,7 +35810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="30" hidden="1">
+    <row r="158" spans="1:23" ht="30">
       <c r="A158" s="4" t="s">
         <v>34</v>
       </c>
@@ -35618,7 +35881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:23" hidden="1">
+    <row r="159" spans="1:23">
       <c r="A159" s="4" t="s">
         <v>34</v>
       </c>
@@ -35689,7 +35952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="30" hidden="1">
+    <row r="160" spans="1:23" ht="30">
       <c r="A160" s="4" t="s">
         <v>34</v>
       </c>
@@ -35760,7 +36023,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:23" ht="30" hidden="1">
+    <row r="161" spans="1:23" ht="30">
       <c r="A161" s="4" t="s">
         <v>34</v>
       </c>
@@ -35831,7 +36094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="30" hidden="1">
+    <row r="162" spans="1:23" ht="30">
       <c r="A162" s="4" t="s">
         <v>34</v>
       </c>
@@ -35902,7 +36165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="30" hidden="1">
+    <row r="163" spans="1:23" ht="30">
       <c r="A163" s="4" t="s">
         <v>34</v>
       </c>
@@ -35973,7 +36236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="30" hidden="1">
+    <row r="164" spans="1:23" ht="30">
       <c r="A164" s="4" t="s">
         <v>34</v>
       </c>
@@ -36044,7 +36307,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="30" hidden="1">
+    <row r="165" spans="1:23" ht="30">
       <c r="A165" s="4" t="s">
         <v>34</v>
       </c>
@@ -36115,7 +36378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="30" hidden="1">
+    <row r="166" spans="1:23" ht="30">
       <c r="A166" s="4" t="s">
         <v>34</v>
       </c>
@@ -36186,7 +36449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="30" hidden="1">
+    <row r="167" spans="1:23" ht="30">
       <c r="A167" s="4" t="s">
         <v>34</v>
       </c>
@@ -36257,7 +36520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="30" hidden="1">
+    <row r="168" spans="1:23" ht="30">
       <c r="A168" s="4" t="s">
         <v>34</v>
       </c>
@@ -36328,7 +36591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="30" hidden="1">
+    <row r="169" spans="1:23" ht="30">
       <c r="A169" s="4" t="s">
         <v>34</v>
       </c>
@@ -36399,7 +36662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="30" hidden="1">
+    <row r="170" spans="1:23" ht="30">
       <c r="A170" s="4" t="s">
         <v>34</v>
       </c>
@@ -36470,7 +36733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="30" hidden="1">
+    <row r="171" spans="1:23" ht="30">
       <c r="A171" s="4" t="s">
         <v>34</v>
       </c>
@@ -36541,7 +36804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="30" hidden="1">
+    <row r="172" spans="1:23" ht="30">
       <c r="A172" s="4" t="s">
         <v>34</v>
       </c>
@@ -36612,7 +36875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:23" hidden="1">
+    <row r="173" spans="1:23">
       <c r="A173" s="4" t="s">
         <v>34</v>
       </c>
@@ -36683,7 +36946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="30" hidden="1">
+    <row r="174" spans="1:23" ht="30">
       <c r="A174" s="4" t="s">
         <v>34</v>
       </c>
@@ -36754,7 +37017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="30" hidden="1">
+    <row r="175" spans="1:23" ht="30">
       <c r="A175" s="4" t="s">
         <v>34</v>
       </c>
@@ -36825,7 +37088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="30" hidden="1">
+    <row r="176" spans="1:23" ht="30">
       <c r="A176" s="4" t="s">
         <v>34</v>
       </c>
@@ -36896,7 +37159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="30" hidden="1">
+    <row r="177" spans="1:23" ht="30">
       <c r="A177" s="4" t="s">
         <v>34</v>
       </c>
@@ -36967,7 +37230,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="30" hidden="1">
+    <row r="178" spans="1:23" ht="30">
       <c r="A178" s="4" t="s">
         <v>35</v>
       </c>
@@ -37038,7 +37301,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="30" hidden="1">
+    <row r="179" spans="1:23" ht="30">
       <c r="A179" s="4" t="s">
         <v>35</v>
       </c>
@@ -37109,7 +37372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="30" hidden="1">
+    <row r="180" spans="1:23" ht="30">
       <c r="A180" s="4" t="s">
         <v>35</v>
       </c>
@@ -37180,7 +37443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="30" hidden="1">
+    <row r="181" spans="1:23" ht="30">
       <c r="A181" s="4" t="s">
         <v>35</v>
       </c>
@@ -37251,7 +37514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:23" hidden="1">
+    <row r="182" spans="1:23">
       <c r="A182" s="4" t="s">
         <v>35</v>
       </c>
@@ -37302,7 +37565,7 @@
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
     </row>
-    <row r="183" spans="1:23" hidden="1">
+    <row r="183" spans="1:23">
       <c r="A183" s="4" t="s">
         <v>35</v>
       </c>
@@ -37351,7 +37614,7 @@
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
     </row>
-    <row r="184" spans="1:23" ht="30" hidden="1">
+    <row r="184" spans="1:23" ht="30">
       <c r="A184" s="3" t="s">
         <v>35</v>
       </c>
@@ -37422,7 +37685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="30" hidden="1">
+    <row r="185" spans="1:23" ht="30">
       <c r="A185" s="3" t="s">
         <v>35</v>
       </c>
@@ -37493,7 +37756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="30" hidden="1">
+    <row r="186" spans="1:23" ht="30">
       <c r="A186" s="4" t="s">
         <v>35</v>
       </c>
@@ -37564,7 +37827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="30" hidden="1">
+    <row r="187" spans="1:23" ht="30">
       <c r="A187" s="4" t="s">
         <v>35</v>
       </c>
@@ -37635,7 +37898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:23" ht="30" hidden="1">
+    <row r="188" spans="1:23" ht="30">
       <c r="A188" s="4" t="s">
         <v>35</v>
       </c>
@@ -37706,7 +37969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:23" ht="30" hidden="1">
+    <row r="189" spans="1:23" ht="30">
       <c r="A189" s="4" t="s">
         <v>35</v>
       </c>
@@ -37777,7 +38040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="30" hidden="1">
+    <row r="190" spans="1:23" ht="30">
       <c r="A190" s="4" t="s">
         <v>35</v>
       </c>
@@ -37848,7 +38111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:23" ht="30" hidden="1">
+    <row r="191" spans="1:23" ht="30">
       <c r="A191" s="4" t="s">
         <v>35</v>
       </c>
@@ -37919,7 +38182,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:23" ht="30" hidden="1">
+    <row r="192" spans="1:23" ht="30">
       <c r="A192" s="4" t="s">
         <v>35</v>
       </c>
@@ -37990,7 +38253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:23" ht="30" hidden="1">
+    <row r="193" spans="1:23" ht="30">
       <c r="A193" s="4" t="s">
         <v>35</v>
       </c>
@@ -38061,7 +38324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:23" ht="30" hidden="1">
+    <row r="194" spans="1:23" ht="30">
       <c r="A194" s="4" t="s">
         <v>35</v>
       </c>
@@ -38132,7 +38395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:23" ht="30" hidden="1">
+    <row r="195" spans="1:23" ht="30">
       <c r="A195" s="4" t="s">
         <v>35</v>
       </c>
@@ -38203,7 +38466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:23" ht="30" hidden="1">
+    <row r="196" spans="1:23" ht="30">
       <c r="A196" s="4" t="s">
         <v>35</v>
       </c>
@@ -38274,7 +38537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:23" ht="30" hidden="1">
+    <row r="197" spans="1:23" ht="30">
       <c r="A197" s="3" t="s">
         <v>94</v>
       </c>
@@ -38341,7 +38604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="30" hidden="1">
+    <row r="198" spans="1:23" ht="30">
       <c r="A198" s="3" t="s">
         <v>94</v>
       </c>
@@ -38410,7 +38673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="30" hidden="1">
+    <row r="199" spans="1:23" ht="30">
       <c r="A199" s="3" t="s">
         <v>94</v>
       </c>
@@ -38479,7 +38742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:23" ht="30" hidden="1">
+    <row r="200" spans="1:23" ht="30">
       <c r="A200" s="3" t="s">
         <v>94</v>
       </c>
@@ -38548,7 +38811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:23" ht="30" hidden="1">
+    <row r="201" spans="1:23" ht="30">
       <c r="A201" s="3" t="s">
         <v>94</v>
       </c>
@@ -38617,7 +38880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:23" ht="30" hidden="1">
+    <row r="202" spans="1:23" ht="30">
       <c r="A202" s="3" t="s">
         <v>94</v>
       </c>
@@ -38686,7 +38949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:23" hidden="1">
+    <row r="203" spans="1:23">
       <c r="A203" s="3" t="s">
         <v>42</v>
       </c>
@@ -38753,7 +39016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:23" hidden="1">
+    <row r="204" spans="1:23">
       <c r="A204" s="3" t="s">
         <v>42</v>
       </c>
@@ -38822,7 +39085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:23" hidden="1">
+    <row r="205" spans="1:23">
       <c r="A205" s="3" t="s">
         <v>42</v>
       </c>
@@ -38891,7 +39154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="30" hidden="1">
+    <row r="206" spans="1:23" ht="30">
       <c r="A206" s="3" t="s">
         <v>42</v>
       </c>
@@ -38960,7 +39223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:23" hidden="1">
+    <row r="207" spans="1:23">
       <c r="A207" s="3" t="s">
         <v>42</v>
       </c>
@@ -39029,7 +39292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="30" hidden="1">
+    <row r="208" spans="1:23" ht="30">
       <c r="A208" s="3" t="s">
         <v>42</v>
       </c>
@@ -39098,7 +39361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:23" hidden="1">
+    <row r="209" spans="1:23">
       <c r="A209" s="3" t="s">
         <v>129</v>
       </c>
@@ -39165,7 +39428,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:23" hidden="1">
+    <row r="210" spans="1:23">
       <c r="A210" s="3" t="s">
         <v>129</v>
       </c>
@@ -39234,7 +39497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:23" hidden="1">
+    <row r="211" spans="1:23">
       <c r="A211" s="3" t="s">
         <v>129</v>
       </c>
@@ -39303,7 +39566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:23" hidden="1">
+    <row r="212" spans="1:23">
       <c r="A212" s="3" t="s">
         <v>129</v>
       </c>
@@ -39372,7 +39635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:23" hidden="1">
+    <row r="213" spans="1:23">
       <c r="A213" s="3" t="s">
         <v>129</v>
       </c>
@@ -39441,7 +39704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="30" hidden="1">
+    <row r="214" spans="1:23" ht="30">
       <c r="A214" s="3" t="s">
         <v>129</v>
       </c>
@@ -39510,7 +39773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="30" hidden="1">
+    <row r="215" spans="1:23" ht="30">
       <c r="A215" s="3" t="s">
         <v>129</v>
       </c>
@@ -39579,7 +39842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:23" hidden="1">
+    <row r="216" spans="1:23">
       <c r="A216" s="3" t="s">
         <v>126</v>
       </c>
@@ -39646,7 +39909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:23" hidden="1">
+    <row r="217" spans="1:23">
       <c r="A217" s="3" t="s">
         <v>126</v>
       </c>
@@ -39715,7 +39978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:23" hidden="1">
+    <row r="218" spans="1:23">
       <c r="A218" s="3" t="s">
         <v>126</v>
       </c>
@@ -39784,7 +40047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="30" hidden="1">
+    <row r="219" spans="1:23" ht="30">
       <c r="A219" s="3" t="s">
         <v>126</v>
       </c>
@@ -39853,7 +40116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="30" hidden="1">
+    <row r="220" spans="1:23" ht="30">
       <c r="A220" s="3" t="s">
         <v>126</v>
       </c>
@@ -39922,7 +40185,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:23" hidden="1">
+    <row r="221" spans="1:23">
       <c r="A221" s="3" t="s">
         <v>126</v>
       </c>
@@ -39991,7 +40254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="30" hidden="1">
+    <row r="222" spans="1:23" ht="30">
       <c r="A222" s="3" t="s">
         <v>126</v>
       </c>
@@ -40060,7 +40323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="30" hidden="1">
+    <row r="223" spans="1:23" ht="30">
       <c r="A223" s="3" t="s">
         <v>126</v>
       </c>
@@ -40129,7 +40392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:23" ht="30" hidden="1">
+    <row r="224" spans="1:23" ht="30">
       <c r="A224" s="3" t="s">
         <v>313</v>
       </c>
@@ -40196,7 +40459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="30" hidden="1">
+    <row r="225" spans="1:23" ht="30">
       <c r="A225" s="3" t="s">
         <v>313</v>
       </c>
@@ -40265,7 +40528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="30" hidden="1">
+    <row r="226" spans="1:23" ht="30">
       <c r="A226" s="3" t="s">
         <v>313</v>
       </c>
@@ -40334,7 +40597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="30" hidden="1">
+    <row r="227" spans="1:23" ht="30">
       <c r="A227" s="3" t="s">
         <v>313</v>
       </c>
@@ -40403,7 +40666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="30" hidden="1">
+    <row r="228" spans="1:23" ht="30">
       <c r="A228" s="3" t="s">
         <v>313</v>
       </c>
@@ -40472,7 +40735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="45" hidden="1">
+    <row r="229" spans="1:23" ht="45">
       <c r="A229" s="3" t="s">
         <v>313</v>
       </c>
@@ -40541,7 +40804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="30" hidden="1">
+    <row r="230" spans="1:23" ht="30">
       <c r="A230" s="3" t="s">
         <v>445</v>
       </c>
@@ -40608,7 +40871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="30" hidden="1">
+    <row r="231" spans="1:23" ht="30">
       <c r="A231" s="3" t="s">
         <v>445</v>
       </c>
@@ -40677,7 +40940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="30" hidden="1">
+    <row r="232" spans="1:23" ht="30">
       <c r="A232" s="3" t="s">
         <v>445</v>
       </c>
@@ -40746,7 +41009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:23" ht="30" hidden="1">
+    <row r="233" spans="1:23" ht="30">
       <c r="A233" s="3" t="s">
         <v>445</v>
       </c>
@@ -40815,7 +41078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:23" ht="30" hidden="1">
+    <row r="234" spans="1:23" ht="30">
       <c r="A234" s="3" t="s">
         <v>445</v>
       </c>
@@ -40884,7 +41147,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="30" hidden="1">
+    <row r="235" spans="1:23" ht="30">
       <c r="A235" s="3" t="s">
         <v>445</v>
       </c>
@@ -40953,7 +41216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:23" ht="30" hidden="1">
+    <row r="236" spans="1:23" ht="30">
       <c r="A236" s="3" t="s">
         <v>451</v>
       </c>
@@ -41020,7 +41283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:23" hidden="1">
+    <row r="237" spans="1:23">
       <c r="A237" s="3" t="s">
         <v>451</v>
       </c>
@@ -41089,7 +41352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:23" hidden="1">
+    <row r="238" spans="1:23">
       <c r="A238" s="3" t="s">
         <v>451</v>
       </c>
@@ -41158,7 +41421,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:23" ht="30" hidden="1">
+    <row r="239" spans="1:23" ht="30">
       <c r="A239" s="3" t="s">
         <v>451</v>
       </c>
@@ -41227,7 +41490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:23" hidden="1">
+    <row r="240" spans="1:23">
       <c r="A240" s="3" t="s">
         <v>451</v>
       </c>
@@ -41296,7 +41559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:23" ht="30" hidden="1">
+    <row r="241" spans="1:23" ht="30">
       <c r="A241" s="3" t="s">
         <v>451</v>
       </c>
@@ -41365,7 +41628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:23" ht="30" hidden="1">
+    <row r="242" spans="1:23" ht="30">
       <c r="A242" s="3" t="s">
         <v>512</v>
       </c>
@@ -41432,7 +41695,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="30" hidden="1">
+    <row r="243" spans="1:23" ht="30">
       <c r="A243" s="3" t="s">
         <v>512</v>
       </c>
@@ -41501,7 +41764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="30" hidden="1">
+    <row r="244" spans="1:23" ht="30">
       <c r="A244" s="3" t="s">
         <v>512</v>
       </c>
@@ -41570,7 +41833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="30" hidden="1">
+    <row r="245" spans="1:23" ht="30">
       <c r="A245" s="3" t="s">
         <v>512</v>
       </c>
@@ -41639,7 +41902,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="30" hidden="1">
+    <row r="246" spans="1:23" ht="30">
       <c r="A246" s="3" t="s">
         <v>512</v>
       </c>
@@ -41708,7 +41971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:23" ht="30" hidden="1">
+    <row r="247" spans="1:23" ht="30">
       <c r="A247" s="3" t="s">
         <v>512</v>
       </c>
@@ -41777,7 +42040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:23" ht="30" hidden="1">
+    <row r="248" spans="1:23" ht="30">
       <c r="A248" s="3" t="s">
         <v>518</v>
       </c>
@@ -41844,7 +42107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:23" hidden="1">
+    <row r="249" spans="1:23">
       <c r="A249" s="3" t="s">
         <v>518</v>
       </c>
@@ -41913,7 +42176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:23" hidden="1">
+    <row r="250" spans="1:23">
       <c r="A250" s="3" t="s">
         <v>518</v>
       </c>
@@ -41982,7 +42245,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:23" ht="30" hidden="1">
+    <row r="251" spans="1:23" ht="30">
       <c r="A251" s="3" t="s">
         <v>518</v>
       </c>
@@ -42051,7 +42314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:23" hidden="1">
+    <row r="252" spans="1:23">
       <c r="A252" s="3" t="s">
         <v>518</v>
       </c>
@@ -42120,7 +42383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:23" ht="30" hidden="1">
+    <row r="253" spans="1:23" ht="30">
       <c r="A253" s="3" t="s">
         <v>518</v>
       </c>
@@ -42189,7 +42452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:23" ht="30" hidden="1">
+    <row r="254" spans="1:23" ht="30">
       <c r="A254" s="3" t="s">
         <v>756</v>
       </c>
@@ -42256,7 +42519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:23" hidden="1">
+    <row r="255" spans="1:23">
       <c r="A255" s="3" t="s">
         <v>756</v>
       </c>
@@ -42325,7 +42588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:23" hidden="1">
+    <row r="256" spans="1:23">
       <c r="A256" s="3" t="s">
         <v>756</v>
       </c>
@@ -42394,7 +42657,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:23" hidden="1">
+    <row r="257" spans="1:23">
       <c r="A257" s="3" t="s">
         <v>756</v>
       </c>
@@ -42463,7 +42726,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:23" hidden="1">
+    <row r="258" spans="1:23">
       <c r="A258" s="3" t="s">
         <v>756</v>
       </c>
@@ -42532,7 +42795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:23" ht="30" hidden="1">
+    <row r="259" spans="1:23" ht="30">
       <c r="A259" s="3" t="s">
         <v>756</v>
       </c>
@@ -42601,7 +42864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:23" ht="30" hidden="1">
+    <row r="260" spans="1:23" ht="30">
       <c r="A260" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42668,7 +42931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:23" ht="30" hidden="1">
+    <row r="261" spans="1:23" ht="30">
       <c r="A261" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42735,7 +42998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="30" hidden="1">
+    <row r="262" spans="1:23" ht="30">
       <c r="A262" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42804,7 +43067,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30" hidden="1">
+    <row r="263" spans="1:23" ht="30">
       <c r="A263" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42873,7 +43136,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="264" spans="1:23" hidden="1">
+    <row r="264" spans="1:23">
       <c r="A264" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42942,7 +43205,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30" hidden="1">
+    <row r="265" spans="1:23" ht="30">
       <c r="A265" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43011,7 +43274,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="266" spans="1:23" hidden="1">
+    <row r="266" spans="1:23">
       <c r="A266" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43080,7 +43343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23" hidden="1">
+    <row r="267" spans="1:23">
       <c r="A267" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43149,7 +43412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23" hidden="1">
+    <row r="268" spans="1:23">
       <c r="A268" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43218,7 +43481,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23" hidden="1">
+    <row r="269" spans="1:23">
       <c r="A269" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43287,7 +43550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23" hidden="1">
+    <row r="270" spans="1:23">
       <c r="A270" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43356,7 +43619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23" hidden="1">
+    <row r="271" spans="1:23">
       <c r="A271" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43425,7 +43688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="30" hidden="1">
+    <row r="272" spans="1:23" ht="30">
       <c r="A272" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43494,7 +43757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="30" hidden="1">
+    <row r="273" spans="1:23" ht="30">
       <c r="A273" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43563,7 +43826,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23" hidden="1">
+    <row r="274" spans="1:23">
       <c r="A274" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43630,7 +43893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23" hidden="1">
+    <row r="275" spans="1:23">
       <c r="A275" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43697,7 +43960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23" hidden="1">
+    <row r="276" spans="1:23">
       <c r="A276" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43764,7 +44027,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:23" hidden="1">
+    <row r="277" spans="1:23">
       <c r="A277" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43833,7 +44096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:23" hidden="1">
+    <row r="278" spans="1:23">
       <c r="A278" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43902,7 +44165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="30" hidden="1">
+    <row r="279" spans="1:23" ht="30">
       <c r="A279" s="3" t="s">
         <v>1515</v>
       </c>
@@ -43969,7 +44232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="30" hidden="1">
+    <row r="280" spans="1:23" ht="30">
       <c r="A280" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44036,7 +44299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="30" hidden="1">
+    <row r="281" spans="1:23" ht="30">
       <c r="A281" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44107,7 +44370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:23" hidden="1">
+    <row r="282" spans="1:23">
       <c r="A282" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44174,7 +44437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="30" hidden="1">
+    <row r="283" spans="1:23" ht="30">
       <c r="A283" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44243,7 +44506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:23" hidden="1">
+    <row r="284" spans="1:23">
       <c r="A284" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44312,7 +44575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:23" hidden="1">
+    <row r="285" spans="1:23">
       <c r="A285" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44381,7 +44644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="45" hidden="1">
+    <row r="286" spans="1:23" ht="45">
       <c r="A286" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44450,7 +44713,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="30" hidden="1">
+    <row r="287" spans="1:23" ht="30">
       <c r="A287" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44519,7 +44782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="45" hidden="1">
+    <row r="288" spans="1:23" ht="45">
       <c r="A288" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44588,7 +44851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="45" hidden="1">
+    <row r="289" spans="1:23" ht="45">
       <c r="A289" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44657,7 +44920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="30" hidden="1">
+    <row r="290" spans="1:23" ht="30">
       <c r="A290" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44724,7 +44987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="30" hidden="1">
+    <row r="291" spans="1:23" ht="30">
       <c r="A291" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44791,7 +45054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:23" hidden="1">
+    <row r="292" spans="1:23">
       <c r="A292" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44856,7 +45119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:23" hidden="1">
+    <row r="293" spans="1:23">
       <c r="A293" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44921,7 +45184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:23" hidden="1">
+    <row r="294" spans="1:23">
       <c r="A294" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44986,7 +45249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:23" hidden="1">
+    <row r="295" spans="1:23">
       <c r="A295" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45055,7 +45318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23" hidden="1">
+    <row r="296" spans="1:23">
       <c r="A296" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45124,7 +45387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="30" hidden="1">
+    <row r="297" spans="1:23" ht="30">
       <c r="A297" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45191,7 +45454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:23" ht="30" hidden="1">
+    <row r="298" spans="1:23" ht="30">
       <c r="A298" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45258,7 +45521,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="45" hidden="1">
+    <row r="299" spans="1:23" ht="45">
       <c r="A299" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45329,7 +45592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="30" hidden="1">
+    <row r="300" spans="1:23" ht="30">
       <c r="A300" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45398,7 +45661,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="30" hidden="1">
+    <row r="301" spans="1:23" ht="30">
       <c r="A301" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45467,7 +45730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="30" hidden="1">
+    <row r="302" spans="1:23" ht="30">
       <c r="A302" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45536,7 +45799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="30" hidden="1">
+    <row r="303" spans="1:23" ht="30">
       <c r="A303" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45605,7 +45868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="30" hidden="1">
+    <row r="304" spans="1:23" ht="30">
       <c r="A304" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45674,7 +45937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="30" hidden="1">
+    <row r="305" spans="1:23" ht="30">
       <c r="A305" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45741,7 +46004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30" hidden="1">
+    <row r="306" spans="1:23" ht="30">
       <c r="A306" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45808,7 +46071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="30" hidden="1">
+    <row r="307" spans="1:23" ht="30">
       <c r="A307" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45873,7 +46136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="30" hidden="1">
+    <row r="308" spans="1:23" ht="30">
       <c r="A308" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45938,7 +46201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="30" hidden="1">
+    <row r="309" spans="1:23" ht="30">
       <c r="A309" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46003,7 +46266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="30" hidden="1">
+    <row r="310" spans="1:23" ht="30">
       <c r="A310" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46072,7 +46335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="30" hidden="1">
+    <row r="311" spans="1:23" ht="30">
       <c r="A311" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46141,7 +46404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="30" hidden="1">
+    <row r="312" spans="1:23" ht="30">
       <c r="A312" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46208,7 +46471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="30" hidden="1">
+    <row r="313" spans="1:23" ht="30">
       <c r="A313" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46275,7 +46538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="45" hidden="1">
+    <row r="314" spans="1:23" ht="45">
       <c r="A314" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46344,7 +46607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:23" hidden="1">
+    <row r="315" spans="1:23">
       <c r="A315" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46411,7 +46674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:23" hidden="1">
+    <row r="316" spans="1:23">
       <c r="A316" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46478,7 +46741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:23" ht="30" hidden="1">
+    <row r="317" spans="1:23" ht="30">
       <c r="A317" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46545,7 +46808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:23" hidden="1">
+    <row r="318" spans="1:23">
       <c r="A318" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46612,7 +46875,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:23" ht="45" hidden="1">
+    <row r="319" spans="1:23" ht="45">
       <c r="A319" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46681,7 +46944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="30" hidden="1">
+    <row r="320" spans="1:23" ht="30">
       <c r="A320" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46746,7 +47009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="30" hidden="1">
+    <row r="321" spans="1:23" ht="30">
       <c r="A321" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46815,7 +47078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:23" ht="30" hidden="1">
+    <row r="322" spans="1:23" ht="30">
       <c r="A322" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46882,7 +47145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="30" hidden="1">
+    <row r="323" spans="1:23" ht="30">
       <c r="A323" s="3" t="s">
         <v>1686</v>
       </c>
@@ -46949,7 +47212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="30" hidden="1">
+    <row r="324" spans="1:23" ht="30">
       <c r="A324" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47016,7 +47279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="30" hidden="1">
+    <row r="325" spans="1:23" ht="30">
       <c r="A325" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47085,7 +47348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="30" hidden="1">
+    <row r="326" spans="1:23" ht="30">
       <c r="A326" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47152,7 +47415,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="30" hidden="1">
+    <row r="327" spans="1:23" ht="30">
       <c r="A327" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47221,7 +47484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="30" hidden="1">
+    <row r="328" spans="1:23" ht="30">
       <c r="A328" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47290,7 +47553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="30" hidden="1">
+    <row r="329" spans="1:23" ht="30">
       <c r="A329" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47357,7 +47620,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="30" hidden="1">
+    <row r="330" spans="1:23" ht="30">
       <c r="A330" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47424,7 +47687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="30" hidden="1">
+    <row r="331" spans="1:23" ht="30">
       <c r="A331" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47489,7 +47752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="30" hidden="1">
+    <row r="332" spans="1:23" ht="30">
       <c r="A332" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47556,7 +47819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="45" hidden="1">
+    <row r="333" spans="1:23" ht="45">
       <c r="A333" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47625,7 +47888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="30" hidden="1">
+    <row r="334" spans="1:23" ht="30">
       <c r="A334" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47694,7 +47957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="30" hidden="1">
+    <row r="335" spans="1:23" ht="30">
       <c r="A335" s="3" t="s">
         <v>1701</v>
       </c>
@@ -47761,7 +48024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="30" hidden="1">
+    <row r="336" spans="1:23" ht="30">
       <c r="A336" s="3" t="s">
         <v>1701</v>
       </c>
@@ -47830,7 +48093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:23" hidden="1">
+    <row r="337" spans="1:23">
       <c r="A337" s="3" t="s">
         <v>1701</v>
       </c>
@@ -47899,7 +48162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="30" hidden="1">
+    <row r="338" spans="1:23" ht="30">
       <c r="A338" s="3" t="s">
         <v>1701</v>
       </c>
@@ -47968,7 +48231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:23" hidden="1">
+    <row r="339" spans="1:23">
       <c r="A339" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48037,7 +48300,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="30" hidden="1">
+    <row r="340" spans="1:23" ht="30">
       <c r="A340" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48106,7 +48369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:23" ht="30" hidden="1">
+    <row r="341" spans="1:23" ht="30">
       <c r="A341" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48173,7 +48436,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="342" spans="1:23" hidden="1">
+    <row r="342" spans="1:23">
       <c r="A342" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48238,7 +48501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="30" hidden="1">
+    <row r="343" spans="1:23" ht="30">
       <c r="A343" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48307,7 +48570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:23" hidden="1">
+    <row r="344" spans="1:23">
       <c r="A344" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48376,7 +48639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="30" hidden="1">
+    <row r="345" spans="1:23" ht="30">
       <c r="A345" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48443,7 +48706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="30" hidden="1">
+    <row r="346" spans="1:23" ht="30">
       <c r="A346" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48510,7 +48773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="30" hidden="1">
+    <row r="347" spans="1:23" ht="30">
       <c r="A347" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48577,7 +48840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="30" hidden="1">
+    <row r="348" spans="1:23" ht="30">
       <c r="A348" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48646,7 +48909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="45" hidden="1">
+    <row r="349" spans="1:23" ht="45">
       <c r="A349" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48715,7 +48978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="30" hidden="1">
+    <row r="350" spans="1:23" ht="30">
       <c r="A350" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48782,7 +49045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="30" hidden="1">
+    <row r="351" spans="1:23" ht="30">
       <c r="A351" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48849,7 +49112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="30" hidden="1">
+    <row r="352" spans="1:23" ht="30">
       <c r="A352" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48918,7 +49181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="30" hidden="1">
+    <row r="353" spans="1:23" ht="30">
       <c r="A353" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48985,7 +49248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="30" hidden="1">
+    <row r="354" spans="1:23" ht="30">
       <c r="A354" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49052,7 +49315,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="30" hidden="1">
+    <row r="355" spans="1:23" ht="30">
       <c r="A355" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49117,7 +49380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="30" hidden="1">
+    <row r="356" spans="1:23" ht="30">
       <c r="A356" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49184,7 +49447,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="45" hidden="1">
+    <row r="357" spans="1:23" ht="45">
       <c r="A357" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49253,7 +49516,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="30" hidden="1">
+    <row r="358" spans="1:23" ht="30">
       <c r="A358" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49322,7 +49585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:23" hidden="1">
+    <row r="359" spans="1:23">
       <c r="A359" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49391,7 +49654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:23" hidden="1">
+    <row r="360" spans="1:23">
       <c r="A360" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49460,7 +49723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:23" hidden="1">
+    <row r="361" spans="1:23">
       <c r="A361" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49529,7 +49792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:23" ht="30" hidden="1">
+    <row r="362" spans="1:23" ht="30">
       <c r="A362" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49598,7 +49861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="30" hidden="1">
+    <row r="363" spans="1:23" ht="30">
       <c r="A363" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49667,7 +49930,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="30" hidden="1">
+    <row r="364" spans="1:23" ht="30">
       <c r="A364" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49738,7 +50001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="30" hidden="1">
+    <row r="365" spans="1:23" ht="30">
       <c r="A365" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49807,7 +50070,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="366" spans="1:23" hidden="1">
+    <row r="366" spans="1:23">
       <c r="A366" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49878,7 +50141,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="30" hidden="1">
+    <row r="367" spans="1:23" ht="30">
       <c r="A367" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49949,7 +50212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="45" hidden="1">
+    <row r="368" spans="1:23" ht="45">
       <c r="A368" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50020,7 +50283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="30" hidden="1">
+    <row r="369" spans="1:23" ht="30">
       <c r="A369" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50091,7 +50354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:23" hidden="1">
+    <row r="370" spans="1:23">
       <c r="A370" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50160,7 +50423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="30" hidden="1">
+    <row r="371" spans="1:23" ht="30">
       <c r="A371" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50231,7 +50494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="30" hidden="1">
+    <row r="372" spans="1:23" ht="30">
       <c r="A372" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50300,7 +50563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="30" hidden="1">
+    <row r="373" spans="1:23" ht="30">
       <c r="A373" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50371,7 +50634,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:23" ht="30" hidden="1">
+    <row r="374" spans="1:23" ht="30">
       <c r="A374" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50442,7 +50705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="30" hidden="1">
+    <row r="375" spans="1:23" ht="30">
       <c r="A375" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50511,7 +50774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="30" hidden="1">
+    <row r="376" spans="1:23" ht="30">
       <c r="A376" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50580,7 +50843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:23" hidden="1">
+    <row r="377" spans="1:23">
       <c r="A377" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50649,7 +50912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:23" ht="45" hidden="1">
+    <row r="378" spans="1:23" ht="45">
       <c r="A378" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50718,7 +50981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:23" ht="30" hidden="1">
+    <row r="379" spans="1:23" ht="30">
       <c r="A379" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50789,7 +51052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:23" ht="30" hidden="1">
+    <row r="380" spans="1:23" ht="30">
       <c r="A380" s="4" t="s">
         <v>2014</v>
       </c>
@@ -50860,7 +51123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="30" hidden="1">
+    <row r="381" spans="1:23" ht="30">
       <c r="A381" s="4" t="s">
         <v>2014</v>
       </c>
@@ -50931,7 +51194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:23" ht="30" hidden="1">
+    <row r="382" spans="1:23" ht="30">
       <c r="A382" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51002,7 +51265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="45" hidden="1">
+    <row r="383" spans="1:23" ht="45">
       <c r="A383" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51073,7 +51336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:23" ht="30" hidden="1">
+    <row r="384" spans="1:23" ht="30">
       <c r="A384" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51144,7 +51407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:23" ht="30" hidden="1">
+    <row r="385" spans="1:23" ht="30">
       <c r="A385" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51215,7 +51478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="30" hidden="1">
+    <row r="386" spans="1:23" ht="30">
       <c r="A386" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51286,7 +51549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:23" ht="30" hidden="1">
+    <row r="387" spans="1:23" ht="30">
       <c r="A387" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51357,7 +51620,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:23" ht="30" hidden="1">
+    <row r="388" spans="1:23" ht="30">
       <c r="A388" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51428,7 +51691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="30" hidden="1">
+    <row r="389" spans="1:23" ht="30">
       <c r="A389" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51499,7 +51762,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:23" ht="30" hidden="1">
+    <row r="390" spans="1:23" ht="30">
       <c r="A390" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51570,7 +51833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:23" ht="30" hidden="1">
+    <row r="391" spans="1:23" ht="30">
       <c r="A391" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51641,7 +51904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:23" ht="30" hidden="1">
+    <row r="392" spans="1:23" ht="30">
       <c r="A392" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51712,7 +51975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="30" hidden="1">
+    <row r="393" spans="1:23" ht="30">
       <c r="A393" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51783,7 +52046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:23" ht="30" hidden="1">
+    <row r="394" spans="1:23" ht="30">
       <c r="A394" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51854,7 +52117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:23" ht="45" hidden="1">
+    <row r="395" spans="1:23" ht="45">
       <c r="A395" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51925,7 +52188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:23" ht="30" hidden="1">
+    <row r="396" spans="1:23" ht="30">
       <c r="A396" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51996,7 +52259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:23" ht="30" hidden="1">
+    <row r="397" spans="1:23" ht="30">
       <c r="A397" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52067,7 +52330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="398" spans="1:23" ht="30" hidden="1">
+    <row r="398" spans="1:23" ht="30">
       <c r="A398" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52138,7 +52401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:23" ht="30" hidden="1">
+    <row r="399" spans="1:23" ht="30">
       <c r="A399" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52209,7 +52472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="400" spans="1:23" ht="30" hidden="1">
+    <row r="400" spans="1:23" ht="30">
       <c r="A400" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52280,7 +52543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:23" ht="30" hidden="1">
+    <row r="401" spans="1:23" ht="30">
       <c r="A401" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52351,7 +52614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:23" hidden="1">
+    <row r="402" spans="1:23">
       <c r="A402" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52422,7 +52685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:23" ht="30" hidden="1">
+    <row r="403" spans="1:23" ht="30">
       <c r="A403" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52493,7 +52756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:23" ht="30" hidden="1">
+    <row r="404" spans="1:23" ht="30">
       <c r="A404" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52531,7 +52794,7 @@
         <v>7</v>
       </c>
       <c r="M404" s="4" t="s">
-        <v>8</v>
+        <v>3979</v>
       </c>
       <c r="N404" s="4" t="s">
         <v>2124</v>
@@ -52558,13 +52821,13 @@
         <v>7</v>
       </c>
       <c r="V404" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W404" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:23" ht="45" hidden="1">
+    <row r="405" spans="1:23" ht="45">
       <c r="A405" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52632,7 +52895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:23" ht="30" hidden="1">
+    <row r="406" spans="1:23" ht="30">
       <c r="A406" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52700,7 +52963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:23" ht="45" hidden="1">
+    <row r="407" spans="1:23" ht="45">
       <c r="A407" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52771,7 +53034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:23" ht="30" hidden="1">
+    <row r="408" spans="1:23" ht="30">
       <c r="A408" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52842,7 +53105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:23" ht="30" hidden="1">
+    <row r="409" spans="1:23" ht="30">
       <c r="A409" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52850,22 +53113,22 @@
         <v>8</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>2142</v>
+        <v>3980</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>2143</v>
+        <v>3981</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F409" s="4" t="s">
-        <v>2144</v>
+        <v>171</v>
+      </c>
+      <c r="F409" s="4">
+        <v>500</v>
       </c>
       <c r="G409" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H409" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I409" s="4" t="s">
         <v>6</v>
@@ -52880,37 +53143,40 @@
         <v>6</v>
       </c>
       <c r="M409" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N409" s="4" t="s">
-        <v>2145</v>
+        <v>3982</v>
       </c>
       <c r="O409" s="4" t="s">
-        <v>2146</v>
-      </c>
-      <c r="P409" s="4">
-        <v>20</v>
+        <v>3983</v>
+      </c>
+      <c r="P409" s="4" t="s">
+        <v>3984</v>
       </c>
       <c r="Q409" s="4" t="s">
+        <v>3985</v>
+      </c>
+      <c r="R409" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="R409" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="S409" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T409" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U409" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V409" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W409" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:23" ht="30" hidden="1">
+    <row r="410" spans="1:23" ht="30">
       <c r="A410" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52918,22 +53184,22 @@
         <v>9</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>466</v>
+        <v>3986</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>467</v>
+        <v>3987</v>
       </c>
       <c r="E410" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="F410" s="4" t="s">
-        <v>269</v>
+        <v>171</v>
+      </c>
+      <c r="F410" s="4">
+        <v>50</v>
       </c>
       <c r="G410" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H410" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I410" s="4" t="s">
         <v>6</v>
@@ -52951,20 +53217,20 @@
         <v>8</v>
       </c>
       <c r="N410" s="4" t="s">
-        <v>2147</v>
+        <v>3988</v>
       </c>
       <c r="O410" s="4" t="s">
-        <v>2148</v>
-      </c>
-      <c r="P410" s="17">
-        <v>46249</v>
+        <v>3989</v>
+      </c>
+      <c r="P410" s="4" t="s">
+        <v>3990</v>
       </c>
       <c r="Q410" s="4" t="s">
+        <v>3991</v>
+      </c>
+      <c r="R410" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="R410" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="S410" s="4" t="s">
         <v>7</v>
       </c>
@@ -52975,10 +53241,13 @@
         <v>7</v>
       </c>
       <c r="V410" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W410" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:23" ht="30" hidden="1">
+    <row r="411" spans="1:23" ht="45">
       <c r="A411" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52986,16 +53255,16 @@
         <v>10</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>471</v>
+        <v>3992</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>472</v>
+        <v>3993</v>
       </c>
       <c r="E411" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="F411" s="4" t="s">
-        <v>269</v>
+        <v>171</v>
+      </c>
+      <c r="F411" s="4">
+        <v>100</v>
       </c>
       <c r="G411" s="4" t="s">
         <v>6</v>
@@ -53019,20 +53288,20 @@
         <v>8</v>
       </c>
       <c r="N411" s="4" t="s">
-        <v>2149</v>
+        <v>3994</v>
       </c>
       <c r="O411" s="4" t="s">
-        <v>2150</v>
-      </c>
-      <c r="P411" s="17">
-        <v>46295</v>
+        <v>3995</v>
+      </c>
+      <c r="P411" s="4" t="s">
+        <v>3996</v>
       </c>
       <c r="Q411" s="4" t="s">
+        <v>3997</v>
+      </c>
+      <c r="R411" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="R411" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="S411" s="4" t="s">
         <v>7</v>
       </c>
@@ -53043,10 +53312,13 @@
         <v>7</v>
       </c>
       <c r="V411" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W411" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:23" ht="30" hidden="1">
+    <row r="412" spans="1:23" ht="30">
       <c r="A412" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53054,16 +53326,16 @@
         <v>11</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>42</v>
+        <v>3998</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>1013</v>
+        <v>3999</v>
       </c>
       <c r="E412" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F412" s="4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G412" s="4" t="s">
         <v>7</v>
@@ -53075,34 +53347,34 @@
         <v>6</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>42</v>
+        <v>269</v>
       </c>
       <c r="L412" s="4" t="s">
         <v>6</v>
       </c>
       <c r="M412" s="4" t="s">
-        <v>197</v>
+        <v>8</v>
       </c>
       <c r="N412" s="4" t="s">
-        <v>2151</v>
+        <v>4000</v>
       </c>
       <c r="O412" s="4" t="s">
-        <v>2152</v>
+        <v>4001</v>
       </c>
       <c r="P412" s="4" t="s">
-        <v>2153</v>
+        <v>4002</v>
       </c>
       <c r="Q412" s="4" t="s">
-        <v>865</v>
+        <v>4003</v>
       </c>
       <c r="R412" s="4" t="s">
         <v>269</v>
       </c>
       <c r="S412" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T412" s="4" t="s">
         <v>7</v>
@@ -53117,7 +53389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:23" ht="30" hidden="1">
+    <row r="413" spans="1:23" ht="45">
       <c r="A413" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53125,16 +53397,16 @@
         <v>12</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>132</v>
+        <v>4004</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>133</v>
+        <v>4005</v>
       </c>
       <c r="E413" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F413" s="4" t="s">
-        <v>269</v>
+        <v>171</v>
+      </c>
+      <c r="F413" s="4">
+        <v>30</v>
       </c>
       <c r="G413" s="4" t="s">
         <v>7</v>
@@ -53155,25 +53427,25 @@
         <v>6</v>
       </c>
       <c r="M413" s="4" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="N413" s="4" t="s">
-        <v>2154</v>
+        <v>4006</v>
       </c>
       <c r="O413" s="4" t="s">
-        <v>2155</v>
+        <v>4007</v>
       </c>
       <c r="P413" s="4" t="s">
-        <v>2037</v>
-      </c>
-      <c r="Q413" s="15">
-        <v>46248.583333333336</v>
+        <v>4008</v>
+      </c>
+      <c r="Q413" s="4" t="s">
+        <v>4009</v>
       </c>
       <c r="R413" s="4" t="s">
         <v>269</v>
       </c>
       <c r="S413" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T413" s="4" t="s">
         <v>7</v>
@@ -53182,13 +53454,13 @@
         <v>7</v>
       </c>
       <c r="V413" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W413" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:23" ht="30" hidden="1">
+    <row r="414" spans="1:23" ht="30">
       <c r="A414" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53196,55 +53468,55 @@
         <v>13</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>137</v>
+        <v>4010</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>138</v>
+        <v>4011</v>
       </c>
       <c r="E414" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F414" s="4">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="G414" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H414" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I414" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K414" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L414" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M414" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L414" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M414" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="N414" s="4" t="s">
-        <v>2156</v>
+        <v>4012</v>
       </c>
       <c r="O414" s="4" t="s">
-        <v>2157</v>
+        <v>4013</v>
       </c>
       <c r="P414" s="4" t="s">
-        <v>140</v>
+        <v>4014</v>
       </c>
       <c r="Q414" s="4" t="s">
-        <v>2040</v>
+        <v>4015</v>
       </c>
       <c r="R414" s="4" t="s">
         <v>269</v>
       </c>
       <c r="S414" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T414" s="4" t="s">
         <v>7</v>
@@ -53253,13 +53525,13 @@
         <v>6</v>
       </c>
       <c r="V414" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W414" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:23" ht="30" hidden="1">
+    <row r="415" spans="1:23" ht="30">
       <c r="A415" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53267,22 +53539,22 @@
         <v>14</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>241</v>
+        <v>2142</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>141</v>
+        <v>2143</v>
       </c>
       <c r="E415" s="4" t="s">
-        <v>296</v>
+        <v>173</v>
       </c>
       <c r="F415" s="4" t="s">
-        <v>269</v>
+        <v>2144</v>
       </c>
       <c r="G415" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H415" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I415" s="4" t="s">
         <v>6</v>
@@ -53297,25 +53569,25 @@
         <v>6</v>
       </c>
       <c r="M415" s="4" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="N415" s="4" t="s">
-        <v>2087</v>
+        <v>2145</v>
       </c>
       <c r="O415" s="4" t="s">
-        <v>2158</v>
-      </c>
-      <c r="P415" s="4" t="s">
-        <v>2088</v>
-      </c>
-      <c r="Q415" s="15">
-        <v>46248.586805555555</v>
+        <v>2146</v>
+      </c>
+      <c r="P415" s="4">
+        <v>20</v>
+      </c>
+      <c r="Q415" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="R415" s="4" t="s">
-        <v>269</v>
+        <v>7</v>
       </c>
       <c r="S415" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T415" s="4" t="s">
         <v>7</v>
@@ -53324,13 +53596,10 @@
         <v>7</v>
       </c>
       <c r="V415" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="W415" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="416" spans="1:23" ht="30" hidden="1">
+    <row r="416" spans="1:23" ht="30">
       <c r="A416" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53338,16 +53607,16 @@
         <v>15</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>245</v>
+        <v>466</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>144</v>
+        <v>467</v>
       </c>
       <c r="E416" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F416" s="4">
-        <v>36</v>
+        <v>291</v>
+      </c>
+      <c r="F416" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="G416" s="4" t="s">
         <v>7</v>
@@ -53359,49 +53628,46 @@
         <v>6</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K416" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L416" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M416" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L416" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M416" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="N416" s="4" t="s">
-        <v>2159</v>
+        <v>2147</v>
       </c>
       <c r="O416" s="4" t="s">
-        <v>2089</v>
-      </c>
-      <c r="P416" s="4" t="s">
-        <v>2160</v>
+        <v>2148</v>
+      </c>
+      <c r="P416" s="17">
+        <v>46249</v>
       </c>
       <c r="Q416" s="4" t="s">
-        <v>2040</v>
+        <v>269</v>
       </c>
       <c r="R416" s="4" t="s">
-        <v>269</v>
+        <v>6</v>
       </c>
       <c r="S416" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T416" s="4" t="s">
         <v>7</v>
       </c>
       <c r="U416" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V416" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="W416" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="1:23" ht="30" hidden="1">
+    <row r="417" spans="1:23" ht="30">
       <c r="A417" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53409,22 +53675,22 @@
         <v>16</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>147</v>
+        <v>471</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>148</v>
+        <v>472</v>
       </c>
       <c r="E417" s="4" t="s">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="F417" s="4" t="s">
         <v>269</v>
       </c>
       <c r="G417" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H417" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I417" s="4" t="s">
         <v>6</v>
@@ -53439,40 +53705,37 @@
         <v>6</v>
       </c>
       <c r="M417" s="4" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="N417" s="4" t="s">
-        <v>615</v>
+        <v>2149</v>
       </c>
       <c r="O417" s="4" t="s">
-        <v>2161</v>
-      </c>
-      <c r="P417" s="4" t="s">
-        <v>2162</v>
+        <v>2150</v>
+      </c>
+      <c r="P417" s="17">
+        <v>46295</v>
       </c>
       <c r="Q417" s="4" t="s">
-        <v>6</v>
+        <v>269</v>
       </c>
       <c r="R417" s="4" t="s">
         <v>6</v>
       </c>
       <c r="S417" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T417" s="4" t="s">
         <v>7</v>
       </c>
       <c r="U417" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V417" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="W417" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="418" spans="1:23" ht="30" hidden="1">
+    <row r="418" spans="1:23" ht="30">
       <c r="A418" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53480,522 +53743,522 @@
         <v>17</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>252</v>
+        <v>42</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>152</v>
+        <v>1013</v>
       </c>
       <c r="E418" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F418" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F418" s="4">
+        <v>36</v>
+      </c>
+      <c r="G418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H418" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I418" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J418" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K418" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L418" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M418" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="N418" s="4" t="s">
+        <v>2151</v>
+      </c>
+      <c r="O418" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="P418" s="4" t="s">
+        <v>2153</v>
+      </c>
+      <c r="Q418" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="R418" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="G418" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H418" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I418" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J418" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K418" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="L418" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M418" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N418" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="O418" s="4" t="s">
-        <v>2047</v>
-      </c>
-      <c r="P418" s="4" t="s">
-        <v>2163</v>
-      </c>
-      <c r="Q418" s="4">
-        <v>1</v>
-      </c>
-      <c r="R418" s="4">
-        <v>1</v>
-      </c>
       <c r="S418" s="4" t="s">
         <v>6</v>
       </c>
       <c r="T418" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U418" s="4" t="s">
         <v>7</v>
       </c>
       <c r="V418" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W418" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:23" ht="45" hidden="1">
-      <c r="A419" s="3" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B419" s="5">
+    <row r="419" spans="1:23" ht="30">
+      <c r="A419" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B419" s="4">
+        <v>18</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E419" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F419" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K419" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M419" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N419" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="O419" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="P419" s="4" t="s">
+        <v>2037</v>
+      </c>
+      <c r="Q419" s="15">
+        <v>46248.583333333336</v>
+      </c>
+      <c r="R419" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U419" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V419" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W419" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="420" spans="1:23" ht="30">
+      <c r="A420" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B420" s="4">
+        <v>19</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E420" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F420" s="4">
+        <v>36</v>
+      </c>
+      <c r="G420" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J420" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K420" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M420" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N420" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="O420" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="P420" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q420" s="4" t="s">
+        <v>2040</v>
+      </c>
+      <c r="R420" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T420" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V420" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W420" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="421" spans="1:23" ht="30">
+      <c r="A421" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B421" s="4">
+        <v>20</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E421" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F421" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K421" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M421" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N421" s="4" t="s">
+        <v>2087</v>
+      </c>
+      <c r="O421" s="4" t="s">
+        <v>2158</v>
+      </c>
+      <c r="P421" s="4" t="s">
+        <v>2088</v>
+      </c>
+      <c r="Q421" s="15">
+        <v>46248.586805555555</v>
+      </c>
+      <c r="R421" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U421" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V421" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W421" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="422" spans="1:23" ht="30">
+      <c r="A422" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B422" s="4">
+        <v>21</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E422" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F422" s="4">
+        <v>36</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J422" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K422" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M422" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N422" s="4" t="s">
+        <v>2159</v>
+      </c>
+      <c r="O422" s="4" t="s">
+        <v>2089</v>
+      </c>
+      <c r="P422" s="4" t="s">
+        <v>2160</v>
+      </c>
+      <c r="Q422" s="4" t="s">
+        <v>2040</v>
+      </c>
+      <c r="R422" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T422" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V422" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W422" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="423" spans="1:23" ht="30">
+      <c r="A423" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B423" s="4">
+        <v>22</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K423" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M423" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N423" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="O423" s="4" t="s">
+        <v>2161</v>
+      </c>
+      <c r="P423" s="4" t="s">
+        <v>2162</v>
+      </c>
+      <c r="Q423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="R423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="S423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T423" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V423" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W423" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="424" spans="1:23" ht="30">
+      <c r="A424" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B424" s="4">
+        <v>23</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E424" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G424" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K424" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M424" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N424" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="O424" s="4" t="s">
+        <v>2047</v>
+      </c>
+      <c r="P424" s="4" t="s">
+        <v>2163</v>
+      </c>
+      <c r="Q424" s="4">
         <v>1</v>
       </c>
-      <c r="C419" s="3" t="s">
-        <v>2355</v>
-      </c>
-      <c r="D419" s="3" t="s">
-        <v>2352</v>
-      </c>
-      <c r="E419" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F419" s="5">
-        <v>36</v>
-      </c>
-      <c r="G419" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H419" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I419" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J419" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K419" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L419" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M419" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N419" s="3" t="s">
-        <v>2356</v>
-      </c>
-      <c r="O419" s="3" t="s">
-        <v>2357</v>
-      </c>
-      <c r="P419" s="3" t="s">
-        <v>2358</v>
-      </c>
-      <c r="Q419" s="3" t="s">
-        <v>2359</v>
-      </c>
-      <c r="R419" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S419" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T419" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="U419" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V419" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="W419" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="420" spans="1:23" ht="30" hidden="1">
-      <c r="A420" s="3" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B420" s="5">
-        <v>2</v>
-      </c>
-      <c r="C420" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D420" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E420" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F420" s="5">
-        <v>36</v>
-      </c>
-      <c r="G420" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H420" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I420" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J420" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K420" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L420" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M420" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N420" s="3" t="s">
-        <v>2360</v>
-      </c>
-      <c r="O420" s="3" t="s">
-        <v>2361</v>
-      </c>
-      <c r="P420" s="3" t="s">
-        <v>2362</v>
-      </c>
-      <c r="Q420" s="3" t="s">
-        <v>2363</v>
-      </c>
-      <c r="R420" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S420" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T420" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U420" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V420" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="W420" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="421" spans="1:23" ht="45" hidden="1">
-      <c r="A421" s="3" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B421" s="5">
-        <v>3</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>1924</v>
-      </c>
-      <c r="D421" s="3" t="s">
-        <v>1915</v>
-      </c>
-      <c r="E421" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F421" s="5">
-        <v>36</v>
-      </c>
-      <c r="G421" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H421" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I421" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J421" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K421" s="3" t="s">
-        <v>1911</v>
-      </c>
-      <c r="L421" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M421" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N421" s="3" t="s">
-        <v>2364</v>
-      </c>
-      <c r="O421" s="3" t="s">
-        <v>2365</v>
-      </c>
-      <c r="P421" s="3" t="s">
-        <v>2366</v>
-      </c>
-      <c r="Q421" s="3" t="s">
-        <v>2367</v>
-      </c>
-      <c r="R421" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S421" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T421" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U421" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V421" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W421" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="422" spans="1:23" ht="30" hidden="1">
-      <c r="A422" s="3" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B422" s="5">
-        <v>4</v>
-      </c>
-      <c r="C422" s="3" t="s">
-        <v>2353</v>
-      </c>
-      <c r="D422" s="3" t="s">
-        <v>2368</v>
-      </c>
-      <c r="E422" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F422" s="5">
-        <v>150</v>
-      </c>
-      <c r="G422" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K422" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N422" s="3" t="s">
-        <v>2369</v>
-      </c>
-      <c r="O422" s="3" t="s">
-        <v>2370</v>
-      </c>
-      <c r="P422" s="3" t="s">
-        <v>2371</v>
-      </c>
-      <c r="Q422" s="3" t="s">
-        <v>2372</v>
-      </c>
-      <c r="R422" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S422" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T422" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U422" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V422" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W422" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="423" spans="1:23" ht="45" hidden="1">
-      <c r="A423" s="3" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B423" s="5">
-        <v>5</v>
-      </c>
-      <c r="C423" s="3" t="s">
-        <v>2373</v>
-      </c>
-      <c r="D423" s="3" t="s">
-        <v>2374</v>
-      </c>
-      <c r="E423" s="3" t="s">
-        <v>1951</v>
-      </c>
-      <c r="F423" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G423" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K423" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N423" s="3" t="s">
-        <v>2375</v>
-      </c>
-      <c r="O423" s="3" t="s">
-        <v>2376</v>
-      </c>
-      <c r="P423" s="3" t="s">
-        <v>2411</v>
-      </c>
-      <c r="Q423" s="3" t="s">
-        <v>2377</v>
-      </c>
-      <c r="R423" s="3" t="s">
-        <v>2378</v>
-      </c>
-      <c r="S423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="U423" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V423" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W423" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="424" spans="1:23" ht="45" hidden="1">
-      <c r="A424" s="3" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B424" s="5">
-        <v>6</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>2379</v>
-      </c>
-      <c r="D424" s="3" t="s">
-        <v>2380</v>
-      </c>
-      <c r="E424" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F424" s="5">
-        <v>36</v>
-      </c>
-      <c r="G424" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H424" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I424" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J424" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K424" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L424" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M424" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N424" s="3" t="s">
-        <v>2381</v>
-      </c>
-      <c r="O424" s="3" t="s">
-        <v>2382</v>
-      </c>
-      <c r="P424" s="3" t="s">
-        <v>2383</v>
-      </c>
-      <c r="Q424" s="3" t="s">
-        <v>2384</v>
-      </c>
-      <c r="R424" s="3" t="s">
-        <v>2412</v>
-      </c>
-      <c r="S424" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T424" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U424" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V424" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W424" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="425" spans="1:23" ht="45" hidden="1">
+      <c r="R424" s="4">
+        <v>1</v>
+      </c>
+      <c r="S424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U424" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V424" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W424" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="425" spans="1:23" ht="45">
       <c r="A425" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B425" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>2385</v>
+        <v>2355</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>2386</v>
+        <v>2352</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F425" s="5" t="s">
-        <v>72</v>
+        <v>168</v>
+      </c>
+      <c r="F425" s="5">
+        <v>36</v>
       </c>
       <c r="G425" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H425" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I425" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J425" s="3" t="s">
         <v>6</v>
@@ -54004,31 +54267,31 @@
         <v>72</v>
       </c>
       <c r="L425" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M425" s="3" t="s">
         <v>73</v>
       </c>
       <c r="N425" s="3" t="s">
-        <v>2387</v>
+        <v>2356</v>
       </c>
       <c r="O425" s="3" t="s">
-        <v>2388</v>
+        <v>2357</v>
       </c>
       <c r="P425" s="3" t="s">
-        <v>2389</v>
+        <v>2358</v>
       </c>
       <c r="Q425" s="3" t="s">
-        <v>2390</v>
+        <v>2359</v>
       </c>
       <c r="R425" s="3" t="s">
         <v>72</v>
       </c>
       <c r="S425" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T425" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U425" s="3" t="s">
         <v>7</v>
@@ -54040,18 +54303,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="1:23" ht="30" hidden="1">
+    <row r="426" spans="1:23" ht="30">
       <c r="A426" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B426" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>2391</v>
+        <v>71</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>2392</v>
+        <v>23</v>
       </c>
       <c r="E426" s="3" t="s">
         <v>168</v>
@@ -54060,10 +54323,10 @@
         <v>36</v>
       </c>
       <c r="G426" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H426" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I426" s="3" t="s">
         <v>6</v>
@@ -54072,25 +54335,25 @@
         <v>7</v>
       </c>
       <c r="K426" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L426" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M426" s="3" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N426" s="3" t="s">
-        <v>2393</v>
+        <v>2360</v>
       </c>
       <c r="O426" s="3" t="s">
-        <v>2394</v>
+        <v>2361</v>
       </c>
       <c r="P426" s="3" t="s">
-        <v>2395</v>
+        <v>2362</v>
       </c>
       <c r="Q426" s="3" t="s">
-        <v>2396</v>
+        <v>2363</v>
       </c>
       <c r="R426" s="3" t="s">
         <v>72</v>
@@ -54111,24 +54374,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="1:23" ht="30" hidden="1">
+    <row r="427" spans="1:23" ht="45">
       <c r="A427" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B427" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>132</v>
+        <v>1924</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>133</v>
+        <v>1915</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F427" s="5" t="s">
-        <v>72</v>
+        <v>168</v>
+      </c>
+      <c r="F427" s="5">
+        <v>36</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>7</v>
@@ -54140,34 +54403,34 @@
         <v>6</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K427" s="3" t="s">
-        <v>72</v>
+        <v>1911</v>
       </c>
       <c r="L427" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M427" s="3" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N427" s="3" t="s">
-        <v>1967</v>
+        <v>2364</v>
       </c>
       <c r="O427" s="3" t="s">
-        <v>2397</v>
+        <v>2365</v>
       </c>
       <c r="P427" s="3" t="s">
-        <v>2398</v>
+        <v>2366</v>
       </c>
       <c r="Q427" s="3" t="s">
-        <v>2399</v>
+        <v>2367</v>
       </c>
       <c r="R427" s="3" t="s">
         <v>72</v>
       </c>
       <c r="S427" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T427" s="3" t="s">
         <v>7</v>
@@ -54176,30 +54439,30 @@
         <v>7</v>
       </c>
       <c r="V427" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W427" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="428" spans="1:23" ht="30" hidden="1">
+    <row r="428" spans="1:23" ht="30">
       <c r="A428" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B428" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>137</v>
+        <v>2353</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>138</v>
+        <v>2368</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F428" s="5">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="G428" s="3" t="s">
         <v>7</v>
@@ -54211,28 +54474,28 @@
         <v>6</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K428" s="3" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="L428" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M428" s="3" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N428" s="3" t="s">
-        <v>1970</v>
+        <v>2369</v>
       </c>
       <c r="O428" s="3" t="s">
-        <v>2400</v>
+        <v>2370</v>
       </c>
       <c r="P428" s="3" t="s">
-        <v>2401</v>
+        <v>2371</v>
       </c>
       <c r="Q428" s="3" t="s">
-        <v>2396</v>
+        <v>2372</v>
       </c>
       <c r="R428" s="3" t="s">
         <v>72</v>
@@ -54247,27 +54510,27 @@
         <v>7</v>
       </c>
       <c r="V428" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W428" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:23" ht="30" hidden="1">
+    <row r="429" spans="1:23" ht="45">
       <c r="A429" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B429" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>241</v>
+        <v>2373</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>141</v>
+        <v>2374</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>296</v>
+        <v>1951</v>
       </c>
       <c r="F429" s="5" t="s">
         <v>72</v>
@@ -54291,51 +54554,51 @@
         <v>6</v>
       </c>
       <c r="M429" s="3" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N429" s="3" t="s">
-        <v>1973</v>
+        <v>2375</v>
       </c>
       <c r="O429" s="3" t="s">
-        <v>2402</v>
+        <v>2376</v>
       </c>
       <c r="P429" s="3" t="s">
-        <v>2403</v>
+        <v>2411</v>
       </c>
       <c r="Q429" s="3" t="s">
-        <v>2404</v>
+        <v>2377</v>
       </c>
       <c r="R429" s="3" t="s">
-        <v>72</v>
+        <v>2378</v>
       </c>
       <c r="S429" s="3" t="s">
         <v>6</v>
       </c>
       <c r="T429" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U429" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V429" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W429" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="1:23" ht="30" hidden="1">
+    <row r="430" spans="1:23" ht="45">
       <c r="A430" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B430" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>245</v>
+        <v>2379</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>144</v>
+        <v>2380</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>168</v>
@@ -54356,28 +54619,28 @@
         <v>7</v>
       </c>
       <c r="K430" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="L430" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M430" s="3" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N430" s="3" t="s">
-        <v>1975</v>
+        <v>2381</v>
       </c>
       <c r="O430" s="3" t="s">
-        <v>2405</v>
+        <v>2382</v>
       </c>
       <c r="P430" s="3" t="s">
-        <v>2406</v>
+        <v>2383</v>
       </c>
       <c r="Q430" s="3" t="s">
-        <v>2396</v>
+        <v>2384</v>
       </c>
       <c r="R430" s="3" t="s">
-        <v>72</v>
+        <v>2412</v>
       </c>
       <c r="S430" s="3" t="s">
         <v>7</v>
@@ -54389,36 +54652,36 @@
         <v>7</v>
       </c>
       <c r="V430" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W430" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:23" ht="30" hidden="1">
+    <row r="431" spans="1:23" ht="45">
       <c r="A431" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B431" s="5">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>147</v>
+        <v>2385</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>148</v>
+        <v>2386</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>174</v>
+        <v>296</v>
       </c>
       <c r="F431" s="5" t="s">
         <v>72</v>
       </c>
       <c r="G431" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H431" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I431" s="3" t="s">
         <v>6</v>
@@ -54436,19 +54699,19 @@
         <v>73</v>
       </c>
       <c r="N431" s="3" t="s">
-        <v>149</v>
+        <v>2387</v>
       </c>
       <c r="O431" s="3" t="s">
-        <v>2407</v>
+        <v>2388</v>
       </c>
       <c r="P431" s="3" t="s">
-        <v>2408</v>
-      </c>
-      <c r="Q431" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R431" s="3" t="b">
-        <v>0</v>
+        <v>2389</v>
+      </c>
+      <c r="Q431" s="3" t="s">
+        <v>2390</v>
+      </c>
+      <c r="R431" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="S431" s="3" t="s">
         <v>6</v>
@@ -54457,7 +54720,7 @@
         <v>7</v>
       </c>
       <c r="U431" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V431" s="3" t="s">
         <v>6</v>
@@ -54466,39 +54729,39 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:23" ht="30" hidden="1">
+    <row r="432" spans="1:23" ht="30">
       <c r="A432" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B432" s="5">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>252</v>
+        <v>2391</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>152</v>
+        <v>2392</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F432" s="5" t="s">
-        <v>72</v>
+        <v>168</v>
+      </c>
+      <c r="F432" s="5">
+        <v>36</v>
       </c>
       <c r="G432" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H432" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I432" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="L432" s="3" t="s">
         <v>6</v>
@@ -54507,480 +54770,480 @@
         <v>73</v>
       </c>
       <c r="N432" s="3" t="s">
+        <v>2393</v>
+      </c>
+      <c r="O432" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="P432" s="3" t="s">
+        <v>2395</v>
+      </c>
+      <c r="Q432" s="3" t="s">
+        <v>2396</v>
+      </c>
+      <c r="R432" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S432" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T432" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U432" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V432" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W432" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="433" spans="1:23" ht="30">
+      <c r="A433" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B433" s="5">
+        <v>9</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E433" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F433" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G433" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H433" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I433" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J433" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K433" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L433" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M433" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N433" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="O433" s="3" t="s">
+        <v>2397</v>
+      </c>
+      <c r="P433" s="3" t="s">
+        <v>2398</v>
+      </c>
+      <c r="Q433" s="3" t="s">
+        <v>2399</v>
+      </c>
+      <c r="R433" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S433" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T433" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U433" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V433" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W433" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="434" spans="1:23" ht="30">
+      <c r="A434" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B434" s="5">
+        <v>10</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E434" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F434" s="5">
+        <v>36</v>
+      </c>
+      <c r="G434" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H434" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I434" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J434" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K434" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L434" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M434" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N434" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="O434" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="P434" s="3" t="s">
+        <v>2401</v>
+      </c>
+      <c r="Q434" s="3" t="s">
+        <v>2396</v>
+      </c>
+      <c r="R434" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S434" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T434" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U434" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V434" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W434" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="435" spans="1:23" ht="30">
+      <c r="A435" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B435" s="5">
+        <v>11</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E435" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F435" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G435" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H435" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I435" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J435" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K435" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L435" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M435" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N435" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O435" s="3" t="s">
+        <v>2402</v>
+      </c>
+      <c r="P435" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="Q435" s="3" t="s">
+        <v>2404</v>
+      </c>
+      <c r="R435" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S435" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T435" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U435" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V435" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W435" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="436" spans="1:23" ht="30">
+      <c r="A436" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B436" s="5">
+        <v>12</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E436" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F436" s="5">
+        <v>36</v>
+      </c>
+      <c r="G436" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H436" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I436" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J436" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K436" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L436" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M436" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N436" s="3" t="s">
+        <v>1975</v>
+      </c>
+      <c r="O436" s="3" t="s">
+        <v>2405</v>
+      </c>
+      <c r="P436" s="3" t="s">
+        <v>2406</v>
+      </c>
+      <c r="Q436" s="3" t="s">
+        <v>2396</v>
+      </c>
+      <c r="R436" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S436" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T436" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U436" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V436" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W436" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="437" spans="1:23" ht="30">
+      <c r="A437" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B437" s="5">
+        <v>13</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E437" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F437" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G437" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K437" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M437" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N437" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="O437" s="3" t="s">
+        <v>2407</v>
+      </c>
+      <c r="P437" s="3" t="s">
+        <v>2408</v>
+      </c>
+      <c r="Q437" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R437" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T437" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="V437" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W437" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="438" spans="1:23" ht="30">
+      <c r="A438" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B438" s="5">
+        <v>14</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E438" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F438" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G438" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K438" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M438" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N438" s="3" t="s">
         <v>1981</v>
       </c>
-      <c r="O432" s="3" t="s">
+      <c r="O438" s="3" t="s">
         <v>2409</v>
       </c>
-      <c r="P432" s="3" t="s">
+      <c r="P438" s="3" t="s">
         <v>2410</v>
       </c>
-      <c r="Q432" s="3">
+      <c r="Q438" s="3">
         <v>1</v>
       </c>
-      <c r="R432" s="3">
+      <c r="R438" s="3">
         <v>1</v>
       </c>
-      <c r="S432" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T432" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="U432" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V432" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="W432" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="433" spans="1:23" hidden="1">
-      <c r="A433" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B433" s="4">
-        <v>1</v>
-      </c>
-      <c r="C433" s="4" t="s">
-        <v>2504</v>
-      </c>
-      <c r="D433" s="4" t="s">
-        <v>2502</v>
-      </c>
-      <c r="E433" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F433" s="4">
-        <v>36</v>
-      </c>
-      <c r="G433" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H433" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I433" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J433" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K433" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L433" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M433" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N433" s="4" t="s">
-        <v>2505</v>
-      </c>
-      <c r="O433" s="4" t="s">
-        <v>2506</v>
-      </c>
-      <c r="P433" s="4" t="s">
-        <v>2507</v>
-      </c>
-      <c r="Q433" s="4" t="s">
-        <v>2508</v>
-      </c>
-      <c r="R433" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S433" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="T433" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="U433" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="V433" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="W433" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="434" spans="1:23" ht="30" hidden="1">
-      <c r="A434" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B434" s="4">
-        <v>2</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D434" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E434" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F434" s="4">
-        <v>36</v>
-      </c>
-      <c r="G434" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J434" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K434" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N434" s="4" t="s">
-        <v>2509</v>
-      </c>
-      <c r="O434" s="4" t="s">
-        <v>2510</v>
-      </c>
-      <c r="P434" s="4" t="s">
-        <v>2511</v>
-      </c>
-      <c r="Q434" s="4" t="s">
-        <v>2121</v>
-      </c>
-      <c r="R434" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S434" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="T434" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="U434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V434" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="W434" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="435" spans="1:23" ht="30" hidden="1">
-      <c r="A435" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B435" s="4">
-        <v>3</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>2512</v>
-      </c>
-      <c r="D435" s="4" t="s">
-        <v>2513</v>
-      </c>
-      <c r="E435" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F435" s="4">
-        <v>50</v>
-      </c>
-      <c r="G435" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H435" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I435" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J435" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K435" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L435" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M435" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N435" s="4" t="s">
-        <v>2514</v>
-      </c>
-      <c r="O435" s="4" t="s">
-        <v>2515</v>
-      </c>
-      <c r="P435" s="4" t="s">
-        <v>2516</v>
-      </c>
-      <c r="Q435" s="4" t="s">
-        <v>2517</v>
-      </c>
-      <c r="R435" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S435" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="T435" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="U435" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="V435" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="W435" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="436" spans="1:23" ht="45" hidden="1">
-      <c r="A436" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B436" s="4">
-        <v>4</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>1395</v>
-      </c>
-      <c r="D436" s="4" t="s">
-        <v>2518</v>
-      </c>
-      <c r="E436" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F436" s="4">
-        <v>150</v>
-      </c>
-      <c r="G436" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H436" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I436" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J436" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K436" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L436" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M436" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N436" s="4" t="s">
-        <v>2519</v>
-      </c>
-      <c r="O436" s="4" t="s">
-        <v>2520</v>
-      </c>
-      <c r="P436" s="4" t="s">
-        <v>2521</v>
-      </c>
-      <c r="Q436" s="4" t="s">
-        <v>2522</v>
-      </c>
-      <c r="R436" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S436" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="T436" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="U436" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="V436" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="W436" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="437" spans="1:23" ht="30" hidden="1">
-      <c r="A437" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B437" s="4">
-        <v>5</v>
-      </c>
-      <c r="C437" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D437" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="E437" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F437" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G437" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H437" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I437" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J437" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K437" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L437" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M437" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N437" s="4" t="s">
-        <v>2523</v>
-      </c>
-      <c r="O437" s="4" t="s">
-        <v>2524</v>
-      </c>
-      <c r="P437" s="4" t="s">
-        <v>2525</v>
-      </c>
-      <c r="Q437" s="4" t="s">
-        <v>2526</v>
-      </c>
-      <c r="R437" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S437" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="T437" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="U437" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V437" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="W437" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="438" spans="1:23" ht="45" hidden="1">
-      <c r="A438" s="4" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B438" s="4">
-        <v>6</v>
-      </c>
-      <c r="C438" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="D438" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E438" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F438" s="4">
-        <v>36</v>
-      </c>
-      <c r="G438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H438" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I438" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K438" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L438" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M438" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N438" s="4" t="s">
-        <v>2527</v>
-      </c>
-      <c r="O438" s="4" t="s">
-        <v>2528</v>
-      </c>
-      <c r="P438" s="4" t="s">
-        <v>2529</v>
-      </c>
-      <c r="Q438" s="4" t="s">
-        <v>865</v>
-      </c>
-      <c r="R438" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="T438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="U438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="V438" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="W438" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="439" spans="1:23" ht="30" hidden="1">
+      <c r="S438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="U438" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W438" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="439" spans="1:23">
       <c r="A439" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="B439" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>132</v>
+        <v>2504</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>133</v>
+        <v>2502</v>
       </c>
       <c r="E439" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F439" s="4" t="s">
-        <v>72</v>
+        <v>168</v>
+      </c>
+      <c r="F439" s="4">
+        <v>36</v>
       </c>
       <c r="G439" s="4" t="s">
         <v>7</v>
@@ -54989,7 +55252,7 @@
         <v>6</v>
       </c>
       <c r="I439" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J439" s="4" t="s">
         <v>6</v>
@@ -54998,28 +55261,28 @@
         <v>72</v>
       </c>
       <c r="L439" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M439" s="4" t="s">
         <v>73</v>
       </c>
       <c r="N439" s="4" t="s">
-        <v>2530</v>
+        <v>2505</v>
       </c>
       <c r="O439" s="4" t="s">
-        <v>2531</v>
+        <v>2506</v>
       </c>
       <c r="P439" s="4" t="s">
-        <v>2532</v>
+        <v>2507</v>
       </c>
       <c r="Q439" s="4" t="s">
-        <v>2533</v>
+        <v>2508</v>
       </c>
       <c r="R439" s="4" t="s">
-        <v>1567</v>
+        <v>72</v>
       </c>
       <c r="S439" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T439" s="4" t="s">
         <v>6</v>
@@ -55034,18 +55297,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:23" ht="30" hidden="1">
+    <row r="440" spans="1:23" ht="30">
       <c r="A440" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="B440" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="E440" s="4" t="s">
         <v>168</v>
@@ -55066,31 +55329,31 @@
         <v>7</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L440" s="4" t="s">
         <v>6</v>
       </c>
       <c r="M440" s="4" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="N440" s="4" t="s">
-        <v>2534</v>
+        <v>2509</v>
       </c>
       <c r="O440" s="4" t="s">
-        <v>2535</v>
+        <v>2510</v>
       </c>
       <c r="P440" s="4" t="s">
-        <v>2536</v>
+        <v>2511</v>
       </c>
       <c r="Q440" s="4" t="s">
-        <v>2027</v>
+        <v>2121</v>
       </c>
       <c r="R440" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S440" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T440" s="4" t="s">
         <v>7</v>
@@ -55105,24 +55368,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:23" ht="30" hidden="1">
+    <row r="441" spans="1:23" ht="30">
       <c r="A441" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="B441" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>241</v>
+        <v>2512</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>141</v>
+        <v>2513</v>
       </c>
       <c r="E441" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F441" s="4" t="s">
-        <v>72</v>
+        <v>171</v>
+      </c>
+      <c r="F441" s="4">
+        <v>50</v>
       </c>
       <c r="G441" s="4" t="s">
         <v>7</v>
@@ -55140,60 +55403,60 @@
         <v>72</v>
       </c>
       <c r="L441" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M441" s="4" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="N441" s="4" t="s">
-        <v>2537</v>
+        <v>2514</v>
       </c>
       <c r="O441" s="4" t="s">
-        <v>2538</v>
+        <v>2515</v>
       </c>
       <c r="P441" s="4" t="s">
-        <v>2539</v>
+        <v>2516</v>
       </c>
       <c r="Q441" s="4" t="s">
-        <v>2533</v>
+        <v>2517</v>
       </c>
       <c r="R441" s="4" t="s">
-        <v>1567</v>
+        <v>72</v>
       </c>
       <c r="S441" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T441" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U441" s="4" t="s">
         <v>7</v>
       </c>
       <c r="V441" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W441" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:23" ht="30" hidden="1">
+    <row r="442" spans="1:23" ht="45">
       <c r="A442" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="B442" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>245</v>
+        <v>1395</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>144</v>
+        <v>2518</v>
       </c>
       <c r="E442" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F442" s="4">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="G442" s="4" t="s">
         <v>7</v>
@@ -55205,72 +55468,72 @@
         <v>6</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K442" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L442" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M442" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L442" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M442" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="N442" s="4" t="s">
-        <v>2540</v>
+        <v>2519</v>
       </c>
       <c r="O442" s="4" t="s">
-        <v>2541</v>
+        <v>2520</v>
       </c>
       <c r="P442" s="4" t="s">
-        <v>2542</v>
+        <v>2521</v>
       </c>
       <c r="Q442" s="4" t="s">
-        <v>2027</v>
+        <v>2522</v>
       </c>
       <c r="R442" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S442" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T442" s="4" t="s">
         <v>7</v>
       </c>
       <c r="U442" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V442" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W442" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:23" ht="30" hidden="1">
+    <row r="443" spans="1:23" ht="30">
       <c r="A443" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="B443" s="4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>148</v>
+        <v>327</v>
       </c>
       <c r="E443" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F443" s="4" t="s">
-        <v>72</v>
+        <v>171</v>
+      </c>
+      <c r="F443" s="4">
+        <v>1000</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H443" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I443" s="4" t="s">
         <v>6</v>
@@ -55285,57 +55548,57 @@
         <v>6</v>
       </c>
       <c r="M443" s="4" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="N443" s="4" t="s">
-        <v>2543</v>
+        <v>2523</v>
       </c>
       <c r="O443" s="4" t="s">
-        <v>2544</v>
+        <v>2524</v>
       </c>
       <c r="P443" s="4" t="s">
-        <v>2545</v>
-      </c>
-      <c r="Q443" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R443" s="4" t="b">
-        <v>0</v>
+        <v>2525</v>
+      </c>
+      <c r="Q443" s="4" t="s">
+        <v>2526</v>
+      </c>
+      <c r="R443" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="S443" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T443" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U443" s="4" t="s">
         <v>6</v>
       </c>
       <c r="V443" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W443" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="444" spans="1:23" ht="30" hidden="1">
+    <row r="444" spans="1:23" ht="45">
       <c r="A444" s="4" t="s">
         <v>2426</v>
       </c>
       <c r="B444" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>252</v>
+        <v>461</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>152</v>
+        <v>1013</v>
       </c>
       <c r="E444" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F444" s="4" t="s">
-        <v>72</v>
+        <v>168</v>
+      </c>
+      <c r="F444" s="4">
+        <v>36</v>
       </c>
       <c r="G444" s="4" t="s">
         <v>7</v>
@@ -55347,466 +55610,486 @@
         <v>6</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="L444" s="4" t="s">
         <v>6</v>
       </c>
       <c r="M444" s="4" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="N444" s="4" t="s">
-        <v>2546</v>
+        <v>2527</v>
       </c>
       <c r="O444" s="4" t="s">
-        <v>2547</v>
+        <v>2528</v>
       </c>
       <c r="P444" s="4" t="s">
-        <v>2548</v>
-      </c>
-      <c r="Q444" s="4">
-        <v>1</v>
-      </c>
-      <c r="R444" s="4">
-        <v>1</v>
+        <v>2529</v>
+      </c>
+      <c r="Q444" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="R444" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="S444" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T444" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U444" s="4" t="s">
         <v>7</v>
       </c>
       <c r="V444" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W444" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:23" ht="30" hidden="1">
-      <c r="A445" s="3" t="s">
+    <row r="445" spans="1:23" ht="30">
+      <c r="A445" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B445" s="4">
+        <v>7</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E445" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F445" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G445" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K445" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M445" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N445" s="4" t="s">
+        <v>2530</v>
+      </c>
+      <c r="O445" s="4" t="s">
+        <v>2531</v>
+      </c>
+      <c r="P445" s="4" t="s">
+        <v>2532</v>
+      </c>
+      <c r="Q445" s="4" t="s">
+        <v>2533</v>
+      </c>
+      <c r="R445" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="S445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U445" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V445" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W445" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="446" spans="1:23" ht="30">
+      <c r="A446" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B446" s="4">
+        <v>8</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E446" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F446" s="4">
+        <v>36</v>
+      </c>
+      <c r="G446" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H446" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I446" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J446" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K446" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L446" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M446" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N446" s="4" t="s">
+        <v>2534</v>
+      </c>
+      <c r="O446" s="4" t="s">
+        <v>2535</v>
+      </c>
+      <c r="P446" s="4" t="s">
+        <v>2536</v>
+      </c>
+      <c r="Q446" s="4" t="s">
+        <v>2027</v>
+      </c>
+      <c r="R446" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S446" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T446" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U446" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V446" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W446" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="447" spans="1:23" ht="30">
+      <c r="A447" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B447" s="4">
+        <v>9</v>
+      </c>
+      <c r="C447" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E447" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F447" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G447" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K447" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M447" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N447" s="4" t="s">
+        <v>2537</v>
+      </c>
+      <c r="O447" s="4" t="s">
+        <v>2538</v>
+      </c>
+      <c r="P447" s="4" t="s">
+        <v>2539</v>
+      </c>
+      <c r="Q447" s="4" t="s">
+        <v>2533</v>
+      </c>
+      <c r="R447" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="S447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U447" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V447" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W447" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="448" spans="1:23" ht="30">
+      <c r="A448" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B448" s="4">
+        <v>10</v>
+      </c>
+      <c r="C448" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E448" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F448" s="4">
+        <v>36</v>
+      </c>
+      <c r="G448" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H448" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I448" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J448" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K448" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L448" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M448" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N448" s="4" t="s">
+        <v>2540</v>
+      </c>
+      <c r="O448" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="P448" s="4" t="s">
+        <v>2542</v>
+      </c>
+      <c r="Q448" s="4" t="s">
+        <v>2027</v>
+      </c>
+      <c r="R448" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S448" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T448" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U448" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V448" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W448" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="449" spans="1:23" ht="30">
+      <c r="A449" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B449" s="4">
+        <v>11</v>
+      </c>
+      <c r="C449" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E449" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F449" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G449" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K449" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M449" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N449" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="O449" s="4" t="s">
+        <v>2544</v>
+      </c>
+      <c r="P449" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="Q449" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R449" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T449" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V449" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W449" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="450" spans="1:23" ht="30">
+      <c r="A450" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B450" s="4">
+        <v>12</v>
+      </c>
+      <c r="C450" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E450" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F450" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G450" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K450" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M450" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N450" s="4" t="s">
+        <v>2546</v>
+      </c>
+      <c r="O450" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="P450" s="4" t="s">
+        <v>2548</v>
+      </c>
+      <c r="Q450" s="4">
+        <v>1</v>
+      </c>
+      <c r="R450" s="4">
+        <v>1</v>
+      </c>
+      <c r="S450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U450" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V450" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W450" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="451" spans="1:23" ht="30">
+      <c r="A451" s="3" t="s">
         <v>3691</v>
-      </c>
-      <c r="B445" s="5">
-        <v>1</v>
-      </c>
-      <c r="C445" s="3" t="s">
-        <v>3692</v>
-      </c>
-      <c r="D445" s="3" t="s">
-        <v>3693</v>
-      </c>
-      <c r="E445" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F445" s="5"/>
-      <c r="G445" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H445" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I445" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J445" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K445" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L445" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M445" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N445" s="3" t="s">
-        <v>3694</v>
-      </c>
-      <c r="O445" s="3" t="s">
-        <v>3695</v>
-      </c>
-      <c r="P445" s="3" t="s">
-        <v>3696</v>
-      </c>
-      <c r="Q445" s="3" t="s">
-        <v>3697</v>
-      </c>
-      <c r="R445" s="3"/>
-      <c r="S445" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T445" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U445" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V445" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="W445" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="446" spans="1:23" ht="30" hidden="1">
-      <c r="A446" s="3" t="s">
-        <v>3691</v>
-      </c>
-      <c r="B446" s="5">
-        <v>2</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>3698</v>
-      </c>
-      <c r="D446" s="3" t="s">
-        <v>3688</v>
-      </c>
-      <c r="E446" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F446" s="5"/>
-      <c r="G446" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H446" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I446" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J446" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K446" s="3" t="s">
-        <v>3684</v>
-      </c>
-      <c r="L446" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M446" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N446" s="3" t="s">
-        <v>3699</v>
-      </c>
-      <c r="O446" s="3" t="s">
-        <v>3700</v>
-      </c>
-      <c r="P446" s="3" t="s">
-        <v>3701</v>
-      </c>
-      <c r="Q446" s="3" t="s">
-        <v>3702</v>
-      </c>
-      <c r="R446" s="3"/>
-      <c r="S446" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T446" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U446" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V446" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W446" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="447" spans="1:23" ht="30" hidden="1">
-      <c r="A447" s="3" t="s">
-        <v>3691</v>
-      </c>
-      <c r="B447" s="5">
-        <v>3</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D447" s="3" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E447" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F447" s="5"/>
-      <c r="G447" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J447" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K447" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N447" s="3" t="s">
-        <v>3703</v>
-      </c>
-      <c r="O447" s="3" t="s">
-        <v>3704</v>
-      </c>
-      <c r="P447" s="3" t="s">
-        <v>3705</v>
-      </c>
-      <c r="Q447" s="3" t="s">
-        <v>2384</v>
-      </c>
-      <c r="R447" s="3"/>
-      <c r="S447" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T447" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U447" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V447" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W447" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="448" spans="1:23" ht="30" hidden="1">
-      <c r="A448" s="3" t="s">
-        <v>3691</v>
-      </c>
-      <c r="B448" s="5">
-        <v>4</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="D448" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E448" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F448" s="5"/>
-      <c r="G448" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H448" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I448" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J448" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K448" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L448" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M448" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N448" s="3" t="s">
-        <v>3706</v>
-      </c>
-      <c r="O448" s="3" t="s">
-        <v>3707</v>
-      </c>
-      <c r="P448" s="3" t="s">
-        <v>3708</v>
-      </c>
-      <c r="Q448" s="3">
-        <v>2</v>
-      </c>
-      <c r="R448" s="3"/>
-      <c r="S448" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T448" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U448" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="V448" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W448" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="449" spans="1:23" ht="30" hidden="1">
-      <c r="A449" s="3" t="s">
-        <v>3691</v>
-      </c>
-      <c r="B449" s="5">
-        <v>5</v>
-      </c>
-      <c r="C449" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D449" s="3" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E449" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F449" s="5"/>
-      <c r="G449" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K449" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N449" s="3" t="s">
-        <v>3709</v>
-      </c>
-      <c r="O449" s="3" t="s">
-        <v>3710</v>
-      </c>
-      <c r="P449" s="3" t="s">
-        <v>3711</v>
-      </c>
-      <c r="Q449" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R449" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T449" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U449" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V449" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W449" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="450" spans="1:23" ht="45" hidden="1">
-      <c r="A450" s="3" t="s">
-        <v>3691</v>
-      </c>
-      <c r="B450" s="5">
-        <v>6</v>
-      </c>
-      <c r="C450" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="D450" s="3" t="s">
-        <v>3712</v>
-      </c>
-      <c r="E450" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F450" s="5"/>
-      <c r="G450" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K450" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N450" s="3" t="s">
-        <v>3713</v>
-      </c>
-      <c r="O450" s="3" t="s">
-        <v>3714</v>
-      </c>
-      <c r="P450" s="3" t="s">
-        <v>3715</v>
-      </c>
-      <c r="Q450" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R450" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T450" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U450" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V450" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W450" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="451" spans="1:23" ht="30" hidden="1">
-      <c r="A451" s="3" t="s">
-        <v>3684</v>
       </c>
       <c r="B451" s="5">
         <v>1</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>3698</v>
+        <v>3692</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>3688</v>
+        <v>3693</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>168</v>
@@ -55834,16 +56117,16 @@
         <v>73</v>
       </c>
       <c r="N451" s="3" t="s">
-        <v>3716</v>
+        <v>3694</v>
       </c>
       <c r="O451" s="3" t="s">
-        <v>3717</v>
+        <v>3695</v>
       </c>
       <c r="P451" s="3" t="s">
-        <v>3718</v>
+        <v>3696</v>
       </c>
       <c r="Q451" s="3" t="s">
-        <v>3702</v>
+        <v>3697</v>
       </c>
       <c r="R451" s="3"/>
       <c r="S451" s="3" t="s">
@@ -55862,25 +56145,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="1:23" ht="30" hidden="1">
+    <row r="452" spans="1:23" ht="30">
       <c r="A452" s="3" t="s">
-        <v>3684</v>
+        <v>3691</v>
       </c>
       <c r="B452" s="5">
         <v>2</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>2221</v>
+        <v>3698</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>3719</v>
+        <v>3688</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F452" s="5">
-        <v>50</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="F452" s="5"/>
       <c r="G452" s="3" t="s">
         <v>7</v>
       </c>
@@ -55891,28 +56172,28 @@
         <v>6</v>
       </c>
       <c r="J452" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K452" s="3" t="s">
-        <v>72</v>
+        <v>3684</v>
       </c>
       <c r="L452" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M452" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N452" s="3" t="s">
-        <v>1022</v>
+        <v>3699</v>
       </c>
       <c r="O452" s="3" t="s">
-        <v>3720</v>
+        <v>3700</v>
       </c>
       <c r="P452" s="3" t="s">
-        <v>3721</v>
+        <v>3701</v>
       </c>
       <c r="Q452" s="3" t="s">
-        <v>2222</v>
+        <v>3702</v>
       </c>
       <c r="R452" s="3"/>
       <c r="S452" s="3" t="s">
@@ -55925,31 +56206,29 @@
         <v>7</v>
       </c>
       <c r="V452" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W452" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="453" spans="1:23" hidden="1">
+    <row r="453" spans="1:23" ht="30">
       <c r="A453" s="3" t="s">
-        <v>3684</v>
+        <v>3691</v>
       </c>
       <c r="B453" s="5">
         <v>3</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>3689</v>
+        <v>1040</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>3722</v>
+        <v>1013</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F453" s="5">
-        <v>100</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="F453" s="5"/>
       <c r="G453" s="3" t="s">
         <v>7</v>
       </c>
@@ -55960,10 +56239,10 @@
         <v>6</v>
       </c>
       <c r="J453" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K453" s="3" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="L453" s="3" t="s">
         <v>6</v>
@@ -55972,16 +56251,16 @@
         <v>6</v>
       </c>
       <c r="N453" s="3" t="s">
-        <v>3723</v>
+        <v>3703</v>
       </c>
       <c r="O453" s="3" t="s">
-        <v>3724</v>
+        <v>3704</v>
       </c>
       <c r="P453" s="3" t="s">
-        <v>3725</v>
+        <v>3705</v>
       </c>
       <c r="Q453" s="3" t="s">
-        <v>5</v>
+        <v>2384</v>
       </c>
       <c r="R453" s="3"/>
       <c r="S453" s="3" t="s">
@@ -56000,30 +56279,28 @@
         <v>6</v>
       </c>
     </row>
-    <row r="454" spans="1:23" ht="45" hidden="1">
+    <row r="454" spans="1:23" ht="30">
       <c r="A454" s="3" t="s">
-        <v>3684</v>
+        <v>3691</v>
       </c>
       <c r="B454" s="5">
         <v>4</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>2</v>
+        <v>850</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>327</v>
+        <v>1032</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F454" s="5">
-        <v>500</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="F454" s="5"/>
       <c r="G454" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H454" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I454" s="3" t="s">
         <v>6</v>
@@ -56041,26 +56318,26 @@
         <v>6</v>
       </c>
       <c r="N454" s="3" t="s">
-        <v>3726</v>
+        <v>3706</v>
       </c>
       <c r="O454" s="3" t="s">
-        <v>3727</v>
+        <v>3707</v>
       </c>
       <c r="P454" s="3" t="s">
-        <v>3728</v>
-      </c>
-      <c r="Q454" s="3" t="s">
-        <v>3729</v>
+        <v>3708</v>
+      </c>
+      <c r="Q454" s="3">
+        <v>2</v>
       </c>
       <c r="R454" s="3"/>
       <c r="S454" s="3" t="s">
         <v>6</v>
       </c>
       <c r="T454" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U454" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V454" s="3" t="s">
         <v>7</v>
@@ -56069,21 +56346,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="1:23" ht="30" hidden="1">
+    <row r="455" spans="1:23" ht="30">
       <c r="A455" s="3" t="s">
-        <v>3684</v>
+        <v>3691</v>
       </c>
       <c r="B455" s="5">
         <v>5</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>850</v>
+        <v>46</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F455" s="5"/>
       <c r="G455" s="3" t="s">
@@ -56108,18 +56385,20 @@
         <v>6</v>
       </c>
       <c r="N455" s="3" t="s">
-        <v>1033</v>
+        <v>3709</v>
       </c>
       <c r="O455" s="3" t="s">
-        <v>3730</v>
+        <v>3710</v>
       </c>
       <c r="P455" s="3" t="s">
-        <v>3731</v>
-      </c>
-      <c r="Q455" s="3">
+        <v>3711</v>
+      </c>
+      <c r="Q455" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="R455" s="3"/>
+      <c r="R455" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="S455" s="3" t="s">
         <v>6</v>
       </c>
@@ -56127,7 +56406,7 @@
         <v>7</v>
       </c>
       <c r="U455" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V455" s="3" t="s">
         <v>7</v>
@@ -56136,18 +56415,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="456" spans="1:23" ht="30" hidden="1">
+    <row r="456" spans="1:23" ht="45">
       <c r="A456" s="3" t="s">
-        <v>3684</v>
+        <v>3691</v>
       </c>
       <c r="B456" s="5">
         <v>6</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>46</v>
+        <v>851</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1036</v>
+        <v>3712</v>
       </c>
       <c r="E456" s="3" t="s">
         <v>174</v>
@@ -56175,44 +56454,448 @@
         <v>6</v>
       </c>
       <c r="N456" s="3" t="s">
-        <v>3732</v>
+        <v>3713</v>
       </c>
       <c r="O456" s="3" t="s">
-        <v>3733</v>
+        <v>3714</v>
       </c>
       <c r="P456" s="3" t="s">
-        <v>3734</v>
+        <v>3715</v>
       </c>
       <c r="Q456" s="3" t="b">
         <v>1</v>
       </c>
       <c r="R456" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S456" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T456" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U456" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="V456" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W456" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="457" spans="1:23" ht="30">
+      <c r="A457" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B457" s="5">
         <v>1</v>
       </c>
-      <c r="S456" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T456" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="U456" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V456" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="W456" s="3" t="s">
+      <c r="C457" s="3" t="s">
+        <v>3698</v>
+      </c>
+      <c r="D457" s="3" t="s">
+        <v>3688</v>
+      </c>
+      <c r="E457" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F457" s="5"/>
+      <c r="G457" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H457" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I457" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J457" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K457" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L457" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M457" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N457" s="3" t="s">
+        <v>3716</v>
+      </c>
+      <c r="O457" s="3" t="s">
+        <v>3717</v>
+      </c>
+      <c r="P457" s="3" t="s">
+        <v>3718</v>
+      </c>
+      <c r="Q457" s="3" t="s">
+        <v>3702</v>
+      </c>
+      <c r="R457" s="3"/>
+      <c r="S457" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T457" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U457" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V457" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W457" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="458" spans="1:23" ht="30">
+      <c r="A458" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B458" s="5">
+        <v>2</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D458" s="3" t="s">
+        <v>3719</v>
+      </c>
+      <c r="E458" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F458" s="5">
+        <v>50</v>
+      </c>
+      <c r="G458" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H458" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I458" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J458" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K458" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L458" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M458" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N458" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="O458" s="3" t="s">
+        <v>3720</v>
+      </c>
+      <c r="P458" s="3" t="s">
+        <v>3721</v>
+      </c>
+      <c r="Q458" s="3" t="s">
+        <v>2222</v>
+      </c>
+      <c r="R458" s="3"/>
+      <c r="S458" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T458" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U458" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V458" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W458" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="459" spans="1:23">
+      <c r="A459" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B459" s="5">
+        <v>3</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>3689</v>
+      </c>
+      <c r="D459" s="3" t="s">
+        <v>3722</v>
+      </c>
+      <c r="E459" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F459" s="5">
+        <v>100</v>
+      </c>
+      <c r="G459" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H459" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I459" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J459" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K459" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L459" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M459" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N459" s="3" t="s">
+        <v>3723</v>
+      </c>
+      <c r="O459" s="3" t="s">
+        <v>3724</v>
+      </c>
+      <c r="P459" s="3" t="s">
+        <v>3725</v>
+      </c>
+      <c r="Q459" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R459" s="3"/>
+      <c r="S459" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T459" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U459" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V459" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W459" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="460" spans="1:23" ht="45">
+      <c r="A460" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B460" s="5">
+        <v>4</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E460" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F460" s="5">
+        <v>500</v>
+      </c>
+      <c r="G460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H460" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K460" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N460" s="3" t="s">
+        <v>3726</v>
+      </c>
+      <c r="O460" s="3" t="s">
+        <v>3727</v>
+      </c>
+      <c r="P460" s="3" t="s">
+        <v>3728</v>
+      </c>
+      <c r="Q460" s="3" t="s">
+        <v>3729</v>
+      </c>
+      <c r="R460" s="3"/>
+      <c r="S460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="U460" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="V460" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W460" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="461" spans="1:23" ht="30">
+      <c r="A461" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B461" s="5">
+        <v>5</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E461" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F461" s="5"/>
+      <c r="G461" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H461" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I461" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J461" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K461" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L461" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M461" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N461" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O461" s="3" t="s">
+        <v>3730</v>
+      </c>
+      <c r="P461" s="3" t="s">
+        <v>3731</v>
+      </c>
+      <c r="Q461" s="3">
+        <v>1</v>
+      </c>
+      <c r="R461" s="3"/>
+      <c r="S461" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T461" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U461" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V461" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W461" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="462" spans="1:23" ht="30">
+      <c r="A462" s="3" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B462" s="5">
+        <v>6</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D462" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E462" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F462" s="5"/>
+      <c r="G462" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K462" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N462" s="3" t="s">
+        <v>3732</v>
+      </c>
+      <c r="O462" s="3" t="s">
+        <v>3733</v>
+      </c>
+      <c r="P462" s="3" t="s">
+        <v>3734</v>
+      </c>
+      <c r="Q462" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R462" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T462" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U462" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="V462" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W462" s="3" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W456" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Subscription Plan"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:W462" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}"/>
   <hyperlinks>
     <hyperlink ref="Q9" r:id="rId1" display="mailto:admin@memgine.com" xr:uid="{93170BB8-77D4-4002-829B-D89928109808}"/>
     <hyperlink ref="Q11" r:id="rId2" display="https://memgine.com/" xr:uid="{F8EB4105-6CCB-4B06-B657-948DB365F556}"/>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0694C604-9124-46E7-B720-E703D626DD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB49E44-DBF9-4D80-B910-E461BF0DEE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15086" uniqueCount="4031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15068" uniqueCount="4031">
   <si>
     <t>Domain</t>
   </si>
@@ -24886,6 +24886,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W462"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -24985,7 +24986,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="30">
+    <row r="2" spans="1:23" ht="30" hidden="1">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -25051,7 +25052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30">
+    <row r="3" spans="1:23" ht="30" hidden="1">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -25119,7 +25120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30">
+    <row r="4" spans="1:23" ht="30" hidden="1">
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
@@ -25187,7 +25188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="60">
+    <row r="5" spans="1:23" ht="60" hidden="1">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
@@ -25256,7 +25257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30">
+    <row r="6" spans="1:23" ht="30" hidden="1">
       <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
@@ -25324,7 +25325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" hidden="1">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -25392,7 +25393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" hidden="1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
@@ -25460,7 +25461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9" s="10" t="s">
         <v>5</v>
       </c>
@@ -25528,7 +25529,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
@@ -25596,7 +25597,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
@@ -25664,7 +25665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30">
+    <row r="12" spans="1:23" ht="30" hidden="1">
       <c r="A12" s="10" t="s">
         <v>5</v>
       </c>
@@ -25732,7 +25733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" hidden="1">
       <c r="A13" s="10" t="s">
         <v>5</v>
       </c>
@@ -25800,7 +25801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="30">
+    <row r="14" spans="1:23" ht="30" hidden="1">
       <c r="A14" s="10" t="s">
         <v>5</v>
       </c>
@@ -25868,7 +25869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -25936,7 +25937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="30">
+    <row r="16" spans="1:23" ht="30" hidden="1">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -26004,7 +26005,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" hidden="1">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -27156,7 +27157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="30">
+    <row r="34" spans="1:23" ht="30" hidden="1">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -27227,7 +27228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="30">
+    <row r="35" spans="1:23" ht="30" hidden="1">
       <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
@@ -27298,7 +27299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" hidden="1">
       <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
@@ -27369,7 +27370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="45">
+    <row r="37" spans="1:23" ht="45" hidden="1">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
@@ -27440,7 +27441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="30">
+    <row r="38" spans="1:23" ht="30" hidden="1">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -27511,7 +27512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="30">
+    <row r="39" spans="1:23" ht="30" hidden="1">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
@@ -27582,7 +27583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="30">
+    <row r="40" spans="1:23" ht="30" hidden="1">
       <c r="A40" s="3" t="s">
         <v>37</v>
       </c>
@@ -27653,7 +27654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" hidden="1">
       <c r="A41" s="3" t="s">
         <v>37</v>
       </c>
@@ -27724,7 +27725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="30">
+    <row r="42" spans="1:23" ht="30" hidden="1">
       <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
@@ -27795,7 +27796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" hidden="1">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
@@ -27866,7 +27867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" hidden="1">
       <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
@@ -27937,7 +27938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" hidden="1">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -28008,7 +28009,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="30">
+    <row r="46" spans="1:23" ht="30" hidden="1">
       <c r="A46" s="3" t="s">
         <v>317</v>
       </c>
@@ -28055,7 +28056,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="30">
+    <row r="47" spans="1:23" ht="30" hidden="1">
       <c r="A47" s="3" t="s">
         <v>317</v>
       </c>
@@ -28102,7 +28103,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="45">
+    <row r="48" spans="1:23" ht="45" hidden="1">
       <c r="A48" s="3" t="s">
         <v>317</v>
       </c>
@@ -28149,7 +28150,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="30">
+    <row r="49" spans="1:23" ht="30" hidden="1">
       <c r="A49" s="3" t="s">
         <v>317</v>
       </c>
@@ -28196,7 +28197,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="30">
+    <row r="50" spans="1:23" ht="30" hidden="1">
       <c r="A50" s="3" t="s">
         <v>317</v>
       </c>
@@ -28243,7 +28244,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="30">
+    <row r="51" spans="1:23" ht="30" hidden="1">
       <c r="A51" s="4" t="s">
         <v>341</v>
       </c>
@@ -28311,7 +28312,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="30">
+    <row r="52" spans="1:23" ht="30" hidden="1">
       <c r="A52" s="4" t="s">
         <v>341</v>
       </c>
@@ -28379,7 +28380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="30">
+    <row r="53" spans="1:23" ht="30" hidden="1">
       <c r="A53" s="4" t="s">
         <v>341</v>
       </c>
@@ -28447,7 +28448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="30">
+    <row r="54" spans="1:23" ht="30" hidden="1">
       <c r="A54" s="4" t="s">
         <v>341</v>
       </c>
@@ -28515,7 +28516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="30">
+    <row r="55" spans="1:23" ht="30" hidden="1">
       <c r="A55" s="4" t="s">
         <v>341</v>
       </c>
@@ -28583,7 +28584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="30">
+    <row r="56" spans="1:23" ht="30" hidden="1">
       <c r="A56" s="4" t="s">
         <v>341</v>
       </c>
@@ -28651,7 +28652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="30">
+    <row r="57" spans="1:23" ht="30" hidden="1">
       <c r="A57" s="4" t="s">
         <v>341</v>
       </c>
@@ -28719,7 +28720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="30">
+    <row r="58" spans="1:23" ht="30" hidden="1">
       <c r="A58" s="4" t="s">
         <v>341</v>
       </c>
@@ -28787,7 +28788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="45">
+    <row r="59" spans="1:23" ht="45" hidden="1">
       <c r="A59" s="4" t="s">
         <v>341</v>
       </c>
@@ -28855,7 +28856,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="30">
+    <row r="60" spans="1:23" ht="30" hidden="1">
       <c r="A60" s="4" t="s">
         <v>341</v>
       </c>
@@ -28923,7 +28924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="30">
+    <row r="61" spans="1:23" ht="30" hidden="1">
       <c r="A61" s="4" t="s">
         <v>370</v>
       </c>
@@ -28994,7 +28995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="30">
+    <row r="62" spans="1:23" ht="30" hidden="1">
       <c r="A62" s="4" t="s">
         <v>370</v>
       </c>
@@ -29065,7 +29066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="30">
+    <row r="63" spans="1:23" ht="30" hidden="1">
       <c r="A63" s="4" t="s">
         <v>370</v>
       </c>
@@ -29136,7 +29137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="30">
+    <row r="64" spans="1:23" ht="30" hidden="1">
       <c r="A64" s="4" t="s">
         <v>370</v>
       </c>
@@ -29207,7 +29208,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="30">
+    <row r="65" spans="1:23" ht="30" hidden="1">
       <c r="A65" s="4" t="s">
         <v>370</v>
       </c>
@@ -29278,7 +29279,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="30">
+    <row r="66" spans="1:23" ht="30" hidden="1">
       <c r="A66" s="4" t="s">
         <v>377</v>
       </c>
@@ -29349,7 +29350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="30">
+    <row r="67" spans="1:23" ht="30" hidden="1">
       <c r="A67" s="4" t="s">
         <v>377</v>
       </c>
@@ -29420,7 +29421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="30">
+    <row r="68" spans="1:23" ht="30" hidden="1">
       <c r="A68" s="4" t="s">
         <v>377</v>
       </c>
@@ -29491,7 +29492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="30">
+    <row r="69" spans="1:23" ht="30" hidden="1">
       <c r="A69" s="4" t="s">
         <v>10</v>
       </c>
@@ -29562,7 +29563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="30">
+    <row r="70" spans="1:23" ht="30" hidden="1">
       <c r="A70" s="4" t="s">
         <v>10</v>
       </c>
@@ -29633,7 +29634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="45">
+    <row r="71" spans="1:23" ht="45" hidden="1">
       <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
@@ -29704,7 +29705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="45">
+    <row r="72" spans="1:23" ht="45" hidden="1">
       <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
@@ -29775,7 +29776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="30">
+    <row r="73" spans="1:23" ht="30" hidden="1">
       <c r="A73" s="4" t="s">
         <v>10</v>
       </c>
@@ -29846,7 +29847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="30">
+    <row r="74" spans="1:23" ht="30" hidden="1">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -29917,7 +29918,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="30">
+    <row r="75" spans="1:23" ht="30" hidden="1">
       <c r="A75" s="4" t="s">
         <v>10</v>
       </c>
@@ -29988,7 +29989,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="30">
+    <row r="76" spans="1:23" ht="30" hidden="1">
       <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
@@ -30059,7 +30060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="30">
+    <row r="77" spans="1:23" ht="30" hidden="1">
       <c r="A77" s="4" t="s">
         <v>10</v>
       </c>
@@ -30130,7 +30131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="30">
+    <row r="78" spans="1:23" ht="30" hidden="1">
       <c r="A78" s="4" t="s">
         <v>10</v>
       </c>
@@ -30201,7 +30202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="30">
+    <row r="79" spans="1:23" ht="30" hidden="1">
       <c r="A79" s="4" t="s">
         <v>10</v>
       </c>
@@ -30272,7 +30273,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="45">
+    <row r="80" spans="1:23" ht="45" hidden="1">
       <c r="A80" s="4" t="s">
         <v>10</v>
       </c>
@@ -30343,7 +30344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="45">
+    <row r="81" spans="1:23" ht="45" hidden="1">
       <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
@@ -30414,7 +30415,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="30">
+    <row r="82" spans="1:23" ht="30" hidden="1">
       <c r="A82" s="4" t="s">
         <v>10</v>
       </c>
@@ -30485,7 +30486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="30">
+    <row r="83" spans="1:23" ht="30" hidden="1">
       <c r="A83" s="4" t="s">
         <v>10</v>
       </c>
@@ -30556,7 +30557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="30">
+    <row r="84" spans="1:23" ht="30" hidden="1">
       <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
@@ -30627,7 +30628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="30">
+    <row r="85" spans="1:23" ht="30" hidden="1">
       <c r="A85" s="4" t="s">
         <v>10</v>
       </c>
@@ -30698,7 +30699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="45">
+    <row r="86" spans="1:23" ht="45" hidden="1">
       <c r="A86" s="4" t="s">
         <v>10</v>
       </c>
@@ -30769,7 +30770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="30">
+    <row r="87" spans="1:23" ht="30" hidden="1">
       <c r="A87" s="4" t="s">
         <v>10</v>
       </c>
@@ -30840,7 +30841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="30">
+    <row r="88" spans="1:23" ht="30" hidden="1">
       <c r="A88" s="4" t="s">
         <v>490</v>
       </c>
@@ -30911,7 +30912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="30">
+    <row r="89" spans="1:23" ht="30" hidden="1">
       <c r="A89" s="4" t="s">
         <v>490</v>
       </c>
@@ -30982,7 +30983,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="30">
+    <row r="90" spans="1:23" ht="30" hidden="1">
       <c r="A90" s="4" t="s">
         <v>490</v>
       </c>
@@ -31053,7 +31054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="30">
+    <row r="91" spans="1:23" ht="30" hidden="1">
       <c r="A91" s="4" t="s">
         <v>490</v>
       </c>
@@ -31124,7 +31125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:23" hidden="1">
       <c r="A92" s="4" t="s">
         <v>490</v>
       </c>
@@ -31195,7 +31196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:23" hidden="1">
       <c r="A93" s="4" t="s">
         <v>490</v>
       </c>
@@ -31266,7 +31267,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="45">
+    <row r="94" spans="1:23" ht="45" hidden="1">
       <c r="A94" s="4" t="s">
         <v>490</v>
       </c>
@@ -31337,7 +31338,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="30">
+    <row r="95" spans="1:23" ht="30" hidden="1">
       <c r="A95" s="4" t="s">
         <v>490</v>
       </c>
@@ -31408,7 +31409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="30">
+    <row r="96" spans="1:23" ht="30" hidden="1">
       <c r="A96" s="4" t="s">
         <v>490</v>
       </c>
@@ -31479,7 +31480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="45">
+    <row r="97" spans="1:23" ht="45" hidden="1">
       <c r="A97" s="4" t="s">
         <v>490</v>
       </c>
@@ -31550,7 +31551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="30">
+    <row r="98" spans="1:23" ht="30" hidden="1">
       <c r="A98" s="4" t="s">
         <v>490</v>
       </c>
@@ -31621,7 +31622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="30">
+    <row r="99" spans="1:23" ht="30" hidden="1">
       <c r="A99" s="4" t="s">
         <v>490</v>
       </c>
@@ -31692,7 +31693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="30">
+    <row r="100" spans="1:23" ht="30" hidden="1">
       <c r="A100" s="4" t="s">
         <v>490</v>
       </c>
@@ -31763,7 +31764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="30">
+    <row r="101" spans="1:23" ht="30" hidden="1">
       <c r="A101" s="4" t="s">
         <v>490</v>
       </c>
@@ -31834,7 +31835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="30">
+    <row r="102" spans="1:23" ht="30" hidden="1">
       <c r="A102" s="4" t="s">
         <v>490</v>
       </c>
@@ -31905,7 +31906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="30">
+    <row r="103" spans="1:23" ht="30" hidden="1">
       <c r="A103" s="4" t="s">
         <v>490</v>
       </c>
@@ -31976,7 +31977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="30">
+    <row r="104" spans="1:23" ht="30" hidden="1">
       <c r="A104" s="4" t="s">
         <v>490</v>
       </c>
@@ -32047,7 +32048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="30">
+    <row r="105" spans="1:23" ht="30" hidden="1">
       <c r="A105" s="4" t="s">
         <v>490</v>
       </c>
@@ -32118,7 +32119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="30">
+    <row r="106" spans="1:23" ht="30" hidden="1">
       <c r="A106" s="4" t="s">
         <v>490</v>
       </c>
@@ -32189,7 +32190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="30">
+    <row r="107" spans="1:23" ht="30" hidden="1">
       <c r="A107" s="4" t="s">
         <v>548</v>
       </c>
@@ -32260,7 +32261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="30">
+    <row r="108" spans="1:23" ht="30" hidden="1">
       <c r="A108" s="4" t="s">
         <v>548</v>
       </c>
@@ -32331,7 +32332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:23" ht="30">
+    <row r="109" spans="1:23" ht="30" hidden="1">
       <c r="A109" s="4" t="s">
         <v>548</v>
       </c>
@@ -32402,7 +32403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="30">
+    <row r="110" spans="1:23" ht="30" hidden="1">
       <c r="A110" s="4" t="s">
         <v>548</v>
       </c>
@@ -32473,7 +32474,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="30">
+    <row r="111" spans="1:23" ht="30" hidden="1">
       <c r="A111" s="4" t="s">
         <v>548</v>
       </c>
@@ -32544,7 +32545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" hidden="1">
       <c r="A112" s="4" t="s">
         <v>548</v>
       </c>
@@ -32615,7 +32616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" hidden="1">
       <c r="A113" s="4" t="s">
         <v>548</v>
       </c>
@@ -32686,7 +32687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:23">
+    <row r="114" spans="1:23" hidden="1">
       <c r="A114" s="4" t="s">
         <v>548</v>
       </c>
@@ -32757,7 +32758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="30">
+    <row r="115" spans="1:23" ht="30" hidden="1">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
@@ -32828,7 +32829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:23">
+    <row r="116" spans="1:23" hidden="1">
       <c r="A116" s="4" t="s">
         <v>548</v>
       </c>
@@ -32899,7 +32900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="30">
+    <row r="117" spans="1:23" ht="30" hidden="1">
       <c r="A117" s="4" t="s">
         <v>548</v>
       </c>
@@ -32970,7 +32971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" hidden="1">
       <c r="A118" s="4" t="s">
         <v>548</v>
       </c>
@@ -33041,7 +33042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="30">
+    <row r="119" spans="1:23" ht="30" hidden="1">
       <c r="A119" s="4" t="s">
         <v>548</v>
       </c>
@@ -33112,7 +33113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:23">
+    <row r="120" spans="1:23" hidden="1">
       <c r="A120" s="4" t="s">
         <v>548</v>
       </c>
@@ -33183,7 +33184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="30">
+    <row r="121" spans="1:23" ht="30" hidden="1">
       <c r="A121" s="4" t="s">
         <v>548</v>
       </c>
@@ -33254,7 +33255,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" hidden="1">
       <c r="A122" s="4" t="s">
         <v>548</v>
       </c>
@@ -33325,7 +33326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:23">
+    <row r="123" spans="1:23" hidden="1">
       <c r="A123" s="4" t="s">
         <v>548</v>
       </c>
@@ -33396,7 +33397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" hidden="1">
       <c r="A124" s="4" t="s">
         <v>548</v>
       </c>
@@ -33467,7 +33468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="30">
+    <row r="125" spans="1:23" ht="30" hidden="1">
       <c r="A125" s="4" t="s">
         <v>620</v>
       </c>
@@ -33538,7 +33539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:23" ht="30">
+    <row r="126" spans="1:23" ht="30" hidden="1">
       <c r="A126" s="4" t="s">
         <v>620</v>
       </c>
@@ -33609,7 +33610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" hidden="1">
       <c r="A127" s="4" t="s">
         <v>620</v>
       </c>
@@ -33680,7 +33681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="30">
+    <row r="128" spans="1:23" ht="30" hidden="1">
       <c r="A128" s="4" t="s">
         <v>620</v>
       </c>
@@ -33751,7 +33752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:23">
+    <row r="129" spans="1:23" hidden="1">
       <c r="A129" s="4" t="s">
         <v>620</v>
       </c>
@@ -33822,7 +33823,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:23" ht="30">
+    <row r="130" spans="1:23" ht="30" hidden="1">
       <c r="A130" s="4" t="s">
         <v>620</v>
       </c>
@@ -33893,7 +33894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:23">
+    <row r="131" spans="1:23" hidden="1">
       <c r="A131" s="4" t="s">
         <v>620</v>
       </c>
@@ -33964,7 +33965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" hidden="1">
       <c r="A132" s="4" t="s">
         <v>620</v>
       </c>
@@ -34035,7 +34036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:23" ht="30">
+    <row r="133" spans="1:23" ht="30" hidden="1">
       <c r="A133" s="4" t="s">
         <v>620</v>
       </c>
@@ -34106,7 +34107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:23" ht="30">
+    <row r="134" spans="1:23" ht="30" hidden="1">
       <c r="A134" s="4" t="s">
         <v>620</v>
       </c>
@@ -34177,7 +34178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:23">
+    <row r="135" spans="1:23" hidden="1">
       <c r="A135" s="4" t="s">
         <v>620</v>
       </c>
@@ -34248,7 +34249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="30">
+    <row r="136" spans="1:23" ht="30" hidden="1">
       <c r="A136" s="4" t="s">
         <v>620</v>
       </c>
@@ -34319,7 +34320,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:23">
+    <row r="137" spans="1:23" hidden="1">
       <c r="A137" s="4" t="s">
         <v>620</v>
       </c>
@@ -34390,7 +34391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:23">
+    <row r="138" spans="1:23" hidden="1">
       <c r="A138" s="4" t="s">
         <v>620</v>
       </c>
@@ -34461,7 +34462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:23">
+    <row r="139" spans="1:23" hidden="1">
       <c r="A139" s="4" t="s">
         <v>620</v>
       </c>
@@ -34532,7 +34533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="30">
+    <row r="140" spans="1:23" ht="30" hidden="1">
       <c r="A140" s="4" t="s">
         <v>673</v>
       </c>
@@ -34603,7 +34604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="30">
+    <row r="141" spans="1:23" ht="30" hidden="1">
       <c r="A141" s="4" t="s">
         <v>673</v>
       </c>
@@ -34674,7 +34675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:23" ht="30">
+    <row r="142" spans="1:23" ht="30" hidden="1">
       <c r="A142" s="4" t="s">
         <v>673</v>
       </c>
@@ -34745,7 +34746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="30">
+    <row r="143" spans="1:23" ht="30" hidden="1">
       <c r="A143" s="4" t="s">
         <v>673</v>
       </c>
@@ -34816,7 +34817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="30">
+    <row r="144" spans="1:23" ht="30" hidden="1">
       <c r="A144" s="4" t="s">
         <v>673</v>
       </c>
@@ -34887,7 +34888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="30">
+    <row r="145" spans="1:23" ht="30" hidden="1">
       <c r="A145" s="4" t="s">
         <v>673</v>
       </c>
@@ -34958,7 +34959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="30">
+    <row r="146" spans="1:23" ht="30" hidden="1">
       <c r="A146" s="4" t="s">
         <v>673</v>
       </c>
@@ -35029,7 +35030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:23">
+    <row r="147" spans="1:23" hidden="1">
       <c r="A147" s="4" t="s">
         <v>673</v>
       </c>
@@ -35100,7 +35101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="30">
+    <row r="148" spans="1:23" ht="30" hidden="1">
       <c r="A148" s="4" t="s">
         <v>673</v>
       </c>
@@ -35171,7 +35172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:23" ht="30">
+    <row r="149" spans="1:23" ht="30" hidden="1">
       <c r="A149" s="4" t="s">
         <v>673</v>
       </c>
@@ -35242,7 +35243,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="30">
+    <row r="150" spans="1:23" ht="30" hidden="1">
       <c r="A150" s="4" t="s">
         <v>673</v>
       </c>
@@ -35313,7 +35314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="30">
+    <row r="151" spans="1:23" ht="30" hidden="1">
       <c r="A151" s="4" t="s">
         <v>673</v>
       </c>
@@ -35384,7 +35385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="30">
+    <row r="152" spans="1:23" ht="30" hidden="1">
       <c r="A152" s="4" t="s">
         <v>673</v>
       </c>
@@ -35455,7 +35456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="30">
+    <row r="153" spans="1:23" ht="30" hidden="1">
       <c r="A153" s="4" t="s">
         <v>673</v>
       </c>
@@ -35526,7 +35527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:23" hidden="1">
       <c r="A154" s="4" t="s">
         <v>673</v>
       </c>
@@ -35597,7 +35598,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="30">
+    <row r="155" spans="1:23" ht="30" hidden="1">
       <c r="A155" s="4" t="s">
         <v>34</v>
       </c>
@@ -35668,7 +35669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="30">
+    <row r="156" spans="1:23" ht="30" hidden="1">
       <c r="A156" s="4" t="s">
         <v>34</v>
       </c>
@@ -35739,7 +35740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="30">
+    <row r="157" spans="1:23" ht="30" hidden="1">
       <c r="A157" s="4" t="s">
         <v>34</v>
       </c>
@@ -35810,7 +35811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="30">
+    <row r="158" spans="1:23" ht="30" hidden="1">
       <c r="A158" s="4" t="s">
         <v>34</v>
       </c>
@@ -35881,7 +35882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:23">
+    <row r="159" spans="1:23" hidden="1">
       <c r="A159" s="4" t="s">
         <v>34</v>
       </c>
@@ -35952,7 +35953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="30">
+    <row r="160" spans="1:23" ht="30" hidden="1">
       <c r="A160" s="4" t="s">
         <v>34</v>
       </c>
@@ -36023,7 +36024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:23" ht="30">
+    <row r="161" spans="1:23" ht="30" hidden="1">
       <c r="A161" s="4" t="s">
         <v>34</v>
       </c>
@@ -36094,7 +36095,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="30">
+    <row r="162" spans="1:23" ht="30" hidden="1">
       <c r="A162" s="4" t="s">
         <v>34</v>
       </c>
@@ -36165,7 +36166,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="30">
+    <row r="163" spans="1:23" ht="30" hidden="1">
       <c r="A163" s="4" t="s">
         <v>34</v>
       </c>
@@ -36236,7 +36237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="30">
+    <row r="164" spans="1:23" ht="30" hidden="1">
       <c r="A164" s="4" t="s">
         <v>34</v>
       </c>
@@ -36307,7 +36308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="30">
+    <row r="165" spans="1:23" ht="30" hidden="1">
       <c r="A165" s="4" t="s">
         <v>34</v>
       </c>
@@ -36378,7 +36379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="30">
+    <row r="166" spans="1:23" ht="30" hidden="1">
       <c r="A166" s="4" t="s">
         <v>34</v>
       </c>
@@ -36449,7 +36450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="30">
+    <row r="167" spans="1:23" ht="30" hidden="1">
       <c r="A167" s="4" t="s">
         <v>34</v>
       </c>
@@ -36520,7 +36521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="30">
+    <row r="168" spans="1:23" ht="30" hidden="1">
       <c r="A168" s="4" t="s">
         <v>34</v>
       </c>
@@ -36591,7 +36592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="30">
+    <row r="169" spans="1:23" ht="30" hidden="1">
       <c r="A169" s="4" t="s">
         <v>34</v>
       </c>
@@ -36662,7 +36663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="30">
+    <row r="170" spans="1:23" ht="30" hidden="1">
       <c r="A170" s="4" t="s">
         <v>34</v>
       </c>
@@ -36733,7 +36734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="30">
+    <row r="171" spans="1:23" ht="30" hidden="1">
       <c r="A171" s="4" t="s">
         <v>34</v>
       </c>
@@ -36804,7 +36805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="30">
+    <row r="172" spans="1:23" ht="30" hidden="1">
       <c r="A172" s="4" t="s">
         <v>34</v>
       </c>
@@ -36875,7 +36876,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:23">
+    <row r="173" spans="1:23" hidden="1">
       <c r="A173" s="4" t="s">
         <v>34</v>
       </c>
@@ -36946,7 +36947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="30">
+    <row r="174" spans="1:23" ht="30" hidden="1">
       <c r="A174" s="4" t="s">
         <v>34</v>
       </c>
@@ -37017,7 +37018,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="30">
+    <row r="175" spans="1:23" ht="30" hidden="1">
       <c r="A175" s="4" t="s">
         <v>34</v>
       </c>
@@ -37088,7 +37089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="30">
+    <row r="176" spans="1:23" ht="30" hidden="1">
       <c r="A176" s="4" t="s">
         <v>34</v>
       </c>
@@ -37159,7 +37160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="30">
+    <row r="177" spans="1:23" ht="30" hidden="1">
       <c r="A177" s="4" t="s">
         <v>34</v>
       </c>
@@ -37230,7 +37231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="30">
+    <row r="178" spans="1:23" ht="30" hidden="1">
       <c r="A178" s="4" t="s">
         <v>35</v>
       </c>
@@ -37301,7 +37302,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="30">
+    <row r="179" spans="1:23" ht="30" hidden="1">
       <c r="A179" s="4" t="s">
         <v>35</v>
       </c>
@@ -37372,7 +37373,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="30">
+    <row r="180" spans="1:23" ht="30" hidden="1">
       <c r="A180" s="4" t="s">
         <v>35</v>
       </c>
@@ -37443,7 +37444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="30">
+    <row r="181" spans="1:23" ht="30" hidden="1">
       <c r="A181" s="4" t="s">
         <v>35</v>
       </c>
@@ -37514,7 +37515,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:23">
+    <row r="182" spans="1:23" hidden="1">
       <c r="A182" s="4" t="s">
         <v>35</v>
       </c>
@@ -37565,7 +37566,7 @@
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
     </row>
-    <row r="183" spans="1:23">
+    <row r="183" spans="1:23" hidden="1">
       <c r="A183" s="4" t="s">
         <v>35</v>
       </c>
@@ -37614,7 +37615,7 @@
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
     </row>
-    <row r="184" spans="1:23" ht="30">
+    <row r="184" spans="1:23" ht="30" hidden="1">
       <c r="A184" s="3" t="s">
         <v>35</v>
       </c>
@@ -37685,7 +37686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="30">
+    <row r="185" spans="1:23" ht="30" hidden="1">
       <c r="A185" s="3" t="s">
         <v>35</v>
       </c>
@@ -37756,7 +37757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="30">
+    <row r="186" spans="1:23" ht="30" hidden="1">
       <c r="A186" s="4" t="s">
         <v>35</v>
       </c>
@@ -37827,7 +37828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="30">
+    <row r="187" spans="1:23" ht="30" hidden="1">
       <c r="A187" s="4" t="s">
         <v>35</v>
       </c>
@@ -37898,7 +37899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:23" ht="30">
+    <row r="188" spans="1:23" ht="30" hidden="1">
       <c r="A188" s="4" t="s">
         <v>35</v>
       </c>
@@ -37969,7 +37970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:23" ht="30">
+    <row r="189" spans="1:23" ht="30" hidden="1">
       <c r="A189" s="4" t="s">
         <v>35</v>
       </c>
@@ -38040,7 +38041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="30">
+    <row r="190" spans="1:23" ht="30" hidden="1">
       <c r="A190" s="4" t="s">
         <v>35</v>
       </c>
@@ -38111,7 +38112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:23" ht="30">
+    <row r="191" spans="1:23" ht="30" hidden="1">
       <c r="A191" s="4" t="s">
         <v>35</v>
       </c>
@@ -38182,7 +38183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:23" ht="30">
+    <row r="192" spans="1:23" ht="30" hidden="1">
       <c r="A192" s="4" t="s">
         <v>35</v>
       </c>
@@ -38253,7 +38254,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:23" ht="30">
+    <row r="193" spans="1:23" ht="30" hidden="1">
       <c r="A193" s="4" t="s">
         <v>35</v>
       </c>
@@ -38324,7 +38325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:23" ht="30">
+    <row r="194" spans="1:23" ht="30" hidden="1">
       <c r="A194" s="4" t="s">
         <v>35</v>
       </c>
@@ -38395,7 +38396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:23" ht="30">
+    <row r="195" spans="1:23" ht="30" hidden="1">
       <c r="A195" s="4" t="s">
         <v>35</v>
       </c>
@@ -38466,7 +38467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:23" ht="30">
+    <row r="196" spans="1:23" ht="30" hidden="1">
       <c r="A196" s="4" t="s">
         <v>35</v>
       </c>
@@ -38537,7 +38538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:23" ht="30">
+    <row r="197" spans="1:23" ht="30" hidden="1">
       <c r="A197" s="3" t="s">
         <v>94</v>
       </c>
@@ -38604,7 +38605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="30">
+    <row r="198" spans="1:23" ht="30" hidden="1">
       <c r="A198" s="3" t="s">
         <v>94</v>
       </c>
@@ -38673,7 +38674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="30">
+    <row r="199" spans="1:23" ht="30" hidden="1">
       <c r="A199" s="3" t="s">
         <v>94</v>
       </c>
@@ -38742,7 +38743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:23" ht="30">
+    <row r="200" spans="1:23" ht="30" hidden="1">
       <c r="A200" s="3" t="s">
         <v>94</v>
       </c>
@@ -38811,7 +38812,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:23" ht="30">
+    <row r="201" spans="1:23" ht="30" hidden="1">
       <c r="A201" s="3" t="s">
         <v>94</v>
       </c>
@@ -38880,7 +38881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:23" ht="30">
+    <row r="202" spans="1:23" ht="30" hidden="1">
       <c r="A202" s="3" t="s">
         <v>94</v>
       </c>
@@ -38949,7 +38950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:23">
+    <row r="203" spans="1:23" hidden="1">
       <c r="A203" s="3" t="s">
         <v>42</v>
       </c>
@@ -39016,7 +39017,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:23">
+    <row r="204" spans="1:23" hidden="1">
       <c r="A204" s="3" t="s">
         <v>42</v>
       </c>
@@ -39085,7 +39086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:23">
+    <row r="205" spans="1:23" hidden="1">
       <c r="A205" s="3" t="s">
         <v>42</v>
       </c>
@@ -39154,7 +39155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="30">
+    <row r="206" spans="1:23" ht="30" hidden="1">
       <c r="A206" s="3" t="s">
         <v>42</v>
       </c>
@@ -39223,7 +39224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:23">
+    <row r="207" spans="1:23" hidden="1">
       <c r="A207" s="3" t="s">
         <v>42</v>
       </c>
@@ -39292,7 +39293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="30">
+    <row r="208" spans="1:23" ht="30" hidden="1">
       <c r="A208" s="3" t="s">
         <v>42</v>
       </c>
@@ -39361,7 +39362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:23">
+    <row r="209" spans="1:23" hidden="1">
       <c r="A209" s="3" t="s">
         <v>129</v>
       </c>
@@ -39428,7 +39429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:23">
+    <row r="210" spans="1:23" hidden="1">
       <c r="A210" s="3" t="s">
         <v>129</v>
       </c>
@@ -39497,7 +39498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:23">
+    <row r="211" spans="1:23" hidden="1">
       <c r="A211" s="3" t="s">
         <v>129</v>
       </c>
@@ -39566,7 +39567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:23">
+    <row r="212" spans="1:23" hidden="1">
       <c r="A212" s="3" t="s">
         <v>129</v>
       </c>
@@ -39635,7 +39636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:23">
+    <row r="213" spans="1:23" hidden="1">
       <c r="A213" s="3" t="s">
         <v>129</v>
       </c>
@@ -39704,7 +39705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="30">
+    <row r="214" spans="1:23" ht="30" hidden="1">
       <c r="A214" s="3" t="s">
         <v>129</v>
       </c>
@@ -39773,7 +39774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="30">
+    <row r="215" spans="1:23" ht="30" hidden="1">
       <c r="A215" s="3" t="s">
         <v>129</v>
       </c>
@@ -39842,7 +39843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:23">
+    <row r="216" spans="1:23" hidden="1">
       <c r="A216" s="3" t="s">
         <v>126</v>
       </c>
@@ -39909,7 +39910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:23">
+    <row r="217" spans="1:23" hidden="1">
       <c r="A217" s="3" t="s">
         <v>126</v>
       </c>
@@ -39978,7 +39979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:23">
+    <row r="218" spans="1:23" hidden="1">
       <c r="A218" s="3" t="s">
         <v>126</v>
       </c>
@@ -40047,7 +40048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="30">
+    <row r="219" spans="1:23" ht="30" hidden="1">
       <c r="A219" s="3" t="s">
         <v>126</v>
       </c>
@@ -40116,7 +40117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="30">
+    <row r="220" spans="1:23" ht="30" hidden="1">
       <c r="A220" s="3" t="s">
         <v>126</v>
       </c>
@@ -40185,7 +40186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:23">
+    <row r="221" spans="1:23" hidden="1">
       <c r="A221" s="3" t="s">
         <v>126</v>
       </c>
@@ -40254,7 +40255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="30">
+    <row r="222" spans="1:23" ht="30" hidden="1">
       <c r="A222" s="3" t="s">
         <v>126</v>
       </c>
@@ -40323,7 +40324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="30">
+    <row r="223" spans="1:23" ht="30" hidden="1">
       <c r="A223" s="3" t="s">
         <v>126</v>
       </c>
@@ -40392,7 +40393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:23" ht="30">
+    <row r="224" spans="1:23" ht="30" hidden="1">
       <c r="A224" s="3" t="s">
         <v>313</v>
       </c>
@@ -40459,7 +40460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="30">
+    <row r="225" spans="1:23" ht="30" hidden="1">
       <c r="A225" s="3" t="s">
         <v>313</v>
       </c>
@@ -40528,7 +40529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="30">
+    <row r="226" spans="1:23" ht="30" hidden="1">
       <c r="A226" s="3" t="s">
         <v>313</v>
       </c>
@@ -40597,7 +40598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="30">
+    <row r="227" spans="1:23" ht="30" hidden="1">
       <c r="A227" s="3" t="s">
         <v>313</v>
       </c>
@@ -40666,7 +40667,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="30">
+    <row r="228" spans="1:23" ht="30" hidden="1">
       <c r="A228" s="3" t="s">
         <v>313</v>
       </c>
@@ -40735,7 +40736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="45">
+    <row r="229" spans="1:23" ht="45" hidden="1">
       <c r="A229" s="3" t="s">
         <v>313</v>
       </c>
@@ -40804,7 +40805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="30">
+    <row r="230" spans="1:23" ht="30" hidden="1">
       <c r="A230" s="3" t="s">
         <v>445</v>
       </c>
@@ -40871,7 +40872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="30">
+    <row r="231" spans="1:23" ht="30" hidden="1">
       <c r="A231" s="3" t="s">
         <v>445</v>
       </c>
@@ -40940,7 +40941,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="30">
+    <row r="232" spans="1:23" ht="30" hidden="1">
       <c r="A232" s="3" t="s">
         <v>445</v>
       </c>
@@ -41009,7 +41010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:23" ht="30">
+    <row r="233" spans="1:23" ht="30" hidden="1">
       <c r="A233" s="3" t="s">
         <v>445</v>
       </c>
@@ -41078,7 +41079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:23" ht="30">
+    <row r="234" spans="1:23" ht="30" hidden="1">
       <c r="A234" s="3" t="s">
         <v>445</v>
       </c>
@@ -41147,7 +41148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="30">
+    <row r="235" spans="1:23" ht="30" hidden="1">
       <c r="A235" s="3" t="s">
         <v>445</v>
       </c>
@@ -41216,7 +41217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:23" ht="30">
+    <row r="236" spans="1:23" ht="30" hidden="1">
       <c r="A236" s="3" t="s">
         <v>451</v>
       </c>
@@ -41283,7 +41284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:23">
+    <row r="237" spans="1:23" hidden="1">
       <c r="A237" s="3" t="s">
         <v>451</v>
       </c>
@@ -41352,7 +41353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:23">
+    <row r="238" spans="1:23" hidden="1">
       <c r="A238" s="3" t="s">
         <v>451</v>
       </c>
@@ -41421,7 +41422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:23" ht="30">
+    <row r="239" spans="1:23" ht="30" hidden="1">
       <c r="A239" s="3" t="s">
         <v>451</v>
       </c>
@@ -41490,7 +41491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:23">
+    <row r="240" spans="1:23" hidden="1">
       <c r="A240" s="3" t="s">
         <v>451</v>
       </c>
@@ -41559,7 +41560,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:23" ht="30">
+    <row r="241" spans="1:23" ht="30" hidden="1">
       <c r="A241" s="3" t="s">
         <v>451</v>
       </c>
@@ -41628,7 +41629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:23" ht="30">
+    <row r="242" spans="1:23" ht="30" hidden="1">
       <c r="A242" s="3" t="s">
         <v>512</v>
       </c>
@@ -41695,7 +41696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="30">
+    <row r="243" spans="1:23" ht="30" hidden="1">
       <c r="A243" s="3" t="s">
         <v>512</v>
       </c>
@@ -41764,7 +41765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="30">
+    <row r="244" spans="1:23" ht="30" hidden="1">
       <c r="A244" s="3" t="s">
         <v>512</v>
       </c>
@@ -41833,7 +41834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="30">
+    <row r="245" spans="1:23" ht="30" hidden="1">
       <c r="A245" s="3" t="s">
         <v>512</v>
       </c>
@@ -41902,7 +41903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="30">
+    <row r="246" spans="1:23" ht="30" hidden="1">
       <c r="A246" s="3" t="s">
         <v>512</v>
       </c>
@@ -41971,7 +41972,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:23" ht="30">
+    <row r="247" spans="1:23" ht="30" hidden="1">
       <c r="A247" s="3" t="s">
         <v>512</v>
       </c>
@@ -42040,7 +42041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:23" ht="30">
+    <row r="248" spans="1:23" ht="30" hidden="1">
       <c r="A248" s="3" t="s">
         <v>518</v>
       </c>
@@ -42107,7 +42108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:23">
+    <row r="249" spans="1:23" hidden="1">
       <c r="A249" s="3" t="s">
         <v>518</v>
       </c>
@@ -42176,7 +42177,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:23">
+    <row r="250" spans="1:23" hidden="1">
       <c r="A250" s="3" t="s">
         <v>518</v>
       </c>
@@ -42245,7 +42246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:23" ht="30">
+    <row r="251" spans="1:23" ht="30" hidden="1">
       <c r="A251" s="3" t="s">
         <v>518</v>
       </c>
@@ -42314,7 +42315,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:23">
+    <row r="252" spans="1:23" hidden="1">
       <c r="A252" s="3" t="s">
         <v>518</v>
       </c>
@@ -42383,7 +42384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:23" ht="30">
+    <row r="253" spans="1:23" ht="30" hidden="1">
       <c r="A253" s="3" t="s">
         <v>518</v>
       </c>
@@ -42452,7 +42453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:23" ht="30">
+    <row r="254" spans="1:23" ht="30" hidden="1">
       <c r="A254" s="3" t="s">
         <v>756</v>
       </c>
@@ -42519,7 +42520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:23">
+    <row r="255" spans="1:23" hidden="1">
       <c r="A255" s="3" t="s">
         <v>756</v>
       </c>
@@ -42588,7 +42589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:23">
+    <row r="256" spans="1:23" hidden="1">
       <c r="A256" s="3" t="s">
         <v>756</v>
       </c>
@@ -42657,7 +42658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:23">
+    <row r="257" spans="1:23" hidden="1">
       <c r="A257" s="3" t="s">
         <v>756</v>
       </c>
@@ -42726,7 +42727,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" hidden="1">
       <c r="A258" s="3" t="s">
         <v>756</v>
       </c>
@@ -42795,7 +42796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:23" ht="30">
+    <row r="259" spans="1:23" ht="30" hidden="1">
       <c r="A259" s="3" t="s">
         <v>756</v>
       </c>
@@ -42864,7 +42865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:23" ht="30">
+    <row r="260" spans="1:23" ht="30" hidden="1">
       <c r="A260" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42931,7 +42932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:23" ht="30">
+    <row r="261" spans="1:23" ht="30" hidden="1">
       <c r="A261" s="3" t="s">
         <v>1514</v>
       </c>
@@ -42998,7 +42999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="30">
+    <row r="262" spans="1:23" ht="30" hidden="1">
       <c r="A262" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43067,7 +43068,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="30">
+    <row r="263" spans="1:23" ht="30" hidden="1">
       <c r="A263" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43136,7 +43137,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="264" spans="1:23">
+    <row r="264" spans="1:23" hidden="1">
       <c r="A264" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43205,7 +43206,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="30">
+    <row r="265" spans="1:23" ht="30" hidden="1">
       <c r="A265" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43274,7 +43275,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" hidden="1">
       <c r="A266" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43343,7 +43344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:23">
+    <row r="267" spans="1:23" hidden="1">
       <c r="A267" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43412,7 +43413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" hidden="1">
       <c r="A268" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43481,7 +43482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" hidden="1">
       <c r="A269" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43550,7 +43551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:23">
+    <row r="270" spans="1:23" hidden="1">
       <c r="A270" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43619,7 +43620,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:23">
+    <row r="271" spans="1:23" hidden="1">
       <c r="A271" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43688,7 +43689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="30">
+    <row r="272" spans="1:23" ht="30" hidden="1">
       <c r="A272" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43757,7 +43758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="30">
+    <row r="273" spans="1:23" ht="30" hidden="1">
       <c r="A273" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43826,7 +43827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" hidden="1">
       <c r="A274" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43893,7 +43894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" hidden="1">
       <c r="A275" s="3" t="s">
         <v>1514</v>
       </c>
@@ -43960,7 +43961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" hidden="1">
       <c r="A276" s="3" t="s">
         <v>1514</v>
       </c>
@@ -44027,7 +44028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:23">
+    <row r="277" spans="1:23" hidden="1">
       <c r="A277" s="3" t="s">
         <v>1514</v>
       </c>
@@ -44096,7 +44097,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:23">
+    <row r="278" spans="1:23" hidden="1">
       <c r="A278" s="3" t="s">
         <v>1514</v>
       </c>
@@ -44165,7 +44166,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="30">
+    <row r="279" spans="1:23" ht="30" hidden="1">
       <c r="A279" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44232,7 +44233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="30">
+    <row r="280" spans="1:23" ht="30" hidden="1">
       <c r="A280" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44299,7 +44300,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="30">
+    <row r="281" spans="1:23" ht="30" hidden="1">
       <c r="A281" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44370,7 +44371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:23">
+    <row r="282" spans="1:23" hidden="1">
       <c r="A282" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44437,7 +44438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="30">
+    <row r="283" spans="1:23" ht="30" hidden="1">
       <c r="A283" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44506,7 +44507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:23">
+    <row r="284" spans="1:23" hidden="1">
       <c r="A284" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44575,7 +44576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:23">
+    <row r="285" spans="1:23" hidden="1">
       <c r="A285" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44644,7 +44645,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="45">
+    <row r="286" spans="1:23" ht="45" hidden="1">
       <c r="A286" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44713,7 +44714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="30">
+    <row r="287" spans="1:23" ht="30" hidden="1">
       <c r="A287" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44782,7 +44783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="45">
+    <row r="288" spans="1:23" ht="30" hidden="1">
       <c r="A288" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44851,7 +44852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="45">
+    <row r="289" spans="1:23" ht="45" hidden="1">
       <c r="A289" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44920,7 +44921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="30">
+    <row r="290" spans="1:23" ht="30" hidden="1">
       <c r="A290" s="3" t="s">
         <v>1515</v>
       </c>
@@ -44987,7 +44988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="30">
+    <row r="291" spans="1:23" ht="30" hidden="1">
       <c r="A291" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45054,7 +45055,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:23">
+    <row r="292" spans="1:23" hidden="1">
       <c r="A292" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45119,7 +45120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:23">
+    <row r="293" spans="1:23" hidden="1">
       <c r="A293" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45184,7 +45185,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:23">
+    <row r="294" spans="1:23" hidden="1">
       <c r="A294" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45249,7 +45250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" hidden="1">
       <c r="A295" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45318,7 +45319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" hidden="1">
       <c r="A296" s="3" t="s">
         <v>1515</v>
       </c>
@@ -45387,7 +45388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="30">
+    <row r="297" spans="1:23" ht="30" hidden="1">
       <c r="A297" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45454,7 +45455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:23" ht="30">
+    <row r="298" spans="1:23" ht="30" hidden="1">
       <c r="A298" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45521,7 +45522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="45">
+    <row r="299" spans="1:23" ht="45" hidden="1">
       <c r="A299" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45592,7 +45593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="30">
+    <row r="300" spans="1:23" ht="30" hidden="1">
       <c r="A300" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45661,7 +45662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="30">
+    <row r="301" spans="1:23" ht="30" hidden="1">
       <c r="A301" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45730,7 +45731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="30">
+    <row r="302" spans="1:23" ht="30" hidden="1">
       <c r="A302" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45799,7 +45800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="30">
+    <row r="303" spans="1:23" ht="30" hidden="1">
       <c r="A303" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45868,7 +45869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="30">
+    <row r="304" spans="1:23" ht="30" hidden="1">
       <c r="A304" s="3" t="s">
         <v>1575</v>
       </c>
@@ -45937,7 +45938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="30">
+    <row r="305" spans="1:23" ht="30" hidden="1">
       <c r="A305" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46004,7 +46005,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="30">
+    <row r="306" spans="1:23" ht="30" hidden="1">
       <c r="A306" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46071,7 +46072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="30">
+    <row r="307" spans="1:23" ht="30" hidden="1">
       <c r="A307" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46136,7 +46137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="30">
+    <row r="308" spans="1:23" ht="30" hidden="1">
       <c r="A308" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46201,7 +46202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="30">
+    <row r="309" spans="1:23" ht="30" hidden="1">
       <c r="A309" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46266,7 +46267,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="30">
+    <row r="310" spans="1:23" ht="30" hidden="1">
       <c r="A310" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46335,7 +46336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="30">
+    <row r="311" spans="1:23" ht="30" hidden="1">
       <c r="A311" s="3" t="s">
         <v>1575</v>
       </c>
@@ -46404,7 +46405,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="30">
+    <row r="312" spans="1:23" ht="30" hidden="1">
       <c r="A312" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46471,7 +46472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="30">
+    <row r="313" spans="1:23" ht="30" hidden="1">
       <c r="A313" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46538,7 +46539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="45">
+    <row r="314" spans="1:23" ht="45" hidden="1">
       <c r="A314" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46607,7 +46608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:23">
+    <row r="315" spans="1:23" hidden="1">
       <c r="A315" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46674,7 +46675,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:23">
+    <row r="316" spans="1:23" hidden="1">
       <c r="A316" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46741,7 +46742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:23" ht="30">
+    <row r="317" spans="1:23" ht="30" hidden="1">
       <c r="A317" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46808,7 +46809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:23">
+    <row r="318" spans="1:23" hidden="1">
       <c r="A318" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46875,7 +46876,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:23" ht="45">
+    <row r="319" spans="1:23" ht="45" hidden="1">
       <c r="A319" s="3" t="s">
         <v>1632</v>
       </c>
@@ -46944,7 +46945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="30">
+    <row r="320" spans="1:23" ht="30" hidden="1">
       <c r="A320" s="3" t="s">
         <v>1632</v>
       </c>
@@ -47009,7 +47010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="30">
+    <row r="321" spans="1:23" ht="30" hidden="1">
       <c r="A321" s="3" t="s">
         <v>1632</v>
       </c>
@@ -47078,7 +47079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:23" ht="30">
+    <row r="322" spans="1:23" ht="30" hidden="1">
       <c r="A322" s="3" t="s">
         <v>1632</v>
       </c>
@@ -47145,7 +47146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="30">
+    <row r="323" spans="1:23" ht="30" hidden="1">
       <c r="A323" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47212,7 +47213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="30">
+    <row r="324" spans="1:23" ht="30" hidden="1">
       <c r="A324" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47279,7 +47280,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="30">
+    <row r="325" spans="1:23" ht="30" hidden="1">
       <c r="A325" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47348,7 +47349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="30">
+    <row r="326" spans="1:23" ht="30" hidden="1">
       <c r="A326" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47415,7 +47416,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="30">
+    <row r="327" spans="1:23" ht="30" hidden="1">
       <c r="A327" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47484,7 +47485,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="30">
+    <row r="328" spans="1:23" ht="30" hidden="1">
       <c r="A328" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47553,7 +47554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="30">
+    <row r="329" spans="1:23" ht="30" hidden="1">
       <c r="A329" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47620,7 +47621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="30">
+    <row r="330" spans="1:23" ht="30" hidden="1">
       <c r="A330" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47687,7 +47688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="30">
+    <row r="331" spans="1:23" ht="30" hidden="1">
       <c r="A331" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47752,7 +47753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="30">
+    <row r="332" spans="1:23" ht="30" hidden="1">
       <c r="A332" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47819,7 +47820,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="45">
+    <row r="333" spans="1:23" ht="45" hidden="1">
       <c r="A333" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47888,7 +47889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="30">
+    <row r="334" spans="1:23" ht="30" hidden="1">
       <c r="A334" s="3" t="s">
         <v>1686</v>
       </c>
@@ -47957,7 +47958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="30">
+    <row r="335" spans="1:23" ht="30" hidden="1">
       <c r="A335" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48024,7 +48025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="30">
+    <row r="336" spans="1:23" ht="30" hidden="1">
       <c r="A336" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48093,7 +48094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:23">
+    <row r="337" spans="1:23" hidden="1">
       <c r="A337" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48162,7 +48163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="30">
+    <row r="338" spans="1:23" ht="30" hidden="1">
       <c r="A338" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48231,7 +48232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:23">
+    <row r="339" spans="1:23" hidden="1">
       <c r="A339" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48300,7 +48301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="30">
+    <row r="340" spans="1:23" ht="30" hidden="1">
       <c r="A340" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48369,7 +48370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:23" ht="30">
+    <row r="341" spans="1:23" ht="30" hidden="1">
       <c r="A341" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48436,7 +48437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="342" spans="1:23">
+    <row r="342" spans="1:23" hidden="1">
       <c r="A342" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48501,7 +48502,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="30">
+    <row r="343" spans="1:23" ht="30" hidden="1">
       <c r="A343" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48570,7 +48571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:23">
+    <row r="344" spans="1:23" hidden="1">
       <c r="A344" s="3" t="s">
         <v>1701</v>
       </c>
@@ -48639,7 +48640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="30">
+    <row r="345" spans="1:23" ht="30" hidden="1">
       <c r="A345" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48706,7 +48707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="30">
+    <row r="346" spans="1:23" ht="30" hidden="1">
       <c r="A346" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48773,7 +48774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="30">
+    <row r="347" spans="1:23" ht="30" hidden="1">
       <c r="A347" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48840,7 +48841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="30">
+    <row r="348" spans="1:23" ht="30" hidden="1">
       <c r="A348" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48909,7 +48910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="45">
+    <row r="349" spans="1:23" ht="45" hidden="1">
       <c r="A349" s="3" t="s">
         <v>1803</v>
       </c>
@@ -48978,7 +48979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="30">
+    <row r="350" spans="1:23" ht="30" hidden="1">
       <c r="A350" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49045,7 +49046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="30">
+    <row r="351" spans="1:23" ht="30" hidden="1">
       <c r="A351" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49112,7 +49113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="30">
+    <row r="352" spans="1:23" ht="30" hidden="1">
       <c r="A352" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49181,7 +49182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="30">
+    <row r="353" spans="1:23" ht="30" hidden="1">
       <c r="A353" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49248,7 +49249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="30">
+    <row r="354" spans="1:23" ht="30" hidden="1">
       <c r="A354" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49315,7 +49316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="30">
+    <row r="355" spans="1:23" ht="30" hidden="1">
       <c r="A355" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49380,7 +49381,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="30">
+    <row r="356" spans="1:23" ht="30" hidden="1">
       <c r="A356" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49447,7 +49448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="45">
+    <row r="357" spans="1:23" ht="45" hidden="1">
       <c r="A357" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49516,7 +49517,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="30">
+    <row r="358" spans="1:23" ht="30" hidden="1">
       <c r="A358" s="3" t="s">
         <v>1803</v>
       </c>
@@ -49585,7 +49586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:23">
+    <row r="359" spans="1:23" hidden="1">
       <c r="A359" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49654,7 +49655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:23">
+    <row r="360" spans="1:23" hidden="1">
       <c r="A360" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49723,7 +49724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:23">
+    <row r="361" spans="1:23" hidden="1">
       <c r="A361" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49792,7 +49793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:23" ht="30">
+    <row r="362" spans="1:23" ht="30" hidden="1">
       <c r="A362" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49861,7 +49862,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="30">
+    <row r="363" spans="1:23" ht="30" hidden="1">
       <c r="A363" s="3" t="s">
         <v>1911</v>
       </c>
@@ -49930,7 +49931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="30">
+    <row r="364" spans="1:23" ht="30" hidden="1">
       <c r="A364" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50001,7 +50002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="30">
+    <row r="365" spans="1:23" ht="30" hidden="1">
       <c r="A365" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50070,7 +50071,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="366" spans="1:23">
+    <row r="366" spans="1:23" hidden="1">
       <c r="A366" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50141,7 +50142,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="30">
+    <row r="367" spans="1:23" ht="30" hidden="1">
       <c r="A367" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50212,7 +50213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="45">
+    <row r="368" spans="1:23" ht="45" hidden="1">
       <c r="A368" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50283,7 +50284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="30">
+    <row r="369" spans="1:23" ht="30" hidden="1">
       <c r="A369" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50354,7 +50355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:23">
+    <row r="370" spans="1:23" hidden="1">
       <c r="A370" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50423,7 +50424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="30">
+    <row r="371" spans="1:23" ht="30" hidden="1">
       <c r="A371" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50494,7 +50495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="30">
+    <row r="372" spans="1:23" ht="30" hidden="1">
       <c r="A372" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50563,7 +50564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="30">
+    <row r="373" spans="1:23" ht="30" hidden="1">
       <c r="A373" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50634,7 +50635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:23" ht="30">
+    <row r="374" spans="1:23" ht="30" hidden="1">
       <c r="A374" s="3" t="s">
         <v>1911</v>
       </c>
@@ -50705,7 +50706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="30">
+    <row r="375" spans="1:23" ht="30" hidden="1">
       <c r="A375" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50774,7 +50775,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="30">
+    <row r="376" spans="1:23" ht="30" hidden="1">
       <c r="A376" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50843,7 +50844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:23">
+    <row r="377" spans="1:23" hidden="1">
       <c r="A377" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50912,7 +50913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:23" ht="45">
+    <row r="378" spans="1:23" ht="45" hidden="1">
       <c r="A378" s="3" t="s">
         <v>1919</v>
       </c>
@@ -50981,7 +50982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:23" ht="30">
+    <row r="379" spans="1:23" ht="30" hidden="1">
       <c r="A379" s="3" t="s">
         <v>1919</v>
       </c>
@@ -51052,7 +51053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:23" ht="30">
+    <row r="380" spans="1:23" ht="30" hidden="1">
       <c r="A380" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51123,7 +51124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="30">
+    <row r="381" spans="1:23" ht="30" hidden="1">
       <c r="A381" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51194,7 +51195,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:23" ht="30">
+    <row r="382" spans="1:23" ht="30" hidden="1">
       <c r="A382" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51265,7 +51266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="45">
+    <row r="383" spans="1:23" ht="45" hidden="1">
       <c r="A383" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51336,7 +51337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:23" ht="30">
+    <row r="384" spans="1:23" ht="30" hidden="1">
       <c r="A384" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51407,7 +51408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:23" ht="30">
+    <row r="385" spans="1:23" ht="30" hidden="1">
       <c r="A385" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51478,7 +51479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="30">
+    <row r="386" spans="1:23" ht="30" hidden="1">
       <c r="A386" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51549,7 +51550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:23" ht="30">
+    <row r="387" spans="1:23" ht="30" hidden="1">
       <c r="A387" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51620,7 +51621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:23" ht="30">
+    <row r="388" spans="1:23" ht="30" hidden="1">
       <c r="A388" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51691,7 +51692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="30">
+    <row r="389" spans="1:23" ht="30" hidden="1">
       <c r="A389" s="4" t="s">
         <v>2014</v>
       </c>
@@ -51762,7 +51763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:23" ht="30">
+    <row r="390" spans="1:23" ht="30" hidden="1">
       <c r="A390" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51833,7 +51834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:23" ht="30">
+    <row r="391" spans="1:23" ht="30" hidden="1">
       <c r="A391" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51904,7 +51905,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:23" ht="30">
+    <row r="392" spans="1:23" ht="30" hidden="1">
       <c r="A392" s="4" t="s">
         <v>2058</v>
       </c>
@@ -51975,7 +51976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="30">
+    <row r="393" spans="1:23" ht="30" hidden="1">
       <c r="A393" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52046,7 +52047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:23" ht="30">
+    <row r="394" spans="1:23" ht="30" hidden="1">
       <c r="A394" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52117,7 +52118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:23" ht="45">
+    <row r="395" spans="1:23" ht="45" hidden="1">
       <c r="A395" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52188,7 +52189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:23" ht="30">
+    <row r="396" spans="1:23" ht="30" hidden="1">
       <c r="A396" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52259,7 +52260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:23" ht="30">
+    <row r="397" spans="1:23" ht="30" hidden="1">
       <c r="A397" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52330,7 +52331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="398" spans="1:23" ht="30">
+    <row r="398" spans="1:23" ht="30" hidden="1">
       <c r="A398" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52401,7 +52402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:23" ht="30">
+    <row r="399" spans="1:23" ht="30" hidden="1">
       <c r="A399" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52472,7 +52473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="400" spans="1:23" ht="30">
+    <row r="400" spans="1:23" ht="30" hidden="1">
       <c r="A400" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52543,7 +52544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:23" ht="30">
+    <row r="401" spans="1:23" ht="30" hidden="1">
       <c r="A401" s="4" t="s">
         <v>2058</v>
       </c>
@@ -52614,7 +52615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:23">
+    <row r="402" spans="1:23" hidden="1">
       <c r="A402" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52685,7 +52686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:23" ht="30">
+    <row r="403" spans="1:23" ht="30" hidden="1">
       <c r="A403" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52756,7 +52757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:23" ht="30">
+    <row r="404" spans="1:23" ht="30" hidden="1">
       <c r="A404" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52827,7 +52828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:23" ht="45">
+    <row r="405" spans="1:23" ht="45" hidden="1">
       <c r="A405" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52895,7 +52896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:23" ht="30">
+    <row r="406" spans="1:23" ht="30" hidden="1">
       <c r="A406" s="4" t="s">
         <v>2106</v>
       </c>
@@ -52963,7 +52964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:23" ht="45">
+    <row r="407" spans="1:23" ht="45" hidden="1">
       <c r="A407" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53034,7 +53035,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:23" ht="30">
+    <row r="408" spans="1:23" ht="30" hidden="1">
       <c r="A408" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53105,7 +53106,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:23" ht="30">
+    <row r="409" spans="1:23" ht="30" hidden="1">
       <c r="A409" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53176,7 +53177,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:23" ht="30">
+    <row r="410" spans="1:23" ht="30" hidden="1">
       <c r="A410" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53247,7 +53248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:23" ht="45">
+    <row r="411" spans="1:23" ht="45" hidden="1">
       <c r="A411" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53318,7 +53319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:23" ht="30">
+    <row r="412" spans="1:23" ht="30" hidden="1">
       <c r="A412" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53389,7 +53390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:23" ht="45">
+    <row r="413" spans="1:23" ht="45" hidden="1">
       <c r="A413" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53460,7 +53461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:23" ht="30">
+    <row r="414" spans="1:23" ht="30" hidden="1">
       <c r="A414" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53531,7 +53532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:23" ht="30">
+    <row r="415" spans="1:23" ht="30" hidden="1">
       <c r="A415" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53599,7 +53600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="416" spans="1:23" ht="30">
+    <row r="416" spans="1:23" ht="30" hidden="1">
       <c r="A416" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53667,7 +53668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="1:23" ht="30">
+    <row r="417" spans="1:23" ht="30" hidden="1">
       <c r="A417" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53735,7 +53736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="418" spans="1:23" ht="30">
+    <row r="418" spans="1:23" ht="30" hidden="1">
       <c r="A418" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53806,7 +53807,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:23" ht="30">
+    <row r="419" spans="1:23" ht="30" hidden="1">
       <c r="A419" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53877,7 +53878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:23" ht="30">
+    <row r="420" spans="1:23" ht="30" hidden="1">
       <c r="A420" s="4" t="s">
         <v>2106</v>
       </c>
@@ -53948,7 +53949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="1:23" ht="30">
+    <row r="421" spans="1:23" ht="30" hidden="1">
       <c r="A421" s="4" t="s">
         <v>2106</v>
       </c>
@@ -54019,7 +54020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="422" spans="1:23" ht="30">
+    <row r="422" spans="1:23" ht="30" hidden="1">
       <c r="A422" s="4" t="s">
         <v>2106</v>
       </c>
@@ -54090,7 +54091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:23" ht="30">
+    <row r="423" spans="1:23" ht="30" hidden="1">
       <c r="A423" s="4" t="s">
         <v>2106</v>
       </c>
@@ -54161,7 +54162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="424" spans="1:23" ht="30">
+    <row r="424" spans="1:23" ht="30" hidden="1">
       <c r="A424" s="4" t="s">
         <v>2106</v>
       </c>
@@ -54232,7 +54233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="425" spans="1:23" ht="45">
+    <row r="425" spans="1:23" ht="45" hidden="1">
       <c r="A425" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54303,7 +54304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="1:23" ht="30">
+    <row r="426" spans="1:23" ht="30" hidden="1">
       <c r="A426" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54374,7 +54375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="427" spans="1:23" ht="45">
+    <row r="427" spans="1:23" ht="45" hidden="1">
       <c r="A427" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54445,7 +54446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="428" spans="1:23" ht="30">
+    <row r="428" spans="1:23" ht="30" hidden="1">
       <c r="A428" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54516,7 +54517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="429" spans="1:23" ht="45">
+    <row r="429" spans="1:23" ht="45" hidden="1">
       <c r="A429" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54587,7 +54588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="430" spans="1:23" ht="45">
+    <row r="430" spans="1:23" ht="45" hidden="1">
       <c r="A430" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54658,7 +54659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:23" ht="45">
+    <row r="431" spans="1:23" ht="45" hidden="1">
       <c r="A431" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54729,7 +54730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:23" ht="30">
+    <row r="432" spans="1:23" ht="30" hidden="1">
       <c r="A432" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54800,7 +54801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:23" ht="30">
+    <row r="433" spans="1:23" ht="30" hidden="1">
       <c r="A433" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54871,7 +54872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:23" ht="30">
+    <row r="434" spans="1:23" ht="30" hidden="1">
       <c r="A434" s="3" t="s">
         <v>2349</v>
       </c>
@@ -54942,7 +54943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="435" spans="1:23" ht="30">
+    <row r="435" spans="1:23" ht="30" hidden="1">
       <c r="A435" s="3" t="s">
         <v>2349</v>
       </c>
@@ -55013,7 +55014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="436" spans="1:23" ht="30">
+    <row r="436" spans="1:23" ht="30" hidden="1">
       <c r="A436" s="3" t="s">
         <v>2349</v>
       </c>
@@ -55084,7 +55085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="437" spans="1:23" ht="30">
+    <row r="437" spans="1:23" ht="30" hidden="1">
       <c r="A437" s="3" t="s">
         <v>2349</v>
       </c>
@@ -55155,7 +55156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="1:23" ht="30">
+    <row r="438" spans="1:23" ht="30" hidden="1">
       <c r="A438" s="3" t="s">
         <v>2349</v>
       </c>
@@ -55226,7 +55227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="439" spans="1:23">
+    <row r="439" spans="1:23" hidden="1">
       <c r="A439" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55297,7 +55298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:23" ht="30">
+    <row r="440" spans="1:23" ht="30" hidden="1">
       <c r="A440" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55368,7 +55369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:23" ht="30">
+    <row r="441" spans="1:23" ht="30" hidden="1">
       <c r="A441" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55439,7 +55440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:23" ht="45">
+    <row r="442" spans="1:23" ht="45" hidden="1">
       <c r="A442" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55510,7 +55511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:23" ht="30">
+    <row r="443" spans="1:23" ht="30" hidden="1">
       <c r="A443" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55581,7 +55582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="444" spans="1:23" ht="45">
+    <row r="444" spans="1:23" ht="45" hidden="1">
       <c r="A444" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55652,7 +55653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:23" ht="30">
+    <row r="445" spans="1:23" ht="30" hidden="1">
       <c r="A445" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55723,7 +55724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="446" spans="1:23" ht="30">
+    <row r="446" spans="1:23" ht="30" hidden="1">
       <c r="A446" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55794,7 +55795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:23" ht="30">
+    <row r="447" spans="1:23" ht="30" hidden="1">
       <c r="A447" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55865,7 +55866,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:23" ht="30">
+    <row r="448" spans="1:23" ht="30" hidden="1">
       <c r="A448" s="4" t="s">
         <v>2426</v>
       </c>
@@ -55936,7 +55937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:23" ht="30">
+    <row r="449" spans="1:23" ht="30" hidden="1">
       <c r="A449" s="4" t="s">
         <v>2426</v>
       </c>
@@ -56007,7 +56008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:23" ht="30">
+    <row r="450" spans="1:23" ht="30" hidden="1">
       <c r="A450" s="4" t="s">
         <v>2426</v>
       </c>
@@ -56078,7 +56079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="451" spans="1:23" ht="30">
+    <row r="451" spans="1:23" ht="30" hidden="1">
       <c r="A451" s="3" t="s">
         <v>3691</v>
       </c>
@@ -56145,7 +56146,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="1:23" ht="30">
+    <row r="452" spans="1:23" ht="30" hidden="1">
       <c r="A452" s="3" t="s">
         <v>3691</v>
       </c>
@@ -56212,7 +56213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="453" spans="1:23" ht="30">
+    <row r="453" spans="1:23" ht="30" hidden="1">
       <c r="A453" s="3" t="s">
         <v>3691</v>
       </c>
@@ -56279,7 +56280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="454" spans="1:23" ht="30">
+    <row r="454" spans="1:23" ht="30" hidden="1">
       <c r="A454" s="3" t="s">
         <v>3691</v>
       </c>
@@ -56346,7 +56347,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="1:23" ht="30">
+    <row r="455" spans="1:23" ht="30" hidden="1">
       <c r="A455" s="3" t="s">
         <v>3691</v>
       </c>
@@ -56415,7 +56416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="456" spans="1:23" ht="45">
+    <row r="456" spans="1:23" ht="45" hidden="1">
       <c r="A456" s="3" t="s">
         <v>3691</v>
       </c>
@@ -56484,7 +56485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="457" spans="1:23" ht="30">
+    <row r="457" spans="1:23" ht="30" hidden="1">
       <c r="A457" s="3" t="s">
         <v>3684</v>
       </c>
@@ -56551,7 +56552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="458" spans="1:23" ht="30">
+    <row r="458" spans="1:23" ht="30" hidden="1">
       <c r="A458" s="3" t="s">
         <v>3684</v>
       </c>
@@ -56620,7 +56621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="459" spans="1:23">
+    <row r="459" spans="1:23" hidden="1">
       <c r="A459" s="3" t="s">
         <v>3684</v>
       </c>
@@ -56689,7 +56690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="460" spans="1:23" ht="45">
+    <row r="460" spans="1:23" ht="45" hidden="1">
       <c r="A460" s="3" t="s">
         <v>3684</v>
       </c>
@@ -56758,7 +56759,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:23" ht="30">
+    <row r="461" spans="1:23" ht="30" hidden="1">
       <c r="A461" s="3" t="s">
         <v>3684</v>
       </c>
@@ -56825,7 +56826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="462" spans="1:23" ht="30">
+    <row r="462" spans="1:23" ht="30" hidden="1">
       <c r="A462" s="3" t="s">
         <v>3684</v>
       </c>
@@ -56895,7 +56896,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W462" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}"/>
+  <autoFilter ref="A1:W462" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="User"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="Q9" r:id="rId1" display="mailto:admin@memgine.com" xr:uid="{93170BB8-77D4-4002-829B-D89928109808}"/>
     <hyperlink ref="Q11" r:id="rId2" display="https://memgine.com/" xr:uid="{F8EB4105-6CCB-4B06-B657-948DB365F556}"/>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33515F69-0C57-4F6E-B889-AE4FF4F8E54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A35921-CCDD-42A1-93FE-2620AF86A747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15096" uniqueCount="4043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16422" uniqueCount="4308">
   <si>
     <t>Domain</t>
   </si>
@@ -12173,6 +12173,801 @@
   </si>
   <si>
     <t>https://cdn.example.com/org/hero.png</t>
+  </si>
+  <si>
+    <t>customer_preference</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Customer Preference</t>
+  </si>
+  <si>
+    <t>Customer Preference ID</t>
+  </si>
+  <si>
+    <t>referral_program</t>
+  </si>
+  <si>
+    <t>Customer Engagement</t>
+  </si>
+  <si>
+    <t>Referral</t>
+  </si>
+  <si>
+    <t>Referral Program</t>
+  </si>
+  <si>
+    <t>Organization-owned referral rules and reward configuration.</t>
+  </si>
+  <si>
+    <t>Referral Program ID</t>
+  </si>
+  <si>
+    <t>Referral Program Name</t>
+  </si>
+  <si>
+    <t>referral</t>
+  </si>
+  <si>
+    <t>A concrete referral generated by a customer and tracked through acceptance and conversion.</t>
+  </si>
+  <si>
+    <t>Referral ID</t>
+  </si>
+  <si>
+    <t>Referral Code</t>
+  </si>
+  <si>
+    <t>customer_preference_id</t>
+  </si>
+  <si>
+    <t>USR-001</t>
+  </si>
+  <si>
+    <t>Preference Status ID</t>
+  </si>
+  <si>
+    <t>preference_status_id</t>
+  </si>
+  <si>
+    <t>preference-status-active</t>
+  </si>
+  <si>
+    <t>2026-09-10T10:00:00Z</t>
+  </si>
+  <si>
+    <t>User ID</t>
+  </si>
+  <si>
+    <t>owns referral program</t>
+  </si>
+  <si>
+    <t>1:N</t>
+  </si>
+  <si>
+    <t>An organization may configure referral programs.</t>
+  </si>
+  <si>
+    <t>contains referrals</t>
+  </si>
+  <si>
+    <t>Referrals are organization-scoped transactions.</t>
+  </si>
+  <si>
+    <t>generates referrals</t>
+  </si>
+  <si>
+    <t>Each referral is created under one referral program.</t>
+  </si>
+  <si>
+    <t>creates referrals</t>
+  </si>
+  <si>
+    <t>Referrer User</t>
+  </si>
+  <si>
+    <t>A global customer can create multiple referrals.</t>
+  </si>
+  <si>
+    <t>is referred by</t>
+  </si>
+  <si>
+    <t>Referred User</t>
+  </si>
+  <si>
+    <t>A User may be the referred user for a referral record.</t>
+  </si>
+  <si>
+    <t>REL068</t>
+  </si>
+  <si>
+    <t>REL069</t>
+  </si>
+  <si>
+    <t>REL070</t>
+  </si>
+  <si>
+    <t>REL071</t>
+  </si>
+  <si>
+    <t>REL072</t>
+  </si>
+  <si>
+    <t>REL073</t>
+  </si>
+  <si>
+    <t>DateTime</t>
+  </si>
+  <si>
+    <t>Audit preference creation</t>
+  </si>
+  <si>
+    <t>System audit timestamp.</t>
+  </si>
+  <si>
+    <t>Audit preference updates</t>
+  </si>
+  <si>
+    <t>Audit reference to the last updater.</t>
+  </si>
+  <si>
+    <t>Support logical deletion</t>
+  </si>
+  <si>
+    <t>Support optimistic concurrency</t>
+  </si>
+  <si>
+    <t>Incremented whenever the record is updated.</t>
+  </si>
+  <si>
+    <t>referral_program_id</t>
+  </si>
+  <si>
+    <t>Uniquely identify a referral program</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the referral program.</t>
+  </si>
+  <si>
+    <t>Primary identifier for an organization's referral program configuration.</t>
+  </si>
+  <si>
+    <t>REFPROG-001</t>
+  </si>
+  <si>
+    <t>Organization that owns and configures the referral program.</t>
+  </si>
+  <si>
+    <t>Identifies the business whose customers participate in the referral program.</t>
+  </si>
+  <si>
+    <t>org-sunrise</t>
+  </si>
+  <si>
+    <t>Referral Program Code</t>
+  </si>
+  <si>
+    <t>referral_program_code</t>
+  </si>
+  <si>
+    <t>Provide a business identifier for the referral program</t>
+  </si>
+  <si>
+    <t>Unique business code assigned to the referral program.</t>
+  </si>
+  <si>
+    <t>Human-readable code used in administration, reporting and integrations.</t>
+  </si>
+  <si>
+    <t>SUNRISE-REFER</t>
+  </si>
+  <si>
+    <t>referral_program_name</t>
+  </si>
+  <si>
+    <t>Identify the referral program</t>
+  </si>
+  <si>
+    <t>Customer-facing and administrative name of the referral program.</t>
+  </si>
+  <si>
+    <t>Display name used when presenting the referral program to customers.</t>
+  </si>
+  <si>
+    <t>Refer a Friend</t>
+  </si>
+  <si>
+    <t>Describe the referral program</t>
+  </si>
+  <si>
+    <t>Explanation of the referral program and its purpose.</t>
+  </si>
+  <si>
+    <t>Customer-facing description of how the referral program works.</t>
+  </si>
+  <si>
+    <t>Invite a friend and earn a reward.</t>
+  </si>
+  <si>
+    <t>Referrer Reward Type ID</t>
+  </si>
+  <si>
+    <t>referrer_reward_type_id</t>
+  </si>
+  <si>
+    <t>Reward Type</t>
+  </si>
+  <si>
+    <t>Define the referrer reward type</t>
+  </si>
+  <si>
+    <t>Identifies the type of reward provided to the customer making the referral.</t>
+  </si>
+  <si>
+    <t>Reference to the reward configuration used for the referring customer.</t>
+  </si>
+  <si>
+    <t>reward-type-discount</t>
+  </si>
+  <si>
+    <t>Referrer Reward Value</t>
+  </si>
+  <si>
+    <t>referrer_reward_value</t>
+  </si>
+  <si>
+    <t>Define the referrer reward value</t>
+  </si>
+  <si>
+    <t>Stores the configured value associated with the referrer reward.</t>
+  </si>
+  <si>
+    <t>Reward amount or percentage interpreted according to the reward type.</t>
+  </si>
+  <si>
+    <t>Referee Reward Type ID</t>
+  </si>
+  <si>
+    <t>referee_reward_type_id</t>
+  </si>
+  <si>
+    <t>Define the referred customer reward type</t>
+  </si>
+  <si>
+    <t>Identifies the type of reward provided to the referred customer.</t>
+  </si>
+  <si>
+    <t>Reference to the reward configuration used for the referred customer.</t>
+  </si>
+  <si>
+    <t>Referee Reward Value</t>
+  </si>
+  <si>
+    <t>referee_reward_value</t>
+  </si>
+  <si>
+    <t>Define the referred customer reward value</t>
+  </si>
+  <si>
+    <t>Stores the configured value associated with the referee reward.</t>
+  </si>
+  <si>
+    <t>Define referral program start date</t>
+  </si>
+  <si>
+    <t>Records when the referral program becomes effective.</t>
+  </si>
+  <si>
+    <t>Beginning of the period during which the referral program can be used.</t>
+  </si>
+  <si>
+    <t>2026-09-01T00:00:00Z</t>
+  </si>
+  <si>
+    <t>Define referral program end date</t>
+  </si>
+  <si>
+    <t>Records the optional date after which the referral program is no longer effective.</t>
+  </si>
+  <si>
+    <t>End of the referral program validity period.</t>
+  </si>
+  <si>
+    <t>2027-03-31T23:59:59Z</t>
+  </si>
+  <si>
+    <t>Referral Program Status ID</t>
+  </si>
+  <si>
+    <t>referral_program_status_id</t>
+  </si>
+  <si>
+    <t>Track referral program lifecycle</t>
+  </si>
+  <si>
+    <t>Identifies the current lifecycle status of the referral program.</t>
+  </si>
+  <si>
+    <t>Reference to the applicable referral program status.</t>
+  </si>
+  <si>
+    <t>referral-program-status-active</t>
+  </si>
+  <si>
+    <t>Audit referral program creation</t>
+  </si>
+  <si>
+    <t>Records when the referral program was created.</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that created the referral program.</t>
+  </si>
+  <si>
+    <t>USR-SYSTEM</t>
+  </si>
+  <si>
+    <t>Audit referral program updates</t>
+  </si>
+  <si>
+    <t>Records when the referral program was last updated.</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that last updated the referral program.</t>
+  </si>
+  <si>
+    <t>Indicates whether the referral program has been logically deleted.</t>
+  </si>
+  <si>
+    <t>Soft-delete indicator for the referral program.</t>
+  </si>
+  <si>
+    <t>Stores the version of the referral program for concurrency control.</t>
+  </si>
+  <si>
+    <t>referral_id</t>
+  </si>
+  <si>
+    <t>Uniquely identify a referral</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the referral transaction.</t>
+  </si>
+  <si>
+    <t>Primary identifier for a concrete referral generated by a customer.</t>
+  </si>
+  <si>
+    <t>REF-001</t>
+  </si>
+  <si>
+    <t>Organization in which the referral was created.</t>
+  </si>
+  <si>
+    <t>Establishes the business context of the referral.</t>
+  </si>
+  <si>
+    <t>Referral program under which the referral was generated.</t>
+  </si>
+  <si>
+    <t>Links the referral to the organization's configured referral rules.</t>
+  </si>
+  <si>
+    <t>referrer_user_id</t>
+  </si>
+  <si>
+    <t>Identify the referring customer</t>
+  </si>
+  <si>
+    <t>Global User who generated the referral.</t>
+  </si>
+  <si>
+    <t>Identifies the customer who owns the referral relationship.</t>
+  </si>
+  <si>
+    <t>referral_code</t>
+  </si>
+  <si>
+    <t>Provide a shareable referral identifier</t>
+  </si>
+  <si>
+    <t>Persisted code used to identify the referral when shared with another customer.</t>
+  </si>
+  <si>
+    <t>Unique code that can later be resolved when the referred customer joins or converts.</t>
+  </si>
+  <si>
+    <t>MG-SUNR-USR01-A1B2</t>
+  </si>
+  <si>
+    <t>referred_user_id</t>
+  </si>
+  <si>
+    <t>Identify the referred customer</t>
+  </si>
+  <si>
+    <t>Identifies the global User associated with the referral after acceptance.</t>
+  </si>
+  <si>
+    <t>Links the referral to the referred customer when that customer becomes known.</t>
+  </si>
+  <si>
+    <t>USR-002</t>
+  </si>
+  <si>
+    <t>Referred Email</t>
+  </si>
+  <si>
+    <t>referred_email</t>
+  </si>
+  <si>
+    <t>Capture referred customer email</t>
+  </si>
+  <si>
+    <t>Stores the optional email address of the person invited through the referral.</t>
+  </si>
+  <si>
+    <t>Invite target email retained for referral resolution.</t>
+  </si>
+  <si>
+    <t>friend@example.com</t>
+  </si>
+  <si>
+    <t>Referred Phone</t>
+  </si>
+  <si>
+    <t>referred_phone</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>Capture referred customer phone</t>
+  </si>
+  <si>
+    <t>Stores the optional phone number of the person invited through the referral.</t>
+  </si>
+  <si>
+    <t>Invite target phone retained for referral resolution.</t>
+  </si>
+  <si>
+    <t>+1 416 555 0100</t>
+  </si>
+  <si>
+    <t>Referral Status ID</t>
+  </si>
+  <si>
+    <t>referral_status_id</t>
+  </si>
+  <si>
+    <t>Track referral lifecycle</t>
+  </si>
+  <si>
+    <t>Identifies the current lifecycle status of the referral.</t>
+  </si>
+  <si>
+    <t>Reference to the applicable referral status.</t>
+  </si>
+  <si>
+    <t>referral-status-created</t>
+  </si>
+  <si>
+    <t>Audit referral creation</t>
+  </si>
+  <si>
+    <t>Records when the referral was created.</t>
+  </si>
+  <si>
+    <t>Accepted At</t>
+  </si>
+  <si>
+    <t>accepted_at</t>
+  </si>
+  <si>
+    <t>Track referral acceptance</t>
+  </si>
+  <si>
+    <t>Records when the referred person accepted the referral.</t>
+  </si>
+  <si>
+    <t>Marks the point at which the referral was accepted.</t>
+  </si>
+  <si>
+    <t>Converted At</t>
+  </si>
+  <si>
+    <t>converted_at</t>
+  </si>
+  <si>
+    <t>Track referral conversion</t>
+  </si>
+  <si>
+    <t>Records when the referred customer completed the qualifying action.</t>
+  </si>
+  <si>
+    <t>Marks successful conversion according to the referral program rules.</t>
+  </si>
+  <si>
+    <t>Reward Issued At</t>
+  </si>
+  <si>
+    <t>reward_issued_at</t>
+  </si>
+  <si>
+    <t>Track reward issuance</t>
+  </si>
+  <si>
+    <t>Records when the referral reward was issued.</t>
+  </si>
+  <si>
+    <t>Provides an audit point for referral reward fulfilment.</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that created the referral.</t>
+  </si>
+  <si>
+    <t>Audit referral updates</t>
+  </si>
+  <si>
+    <t>Records when the referral was last updated.</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that last updated the referral.</t>
+  </si>
+  <si>
+    <t>Indicates whether the referral has been logically deleted.</t>
+  </si>
+  <si>
+    <t>Soft-delete indicator for the referral.</t>
+  </si>
+  <si>
+    <t>Stores the version of the referral for concurrency control.</t>
+  </si>
+  <si>
+    <t>preference_type</t>
+  </si>
+  <si>
+    <t>Preference Type</t>
+  </si>
+  <si>
+    <t>Defines the supported customer preference types, their data types, defaults and validation semantics.</t>
+  </si>
+  <si>
+    <t>Preference Type ID</t>
+  </si>
+  <si>
+    <t>Preference Type Name</t>
+  </si>
+  <si>
+    <t>Stores a customer's value for a supported preference type.</t>
+  </si>
+  <si>
+    <t>defines customer preference</t>
+  </si>
+  <si>
+    <t>Each Customer Preference references one supported Preference Type.</t>
+  </si>
+  <si>
+    <t>has customer preferences</t>
+  </si>
+  <si>
+    <t>A User may have multiple Customer Preference records, normally one per Preference Type.</t>
+  </si>
+  <si>
+    <t>REL074</t>
+  </si>
+  <si>
+    <t>preference_type_id</t>
+  </si>
+  <si>
+    <t>Uniquely identify a preference type</t>
+  </si>
+  <si>
+    <t>System-generated identifier for a supported customer preference type</t>
+  </si>
+  <si>
+    <t>Primary identifier for reference and configuration of customer preference semantics</t>
+  </si>
+  <si>
+    <t>PT-001</t>
+  </si>
+  <si>
+    <t>Preference Type Code</t>
+  </si>
+  <si>
+    <t>preference_type_code</t>
+  </si>
+  <si>
+    <t>Provide a stable business code</t>
+  </si>
+  <si>
+    <t>Unique code used by application logic to identify the preference type</t>
+  </si>
+  <si>
+    <t>Stable machine-readable key such as NOTIFICATIONS, MARKETING_EMAILS or THEME</t>
+  </si>
+  <si>
+    <t>NOTIFICATIONS</t>
+  </si>
+  <si>
+    <t>preference_type_name</t>
+  </si>
+  <si>
+    <t>Identify the preference type</t>
+  </si>
+  <si>
+    <t>Human-readable name of the supported preference</t>
+  </si>
+  <si>
+    <t>Display name used by administration and customer-facing configuration</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>Define the preference value type</t>
+  </si>
+  <si>
+    <t>Identifies how the associated Preference Value must be interpreted and validated</t>
+  </si>
+  <si>
+    <t>Determines whether the preference value is Boolean, Text, Integer, Decimal, Identifier, Date or another supported type</t>
+  </si>
+  <si>
+    <t>default_value</t>
+  </si>
+  <si>
+    <t>Define default preference value</t>
+  </si>
+  <si>
+    <t>Stores the default value used when a customer has not explicitly configured the preference</t>
+  </si>
+  <si>
+    <t>Default value is interpreted according to the Preference Type Data Type</t>
+  </si>
+  <si>
+    <t>Describe the preference type</t>
+  </si>
+  <si>
+    <t>Explains the meaning and expected use of the preference</t>
+  </si>
+  <si>
+    <t>Business description of the preference for administration and product configuration</t>
+  </si>
+  <si>
+    <t>Controls whether customer notifications are enabled</t>
+  </si>
+  <si>
+    <t>Preference Type Status ID</t>
+  </si>
+  <si>
+    <t>preference_type_status_id</t>
+  </si>
+  <si>
+    <t>Track preference type lifecycle</t>
+  </si>
+  <si>
+    <t>Identifies the lifecycle status of the preference type</t>
+  </si>
+  <si>
+    <t>Reference to the applicable status value</t>
+  </si>
+  <si>
+    <t>preference-type-status-active</t>
+  </si>
+  <si>
+    <t>Audit preference type creation</t>
+  </si>
+  <si>
+    <t>Records when the preference type was created</t>
+  </si>
+  <si>
+    <t>System audit timestamp</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that created the preference type</t>
+  </si>
+  <si>
+    <t>Audit reference to the creator</t>
+  </si>
+  <si>
+    <t>Audit preference type updates</t>
+  </si>
+  <si>
+    <t>Records when the preference type was last updated</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that last updated the preference type</t>
+  </si>
+  <si>
+    <t>Audit reference to the last updater</t>
+  </si>
+  <si>
+    <t>Indicates whether the preference type has been logically deleted</t>
+  </si>
+  <si>
+    <t>Soft-delete indicator for the preference type</t>
+  </si>
+  <si>
+    <t>Stores the version of the preference type for concurrency control</t>
+  </si>
+  <si>
+    <t>Incremented whenever the record is updated</t>
+  </si>
+  <si>
+    <t>Uniquely identify a customer preference</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the customer's preference record</t>
+  </si>
+  <si>
+    <t>Primary identifier for one customer's preference value</t>
+  </si>
+  <si>
+    <t>CP-001</t>
+  </si>
+  <si>
+    <t>Identify the customer</t>
+  </si>
+  <si>
+    <t>Global User who owns the preference</t>
+  </si>
+  <si>
+    <t>Links the preference to the global customer identity, independent of membership or organization</t>
+  </si>
+  <si>
+    <t>Identify the preference being stored</t>
+  </si>
+  <si>
+    <t>Identifies the type of preference represented by this record</t>
+  </si>
+  <si>
+    <t>Defines the semantics and data type of Preference Value</t>
+  </si>
+  <si>
+    <t>Preference Value</t>
+  </si>
+  <si>
+    <t>preference_value</t>
+  </si>
+  <si>
+    <t>Store the customer's preference value</t>
+  </si>
+  <si>
+    <t>Stores the customer-selected value for the associated Preference Type</t>
+  </si>
+  <si>
+    <t>Value is interpreted and validated according to Preference Type Data Type</t>
+  </si>
+  <si>
+    <t>Track customer preference lifecycle</t>
+  </si>
+  <si>
+    <t>Identifies the lifecycle status of the customer preference record</t>
+  </si>
+  <si>
+    <t>Records when the customer preference was created</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that created the preference</t>
+  </si>
+  <si>
+    <t>Records when the customer preference was last updated</t>
+  </si>
+  <si>
+    <t>Identifies the user or process that last updated the preference</t>
+  </si>
+  <si>
+    <t>Indicates whether the customer preference has been logically deleted</t>
+  </si>
+  <si>
+    <t>Soft-delete indicator for the customer preference record</t>
+  </si>
+  <si>
+    <t>Stores the version of the customer preference for concurrency control</t>
   </si>
 </sst>
 </file>
@@ -12401,7 +13196,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q41" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q45" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -12722,7 +13517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -14909,6 +15704,206 @@
         <v>3739</v>
       </c>
     </row>
+    <row r="42" spans="1:17" ht="30">
+      <c r="A42" s="4" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>4048</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>4047</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>4051</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>4052</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>4053</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="30">
+      <c r="A43" s="4" t="s">
+        <v>4054</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>4048</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>4054</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>4055</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>4056</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>4057</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="30">
+      <c r="A44" s="4" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>4226</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>4228</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>4229</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>4230</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="30">
+      <c r="A45" s="4" t="s">
+        <v>4043</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>4231</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>4046</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>4046</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18470,7 +19465,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -20865,6 +21860,251 @@
       </c>
       <c r="K68" s="3" t="s">
         <v>3976</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="3" t="s">
+        <v>4078</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>4050</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>4065</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="3" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>4068</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="3" t="s">
+        <v>4080</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>4050</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>4070</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>4052</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>4050</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="3" t="s">
+        <v>4081</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>4072</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4064</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4073</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="3" t="s">
+        <v>4082</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>4075</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>4064</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>4076</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="30">
+      <c r="A74" s="3" t="s">
+        <v>4083</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>4227</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>4045</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>4232</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>4229</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>4227</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="30">
+      <c r="A75" s="3" t="s">
+        <v>4236</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>4045</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>4234</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>4064</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>4235</v>
       </c>
     </row>
   </sheetData>
@@ -24922,7 +26162,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <dimension ref="A1:W464"/>
+  <dimension ref="A1:W524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -57044,6 +58284,3954 @@
         <v>6</v>
       </c>
     </row>
+    <row r="465" spans="1:23" ht="30">
+      <c r="A465" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B465" s="4">
+        <v>1</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>4052</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>4092</v>
+      </c>
+      <c r="E465" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G465" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H465" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I465" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J465" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K465" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L465" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M465" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N465" s="4" t="s">
+        <v>4093</v>
+      </c>
+      <c r="O465" s="4" t="s">
+        <v>4094</v>
+      </c>
+      <c r="P465" s="4" t="s">
+        <v>4095</v>
+      </c>
+      <c r="Q465" s="4" t="s">
+        <v>4096</v>
+      </c>
+      <c r="S465" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T465" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U465" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V465" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W465" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="466" spans="1:23">
+      <c r="A466" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B466" s="4">
+        <v>2</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E466" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G466" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H466" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I466" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J466" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K466" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L466" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M466" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N466" s="4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="O466" s="4" t="s">
+        <v>4097</v>
+      </c>
+      <c r="P466" s="4" t="s">
+        <v>4098</v>
+      </c>
+      <c r="Q466" s="4" t="s">
+        <v>4099</v>
+      </c>
+      <c r="S466" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T466" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U466" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V466" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W466" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="467" spans="1:23">
+      <c r="A467" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B467" s="4">
+        <v>3</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>4100</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>4101</v>
+      </c>
+      <c r="E467" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F467" s="4">
+        <v>50</v>
+      </c>
+      <c r="G467" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H467" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I467" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J467" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K467" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L467" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M467" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N467" s="4" t="s">
+        <v>4102</v>
+      </c>
+      <c r="O467" s="4" t="s">
+        <v>4103</v>
+      </c>
+      <c r="P467" s="4" t="s">
+        <v>4104</v>
+      </c>
+      <c r="Q467" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="S467" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T467" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U467" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V467" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W467" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="468" spans="1:23">
+      <c r="A468" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B468" s="4">
+        <v>4</v>
+      </c>
+      <c r="C468" s="4" t="s">
+        <v>4053</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>4106</v>
+      </c>
+      <c r="E468" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F468" s="4">
+        <v>200</v>
+      </c>
+      <c r="G468" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H468" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I468" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J468" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K468" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L468" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M468" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N468" s="4" t="s">
+        <v>4107</v>
+      </c>
+      <c r="O468" s="4" t="s">
+        <v>4108</v>
+      </c>
+      <c r="P468" s="4" t="s">
+        <v>4109</v>
+      </c>
+      <c r="Q468" s="4" t="s">
+        <v>4110</v>
+      </c>
+      <c r="S468" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T468" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U468" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V468" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W468" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="469" spans="1:23">
+      <c r="A469" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B469" s="4">
+        <v>5</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E469" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F469" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G469" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H469" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I469" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J469" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K469" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L469" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M469" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N469" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="O469" s="4" t="s">
+        <v>4112</v>
+      </c>
+      <c r="P469" s="4" t="s">
+        <v>4113</v>
+      </c>
+      <c r="Q469" s="4" t="s">
+        <v>4114</v>
+      </c>
+      <c r="S469" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T469" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U469" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V469" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W469" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="470" spans="1:23">
+      <c r="A470" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B470" s="4">
+        <v>6</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>4115</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>4116</v>
+      </c>
+      <c r="E470" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G470" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H470" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I470" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J470" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K470" s="4" t="s">
+        <v>4117</v>
+      </c>
+      <c r="L470" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M470" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N470" s="4" t="s">
+        <v>4118</v>
+      </c>
+      <c r="O470" s="4" t="s">
+        <v>4119</v>
+      </c>
+      <c r="P470" s="4" t="s">
+        <v>4120</v>
+      </c>
+      <c r="Q470" s="4" t="s">
+        <v>4121</v>
+      </c>
+      <c r="S470" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T470" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U470" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V470" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W470" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="471" spans="1:23">
+      <c r="A471" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B471" s="4">
+        <v>7</v>
+      </c>
+      <c r="C471" s="4" t="s">
+        <v>4122</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>4123</v>
+      </c>
+      <c r="E471" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G471" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H471" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I471" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J471" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K471" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L471" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M471" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N471" s="4" t="s">
+        <v>4124</v>
+      </c>
+      <c r="O471" s="4" t="s">
+        <v>4125</v>
+      </c>
+      <c r="P471" s="4" t="s">
+        <v>4126</v>
+      </c>
+      <c r="Q471" s="4">
+        <v>10</v>
+      </c>
+      <c r="S471" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T471" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U471" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V471" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W471" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="472" spans="1:23">
+      <c r="A472" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B472" s="4">
+        <v>8</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>4127</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>4128</v>
+      </c>
+      <c r="E472" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G472" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H472" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I472" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J472" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K472" s="4" t="s">
+        <v>4117</v>
+      </c>
+      <c r="L472" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M472" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N472" s="4" t="s">
+        <v>4129</v>
+      </c>
+      <c r="O472" s="4" t="s">
+        <v>4130</v>
+      </c>
+      <c r="P472" s="4" t="s">
+        <v>4131</v>
+      </c>
+      <c r="Q472" s="4" t="s">
+        <v>4121</v>
+      </c>
+      <c r="S472" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T472" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U472" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V472" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W472" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="473" spans="1:23">
+      <c r="A473" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B473" s="4">
+        <v>9</v>
+      </c>
+      <c r="C473" s="4" t="s">
+        <v>4132</v>
+      </c>
+      <c r="D473" s="4" t="s">
+        <v>4133</v>
+      </c>
+      <c r="E473" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G473" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H473" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I473" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J473" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K473" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L473" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M473" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N473" s="4" t="s">
+        <v>4134</v>
+      </c>
+      <c r="O473" s="4" t="s">
+        <v>4135</v>
+      </c>
+      <c r="P473" s="4" t="s">
+        <v>4126</v>
+      </c>
+      <c r="Q473" s="4">
+        <v>10</v>
+      </c>
+      <c r="S473" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T473" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U473" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V473" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W473" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="474" spans="1:23">
+      <c r="A474" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B474" s="4">
+        <v>10</v>
+      </c>
+      <c r="C474" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="D474" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E474" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G474" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H474" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I474" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J474" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K474" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L474" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M474" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N474" s="4" t="s">
+        <v>4136</v>
+      </c>
+      <c r="O474" s="4" t="s">
+        <v>4137</v>
+      </c>
+      <c r="P474" s="4" t="s">
+        <v>4138</v>
+      </c>
+      <c r="Q474" s="4" t="s">
+        <v>4139</v>
+      </c>
+      <c r="S474" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T474" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U474" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V474" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W474" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="475" spans="1:23">
+      <c r="A475" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B475" s="4">
+        <v>11</v>
+      </c>
+      <c r="C475" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D475" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E475" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G475" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H475" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I475" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J475" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K475" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L475" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M475" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N475" s="4" t="s">
+        <v>4140</v>
+      </c>
+      <c r="O475" s="4" t="s">
+        <v>4141</v>
+      </c>
+      <c r="P475" s="4" t="s">
+        <v>4142</v>
+      </c>
+      <c r="Q475" s="4" t="s">
+        <v>4143</v>
+      </c>
+      <c r="S475" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T475" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U475" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V475" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W475" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="476" spans="1:23">
+      <c r="A476" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B476" s="4">
+        <v>12</v>
+      </c>
+      <c r="C476" s="4" t="s">
+        <v>4144</v>
+      </c>
+      <c r="D476" s="4" t="s">
+        <v>4145</v>
+      </c>
+      <c r="E476" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G476" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H476" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I476" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J476" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K476" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L476" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M476" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N476" s="4" t="s">
+        <v>4146</v>
+      </c>
+      <c r="O476" s="4" t="s">
+        <v>4147</v>
+      </c>
+      <c r="P476" s="4" t="s">
+        <v>4148</v>
+      </c>
+      <c r="Q476" s="4" t="s">
+        <v>4149</v>
+      </c>
+      <c r="S476" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T476" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U476" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V476" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W476" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="477" spans="1:23">
+      <c r="A477" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B477" s="4">
+        <v>13</v>
+      </c>
+      <c r="C477" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E477" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G477" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K477" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M477" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N477" s="4" t="s">
+        <v>4150</v>
+      </c>
+      <c r="O477" s="4" t="s">
+        <v>4151</v>
+      </c>
+      <c r="P477" s="4" t="s">
+        <v>4086</v>
+      </c>
+      <c r="Q477" s="4" t="s">
+        <v>4139</v>
+      </c>
+      <c r="S477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U477" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V477" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W477" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="478" spans="1:23">
+      <c r="A478" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B478" s="4">
+        <v>14</v>
+      </c>
+      <c r="C478" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D478" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E478" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G478" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H478" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I478" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J478" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K478" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L478" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M478" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N478" s="4" t="s">
+        <v>4150</v>
+      </c>
+      <c r="O478" s="4" t="s">
+        <v>4152</v>
+      </c>
+      <c r="P478" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q478" s="4" t="s">
+        <v>4153</v>
+      </c>
+      <c r="S478" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T478" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U478" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V478" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W478" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="479" spans="1:23">
+      <c r="A479" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B479" s="4">
+        <v>15</v>
+      </c>
+      <c r="C479" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D479" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E479" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G479" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K479" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M479" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N479" s="4" t="s">
+        <v>4154</v>
+      </c>
+      <c r="O479" s="4" t="s">
+        <v>4155</v>
+      </c>
+      <c r="P479" s="4" t="s">
+        <v>4086</v>
+      </c>
+      <c r="Q479" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U479" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V479" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W479" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="480" spans="1:23">
+      <c r="A480" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B480" s="4">
+        <v>16</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D480" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E480" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G480" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H480" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I480" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J480" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K480" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L480" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M480" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N480" s="4" t="s">
+        <v>4154</v>
+      </c>
+      <c r="O480" s="4" t="s">
+        <v>4156</v>
+      </c>
+      <c r="P480" s="4" t="s">
+        <v>4088</v>
+      </c>
+      <c r="Q480" s="4" t="s">
+        <v>4153</v>
+      </c>
+      <c r="S480" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T480" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U480" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V480" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W480" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="481" spans="1:23">
+      <c r="A481" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B481" s="4">
+        <v>17</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D481" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E481" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G481" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H481" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I481" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J481" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K481" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L481" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M481" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N481" s="4" t="s">
+        <v>4089</v>
+      </c>
+      <c r="O481" s="4" t="s">
+        <v>4157</v>
+      </c>
+      <c r="P481" s="4" t="s">
+        <v>4158</v>
+      </c>
+      <c r="Q481" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R481" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S481" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T481" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U481" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V481" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W481" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="482" spans="1:23" ht="30">
+      <c r="A482" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B482" s="4">
+        <v>18</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D482" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E482" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G482" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K482" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M482" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N482" s="4" t="s">
+        <v>4090</v>
+      </c>
+      <c r="O482" s="4" t="s">
+        <v>4159</v>
+      </c>
+      <c r="P482" s="4" t="s">
+        <v>4091</v>
+      </c>
+      <c r="Q482" s="4">
+        <v>1</v>
+      </c>
+      <c r="R482" s="4">
+        <v>1</v>
+      </c>
+      <c r="S482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U482" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W482" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="483" spans="1:23" ht="30">
+      <c r="A483" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B483" s="4">
+        <v>1</v>
+      </c>
+      <c r="C483" s="4" t="s">
+        <v>4056</v>
+      </c>
+      <c r="D483" s="4" t="s">
+        <v>4160</v>
+      </c>
+      <c r="E483" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G483" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H483" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I483" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J483" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K483" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L483" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M483" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N483" s="4" t="s">
+        <v>4161</v>
+      </c>
+      <c r="O483" s="4" t="s">
+        <v>4162</v>
+      </c>
+      <c r="P483" s="4" t="s">
+        <v>4163</v>
+      </c>
+      <c r="Q483" s="4" t="s">
+        <v>4164</v>
+      </c>
+      <c r="S483" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T483" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U483" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V483" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W483" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="484" spans="1:23">
+      <c r="A484" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B484" s="4">
+        <v>2</v>
+      </c>
+      <c r="C484" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D484" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E484" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G484" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H484" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I484" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J484" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K484" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L484" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M484" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N484" s="4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="O484" s="4" t="s">
+        <v>4165</v>
+      </c>
+      <c r="P484" s="4" t="s">
+        <v>4166</v>
+      </c>
+      <c r="Q484" s="4" t="s">
+        <v>4099</v>
+      </c>
+      <c r="S484" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T484" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U484" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V484" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W484" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="485" spans="1:23">
+      <c r="A485" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B485" s="4">
+        <v>3</v>
+      </c>
+      <c r="C485" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="D485" s="4" t="s">
+        <v>4092</v>
+      </c>
+      <c r="E485" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H485" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I485" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J485" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K485" s="4" t="s">
+        <v>4050</v>
+      </c>
+      <c r="L485" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M485" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N485" s="4" t="s">
+        <v>4107</v>
+      </c>
+      <c r="O485" s="4" t="s">
+        <v>4167</v>
+      </c>
+      <c r="P485" s="4" t="s">
+        <v>4168</v>
+      </c>
+      <c r="Q485" s="4" t="s">
+        <v>4096</v>
+      </c>
+      <c r="S485" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T485" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U485" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V485" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W485" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="486" spans="1:23">
+      <c r="A486" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B486" s="4">
+        <v>4</v>
+      </c>
+      <c r="C486" s="4" t="s">
+        <v>4073</v>
+      </c>
+      <c r="D486" s="4" t="s">
+        <v>4169</v>
+      </c>
+      <c r="E486" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G486" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H486" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I486" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J486" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K486" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L486" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M486" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N486" s="4" t="s">
+        <v>4170</v>
+      </c>
+      <c r="O486" s="4" t="s">
+        <v>4171</v>
+      </c>
+      <c r="P486" s="4" t="s">
+        <v>4172</v>
+      </c>
+      <c r="Q486" s="4" t="s">
+        <v>4059</v>
+      </c>
+      <c r="S486" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T486" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U486" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V486" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W486" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="487" spans="1:23">
+      <c r="A487" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B487" s="4">
+        <v>5</v>
+      </c>
+      <c r="C487" s="4" t="s">
+        <v>4057</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>4173</v>
+      </c>
+      <c r="E487" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F487" s="4">
+        <v>100</v>
+      </c>
+      <c r="G487" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H487" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I487" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J487" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K487" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L487" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M487" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N487" s="4" t="s">
+        <v>4174</v>
+      </c>
+      <c r="O487" s="4" t="s">
+        <v>4175</v>
+      </c>
+      <c r="P487" s="4" t="s">
+        <v>4176</v>
+      </c>
+      <c r="Q487" s="4" t="s">
+        <v>4177</v>
+      </c>
+      <c r="S487" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T487" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U487" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V487" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W487" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="488" spans="1:23">
+      <c r="A488" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B488" s="4">
+        <v>6</v>
+      </c>
+      <c r="C488" s="4" t="s">
+        <v>4076</v>
+      </c>
+      <c r="D488" s="4" t="s">
+        <v>4178</v>
+      </c>
+      <c r="E488" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G488" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H488" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I488" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J488" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K488" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L488" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M488" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N488" s="4" t="s">
+        <v>4179</v>
+      </c>
+      <c r="O488" s="4" t="s">
+        <v>4180</v>
+      </c>
+      <c r="P488" s="4" t="s">
+        <v>4181</v>
+      </c>
+      <c r="Q488" s="4" t="s">
+        <v>4182</v>
+      </c>
+      <c r="S488" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T488" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U488" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V488" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W488" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="489" spans="1:23">
+      <c r="A489" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B489" s="4">
+        <v>7</v>
+      </c>
+      <c r="C489" s="4" t="s">
+        <v>4183</v>
+      </c>
+      <c r="D489" s="4" t="s">
+        <v>4184</v>
+      </c>
+      <c r="E489" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F489" s="4">
+        <v>320</v>
+      </c>
+      <c r="G489" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H489" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I489" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J489" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K489" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L489" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M489" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N489" s="4" t="s">
+        <v>4185</v>
+      </c>
+      <c r="O489" s="4" t="s">
+        <v>4186</v>
+      </c>
+      <c r="P489" s="4" t="s">
+        <v>4187</v>
+      </c>
+      <c r="Q489" s="4" t="s">
+        <v>4188</v>
+      </c>
+      <c r="S489" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T489" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U489" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V489" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W489" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="490" spans="1:23">
+      <c r="A490" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B490" s="4">
+        <v>8</v>
+      </c>
+      <c r="C490" s="4" t="s">
+        <v>4189</v>
+      </c>
+      <c r="D490" s="4" t="s">
+        <v>4190</v>
+      </c>
+      <c r="E490" s="4" t="s">
+        <v>4191</v>
+      </c>
+      <c r="G490" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H490" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I490" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J490" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K490" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L490" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M490" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N490" s="4" t="s">
+        <v>4192</v>
+      </c>
+      <c r="O490" s="4" t="s">
+        <v>4193</v>
+      </c>
+      <c r="P490" s="4" t="s">
+        <v>4194</v>
+      </c>
+      <c r="Q490" s="4" t="s">
+        <v>4195</v>
+      </c>
+      <c r="S490" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T490" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U490" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V490" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W490" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="491" spans="1:23">
+      <c r="A491" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B491" s="4">
+        <v>9</v>
+      </c>
+      <c r="C491" s="4" t="s">
+        <v>4196</v>
+      </c>
+      <c r="D491" s="4" t="s">
+        <v>4197</v>
+      </c>
+      <c r="E491" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G491" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H491" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I491" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J491" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K491" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L491" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M491" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N491" s="4" t="s">
+        <v>4198</v>
+      </c>
+      <c r="O491" s="4" t="s">
+        <v>4199</v>
+      </c>
+      <c r="P491" s="4" t="s">
+        <v>4200</v>
+      </c>
+      <c r="Q491" s="4" t="s">
+        <v>4201</v>
+      </c>
+      <c r="S491" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T491" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U491" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V491" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W491" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="492" spans="1:23">
+      <c r="A492" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B492" s="4">
+        <v>10</v>
+      </c>
+      <c r="C492" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D492" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E492" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G492" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K492" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M492" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N492" s="4" t="s">
+        <v>4202</v>
+      </c>
+      <c r="O492" s="4" t="s">
+        <v>4203</v>
+      </c>
+      <c r="P492" s="4" t="s">
+        <v>4086</v>
+      </c>
+      <c r="Q492" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U492" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V492" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W492" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="493" spans="1:23">
+      <c r="A493" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B493" s="4">
+        <v>11</v>
+      </c>
+      <c r="C493" s="4" t="s">
+        <v>4204</v>
+      </c>
+      <c r="D493" s="4" t="s">
+        <v>4205</v>
+      </c>
+      <c r="E493" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G493" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H493" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I493" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J493" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K493" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L493" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M493" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N493" s="4" t="s">
+        <v>4206</v>
+      </c>
+      <c r="O493" s="4" t="s">
+        <v>4207</v>
+      </c>
+      <c r="P493" s="4" t="s">
+        <v>4208</v>
+      </c>
+      <c r="S493" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T493" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U493" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V493" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W493" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="494" spans="1:23">
+      <c r="A494" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B494" s="4">
+        <v>12</v>
+      </c>
+      <c r="C494" s="4" t="s">
+        <v>4209</v>
+      </c>
+      <c r="D494" s="4" t="s">
+        <v>4210</v>
+      </c>
+      <c r="E494" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G494" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H494" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I494" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J494" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K494" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L494" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M494" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N494" s="4" t="s">
+        <v>4211</v>
+      </c>
+      <c r="O494" s="4" t="s">
+        <v>4212</v>
+      </c>
+      <c r="P494" s="4" t="s">
+        <v>4213</v>
+      </c>
+      <c r="S494" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T494" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U494" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V494" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W494" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="495" spans="1:23">
+      <c r="A495" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B495" s="4">
+        <v>13</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>4214</v>
+      </c>
+      <c r="D495" s="4" t="s">
+        <v>4215</v>
+      </c>
+      <c r="E495" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G495" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H495" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I495" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J495" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K495" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L495" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M495" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N495" s="4" t="s">
+        <v>4216</v>
+      </c>
+      <c r="O495" s="4" t="s">
+        <v>4217</v>
+      </c>
+      <c r="P495" s="4" t="s">
+        <v>4218</v>
+      </c>
+      <c r="S495" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T495" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U495" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V495" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W495" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="496" spans="1:23">
+      <c r="A496" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B496" s="4">
+        <v>14</v>
+      </c>
+      <c r="C496" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D496" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E496" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G496" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H496" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I496" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J496" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K496" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L496" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M496" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N496" s="4" t="s">
+        <v>4202</v>
+      </c>
+      <c r="O496" s="4" t="s">
+        <v>4219</v>
+      </c>
+      <c r="P496" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q496" s="4" t="s">
+        <v>4059</v>
+      </c>
+      <c r="S496" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T496" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U496" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V496" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W496" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="497" spans="1:23">
+      <c r="A497" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B497" s="4">
+        <v>15</v>
+      </c>
+      <c r="C497" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E497" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G497" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K497" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M497" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N497" s="4" t="s">
+        <v>4220</v>
+      </c>
+      <c r="O497" s="4" t="s">
+        <v>4221</v>
+      </c>
+      <c r="P497" s="4" t="s">
+        <v>4086</v>
+      </c>
+      <c r="Q497" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U497" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V497" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W497" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="498" spans="1:23">
+      <c r="A498" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B498" s="4">
+        <v>16</v>
+      </c>
+      <c r="C498" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D498" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E498" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G498" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H498" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I498" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J498" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K498" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L498" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M498" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N498" s="4" t="s">
+        <v>4220</v>
+      </c>
+      <c r="O498" s="4" t="s">
+        <v>4222</v>
+      </c>
+      <c r="P498" s="4" t="s">
+        <v>4088</v>
+      </c>
+      <c r="Q498" s="4" t="s">
+        <v>4059</v>
+      </c>
+      <c r="S498" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T498" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U498" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V498" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W498" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="499" spans="1:23">
+      <c r="A499" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B499" s="4">
+        <v>17</v>
+      </c>
+      <c r="C499" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D499" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E499" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G499" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H499" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I499" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J499" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K499" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L499" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M499" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N499" s="4" t="s">
+        <v>4089</v>
+      </c>
+      <c r="O499" s="4" t="s">
+        <v>4223</v>
+      </c>
+      <c r="P499" s="4" t="s">
+        <v>4224</v>
+      </c>
+      <c r="Q499" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R499" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S499" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T499" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U499" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V499" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W499" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="500" spans="1:23" ht="30">
+      <c r="A500" s="4" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B500" s="4">
+        <v>18</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D500" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E500" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G500" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K500" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M500" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N500" s="4" t="s">
+        <v>4090</v>
+      </c>
+      <c r="O500" s="4" t="s">
+        <v>4225</v>
+      </c>
+      <c r="P500" s="4" t="s">
+        <v>4091</v>
+      </c>
+      <c r="Q500" s="4">
+        <v>1</v>
+      </c>
+      <c r="R500" s="4">
+        <v>1</v>
+      </c>
+      <c r="S500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U500" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V500" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W500" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="501" spans="1:23" ht="30">
+      <c r="A501" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B501" s="4">
+        <v>1</v>
+      </c>
+      <c r="C501" s="4" t="s">
+        <v>4229</v>
+      </c>
+      <c r="D501" s="4" t="s">
+        <v>4237</v>
+      </c>
+      <c r="E501" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G501" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H501" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I501" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J501" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K501" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L501" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M501" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N501" s="4" t="s">
+        <v>4238</v>
+      </c>
+      <c r="O501" s="4" t="s">
+        <v>4239</v>
+      </c>
+      <c r="P501" s="4" t="s">
+        <v>4240</v>
+      </c>
+      <c r="Q501" s="4" t="s">
+        <v>4241</v>
+      </c>
+      <c r="S501" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T501" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U501" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V501" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W501" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="502" spans="1:23">
+      <c r="A502" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B502" s="4">
+        <v>2</v>
+      </c>
+      <c r="C502" s="4" t="s">
+        <v>4242</v>
+      </c>
+      <c r="D502" s="4" t="s">
+        <v>4243</v>
+      </c>
+      <c r="E502" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F502" s="4">
+        <v>50</v>
+      </c>
+      <c r="G502" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H502" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I502" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J502" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K502" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L502" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M502" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N502" s="4" t="s">
+        <v>4244</v>
+      </c>
+      <c r="O502" s="4" t="s">
+        <v>4245</v>
+      </c>
+      <c r="P502" s="4" t="s">
+        <v>4246</v>
+      </c>
+      <c r="Q502" s="4" t="s">
+        <v>4247</v>
+      </c>
+      <c r="S502" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T502" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U502" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V502" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W502" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="503" spans="1:23">
+      <c r="A503" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B503" s="4">
+        <v>3</v>
+      </c>
+      <c r="C503" s="4" t="s">
+        <v>4230</v>
+      </c>
+      <c r="D503" s="4" t="s">
+        <v>4248</v>
+      </c>
+      <c r="E503" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F503" s="4">
+        <v>200</v>
+      </c>
+      <c r="G503" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H503" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I503" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J503" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K503" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L503" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M503" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N503" s="4" t="s">
+        <v>4249</v>
+      </c>
+      <c r="O503" s="4" t="s">
+        <v>4250</v>
+      </c>
+      <c r="P503" s="4" t="s">
+        <v>4251</v>
+      </c>
+      <c r="Q503" s="4" t="s">
+        <v>4252</v>
+      </c>
+      <c r="S503" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T503" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U503" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V503" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W503" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="504" spans="1:23">
+      <c r="A504" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B504" s="4">
+        <v>4</v>
+      </c>
+      <c r="C504" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D504" s="4" t="s">
+        <v>4253</v>
+      </c>
+      <c r="E504" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F504" s="4">
+        <v>30</v>
+      </c>
+      <c r="G504" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H504" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I504" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J504" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K504" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L504" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M504" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N504" s="4" t="s">
+        <v>4254</v>
+      </c>
+      <c r="O504" s="4" t="s">
+        <v>4255</v>
+      </c>
+      <c r="P504" s="4" t="s">
+        <v>4256</v>
+      </c>
+      <c r="Q504" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="S504" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T504" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U504" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V504" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W504" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="505" spans="1:23">
+      <c r="A505" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B505" s="4">
+        <v>5</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D505" s="4" t="s">
+        <v>4257</v>
+      </c>
+      <c r="E505" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F505" s="4">
+        <v>500</v>
+      </c>
+      <c r="G505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H505" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K505" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M505" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N505" s="4" t="s">
+        <v>4258</v>
+      </c>
+      <c r="O505" s="4" t="s">
+        <v>4259</v>
+      </c>
+      <c r="P505" s="4" t="s">
+        <v>4260</v>
+      </c>
+      <c r="Q505" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V505" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W505" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="506" spans="1:23">
+      <c r="A506" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B506" s="4">
+        <v>6</v>
+      </c>
+      <c r="C506" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D506" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E506" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F506" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H506" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K506" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M506" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N506" s="4" t="s">
+        <v>4261</v>
+      </c>
+      <c r="O506" s="4" t="s">
+        <v>4262</v>
+      </c>
+      <c r="P506" s="4" t="s">
+        <v>4263</v>
+      </c>
+      <c r="Q506" s="4" t="s">
+        <v>4264</v>
+      </c>
+      <c r="S506" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V506" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W506" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="507" spans="1:23">
+      <c r="A507" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B507" s="4">
+        <v>7</v>
+      </c>
+      <c r="C507" s="4" t="s">
+        <v>4265</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>4266</v>
+      </c>
+      <c r="E507" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G507" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H507" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I507" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J507" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K507" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L507" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M507" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N507" s="4" t="s">
+        <v>4267</v>
+      </c>
+      <c r="O507" s="4" t="s">
+        <v>4268</v>
+      </c>
+      <c r="P507" s="4" t="s">
+        <v>4269</v>
+      </c>
+      <c r="Q507" s="4" t="s">
+        <v>4270</v>
+      </c>
+      <c r="S507" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T507" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U507" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V507" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W507" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="508" spans="1:23">
+      <c r="A508" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B508" s="4">
+        <v>8</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D508" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E508" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G508" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K508" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M508" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N508" s="4" t="s">
+        <v>4271</v>
+      </c>
+      <c r="O508" s="4" t="s">
+        <v>4272</v>
+      </c>
+      <c r="P508" s="4" t="s">
+        <v>4273</v>
+      </c>
+      <c r="Q508" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U508" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V508" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W508" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="509" spans="1:23">
+      <c r="A509" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B509" s="4">
+        <v>9</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D509" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E509" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G509" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H509" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I509" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J509" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K509" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L509" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M509" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N509" s="4" t="s">
+        <v>4271</v>
+      </c>
+      <c r="O509" s="4" t="s">
+        <v>4274</v>
+      </c>
+      <c r="P509" s="4" t="s">
+        <v>4275</v>
+      </c>
+      <c r="Q509" s="4" t="s">
+        <v>4153</v>
+      </c>
+      <c r="S509" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T509" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U509" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V509" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W509" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="510" spans="1:23">
+      <c r="A510" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B510" s="4">
+        <v>10</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D510" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E510" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G510" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K510" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M510" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N510" s="4" t="s">
+        <v>4276</v>
+      </c>
+      <c r="O510" s="4" t="s">
+        <v>4277</v>
+      </c>
+      <c r="P510" s="4" t="s">
+        <v>4273</v>
+      </c>
+      <c r="Q510" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U510" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V510" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W510" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="511" spans="1:23">
+      <c r="A511" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B511" s="4">
+        <v>11</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D511" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E511" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G511" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H511" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I511" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J511" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K511" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L511" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M511" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N511" s="4" t="s">
+        <v>4276</v>
+      </c>
+      <c r="O511" s="4" t="s">
+        <v>4278</v>
+      </c>
+      <c r="P511" s="4" t="s">
+        <v>4279</v>
+      </c>
+      <c r="Q511" s="4" t="s">
+        <v>4153</v>
+      </c>
+      <c r="S511" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T511" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U511" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V511" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W511" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="512" spans="1:23">
+      <c r="A512" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B512" s="4">
+        <v>12</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D512" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E512" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G512" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H512" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I512" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J512" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K512" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L512" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M512" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N512" s="4" t="s">
+        <v>4089</v>
+      </c>
+      <c r="O512" s="4" t="s">
+        <v>4280</v>
+      </c>
+      <c r="P512" s="4" t="s">
+        <v>4281</v>
+      </c>
+      <c r="Q512" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R512" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S512" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T512" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U512" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V512" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W512" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="513" spans="1:23" ht="30">
+      <c r="A513" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B513" s="4">
+        <v>13</v>
+      </c>
+      <c r="C513" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E513" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G513" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K513" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M513" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N513" s="4" t="s">
+        <v>4090</v>
+      </c>
+      <c r="O513" s="4" t="s">
+        <v>4282</v>
+      </c>
+      <c r="P513" s="4" t="s">
+        <v>4283</v>
+      </c>
+      <c r="Q513" s="4">
+        <v>1</v>
+      </c>
+      <c r="R513" s="4">
+        <v>1</v>
+      </c>
+      <c r="S513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U513" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V513" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W513" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="514" spans="1:23" ht="30">
+      <c r="A514" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B514" s="4">
+        <v>1</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>4046</v>
+      </c>
+      <c r="D514" s="4" t="s">
+        <v>4058</v>
+      </c>
+      <c r="E514" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G514" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H514" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I514" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J514" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K514" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L514" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M514" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N514" s="4" t="s">
+        <v>4284</v>
+      </c>
+      <c r="O514" s="4" t="s">
+        <v>4285</v>
+      </c>
+      <c r="P514" s="4" t="s">
+        <v>4286</v>
+      </c>
+      <c r="Q514" s="4" t="s">
+        <v>4287</v>
+      </c>
+      <c r="S514" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T514" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U514" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V514" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W514" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="515" spans="1:23">
+      <c r="A515" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B515" s="4">
+        <v>2</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E515" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G515" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H515" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I515" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J515" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K515" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L515" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M515" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N515" s="4" t="s">
+        <v>4288</v>
+      </c>
+      <c r="O515" s="4" t="s">
+        <v>4289</v>
+      </c>
+      <c r="P515" s="4" t="s">
+        <v>4290</v>
+      </c>
+      <c r="Q515" s="4" t="s">
+        <v>4059</v>
+      </c>
+      <c r="S515" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T515" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U515" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V515" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W515" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="516" spans="1:23">
+      <c r="A516" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B516" s="4">
+        <v>3</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="D516" s="4" t="s">
+        <v>4237</v>
+      </c>
+      <c r="E516" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G516" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H516" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I516" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J516" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K516" s="4" t="s">
+        <v>4227</v>
+      </c>
+      <c r="L516" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M516" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N516" s="4" t="s">
+        <v>4291</v>
+      </c>
+      <c r="O516" s="4" t="s">
+        <v>4292</v>
+      </c>
+      <c r="P516" s="4" t="s">
+        <v>4293</v>
+      </c>
+      <c r="Q516" s="4" t="s">
+        <v>4241</v>
+      </c>
+      <c r="S516" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T516" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U516" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V516" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W516" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="517" spans="1:23">
+      <c r="A517" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B517" s="4">
+        <v>4</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>4294</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>4295</v>
+      </c>
+      <c r="E517" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F517" s="4">
+        <v>500</v>
+      </c>
+      <c r="G517" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K517" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M517" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N517" s="4" t="s">
+        <v>4296</v>
+      </c>
+      <c r="O517" s="4" t="s">
+        <v>4297</v>
+      </c>
+      <c r="P517" s="4" t="s">
+        <v>4298</v>
+      </c>
+      <c r="Q517" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T517" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V517" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W517" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="518" spans="1:23">
+      <c r="A518" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B518" s="4">
+        <v>5</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>4060</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>4061</v>
+      </c>
+      <c r="E518" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G518" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H518" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I518" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J518" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K518" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L518" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M518" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N518" s="4" t="s">
+        <v>4299</v>
+      </c>
+      <c r="O518" s="4" t="s">
+        <v>4300</v>
+      </c>
+      <c r="P518" s="4" t="s">
+        <v>4269</v>
+      </c>
+      <c r="Q518" s="4" t="s">
+        <v>4062</v>
+      </c>
+      <c r="S518" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T518" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U518" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V518" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W518" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="519" spans="1:23">
+      <c r="A519" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B519" s="4">
+        <v>6</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E519" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G519" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K519" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M519" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N519" s="4" t="s">
+        <v>4085</v>
+      </c>
+      <c r="O519" s="4" t="s">
+        <v>4301</v>
+      </c>
+      <c r="P519" s="4" t="s">
+        <v>4273</v>
+      </c>
+      <c r="Q519" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U519" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V519" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W519" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="520" spans="1:23">
+      <c r="A520" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B520" s="4">
+        <v>7</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E520" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G520" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H520" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I520" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J520" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K520" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L520" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M520" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N520" s="4" t="s">
+        <v>4085</v>
+      </c>
+      <c r="O520" s="4" t="s">
+        <v>4302</v>
+      </c>
+      <c r="P520" s="4" t="s">
+        <v>4275</v>
+      </c>
+      <c r="Q520" s="4" t="s">
+        <v>4059</v>
+      </c>
+      <c r="S520" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T520" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U520" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V520" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W520" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="521" spans="1:23">
+      <c r="A521" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B521" s="4">
+        <v>8</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E521" s="4" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G521" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K521" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M521" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N521" s="4" t="s">
+        <v>4087</v>
+      </c>
+      <c r="O521" s="4" t="s">
+        <v>4303</v>
+      </c>
+      <c r="P521" s="4" t="s">
+        <v>4273</v>
+      </c>
+      <c r="Q521" s="4" t="s">
+        <v>4063</v>
+      </c>
+      <c r="S521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U521" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V521" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W521" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="522" spans="1:23">
+      <c r="A522" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B522" s="4">
+        <v>9</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D522" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E522" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G522" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H522" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I522" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J522" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K522" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L522" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M522" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N522" s="4" t="s">
+        <v>4087</v>
+      </c>
+      <c r="O522" s="4" t="s">
+        <v>4304</v>
+      </c>
+      <c r="P522" s="4" t="s">
+        <v>4279</v>
+      </c>
+      <c r="Q522" s="4" t="s">
+        <v>4059</v>
+      </c>
+      <c r="S522" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T522" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U522" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V522" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W522" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="523" spans="1:23">
+      <c r="A523" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B523" s="4">
+        <v>10</v>
+      </c>
+      <c r="C523" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D523" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E523" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G523" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H523" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I523" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J523" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K523" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L523" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M523" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N523" s="4" t="s">
+        <v>4089</v>
+      </c>
+      <c r="O523" s="4" t="s">
+        <v>4305</v>
+      </c>
+      <c r="P523" s="4" t="s">
+        <v>4306</v>
+      </c>
+      <c r="Q523" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R523" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S523" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T523" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U523" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V523" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W523" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="524" spans="1:23">
+      <c r="A524" s="4" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B524" s="4">
+        <v>11</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E524" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G524" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K524" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M524" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N524" s="4" t="s">
+        <v>4090</v>
+      </c>
+      <c r="O524" s="4" t="s">
+        <v>4307</v>
+      </c>
+      <c r="P524" s="4" t="s">
+        <v>4283</v>
+      </c>
+      <c r="Q524" s="4">
+        <v>1</v>
+      </c>
+      <c r="R524" s="4">
+        <v>1</v>
+      </c>
+      <c r="S524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U524" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V524" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W524" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W464" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}"/>
   <hyperlinks>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A35921-CCDD-42A1-93FE-2620AF86A747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E0F9B4-2252-41F4-AF4D-A47E50054D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16422" uniqueCount="4308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16878" uniqueCount="4397">
   <si>
     <t>Domain</t>
   </si>
@@ -12968,6 +12968,273 @@
   </si>
   <si>
     <t>Stores the version of the customer preference for concurrency control</t>
+  </si>
+  <si>
+    <t>BENRULE</t>
+  </si>
+  <si>
+    <t>Benefit Usage Rule</t>
+  </si>
+  <si>
+    <t>benefit_usage_rule</t>
+  </si>
+  <si>
+    <t>Defines the usage, frequency and time-window rules that control when and how often a customer may redeem a benefit.</t>
+  </si>
+  <si>
+    <t>benefit_usage_rule_id</t>
+  </si>
+  <si>
+    <t>Benefit Usage Rule Name</t>
+  </si>
+  <si>
+    <t>Allows benefits to support recurring usage limits and time-based redemption windows such as daily benefits, monthly benefits and benefits available only during specified hours.</t>
+  </si>
+  <si>
+    <t>Benefit Usage Rule ID</t>
+  </si>
+  <si>
+    <t>Uniquely identifies a benefit usage rule.</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the benefit usage rule.</t>
+  </si>
+  <si>
+    <t>Primary identifier for the usage rule controlling benefit redemption eligibility.</t>
+  </si>
+  <si>
+    <t>Identifies the benefit to which the usage rule applies.</t>
+  </si>
+  <si>
+    <t>References the benefit governed by this usage rule.</t>
+  </si>
+  <si>
+    <t>Associates the usage rule with the applicable benefit.</t>
+  </si>
+  <si>
+    <t>Usage Rule Name</t>
+  </si>
+  <si>
+    <t>rule_name</t>
+  </si>
+  <si>
+    <t>Provides a business-friendly name for the usage rule.</t>
+  </si>
+  <si>
+    <t>Name used to identify the purpose of the rule.</t>
+  </si>
+  <si>
+    <t>Represents the human-readable name of the usage rule.</t>
+  </si>
+  <si>
+    <t>Daily Coffee Rule</t>
+  </si>
+  <si>
+    <t>Frequency Type</t>
+  </si>
+  <si>
+    <t>frequency_type</t>
+  </si>
+  <si>
+    <t>Defines the recurring frequency at which the benefit may be redeemed.</t>
+  </si>
+  <si>
+    <t>Defines whether the benefit usage is Daily, Weekly, Monthly, Yearly or One Time.</t>
+  </si>
+  <si>
+    <t>Determines the recurrence period used when evaluating redemption eligibility.</t>
+  </si>
+  <si>
+    <t>DAILY</t>
+  </si>
+  <si>
+    <t>Frequency Interval</t>
+  </si>
+  <si>
+    <t>frequency_interval</t>
+  </si>
+  <si>
+    <t>Defines the number of frequency units between permitted usage periods.</t>
+  </si>
+  <si>
+    <t>Specifies the interval within the selected frequency unit.</t>
+  </si>
+  <si>
+    <t>Allows rules such as every 1 day, every 2 weeks or every 3 months.</t>
+  </si>
+  <si>
+    <t>Usage Limit</t>
+  </si>
+  <si>
+    <t>usage_limit</t>
+  </si>
+  <si>
+    <t>Defines the maximum number of redemptions permitted within the configured frequency period.</t>
+  </si>
+  <si>
+    <t>Maximum number of times the benefit may be redeemed during each applicable frequency period.</t>
+  </si>
+  <si>
+    <t>Controls limits such as one coffee per day or two visits per month.</t>
+  </si>
+  <si>
+    <t>Window Start Time</t>
+  </si>
+  <si>
+    <t>window_start_time</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Defines the start of the daily redemption time window.</t>
+  </si>
+  <si>
+    <t>Time of day from which the benefit becomes redeemable.</t>
+  </si>
+  <si>
+    <t>Supports benefits that are available only during specified hours.</t>
+  </si>
+  <si>
+    <t>Window End Time</t>
+  </si>
+  <si>
+    <t>window_end_time</t>
+  </si>
+  <si>
+    <t>Defines the end of the daily redemption time window.</t>
+  </si>
+  <si>
+    <t>Time of day after which the benefit is no longer redeemable.</t>
+  </si>
+  <si>
+    <t>Applicable Days</t>
+  </si>
+  <si>
+    <t>applicable_days</t>
+  </si>
+  <si>
+    <t>Defines the days of the week on which the rule applies.</t>
+  </si>
+  <si>
+    <t>Stores the applicable weekdays for recurring redemption rules.</t>
+  </si>
+  <si>
+    <t>Allows rules such as Monday to Friday only or specific days of the week.</t>
+  </si>
+  <si>
+    <t>MON,TUE,WED,THU,FRI</t>
+  </si>
+  <si>
+    <t>Time Zone</t>
+  </si>
+  <si>
+    <t>time_zone</t>
+  </si>
+  <si>
+    <t>Defines the time zone used when evaluating time-based redemption rules.</t>
+  </si>
+  <si>
+    <t>IANA time zone identifier used to interpret the configured time window.</t>
+  </si>
+  <si>
+    <t>Ensures redemption eligibility is evaluated according to the organization's or store's local time.</t>
+  </si>
+  <si>
+    <t>Defines when the usage rule becomes effective.</t>
+  </si>
+  <si>
+    <t>Date from which the rule is applicable.</t>
+  </si>
+  <si>
+    <t>Controls the start of the rule lifecycle.</t>
+  </si>
+  <si>
+    <t>Defines when the usage rule ceases to apply.</t>
+  </si>
+  <si>
+    <t>Date after which the rule is no longer applicable.</t>
+  </si>
+  <si>
+    <t>Controls the end of the rule lifecycle.</t>
+  </si>
+  <si>
+    <t>Benefit Usage Rule Status</t>
+  </si>
+  <si>
+    <t>benefit_usage_rule_status_id</t>
+  </si>
+  <si>
+    <t>Indicates the operational status of the usage rule.</t>
+  </si>
+  <si>
+    <t>References the lifecycle status of the usage rule.</t>
+  </si>
+  <si>
+    <t>Determines whether the rule is Active, Inactive or Retired.</t>
+  </si>
+  <si>
+    <t>Records when the usage rule was created.</t>
+  </si>
+  <si>
+    <t>Timestamp when the usage rule was first created.</t>
+  </si>
+  <si>
+    <t>Records who created the usage rule.</t>
+  </si>
+  <si>
+    <t>References the user who created the usage rule.</t>
+  </si>
+  <si>
+    <t>Records the most recent update to the usage rule.</t>
+  </si>
+  <si>
+    <t>Records who last updated the usage rule.</t>
+  </si>
+  <si>
+    <t>Indicates whether the usage rule has been soft deleted.</t>
+  </si>
+  <si>
+    <t>Represents the current business version of the usage rule.</t>
+  </si>
+  <si>
+    <t>REL076</t>
+  </si>
+  <si>
+    <t>Benefit Usage Rules</t>
+  </si>
+  <si>
+    <t>Each Benefit may have one or more usage rules that define its redemption frequency, limits and time windows.</t>
+  </si>
+  <si>
+    <t>REL077</t>
+  </si>
+  <si>
+    <t>Each Benefit Usage Rule has one lifecycle status.</t>
+  </si>
+  <si>
+    <t>REL078</t>
+  </si>
+  <si>
+    <t>Usage Rule Created By</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> user_id</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>Identifies the user who created the Benefit Usage Rule.</t>
+  </si>
+  <si>
+    <t>Usage Rule Updated By</t>
+  </si>
+  <si>
+    <t>Identifies the user who last updated the Benefit Usage Rule.</t>
+  </si>
+  <si>
+    <t>REL075</t>
   </si>
 </sst>
 </file>
@@ -13043,7 +13310,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13102,6 +13369,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13196,7 +13466,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q45" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q46" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -13517,7 +13787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -15904,6 +16174,59 @@
         <v>46</v>
       </c>
     </row>
+    <row r="46" spans="1:17" ht="75">
+      <c r="A46" s="4" t="s">
+        <v>4308</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>4310</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>4311</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>4312</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>4313</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>4314</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -19465,7 +19788,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -22105,6 +22428,146 @@
       </c>
       <c r="K75" s="3" t="s">
         <v>4235</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="30">
+      <c r="A76" s="3" t="s">
+        <v>4396</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>4385</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="3" t="s">
+        <v>4384</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>4371</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>4372</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="3" t="s">
+        <v>4387</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>4390</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>4391</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>4393</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="3" t="s">
+        <v>4389</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>4394</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>4395</v>
       </c>
     </row>
   </sheetData>
@@ -26162,7 +26625,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <dimension ref="A1:W524"/>
+  <dimension ref="A1:W543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -46058,7 +46521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="45">
+    <row r="288" spans="1:23" ht="30">
       <c r="A288" s="3" t="s">
         <v>1515</v>
       </c>
@@ -56829,7 +57292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="444" spans="1:23" ht="45">
+    <row r="444" spans="1:23" ht="30">
       <c r="A444" s="4" t="s">
         <v>2426</v>
       </c>
@@ -58349,7 +58812,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:23">
+    <row r="466" spans="1:23" ht="30">
       <c r="A466" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58414,7 +58877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:23">
+    <row r="467" spans="1:23" ht="30">
       <c r="A467" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58482,7 +58945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="468" spans="1:23">
+    <row r="468" spans="1:23" ht="30">
       <c r="A468" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58550,7 +59013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="469" spans="1:23">
+    <row r="469" spans="1:23" ht="30">
       <c r="A469" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58618,7 +59081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="470" spans="1:23">
+    <row r="470" spans="1:23" ht="30">
       <c r="A470" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58683,7 +59146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="471" spans="1:23">
+    <row r="471" spans="1:23" ht="30">
       <c r="A471" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58748,7 +59211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="472" spans="1:23">
+    <row r="472" spans="1:23" ht="30">
       <c r="A472" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58813,7 +59276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="473" spans="1:23">
+    <row r="473" spans="1:23" ht="30">
       <c r="A473" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58878,7 +59341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="474" spans="1:23">
+    <row r="474" spans="1:23" ht="30">
       <c r="A474" s="4" t="s">
         <v>4050</v>
       </c>
@@ -58943,7 +59406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="475" spans="1:23">
+    <row r="475" spans="1:23" ht="30">
       <c r="A475" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59008,7 +59471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="476" spans="1:23">
+    <row r="476" spans="1:23" ht="30">
       <c r="A476" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59073,7 +59536,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="477" spans="1:23">
+    <row r="477" spans="1:23" ht="30">
       <c r="A477" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59138,7 +59601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="478" spans="1:23">
+    <row r="478" spans="1:23" ht="30">
       <c r="A478" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59203,7 +59666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:23">
+    <row r="479" spans="1:23" ht="30">
       <c r="A479" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59268,7 +59731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="480" spans="1:23">
+    <row r="480" spans="1:23" ht="30">
       <c r="A480" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59333,7 +59796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:23">
+    <row r="481" spans="1:23" ht="30">
       <c r="A481" s="4" t="s">
         <v>4050</v>
       </c>
@@ -59534,7 +59997,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:23">
+    <row r="484" spans="1:23" ht="30">
       <c r="A484" s="4" t="s">
         <v>4049</v>
       </c>
@@ -59599,7 +60062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="485" spans="1:23">
+    <row r="485" spans="1:23" ht="30">
       <c r="A485" s="4" t="s">
         <v>4049</v>
       </c>
@@ -59729,7 +60192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:23">
+    <row r="487" spans="1:23" ht="30">
       <c r="A487" s="4" t="s">
         <v>4049</v>
       </c>
@@ -59797,7 +60260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="488" spans="1:23">
+    <row r="488" spans="1:23" ht="30">
       <c r="A488" s="4" t="s">
         <v>4049</v>
       </c>
@@ -59862,7 +60325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="489" spans="1:23">
+    <row r="489" spans="1:23" ht="30">
       <c r="A489" s="4" t="s">
         <v>4049</v>
       </c>
@@ -59930,7 +60393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:23">
+    <row r="490" spans="1:23" ht="30">
       <c r="A490" s="4" t="s">
         <v>4049</v>
       </c>
@@ -59995,7 +60458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:23">
+    <row r="491" spans="1:23" ht="30">
       <c r="A491" s="4" t="s">
         <v>4049</v>
       </c>
@@ -60125,7 +60588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="493" spans="1:23">
+    <row r="493" spans="1:23" ht="30">
       <c r="A493" s="4" t="s">
         <v>4049</v>
       </c>
@@ -60187,7 +60650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="494" spans="1:23">
+    <row r="494" spans="1:23" ht="30">
       <c r="A494" s="4" t="s">
         <v>4049</v>
       </c>
@@ -60311,7 +60774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="496" spans="1:23">
+    <row r="496" spans="1:23" ht="30">
       <c r="A496" s="4" t="s">
         <v>4049</v>
       </c>
@@ -60441,7 +60904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:23">
+    <row r="498" spans="1:23" ht="30">
       <c r="A498" s="4" t="s">
         <v>4049</v>
       </c>
@@ -60506,7 +60969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="499" spans="1:23">
+    <row r="499" spans="1:23" ht="30">
       <c r="A499" s="4" t="s">
         <v>4049</v>
       </c>
@@ -60707,7 +61170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="502" spans="1:23">
+    <row r="502" spans="1:23" ht="30">
       <c r="A502" s="4" t="s">
         <v>4227</v>
       </c>
@@ -60775,7 +61238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="503" spans="1:23">
+    <row r="503" spans="1:23" ht="30">
       <c r="A503" s="4" t="s">
         <v>4227</v>
       </c>
@@ -60843,7 +61306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="504" spans="1:23">
+    <row r="504" spans="1:23" ht="30">
       <c r="A504" s="4" t="s">
         <v>4227</v>
       </c>
@@ -60911,7 +61374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="505" spans="1:23">
+    <row r="505" spans="1:23" ht="45">
       <c r="A505" s="4" t="s">
         <v>4227</v>
       </c>
@@ -60979,7 +61442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="506" spans="1:23">
+    <row r="506" spans="1:23" ht="45">
       <c r="A506" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61047,7 +61510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="507" spans="1:23">
+    <row r="507" spans="1:23" ht="30">
       <c r="A507" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61112,7 +61575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="508" spans="1:23">
+    <row r="508" spans="1:23" ht="30">
       <c r="A508" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61177,7 +61640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="509" spans="1:23">
+    <row r="509" spans="1:23" ht="30">
       <c r="A509" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61242,7 +61705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="510" spans="1:23">
+    <row r="510" spans="1:23" ht="30">
       <c r="A510" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61307,7 +61770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:23">
+    <row r="511" spans="1:23" ht="30">
       <c r="A511" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61372,7 +61835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="512" spans="1:23">
+    <row r="512" spans="1:23" ht="30">
       <c r="A512" s="4" t="s">
         <v>4227</v>
       </c>
@@ -61573,7 +62036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="515" spans="1:23">
+    <row r="515" spans="1:23" ht="30">
       <c r="A515" s="4" t="s">
         <v>4045</v>
       </c>
@@ -61638,7 +62101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="516" spans="1:23">
+    <row r="516" spans="1:23" ht="30">
       <c r="A516" s="4" t="s">
         <v>4045</v>
       </c>
@@ -61703,7 +62166,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:23">
+    <row r="517" spans="1:23" ht="30">
       <c r="A517" s="4" t="s">
         <v>4045</v>
       </c>
@@ -61771,7 +62234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="518" spans="1:23">
+    <row r="518" spans="1:23" ht="30">
       <c r="A518" s="4" t="s">
         <v>4045</v>
       </c>
@@ -61836,7 +62299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="519" spans="1:23">
+    <row r="519" spans="1:23" ht="30">
       <c r="A519" s="4" t="s">
         <v>4045</v>
       </c>
@@ -61901,7 +62364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="520" spans="1:23">
+    <row r="520" spans="1:23" ht="30">
       <c r="A520" s="4" t="s">
         <v>4045</v>
       </c>
@@ -61966,7 +62429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="521" spans="1:23">
+    <row r="521" spans="1:23" ht="30">
       <c r="A521" s="4" t="s">
         <v>4045</v>
       </c>
@@ -62031,7 +62494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="522" spans="1:23">
+    <row r="522" spans="1:23" ht="30">
       <c r="A522" s="4" t="s">
         <v>4045</v>
       </c>
@@ -62096,7 +62559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:23">
+    <row r="523" spans="1:23" ht="30">
       <c r="A523" s="4" t="s">
         <v>4045</v>
       </c>
@@ -62164,7 +62627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="524" spans="1:23">
+    <row r="524" spans="1:23" ht="30">
       <c r="A524" s="4" t="s">
         <v>4045</v>
       </c>
@@ -62230,6 +62693,1349 @@
       </c>
       <c r="W524" s="4" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="525" spans="1:23">
+      <c r="A525" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B525" s="4">
+        <v>1</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>4315</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>4312</v>
+      </c>
+      <c r="E525" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F525" s="4">
+        <v>36</v>
+      </c>
+      <c r="G525" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I525" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K525" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L525" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M525" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N525" s="4" t="s">
+        <v>4316</v>
+      </c>
+      <c r="O525" s="4" t="s">
+        <v>4317</v>
+      </c>
+      <c r="P525" s="4" t="s">
+        <v>4318</v>
+      </c>
+      <c r="Q525" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R525" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="S525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W525" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="526" spans="1:23">
+      <c r="A526" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B526" s="4">
+        <v>2</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E526" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F526" s="4">
+        <v>36</v>
+      </c>
+      <c r="G526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H526" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I526" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K526" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="L526" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M526" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N526" s="4" t="s">
+        <v>4319</v>
+      </c>
+      <c r="O526" s="4" t="s">
+        <v>4320</v>
+      </c>
+      <c r="P526" s="4" t="s">
+        <v>4321</v>
+      </c>
+      <c r="Q526" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R526" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W526" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="527" spans="1:23">
+      <c r="A527" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B527" s="4">
+        <v>3</v>
+      </c>
+      <c r="C527" s="4" t="s">
+        <v>4322</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>4323</v>
+      </c>
+      <c r="E527" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F527" s="4">
+        <v>100</v>
+      </c>
+      <c r="G527" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H527" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I527" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J527" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K527" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L527" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M527" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N527" s="4" t="s">
+        <v>4324</v>
+      </c>
+      <c r="O527" s="4" t="s">
+        <v>4325</v>
+      </c>
+      <c r="P527" s="4" t="s">
+        <v>4326</v>
+      </c>
+      <c r="Q527" s="4" t="s">
+        <v>4327</v>
+      </c>
+      <c r="R527" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S527" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T527" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U527" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V527" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W527" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="528" spans="1:23">
+      <c r="A528" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B528" s="4">
+        <v>4</v>
+      </c>
+      <c r="C528" s="4" t="s">
+        <v>4328</v>
+      </c>
+      <c r="D528" s="4" t="s">
+        <v>4329</v>
+      </c>
+      <c r="E528" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F528" s="4">
+        <v>30</v>
+      </c>
+      <c r="G528" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H528" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I528" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J528" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K528" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L528" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M528" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N528" s="4" t="s">
+        <v>4330</v>
+      </c>
+      <c r="O528" s="4" t="s">
+        <v>4331</v>
+      </c>
+      <c r="P528" s="4" t="s">
+        <v>4332</v>
+      </c>
+      <c r="Q528" s="4" t="s">
+        <v>4333</v>
+      </c>
+      <c r="R528" s="4" t="s">
+        <v>4333</v>
+      </c>
+      <c r="S528" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T528" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U528" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V528" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W528" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="529" spans="1:23">
+      <c r="A529" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B529" s="4">
+        <v>5</v>
+      </c>
+      <c r="C529" s="4" t="s">
+        <v>4334</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>4335</v>
+      </c>
+      <c r="E529" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F529" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G529" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H529" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I529" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J529" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K529" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L529" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M529" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N529" s="4" t="s">
+        <v>4336</v>
+      </c>
+      <c r="O529" s="4" t="s">
+        <v>4337</v>
+      </c>
+      <c r="P529" s="4" t="s">
+        <v>4338</v>
+      </c>
+      <c r="Q529" s="4">
+        <v>1</v>
+      </c>
+      <c r="R529" s="4">
+        <v>1</v>
+      </c>
+      <c r="S529" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T529" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U529" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V529" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W529" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="530" spans="1:23">
+      <c r="A530" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B530" s="4">
+        <v>6</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>4339</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>4340</v>
+      </c>
+      <c r="E530" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F530" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G530" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H530" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I530" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J530" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K530" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L530" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M530" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N530" s="4" t="s">
+        <v>4341</v>
+      </c>
+      <c r="O530" s="4" t="s">
+        <v>4342</v>
+      </c>
+      <c r="P530" s="4" t="s">
+        <v>4343</v>
+      </c>
+      <c r="Q530" s="4">
+        <v>1</v>
+      </c>
+      <c r="R530" s="4">
+        <v>1</v>
+      </c>
+      <c r="S530" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T530" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U530" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V530" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W530" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="531" spans="1:23">
+      <c r="A531" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B531" s="4">
+        <v>7</v>
+      </c>
+      <c r="C531" s="4" t="s">
+        <v>4344</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>4345</v>
+      </c>
+      <c r="E531" s="4" t="s">
+        <v>4346</v>
+      </c>
+      <c r="F531" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G531" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H531" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I531" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J531" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K531" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L531" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M531" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N531" s="4" t="s">
+        <v>4347</v>
+      </c>
+      <c r="O531" s="4" t="s">
+        <v>4348</v>
+      </c>
+      <c r="P531" s="4" t="s">
+        <v>4349</v>
+      </c>
+      <c r="Q531" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="R531" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S531" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T531" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U531" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V531" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W531" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="532" spans="1:23">
+      <c r="A532" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B532" s="4">
+        <v>8</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>4350</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>4351</v>
+      </c>
+      <c r="E532" s="4" t="s">
+        <v>4346</v>
+      </c>
+      <c r="F532" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G532" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H532" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I532" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J532" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K532" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L532" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M532" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N532" s="4" t="s">
+        <v>4352</v>
+      </c>
+      <c r="O532" s="4" t="s">
+        <v>4353</v>
+      </c>
+      <c r="P532" s="4" t="s">
+        <v>4349</v>
+      </c>
+      <c r="Q532" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="R532" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S532" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T532" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U532" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V532" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W532" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="533" spans="1:23">
+      <c r="A533" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B533" s="4">
+        <v>9</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>4354</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>4355</v>
+      </c>
+      <c r="E533" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F533" s="4">
+        <v>100</v>
+      </c>
+      <c r="G533" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H533" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I533" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J533" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K533" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L533" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M533" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N533" s="4" t="s">
+        <v>4356</v>
+      </c>
+      <c r="O533" s="4" t="s">
+        <v>4357</v>
+      </c>
+      <c r="P533" s="4" t="s">
+        <v>4358</v>
+      </c>
+      <c r="Q533" s="4" t="s">
+        <v>4359</v>
+      </c>
+      <c r="R533" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S533" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T533" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U533" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V533" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W533" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="534" spans="1:23">
+      <c r="A534" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B534" s="4">
+        <v>10</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>4360</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>4361</v>
+      </c>
+      <c r="E534" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F534" s="4">
+        <v>100</v>
+      </c>
+      <c r="G534" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H534" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I534" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J534" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K534" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L534" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M534" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N534" s="4" t="s">
+        <v>4362</v>
+      </c>
+      <c r="O534" s="4" t="s">
+        <v>4363</v>
+      </c>
+      <c r="P534" s="4" t="s">
+        <v>4364</v>
+      </c>
+      <c r="Q534" s="4" t="s">
+        <v>3963</v>
+      </c>
+      <c r="R534" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S534" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T534" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U534" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V534" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W534" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="535" spans="1:23">
+      <c r="A535" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B535" s="4">
+        <v>11</v>
+      </c>
+      <c r="C535" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E535" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F535" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G535" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H535" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I535" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J535" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K535" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L535" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M535" s="4" t="s">
+        <v>4365</v>
+      </c>
+      <c r="N535" s="4" t="s">
+        <v>4366</v>
+      </c>
+      <c r="O535" s="4" t="s">
+        <v>4367</v>
+      </c>
+      <c r="P535" s="17">
+        <v>46023</v>
+      </c>
+      <c r="Q535" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="R535" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S535" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T535" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U535" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V535" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="536" spans="1:23">
+      <c r="A536" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B536" s="4">
+        <v>12</v>
+      </c>
+      <c r="C536" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E536" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F536" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G536" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H536" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I536" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J536" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K536" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L536" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M536" s="4" t="s">
+        <v>4368</v>
+      </c>
+      <c r="N536" s="4" t="s">
+        <v>4369</v>
+      </c>
+      <c r="O536" s="4" t="s">
+        <v>4370</v>
+      </c>
+      <c r="P536" s="17">
+        <v>47118</v>
+      </c>
+      <c r="Q536" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R536" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S536" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T536" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U536" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V536" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="537" spans="1:23">
+      <c r="A537" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B537" s="4">
+        <v>13</v>
+      </c>
+      <c r="C537" s="4" t="s">
+        <v>4371</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>4372</v>
+      </c>
+      <c r="E537" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F537" s="4">
+        <v>36</v>
+      </c>
+      <c r="G537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H537" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I537" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K537" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L537" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M537" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N537" s="4" t="s">
+        <v>4373</v>
+      </c>
+      <c r="O537" s="4" t="s">
+        <v>4374</v>
+      </c>
+      <c r="P537" s="4" t="s">
+        <v>4375</v>
+      </c>
+      <c r="Q537" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R537" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W537" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="538" spans="1:23">
+      <c r="A538" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B538" s="4">
+        <v>14</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D538" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E538" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F538" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G538" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K538" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M538" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N538" s="4" t="s">
+        <v>4376</v>
+      </c>
+      <c r="O538" s="4" t="s">
+        <v>4377</v>
+      </c>
+      <c r="P538" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q538" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R538" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U538" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V538" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W538" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="539" spans="1:23">
+      <c r="A539" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B539" s="4">
+        <v>15</v>
+      </c>
+      <c r="C539" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E539" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F539" s="4">
+        <v>36</v>
+      </c>
+      <c r="G539" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H539" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I539" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J539" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K539" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L539" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M539" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N539" s="4" t="s">
+        <v>4378</v>
+      </c>
+      <c r="O539" s="4" t="s">
+        <v>4379</v>
+      </c>
+      <c r="P539" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q539" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R539" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S539" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T539" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U539" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V539" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W539" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="540" spans="1:23">
+      <c r="A540" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B540" s="4">
+        <v>16</v>
+      </c>
+      <c r="C540" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D540" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E540" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F540" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G540" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K540" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M540" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N540" s="4" t="s">
+        <v>4380</v>
+      </c>
+      <c r="O540" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="P540" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q540" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R540" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U540" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V540" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W540" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="541" spans="1:23">
+      <c r="A541" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B541" s="4">
+        <v>17</v>
+      </c>
+      <c r="C541" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D541" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E541" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F541" s="4">
+        <v>36</v>
+      </c>
+      <c r="G541" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H541" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I541" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J541" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K541" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L541" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M541" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N541" s="4" t="s">
+        <v>4381</v>
+      </c>
+      <c r="O541" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="P541" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q541" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R541" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S541" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T541" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U541" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V541" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W541" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="542" spans="1:23">
+      <c r="A542" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B542" s="4">
+        <v>18</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E542" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F542" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G542" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K542" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N542" s="4" t="s">
+        <v>4382</v>
+      </c>
+      <c r="O542" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="P542" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q542" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R542" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T542" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V542" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W542" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="543" spans="1:23">
+      <c r="A543" s="4" t="s">
+        <v>4309</v>
+      </c>
+      <c r="B543" s="4">
+        <v>19</v>
+      </c>
+      <c r="C543" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D543" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E543" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F543" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G543" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K543" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M543" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N543" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="O543" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="P543" s="4" t="s">
+        <v>4383</v>
+      </c>
+      <c r="Q543" s="4">
+        <v>1</v>
+      </c>
+      <c r="R543" s="4">
+        <v>1</v>
+      </c>
+      <c r="S543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U543" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V543" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W543" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E0F9B4-2252-41F4-AF4D-A47E50054D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13023519-5769-475F-869A-4F4517D0FB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="13" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16878" uniqueCount="4397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17338" uniqueCount="4432">
   <si>
     <t>Domain</t>
   </si>
@@ -13235,6 +13235,111 @@
   </si>
   <si>
     <t>REL075</t>
+  </si>
+  <si>
+    <t>OFFRULE</t>
+  </si>
+  <si>
+    <t>Promotion</t>
+  </si>
+  <si>
+    <t>Offer Usage Rule</t>
+  </si>
+  <si>
+    <t>offer_usage_rule</t>
+  </si>
+  <si>
+    <t>Defines the usage, frequency and time-window rules that control when and how often a customer may redeem an offer.</t>
+  </si>
+  <si>
+    <t>offer_usage_rule_id</t>
+  </si>
+  <si>
+    <t>Offer Usage Rule Name</t>
+  </si>
+  <si>
+    <t>Allows offers to support recurring usage limits and time-based redemption windows such as daily offers, monthly offers and offers available only during specified hours.</t>
+  </si>
+  <si>
+    <t>Offer Usage Rule ID</t>
+  </si>
+  <si>
+    <t>Uniquely identifies an offer usage rule.</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the offer usage rule.</t>
+  </si>
+  <si>
+    <t>Primary identifier for the usage rule controlling offer redemption eligibility.</t>
+  </si>
+  <si>
+    <t>Identifies the offer to which the usage rule applies.</t>
+  </si>
+  <si>
+    <t>References the offer governed by this usage rule.</t>
+  </si>
+  <si>
+    <t>Associates the usage rule with the applicable offer.</t>
+  </si>
+  <si>
+    <t>Name used to identify the purpose of the usage rule.</t>
+  </si>
+  <si>
+    <t>Weekend Offer Rule</t>
+  </si>
+  <si>
+    <t>Defines the recurring frequency at which the offer may be redeemed.</t>
+  </si>
+  <si>
+    <t>Defines whether the offer usage is Daily, Weekly, Monthly, Yearly or One Time.</t>
+  </si>
+  <si>
+    <t>Maximum number of times the offer may be redeemed during each applicable frequency period.</t>
+  </si>
+  <si>
+    <t>Controls limits such as one offer per day or two redemptions per month.</t>
+  </si>
+  <si>
+    <t>Time of day from which the offer becomes redeemable.</t>
+  </si>
+  <si>
+    <t>Supports offers that are available only during specified hours.</t>
+  </si>
+  <si>
+    <t>Time of day after which the offer is no longer redeemable.</t>
+  </si>
+  <si>
+    <t>Offer Usage Rule Status</t>
+  </si>
+  <si>
+    <t>offer_usage_rule_status_id</t>
+  </si>
+  <si>
+    <t>REL079</t>
+  </si>
+  <si>
+    <t>Offer Usage Rules</t>
+  </si>
+  <si>
+    <t>Each Offer may have one or more usage rules that define its redemption frequency, limits and time windows.</t>
+  </si>
+  <si>
+    <t>REL080</t>
+  </si>
+  <si>
+    <t>Each Offer Usage Rule has one lifecycle status.</t>
+  </si>
+  <si>
+    <t>REL081</t>
+  </si>
+  <si>
+    <t>Identifies the user who created the Offer Usage Rule.</t>
+  </si>
+  <si>
+    <t>REL082</t>
+  </si>
+  <si>
+    <t>Identifies the user who last updated the Offer Usage Rule.</t>
   </si>
 </sst>
 </file>
@@ -13466,7 +13571,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q46" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q47" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -13787,7 +13892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -16227,6 +16332,59 @@
         <v>4314</v>
       </c>
     </row>
+    <row r="47" spans="1:17" ht="75">
+      <c r="A47" s="4" t="s">
+        <v>4397</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>4398</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>4400</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>4401</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>4402</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>4403</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q47" s="4" t="s">
+        <v>4404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -19788,7 +19946,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -22568,6 +22726,146 @@
       </c>
       <c r="K79" s="4" t="s">
         <v>4395</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="4" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>4424</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="4" t="s">
+        <v>4426</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>4421</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>4422</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>4427</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="4" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>4390</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="4" t="s">
+        <v>4430</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>4394</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>4431</v>
       </c>
     </row>
   </sheetData>
@@ -26625,7 +26923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <dimension ref="A1:W543"/>
+  <dimension ref="A1:W562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -62695,7 +62993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="525" spans="1:23">
+    <row r="525" spans="1:23" ht="30">
       <c r="A525" s="4" t="s">
         <v>4309</v>
       </c>
@@ -62766,7 +63064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="526" spans="1:23">
+    <row r="526" spans="1:23" ht="30">
       <c r="A526" s="4" t="s">
         <v>4309</v>
       </c>
@@ -62837,7 +63135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="527" spans="1:23">
+    <row r="527" spans="1:23" ht="30">
       <c r="A527" s="4" t="s">
         <v>4309</v>
       </c>
@@ -62908,7 +63206,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="528" spans="1:23">
+    <row r="528" spans="1:23" ht="45">
       <c r="A528" s="4" t="s">
         <v>4309</v>
       </c>
@@ -62979,7 +63277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="529" spans="1:23">
+    <row r="529" spans="1:23" ht="45">
       <c r="A529" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63050,7 +63348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="530" spans="1:23">
+    <row r="530" spans="1:23" ht="60">
       <c r="A530" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63121,7 +63419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="531" spans="1:23">
+    <row r="531" spans="1:23" ht="30">
       <c r="A531" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63192,7 +63490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:23">
+    <row r="532" spans="1:23" ht="30">
       <c r="A532" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63263,7 +63561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:23">
+    <row r="533" spans="1:23" ht="30">
       <c r="A533" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63334,7 +63632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="534" spans="1:23">
+    <row r="534" spans="1:23" ht="45">
       <c r="A534" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63405,7 +63703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="535" spans="1:23">
+    <row r="535" spans="1:23" ht="60">
       <c r="A535" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63473,7 +63771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="536" spans="1:23">
+    <row r="536" spans="1:23" ht="60">
       <c r="A536" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63541,7 +63839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="537" spans="1:23">
+    <row r="537" spans="1:23" ht="30">
       <c r="A537" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63612,7 +63910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="538" spans="1:23">
+    <row r="538" spans="1:23" ht="30">
       <c r="A538" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63683,7 +63981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="539" spans="1:23">
+    <row r="539" spans="1:23" ht="30">
       <c r="A539" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63754,7 +64052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="540" spans="1:23">
+    <row r="540" spans="1:23" ht="30">
       <c r="A540" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63825,7 +64123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="541" spans="1:23">
+    <row r="541" spans="1:23" ht="30">
       <c r="A541" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63896,7 +64194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="542" spans="1:23">
+    <row r="542" spans="1:23" ht="30">
       <c r="A542" s="4" t="s">
         <v>4309</v>
       </c>
@@ -63967,7 +64265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="543" spans="1:23">
+    <row r="543" spans="1:23" ht="30">
       <c r="A543" s="4" t="s">
         <v>4309</v>
       </c>
@@ -64035,6 +64333,1349 @@
         <v>6</v>
       </c>
       <c r="W543" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="544" spans="1:23">
+      <c r="A544" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B544" s="4">
+        <v>1</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>4405</v>
+      </c>
+      <c r="D544" s="4" t="s">
+        <v>4402</v>
+      </c>
+      <c r="E544" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F544" s="4">
+        <v>36</v>
+      </c>
+      <c r="G544" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H544" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I544" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J544" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K544" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L544" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M544" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N544" s="4" t="s">
+        <v>4406</v>
+      </c>
+      <c r="O544" s="4" t="s">
+        <v>4407</v>
+      </c>
+      <c r="P544" s="4" t="s">
+        <v>4408</v>
+      </c>
+      <c r="Q544" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R544" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="S544" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T544" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U544" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V544" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W544" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="545" spans="1:23">
+      <c r="A545" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B545" s="4">
+        <v>2</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D545" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E545" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F545" s="4">
+        <v>36</v>
+      </c>
+      <c r="G545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H545" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I545" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K545" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="L545" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M545" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N545" s="4" t="s">
+        <v>4409</v>
+      </c>
+      <c r="O545" s="4" t="s">
+        <v>4410</v>
+      </c>
+      <c r="P545" s="4" t="s">
+        <v>4411</v>
+      </c>
+      <c r="Q545" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R545" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W545" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="546" spans="1:23">
+      <c r="A546" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B546" s="4">
+        <v>3</v>
+      </c>
+      <c r="C546" s="4" t="s">
+        <v>4322</v>
+      </c>
+      <c r="D546" s="4" t="s">
+        <v>4323</v>
+      </c>
+      <c r="E546" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F546" s="4">
+        <v>100</v>
+      </c>
+      <c r="G546" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H546" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I546" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J546" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K546" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L546" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M546" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N546" s="4" t="s">
+        <v>4324</v>
+      </c>
+      <c r="O546" s="4" t="s">
+        <v>4412</v>
+      </c>
+      <c r="P546" s="4" t="s">
+        <v>4326</v>
+      </c>
+      <c r="Q546" s="4" t="s">
+        <v>4413</v>
+      </c>
+      <c r="R546" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S546" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T546" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U546" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V546" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W546" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="547" spans="1:23">
+      <c r="A547" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B547" s="4">
+        <v>4</v>
+      </c>
+      <c r="C547" s="4" t="s">
+        <v>4328</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>4329</v>
+      </c>
+      <c r="E547" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F547" s="4">
+        <v>30</v>
+      </c>
+      <c r="G547" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H547" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I547" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J547" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K547" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L547" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M547" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N547" s="4" t="s">
+        <v>4414</v>
+      </c>
+      <c r="O547" s="4" t="s">
+        <v>4415</v>
+      </c>
+      <c r="P547" s="4" t="s">
+        <v>4332</v>
+      </c>
+      <c r="Q547" s="4" t="s">
+        <v>4333</v>
+      </c>
+      <c r="R547" s="4" t="s">
+        <v>4333</v>
+      </c>
+      <c r="S547" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T547" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U547" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V547" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W547" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="548" spans="1:23">
+      <c r="A548" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B548" s="4">
+        <v>5</v>
+      </c>
+      <c r="C548" s="4" t="s">
+        <v>4334</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>4335</v>
+      </c>
+      <c r="E548" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F548" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G548" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H548" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I548" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J548" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K548" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L548" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M548" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N548" s="4" t="s">
+        <v>4336</v>
+      </c>
+      <c r="O548" s="4" t="s">
+        <v>4337</v>
+      </c>
+      <c r="P548" s="4" t="s">
+        <v>4338</v>
+      </c>
+      <c r="Q548" s="4">
+        <v>1</v>
+      </c>
+      <c r="R548" s="4">
+        <v>1</v>
+      </c>
+      <c r="S548" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T548" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U548" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V548" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W548" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="549" spans="1:23">
+      <c r="A549" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B549" s="4">
+        <v>6</v>
+      </c>
+      <c r="C549" s="4" t="s">
+        <v>4339</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>4340</v>
+      </c>
+      <c r="E549" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F549" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G549" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H549" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I549" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J549" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K549" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L549" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M549" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N549" s="4" t="s">
+        <v>4341</v>
+      </c>
+      <c r="O549" s="4" t="s">
+        <v>4416</v>
+      </c>
+      <c r="P549" s="4" t="s">
+        <v>4417</v>
+      </c>
+      <c r="Q549" s="4">
+        <v>1</v>
+      </c>
+      <c r="R549" s="4">
+        <v>1</v>
+      </c>
+      <c r="S549" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T549" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U549" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V549" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W549" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="550" spans="1:23">
+      <c r="A550" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B550" s="4">
+        <v>7</v>
+      </c>
+      <c r="C550" s="4" t="s">
+        <v>4344</v>
+      </c>
+      <c r="D550" s="4" t="s">
+        <v>4345</v>
+      </c>
+      <c r="E550" s="4" t="s">
+        <v>4346</v>
+      </c>
+      <c r="F550" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G550" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H550" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I550" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J550" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K550" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L550" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M550" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N550" s="4" t="s">
+        <v>4347</v>
+      </c>
+      <c r="O550" s="4" t="s">
+        <v>4418</v>
+      </c>
+      <c r="P550" s="4" t="s">
+        <v>4419</v>
+      </c>
+      <c r="Q550" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R550" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S550" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T550" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U550" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V550" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W550" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="551" spans="1:23">
+      <c r="A551" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B551" s="4">
+        <v>8</v>
+      </c>
+      <c r="C551" s="4" t="s">
+        <v>4350</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>4351</v>
+      </c>
+      <c r="E551" s="4" t="s">
+        <v>4346</v>
+      </c>
+      <c r="F551" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G551" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H551" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I551" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J551" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K551" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L551" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M551" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N551" s="4" t="s">
+        <v>4352</v>
+      </c>
+      <c r="O551" s="4" t="s">
+        <v>4420</v>
+      </c>
+      <c r="P551" s="4" t="s">
+        <v>4419</v>
+      </c>
+      <c r="Q551" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R551" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S551" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T551" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U551" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V551" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W551" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="552" spans="1:23">
+      <c r="A552" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B552" s="4">
+        <v>9</v>
+      </c>
+      <c r="C552" s="4" t="s">
+        <v>4354</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>4355</v>
+      </c>
+      <c r="E552" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F552" s="4">
+        <v>100</v>
+      </c>
+      <c r="G552" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H552" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I552" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J552" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K552" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L552" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M552" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N552" s="4" t="s">
+        <v>4356</v>
+      </c>
+      <c r="O552" s="4" t="s">
+        <v>4357</v>
+      </c>
+      <c r="P552" s="4" t="s">
+        <v>4358</v>
+      </c>
+      <c r="Q552" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R552" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S552" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T552" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U552" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V552" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W552" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="553" spans="1:23">
+      <c r="A553" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B553" s="4">
+        <v>10</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>4360</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>4361</v>
+      </c>
+      <c r="E553" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F553" s="4">
+        <v>100</v>
+      </c>
+      <c r="G553" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H553" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I553" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J553" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K553" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L553" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M553" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N553" s="4" t="s">
+        <v>4362</v>
+      </c>
+      <c r="O553" s="4" t="s">
+        <v>4363</v>
+      </c>
+      <c r="P553" s="4" t="s">
+        <v>4364</v>
+      </c>
+      <c r="Q553" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R553" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S553" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T553" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U553" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V553" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W553" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="554" spans="1:23">
+      <c r="A554" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B554" s="4">
+        <v>11</v>
+      </c>
+      <c r="C554" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E554" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F554" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G554" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H554" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I554" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J554" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K554" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L554" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M554" s="4" t="s">
+        <v>4365</v>
+      </c>
+      <c r="N554" s="4" t="s">
+        <v>4366</v>
+      </c>
+      <c r="O554" s="4" t="s">
+        <v>4367</v>
+      </c>
+      <c r="P554" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q554" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="R554" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S554" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T554" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U554" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V554" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="555" spans="1:23">
+      <c r="A555" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B555" s="4">
+        <v>12</v>
+      </c>
+      <c r="C555" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E555" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F555" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G555" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H555" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I555" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J555" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K555" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L555" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M555" s="4" t="s">
+        <v>4368</v>
+      </c>
+      <c r="N555" s="4" t="s">
+        <v>4369</v>
+      </c>
+      <c r="O555" s="4" t="s">
+        <v>4370</v>
+      </c>
+      <c r="P555" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q555" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="R555" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S555" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T555" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U555" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V555" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="556" spans="1:23">
+      <c r="A556" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B556" s="4">
+        <v>13</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>4421</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>4422</v>
+      </c>
+      <c r="E556" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F556" s="4">
+        <v>36</v>
+      </c>
+      <c r="G556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H556" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I556" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K556" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L556" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M556" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N556" s="4" t="s">
+        <v>4373</v>
+      </c>
+      <c r="O556" s="4" t="s">
+        <v>4374</v>
+      </c>
+      <c r="P556" s="4" t="s">
+        <v>4375</v>
+      </c>
+      <c r="Q556" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R556" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W556" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="557" spans="1:23">
+      <c r="A557" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B557" s="4">
+        <v>14</v>
+      </c>
+      <c r="C557" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E557" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F557" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G557" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K557" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M557" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N557" s="4" t="s">
+        <v>4376</v>
+      </c>
+      <c r="O557" s="4" t="s">
+        <v>4377</v>
+      </c>
+      <c r="P557" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q557" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R557" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U557" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W557" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="558" spans="1:23">
+      <c r="A558" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B558" s="4">
+        <v>15</v>
+      </c>
+      <c r="C558" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E558" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F558" s="4">
+        <v>36</v>
+      </c>
+      <c r="G558" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H558" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I558" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J558" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K558" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L558" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M558" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N558" s="4" t="s">
+        <v>4378</v>
+      </c>
+      <c r="O558" s="4" t="s">
+        <v>4379</v>
+      </c>
+      <c r="P558" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q558" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R558" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S558" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T558" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U558" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V558" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W558" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="559" spans="1:23">
+      <c r="A559" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B559" s="4">
+        <v>16</v>
+      </c>
+      <c r="C559" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E559" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F559" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G559" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K559" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M559" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N559" s="4" t="s">
+        <v>4380</v>
+      </c>
+      <c r="O559" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="P559" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q559" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R559" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U559" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V559" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W559" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="560" spans="1:23">
+      <c r="A560" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B560" s="4">
+        <v>17</v>
+      </c>
+      <c r="C560" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E560" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F560" s="4">
+        <v>36</v>
+      </c>
+      <c r="G560" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H560" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I560" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J560" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K560" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L560" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M560" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N560" s="4" t="s">
+        <v>4381</v>
+      </c>
+      <c r="O560" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="P560" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q560" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R560" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S560" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T560" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U560" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V560" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W560" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="561" spans="1:23">
+      <c r="A561" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B561" s="4">
+        <v>18</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E561" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F561" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G561" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K561" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N561" s="4" t="s">
+        <v>4382</v>
+      </c>
+      <c r="O561" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="P561" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q561" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R561" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T561" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V561" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W561" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="562" spans="1:23">
+      <c r="A562" s="4" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B562" s="4">
+        <v>19</v>
+      </c>
+      <c r="C562" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E562" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F562" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G562" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K562" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M562" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N562" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="O562" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="P562" s="4" t="s">
+        <v>4383</v>
+      </c>
+      <c r="Q562" s="4">
+        <v>1</v>
+      </c>
+      <c r="R562" s="4">
+        <v>1</v>
+      </c>
+      <c r="S562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U562" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V562" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W562" s="4" t="s">
         <v>6</v>
       </c>
     </row>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13023519-5769-475F-869A-4F4517D0FB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E648539-C542-4F56-B93B-FFAA79B83836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="13" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="11" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17338" uniqueCount="4432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18252" uniqueCount="4635">
   <si>
     <t>Domain</t>
   </si>
@@ -13340,6 +13340,615 @@
   </si>
   <si>
     <t>Identifies the user who last updated the Offer Usage Rule.</t>
+  </si>
+  <si>
+    <t>QRCODE</t>
+  </si>
+  <si>
+    <t>QR Management</t>
+  </si>
+  <si>
+    <t>QR Code</t>
+  </si>
+  <si>
+    <t>qr_codes</t>
+  </si>
+  <si>
+    <t>Represents a reusable QR code configured by an Organization to initiate a supported Memgine journey such as viewing available memberships, opening a specific membership, or initiating a redemption flow.</t>
+  </si>
+  <si>
+    <t>qr_code_id</t>
+  </si>
+  <si>
+    <t>QR Code Name</t>
+  </si>
+  <si>
+    <t>A generic QR definition that can support multiple QR Code Types and target different business journeys or entities.</t>
+  </si>
+  <si>
+    <t>QRSCNHIST</t>
+  </si>
+  <si>
+    <t>QR Scan History</t>
+  </si>
+  <si>
+    <t>qr_scan_history</t>
+  </si>
+  <si>
+    <t>Records each attempt to scan a QR code, including successful, failed and anonymous scans, to support operational auditing and membership acquisition analysis.</t>
+  </si>
+  <si>
+    <t>qr_scan_history_id</t>
+  </si>
+  <si>
+    <t>QR Scan Time</t>
+  </si>
+  <si>
+    <t>Scan history is retained for analytics and audit purposes and must not be physically deleted.</t>
+  </si>
+  <si>
+    <t>QRCODETYPE</t>
+  </si>
+  <si>
+    <t>QR Code Type</t>
+  </si>
+  <si>
+    <t>qr_code_types</t>
+  </si>
+  <si>
+    <t>Represents the supported business purpose of a QR code, such as displaying all available memberships, opening a specific membership, or initiating an offer or benefit redemption.</t>
+  </si>
+  <si>
+    <t>qr_code_type_id</t>
+  </si>
+  <si>
+    <t>QR Code Type Name</t>
+  </si>
+  <si>
+    <t>Platform-managed reference data defining the supported QR-driven customer journeys.</t>
+  </si>
+  <si>
+    <t>QRSCANRESULT</t>
+  </si>
+  <si>
+    <t>QR Scan Result</t>
+  </si>
+  <si>
+    <t>qr_scan_results</t>
+  </si>
+  <si>
+    <t>Represents the outcome of a QR code scan, such as successful resolution, invalid QR, expired QR or inactive QR.</t>
+  </si>
+  <si>
+    <t>qr_scan_result_id</t>
+  </si>
+  <si>
+    <t>QR Scan Result Name</t>
+  </si>
+  <si>
+    <t>Platform-managed reference data used to classify QR scan outcomes for operational and analytical purposes.</t>
+  </si>
+  <si>
+    <t>QR Code Identifier</t>
+  </si>
+  <si>
+    <t>Uniquely identifies a QR code definition.</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the QR code.</t>
+  </si>
+  <si>
+    <t>Represents the persistent identity of a reusable QR code.</t>
+  </si>
+  <si>
+    <t>Identifies the organization that owns the QR code.</t>
+  </si>
+  <si>
+    <t>References the organization that created and manages the QR code.</t>
+  </si>
+  <si>
+    <t>Establishes tenant ownership of the QR code.</t>
+  </si>
+  <si>
+    <t>qr_code_name</t>
+  </si>
+  <si>
+    <t>Provides a business-friendly name for the QR code.</t>
+  </si>
+  <si>
+    <t>Name used by organization administrators to identify the QR code and its placement or campaign.</t>
+  </si>
+  <si>
+    <t>Represents the human-readable administrative name of the QR code.</t>
+  </si>
+  <si>
+    <t>Store Membership Poster</t>
+  </si>
+  <si>
+    <t>Defines the customer journey initiated by the QR code.</t>
+  </si>
+  <si>
+    <t>References the type of QR-driven journey such as all memberships, a specific membership, offer redemption or benefit redemption.</t>
+  </si>
+  <si>
+    <t>Determines how Memgine interprets the QR code.</t>
+  </si>
+  <si>
+    <t>QR Code Token</t>
+  </si>
+  <si>
+    <t>qr_code_token</t>
+  </si>
+  <si>
+    <t>Stores the opaque value encoded into the QR destination.</t>
+  </si>
+  <si>
+    <t>Unique system-generated token used to resolve the QR code without exposing business data directly in the QR payload.</t>
+  </si>
+  <si>
+    <t>Represents the secure public identifier carried by the QR code.</t>
+  </si>
+  <si>
+    <t>Opaque Token</t>
+  </si>
+  <si>
+    <t>Target Entity Type</t>
+  </si>
+  <si>
+    <t>target_entity_type</t>
+  </si>
+  <si>
+    <t>Identifies the type of business entity targeted by the QR code when applicable.</t>
+  </si>
+  <si>
+    <t>Specifies the target entity represented by target_entity_id, such as Membership Product, Offer or Benefit.</t>
+  </si>
+  <si>
+    <t>Supports generic QR targeting without coupling the QR entity to a single business domain.</t>
+  </si>
+  <si>
+    <t>Target Entity ID</t>
+  </si>
+  <si>
+    <t>target_entity_id</t>
+  </si>
+  <si>
+    <t>Identifies the specific entity targeted by the QR code when applicable.</t>
+  </si>
+  <si>
+    <t>References the business entity to be opened or acted upon according to the QR Code Type.</t>
+  </si>
+  <si>
+    <t>Provides the generic target identifier for a QR-driven journey.</t>
+  </si>
+  <si>
+    <t>Placement Name</t>
+  </si>
+  <si>
+    <t>placement_name</t>
+  </si>
+  <si>
+    <t>Identifies where or how the QR code is promoted.</t>
+  </si>
+  <si>
+    <t>Business-defined placement or campaign label used to distinguish physical or promotional placements for analysis.</t>
+  </si>
+  <si>
+    <t>Supports analysis of membership acquisition by QR placement or promotion source.</t>
+  </si>
+  <si>
+    <t>Store Entrance Poster</t>
+  </si>
+  <si>
+    <t>Identifies the store associated with the QR placement when applicable.</t>
+  </si>
+  <si>
+    <t>References the store where the QR code is displayed when the placement is store-specific.</t>
+  </si>
+  <si>
+    <t>Supports store-level QR scan and acquisition analysis.</t>
+  </si>
+  <si>
+    <t>Indicates the operational status of the QR code.</t>
+  </si>
+  <si>
+    <t>References the lifecycle status of the QR code.</t>
+  </si>
+  <si>
+    <t>Determines whether the QR code is currently usable.</t>
+  </si>
+  <si>
+    <t>Records when the QR code was created.</t>
+  </si>
+  <si>
+    <t>Timestamp when the QR code definition was first created.</t>
+  </si>
+  <si>
+    <t>Records who created the QR code.</t>
+  </si>
+  <si>
+    <t>References the user who created the QR code definition.</t>
+  </si>
+  <si>
+    <t>Records the most recent update to the QR code.</t>
+  </si>
+  <si>
+    <t>Records who last updated the QR code.</t>
+  </si>
+  <si>
+    <t>Indicates whether the QR code has been soft deleted.</t>
+  </si>
+  <si>
+    <t>Logical deletion flag used to preserve the QR code definition and its history.</t>
+  </si>
+  <si>
+    <t>Supports controlled retirement without physical removal.</t>
+  </si>
+  <si>
+    <t>Represents the current business version of the QR code.</t>
+  </si>
+  <si>
+    <t>QR Scan History Identifier</t>
+  </si>
+  <si>
+    <t>Uniquely identifies a QR scan history record.</t>
+  </si>
+  <si>
+    <t>System-generated identifier for each recorded QR scan event.</t>
+  </si>
+  <si>
+    <t>Represents the unique identity of a scan event.</t>
+  </si>
+  <si>
+    <t>Identifies the QR code that was scanned.</t>
+  </si>
+  <si>
+    <t>References the persistent QR code definition associated with the scan.</t>
+  </si>
+  <si>
+    <t>Links each scan event to its QR code for operational and acquisition analysis.</t>
+  </si>
+  <si>
+    <t>Identifies the customer associated with the scan when known.</t>
+  </si>
+  <si>
+    <t>References the global user when the scanner or application can associate the scan with a customer.</t>
+  </si>
+  <si>
+    <t>Supports customer-level acquisition funnel analysis while allowing anonymous scans.</t>
+  </si>
+  <si>
+    <t>qr_scan_datetime</t>
+  </si>
+  <si>
+    <t>Records when the QR scan occurred.</t>
+  </si>
+  <si>
+    <t>Timestamp of the QR scan event.</t>
+  </si>
+  <si>
+    <t>Represents the exact time at which the QR code was scanned.</t>
+  </si>
+  <si>
+    <t>Records the outcome of the QR scan.</t>
+  </si>
+  <si>
+    <t>References the result classification for the scan attempt.</t>
+  </si>
+  <si>
+    <t>Supports operational monitoring and analysis of successful and unsuccessful scans.</t>
+  </si>
+  <si>
+    <t>Identifies the store where the scan occurred when applicable.</t>
+  </si>
+  <si>
+    <t>References the store associated with the scan location when known.</t>
+  </si>
+  <si>
+    <t>Supports store-level scan and acquisition analysis.</t>
+  </si>
+  <si>
+    <t>Identifies the staff member involved in the scan when applicable.</t>
+  </si>
+  <si>
+    <t>References the staff member operating a counter scanner or assisting the customer.</t>
+  </si>
+  <si>
+    <t>Supports operational and redemption analysis.</t>
+  </si>
+  <si>
+    <t>Scan Source</t>
+  </si>
+  <si>
+    <t>scan_source</t>
+  </si>
+  <si>
+    <t>Identifies the channel from which the scan was initiated.</t>
+  </si>
+  <si>
+    <t>Records whether the scan originated from a customer device, counter scanner, web or another supported channel.</t>
+  </si>
+  <si>
+    <t>Supports channel-level QR performance analysis.</t>
+  </si>
+  <si>
+    <t>Customer Device</t>
+  </si>
+  <si>
+    <t>Captures the target entity type resolved at scan time.</t>
+  </si>
+  <si>
+    <t>Records the entity type associated with the QR target when applicable.</t>
+  </si>
+  <si>
+    <t>Preserves scan-time targeting context for historical analysis even if QR configuration later changes.</t>
+  </si>
+  <si>
+    <t>Captures the target entity identifier resolved at scan time.</t>
+  </si>
+  <si>
+    <t>Records the target identifier associated with the QR scan when applicable.</t>
+  </si>
+  <si>
+    <t>Preserves the business target associated with the historical scan event.</t>
+  </si>
+  <si>
+    <t>Failure Reason</t>
+  </si>
+  <si>
+    <t>failure_reason</t>
+  </si>
+  <si>
+    <t>Stores additional information when a QR scan cannot be successfully resolved.</t>
+  </si>
+  <si>
+    <t>Provides a human-readable or system-generated explanation for an unsuccessful scan.</t>
+  </si>
+  <si>
+    <t>Supports operational troubleshooting and analysis of failed scans.</t>
+  </si>
+  <si>
+    <t>Expired QR Code</t>
+  </si>
+  <si>
+    <t>Records when the scan history record was created.</t>
+  </si>
+  <si>
+    <t>Timestamp when the scan event was persisted.</t>
+  </si>
+  <si>
+    <t>Supports auditability of scan history.</t>
+  </si>
+  <si>
+    <t>Records the user responsible for creating the scan history record when applicable.</t>
+  </si>
+  <si>
+    <t>References the authenticated user or system actor that persisted the scan event.</t>
+  </si>
+  <si>
+    <t>Supports auditability while allowing system-generated or anonymous scan records.</t>
+  </si>
+  <si>
+    <t>Supports version tracking for scan history records.</t>
+  </si>
+  <si>
+    <t>Version number for the persisted scan event record.</t>
+  </si>
+  <si>
+    <t>Supports controlled updates if scan history metadata is corrected.</t>
+  </si>
+  <si>
+    <t>REL083</t>
+  </si>
+  <si>
+    <t>Each QR Code has one QR Code Type defining the customer journey it initiates.</t>
+  </si>
+  <si>
+    <t>REL084</t>
+  </si>
+  <si>
+    <t>Organization QR Codes</t>
+  </si>
+  <si>
+    <t>Each Organization may configure multiple QR codes.</t>
+  </si>
+  <si>
+    <t>REL085</t>
+  </si>
+  <si>
+    <t>QR Code Status</t>
+  </si>
+  <si>
+    <t>Each QR Code has one lifecycle status.</t>
+  </si>
+  <si>
+    <t>REL086</t>
+  </si>
+  <si>
+    <t>QR Code Store Placement</t>
+  </si>
+  <si>
+    <t>A QR Code may optionally be associated with a Store when the QR is displayed at a specific store.</t>
+  </si>
+  <si>
+    <t>REL087</t>
+  </si>
+  <si>
+    <t>QR Code Created By</t>
+  </si>
+  <si>
+    <t>Identifies the user who created the QR Code.</t>
+  </si>
+  <si>
+    <t>REL088</t>
+  </si>
+  <si>
+    <t>QR Code Updated By</t>
+  </si>
+  <si>
+    <t>Identifies the user who last updated the QR Code.</t>
+  </si>
+  <si>
+    <t>REL089</t>
+  </si>
+  <si>
+    <t>QR Code Scans</t>
+  </si>
+  <si>
+    <t>Each QR Code may have many scan history records.</t>
+  </si>
+  <si>
+    <t>REL090</t>
+  </si>
+  <si>
+    <t>Customer QR Scans</t>
+  </si>
+  <si>
+    <t>A User may be associated with multiple QR scan history records when the customer is known.</t>
+  </si>
+  <si>
+    <t>REL091</t>
+  </si>
+  <si>
+    <t>Each QR Scan History record has one scan result classification.</t>
+  </si>
+  <si>
+    <t>REL092</t>
+  </si>
+  <si>
+    <t>Store QR Scans</t>
+  </si>
+  <si>
+    <t>A QR Scan History record may optionally identify the Store where the scan occurred.</t>
+  </si>
+  <si>
+    <t>REL093</t>
+  </si>
+  <si>
+    <t>Staff QR Scans</t>
+  </si>
+  <si>
+    <t>A QR Scan History record may optionally identify the Staff member involved in the scan.</t>
+  </si>
+  <si>
+    <t>REL094</t>
+  </si>
+  <si>
+    <t>Scan History Created By</t>
+  </si>
+  <si>
+    <t>Identifies the authenticated user or system actor that created the scan history record.</t>
+  </si>
+  <si>
+    <t>QR_BUSINESS_MEMBERSHIPS</t>
+  </si>
+  <si>
+    <t>Business Memberships</t>
+  </si>
+  <si>
+    <t>Opens the memberships available for the QR code's organization.</t>
+  </si>
+  <si>
+    <t>Customer scans a generic business QR and is taken to the organization's available memberships.</t>
+  </si>
+  <si>
+    <t>QR_MEMBERSHIP</t>
+  </si>
+  <si>
+    <t>Specific Membership</t>
+  </si>
+  <si>
+    <t>Opens a specific membership product for the customer to review and purchase.</t>
+  </si>
+  <si>
+    <t>Customer scans a QR promoting a specific membership.</t>
+  </si>
+  <si>
+    <t>QR_OFFER_REDEMPTION</t>
+  </si>
+  <si>
+    <t>Offer Redemption</t>
+  </si>
+  <si>
+    <t>Represents a QR-driven offer redemption journey.</t>
+  </si>
+  <si>
+    <t>Used when a customer presents a QR for an offer redemption.</t>
+  </si>
+  <si>
+    <t>QR_BENEFIT_REDEMPTION</t>
+  </si>
+  <si>
+    <t>Benefit Redemption</t>
+  </si>
+  <si>
+    <t>Represents a QR-driven benefit redemption journey.</t>
+  </si>
+  <si>
+    <t>Used when a customer presents a QR for a benefit redemption.</t>
+  </si>
+  <si>
+    <t>QR was successfully resolved and the requested journey can proceed.</t>
+  </si>
+  <si>
+    <t>Successful QR resolution.</t>
+  </si>
+  <si>
+    <t>INVALID</t>
+  </si>
+  <si>
+    <t>Invalid QR</t>
+  </si>
+  <si>
+    <t>The QR could not be recognized or its token is invalid.</t>
+  </si>
+  <si>
+    <t>Invalid or malformed QR.</t>
+  </si>
+  <si>
+    <t>Expired QR</t>
+  </si>
+  <si>
+    <t>The QR or its associated journey is no longer valid.</t>
+  </si>
+  <si>
+    <t>QR has expired or its associated target is no longer valid.</t>
+  </si>
+  <si>
+    <t>Inactive QR</t>
+  </si>
+  <si>
+    <t>The QR code has been disabled or is not currently active.</t>
+  </si>
+  <si>
+    <t>QR code is not operational.</t>
+  </si>
+  <si>
+    <t>TARGET_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Target Not Found</t>
+  </si>
+  <si>
+    <t>The QR resolved but its configured target could not be found.</t>
+  </si>
+  <si>
+    <t>Target membership, offer, benefit or other entity could not be resolved.</t>
+  </si>
+  <si>
+    <t>ACCESS_DENIED</t>
+  </si>
+  <si>
+    <t>Access Denied</t>
+  </si>
+  <si>
+    <t>The QR resolved but the requested journey cannot be accessed by the current user or context.</t>
+  </si>
+  <si>
+    <t>QR target exists but access or eligibility prevents proceeding.</t>
+  </si>
+  <si>
+    <t>QR_CODE</t>
   </si>
 </sst>
 </file>
@@ -13571,7 +14180,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q47" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q51" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -13892,7 +14501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -16385,6 +16994,218 @@
         <v>4404</v>
       </c>
     </row>
+    <row r="48" spans="1:17" ht="75">
+      <c r="A48" s="4" t="s">
+        <v>4432</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>4435</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>4436</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>4437</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>4438</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>4439</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="60">
+      <c r="A49" s="4" t="s">
+        <v>4440</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>4442</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>4443</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>4444</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>4445</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="4" t="s">
+        <v>4446</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="60">
+      <c r="A50" s="4" t="s">
+        <v>4447</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>4449</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>4450</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>4451</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>4452</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q50" s="4" t="s">
+        <v>4453</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="45">
+      <c r="A51" s="4" t="s">
+        <v>4454</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>4456</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>4457</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>4458</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>4459</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q51" s="4" t="s">
+        <v>4460</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -17895,7 +18716,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7B29B1-81FD-48F8-9727-C5470F35164D}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" style="4" bestFit="1" customWidth="1"/>
@@ -18253,6 +19074,20 @@
       </c>
       <c r="D25" s="3" t="s">
         <v>2253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>4634</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>2234</v>
       </c>
     </row>
   </sheetData>
@@ -19946,7 +20781,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -22728,7 +23563,7 @@
         <v>4395</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" ht="30">
       <c r="A80" s="4" t="s">
         <v>4423</v>
       </c>
@@ -22866,6 +23701,426 @@
       </c>
       <c r="K83" s="4" t="s">
         <v>4431</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="4" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>4451</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>4451</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>4565</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="4" t="s">
+        <v>4566</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>4567</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="4" t="s">
+        <v>4569</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>4570</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="4" t="s">
+        <v>4572</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>4573</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="4" t="s">
+        <v>4575</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>4576</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>4577</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="4" t="s">
+        <v>4578</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>4579</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>4580</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="4" t="s">
+        <v>4581</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>4582</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>4437</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>4437</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>4583</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="4" t="s">
+        <v>4584</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>4585</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="4" t="s">
+        <v>4587</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>4458</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>4458</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="4" t="s">
+        <v>4589</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>4590</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>4591</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="4" t="s">
+        <v>4592</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>4593</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>4594</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="4" t="s">
+        <v>4595</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>4596</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>4392</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>4597</v>
       </c>
     </row>
   </sheetData>
@@ -26923,7 +28178,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <dimension ref="A1:W562"/>
+  <dimension ref="A1:W592"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -64336,7 +65591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="544" spans="1:23">
+    <row r="544" spans="1:23" ht="30">
       <c r="A544" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64407,7 +65662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="545" spans="1:23">
+    <row r="545" spans="1:23" ht="30">
       <c r="A545" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64478,7 +65733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="546" spans="1:23">
+    <row r="546" spans="1:23" ht="30">
       <c r="A546" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64549,7 +65804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="547" spans="1:23">
+    <row r="547" spans="1:23" ht="45">
       <c r="A547" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64620,7 +65875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:23">
+    <row r="548" spans="1:23" ht="45">
       <c r="A548" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64691,7 +65946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:23">
+    <row r="549" spans="1:23" ht="60">
       <c r="A549" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64762,7 +66017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="550" spans="1:23">
+    <row r="550" spans="1:23" ht="30">
       <c r="A550" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64833,7 +66088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="551" spans="1:23">
+    <row r="551" spans="1:23" ht="30">
       <c r="A551" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64904,7 +66159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="552" spans="1:23">
+    <row r="552" spans="1:23" ht="30">
       <c r="A552" s="4" t="s">
         <v>4399</v>
       </c>
@@ -64975,7 +66230,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="553" spans="1:23">
+    <row r="553" spans="1:23" ht="45">
       <c r="A553" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65046,7 +66301,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="554" spans="1:23">
+    <row r="554" spans="1:23" ht="60">
       <c r="A554" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65114,7 +66369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="555" spans="1:23">
+    <row r="555" spans="1:23" ht="60">
       <c r="A555" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65182,7 +66437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="556" spans="1:23">
+    <row r="556" spans="1:23" ht="30">
       <c r="A556" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65253,7 +66508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="557" spans="1:23">
+    <row r="557" spans="1:23" ht="30">
       <c r="A557" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65324,7 +66579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="558" spans="1:23">
+    <row r="558" spans="1:23" ht="30">
       <c r="A558" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65395,7 +66650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="559" spans="1:23">
+    <row r="559" spans="1:23" ht="30">
       <c r="A559" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65466,7 +66721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="560" spans="1:23">
+    <row r="560" spans="1:23" ht="30">
       <c r="A560" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65537,7 +66792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="561" spans="1:23">
+    <row r="561" spans="1:23" ht="30">
       <c r="A561" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65608,7 +66863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="562" spans="1:23">
+    <row r="562" spans="1:23" ht="30">
       <c r="A562" s="4" t="s">
         <v>4399</v>
       </c>
@@ -65676,6 +66931,2136 @@
         <v>6</v>
       </c>
       <c r="W562" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="563" spans="1:23">
+      <c r="A563" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B563" s="4">
+        <v>1</v>
+      </c>
+      <c r="C563" s="4" t="s">
+        <v>4461</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>4437</v>
+      </c>
+      <c r="E563" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F563" s="4">
+        <v>36</v>
+      </c>
+      <c r="G563" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H563" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I563" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J563" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K563" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L563" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M563" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N563" s="4" t="s">
+        <v>4462</v>
+      </c>
+      <c r="O563" s="4" t="s">
+        <v>4463</v>
+      </c>
+      <c r="P563" s="4" t="s">
+        <v>4464</v>
+      </c>
+      <c r="Q563" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R563" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="S563" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T563" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U563" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V563" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W563" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="564" spans="1:23">
+      <c r="A564" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B564" s="4">
+        <v>2</v>
+      </c>
+      <c r="C564" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E564" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F564" s="4">
+        <v>36</v>
+      </c>
+      <c r="G564" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H564" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I564" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J564" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K564" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L564" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M564" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N564" s="4" t="s">
+        <v>4465</v>
+      </c>
+      <c r="O564" s="4" t="s">
+        <v>4466</v>
+      </c>
+      <c r="P564" s="4" t="s">
+        <v>4467</v>
+      </c>
+      <c r="Q564" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R564" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S564" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T564" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U564" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V564" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W564" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="565" spans="1:23">
+      <c r="A565" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B565" s="4">
+        <v>3</v>
+      </c>
+      <c r="C565" s="4" t="s">
+        <v>4438</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>4468</v>
+      </c>
+      <c r="E565" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F565" s="4">
+        <v>100</v>
+      </c>
+      <c r="G565" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H565" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I565" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J565" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K565" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L565" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M565" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N565" s="4" t="s">
+        <v>4469</v>
+      </c>
+      <c r="O565" s="4" t="s">
+        <v>4470</v>
+      </c>
+      <c r="P565" s="4" t="s">
+        <v>4471</v>
+      </c>
+      <c r="Q565" s="4" t="s">
+        <v>4472</v>
+      </c>
+      <c r="R565" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S565" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T565" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U565" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V565" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W565" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="566" spans="1:23">
+      <c r="A566" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B566" s="4">
+        <v>4</v>
+      </c>
+      <c r="C566" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>4451</v>
+      </c>
+      <c r="E566" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F566" s="4">
+        <v>36</v>
+      </c>
+      <c r="G566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H566" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I566" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K566" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="L566" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M566" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N566" s="4" t="s">
+        <v>4473</v>
+      </c>
+      <c r="O566" s="4" t="s">
+        <v>4474</v>
+      </c>
+      <c r="P566" s="4" t="s">
+        <v>4475</v>
+      </c>
+      <c r="Q566" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R566" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W566" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="567" spans="1:23">
+      <c r="A567" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B567" s="4">
+        <v>5</v>
+      </c>
+      <c r="C567" s="4" t="s">
+        <v>4476</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>4477</v>
+      </c>
+      <c r="E567" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F567" s="4">
+        <v>200</v>
+      </c>
+      <c r="G567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H567" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I567" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K567" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N567" s="4" t="s">
+        <v>4478</v>
+      </c>
+      <c r="O567" s="4" t="s">
+        <v>4479</v>
+      </c>
+      <c r="P567" s="4" t="s">
+        <v>4480</v>
+      </c>
+      <c r="Q567" s="4" t="s">
+        <v>4481</v>
+      </c>
+      <c r="R567" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="S567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V567" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W567" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="568" spans="1:23">
+      <c r="A568" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B568" s="4">
+        <v>6</v>
+      </c>
+      <c r="C568" s="4" t="s">
+        <v>4482</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>4483</v>
+      </c>
+      <c r="E568" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F568" s="4">
+        <v>50</v>
+      </c>
+      <c r="G568" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H568" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I568" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J568" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K568" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L568" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M568" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N568" s="4" t="s">
+        <v>4484</v>
+      </c>
+      <c r="O568" s="4" t="s">
+        <v>4485</v>
+      </c>
+      <c r="P568" s="4" t="s">
+        <v>4486</v>
+      </c>
+      <c r="Q568" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="R568" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S568" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T568" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U568" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V568" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W568" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="569" spans="1:23">
+      <c r="A569" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B569" s="4">
+        <v>7</v>
+      </c>
+      <c r="C569" s="4" t="s">
+        <v>4487</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>4488</v>
+      </c>
+      <c r="E569" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F569" s="4">
+        <v>36</v>
+      </c>
+      <c r="G569" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H569" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I569" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J569" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K569" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L569" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M569" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N569" s="4" t="s">
+        <v>4489</v>
+      </c>
+      <c r="O569" s="4" t="s">
+        <v>4490</v>
+      </c>
+      <c r="P569" s="4" t="s">
+        <v>4491</v>
+      </c>
+      <c r="Q569" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R569" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S569" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T569" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U569" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V569" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W569" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="570" spans="1:23">
+      <c r="A570" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B570" s="4">
+        <v>8</v>
+      </c>
+      <c r="C570" s="4" t="s">
+        <v>4492</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>4493</v>
+      </c>
+      <c r="E570" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F570" s="4">
+        <v>150</v>
+      </c>
+      <c r="G570" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H570" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I570" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J570" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K570" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L570" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M570" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N570" s="4" t="s">
+        <v>4494</v>
+      </c>
+      <c r="O570" s="4" t="s">
+        <v>4495</v>
+      </c>
+      <c r="P570" s="4" t="s">
+        <v>4496</v>
+      </c>
+      <c r="Q570" s="4" t="s">
+        <v>4497</v>
+      </c>
+      <c r="R570" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S570" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T570" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U570" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V570" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W570" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="571" spans="1:23">
+      <c r="A571" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B571" s="4">
+        <v>9</v>
+      </c>
+      <c r="C571" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E571" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F571" s="4">
+        <v>36</v>
+      </c>
+      <c r="G571" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H571" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I571" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J571" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K571" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L571" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M571" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N571" s="4" t="s">
+        <v>4498</v>
+      </c>
+      <c r="O571" s="4" t="s">
+        <v>4499</v>
+      </c>
+      <c r="P571" s="4" t="s">
+        <v>4500</v>
+      </c>
+      <c r="Q571" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R571" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S571" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T571" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U571" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V571" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W571" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="572" spans="1:23">
+      <c r="A572" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B572" s="4">
+        <v>10</v>
+      </c>
+      <c r="C572" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E572" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F572" s="4">
+        <v>36</v>
+      </c>
+      <c r="G572" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H572" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I572" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J572" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K572" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L572" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M572" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N572" s="4" t="s">
+        <v>4501</v>
+      </c>
+      <c r="O572" s="4" t="s">
+        <v>4502</v>
+      </c>
+      <c r="P572" s="4" t="s">
+        <v>4503</v>
+      </c>
+      <c r="Q572" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R572" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S572" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T572" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U572" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V572" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W572" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="573" spans="1:23">
+      <c r="A573" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B573" s="4">
+        <v>11</v>
+      </c>
+      <c r="C573" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E573" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F573" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G573" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K573" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M573" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N573" s="4" t="s">
+        <v>4504</v>
+      </c>
+      <c r="O573" s="4" t="s">
+        <v>4505</v>
+      </c>
+      <c r="P573" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q573" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R573" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U573" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V573" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W573" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="574" spans="1:23">
+      <c r="A574" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B574" s="4">
+        <v>12</v>
+      </c>
+      <c r="C574" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E574" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F574" s="4">
+        <v>36</v>
+      </c>
+      <c r="G574" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H574" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I574" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J574" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K574" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L574" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M574" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N574" s="4" t="s">
+        <v>4506</v>
+      </c>
+      <c r="O574" s="4" t="s">
+        <v>4507</v>
+      </c>
+      <c r="P574" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q574" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R574" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S574" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T574" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U574" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V574" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W574" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="575" spans="1:23">
+      <c r="A575" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B575" s="4">
+        <v>13</v>
+      </c>
+      <c r="C575" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E575" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F575" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G575" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K575" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M575" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N575" s="4" t="s">
+        <v>4508</v>
+      </c>
+      <c r="O575" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="P575" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q575" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R575" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U575" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W575" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="576" spans="1:23">
+      <c r="A576" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B576" s="4">
+        <v>14</v>
+      </c>
+      <c r="C576" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E576" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F576" s="4">
+        <v>36</v>
+      </c>
+      <c r="G576" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J576" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K576" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N576" s="4" t="s">
+        <v>4509</v>
+      </c>
+      <c r="O576" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="P576" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q576" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R576" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S576" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T576" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W576" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="577" spans="1:23">
+      <c r="A577" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B577" s="4">
+        <v>15</v>
+      </c>
+      <c r="C577" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E577" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F577" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G577" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K577" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N577" s="4" t="s">
+        <v>4510</v>
+      </c>
+      <c r="O577" s="4" t="s">
+        <v>4511</v>
+      </c>
+      <c r="P577" s="4" t="s">
+        <v>4512</v>
+      </c>
+      <c r="Q577" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R577" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T577" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W577" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="578" spans="1:23">
+      <c r="A578" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="B578" s="4">
+        <v>16</v>
+      </c>
+      <c r="C578" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E578" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F578" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G578" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K578" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M578" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N578" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="O578" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="P578" s="4" t="s">
+        <v>4513</v>
+      </c>
+      <c r="Q578" s="4">
+        <v>1</v>
+      </c>
+      <c r="R578" s="4">
+        <v>1</v>
+      </c>
+      <c r="S578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U578" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V578" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W578" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="579" spans="1:23">
+      <c r="A579" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B579" s="4">
+        <v>1</v>
+      </c>
+      <c r="C579" s="4" t="s">
+        <v>4514</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>4444</v>
+      </c>
+      <c r="E579" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F579" s="4">
+        <v>36</v>
+      </c>
+      <c r="G579" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H579" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I579" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J579" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K579" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L579" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M579" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N579" s="4" t="s">
+        <v>4515</v>
+      </c>
+      <c r="O579" s="4" t="s">
+        <v>4516</v>
+      </c>
+      <c r="P579" s="4" t="s">
+        <v>4517</v>
+      </c>
+      <c r="Q579" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R579" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="S579" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T579" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U579" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V579" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W579" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="580" spans="1:23">
+      <c r="A580" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B580" s="4">
+        <v>2</v>
+      </c>
+      <c r="C580" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>4437</v>
+      </c>
+      <c r="E580" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F580" s="4">
+        <v>36</v>
+      </c>
+      <c r="G580" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H580" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I580" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J580" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K580" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="L580" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M580" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N580" s="4" t="s">
+        <v>4518</v>
+      </c>
+      <c r="O580" s="4" t="s">
+        <v>4519</v>
+      </c>
+      <c r="P580" s="4" t="s">
+        <v>4520</v>
+      </c>
+      <c r="Q580" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R580" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S580" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T580" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U580" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V580" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W580" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="581" spans="1:23">
+      <c r="A581" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B581" s="4">
+        <v>3</v>
+      </c>
+      <c r="C581" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E581" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F581" s="4">
+        <v>36</v>
+      </c>
+      <c r="G581" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H581" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I581" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J581" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K581" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L581" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M581" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N581" s="4" t="s">
+        <v>4521</v>
+      </c>
+      <c r="O581" s="4" t="s">
+        <v>4522</v>
+      </c>
+      <c r="P581" s="4" t="s">
+        <v>4523</v>
+      </c>
+      <c r="Q581" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R581" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S581" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T581" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U581" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V581" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W581" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="582" spans="1:23">
+      <c r="A582" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B582" s="4">
+        <v>4</v>
+      </c>
+      <c r="C582" s="4" t="s">
+        <v>4445</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>4524</v>
+      </c>
+      <c r="E582" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F582" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G582" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H582" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I582" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J582" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K582" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L582" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M582" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N582" s="4" t="s">
+        <v>4525</v>
+      </c>
+      <c r="O582" s="4" t="s">
+        <v>4526</v>
+      </c>
+      <c r="P582" s="4" t="s">
+        <v>4527</v>
+      </c>
+      <c r="Q582" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R582" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S582" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T582" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U582" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V582" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W582" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="583" spans="1:23">
+      <c r="A583" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B583" s="4">
+        <v>5</v>
+      </c>
+      <c r="C583" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E583" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F583" s="4">
+        <v>36</v>
+      </c>
+      <c r="G583" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H583" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I583" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J583" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K583" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="L583" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M583" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N583" s="4" t="s">
+        <v>4528</v>
+      </c>
+      <c r="O583" s="4" t="s">
+        <v>4529</v>
+      </c>
+      <c r="P583" s="4" t="s">
+        <v>4530</v>
+      </c>
+      <c r="Q583" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R583" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S583" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T583" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U583" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V583" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W583" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="584" spans="1:23">
+      <c r="A584" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B584" s="4">
+        <v>6</v>
+      </c>
+      <c r="C584" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E584" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F584" s="4">
+        <v>36</v>
+      </c>
+      <c r="G584" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H584" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I584" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J584" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K584" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L584" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M584" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N584" s="4" t="s">
+        <v>4531</v>
+      </c>
+      <c r="O584" s="4" t="s">
+        <v>4532</v>
+      </c>
+      <c r="P584" s="4" t="s">
+        <v>4533</v>
+      </c>
+      <c r="Q584" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R584" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S584" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T584" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U584" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V584" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W584" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="585" spans="1:23">
+      <c r="A585" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B585" s="4">
+        <v>7</v>
+      </c>
+      <c r="C585" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="E585" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F585" s="4">
+        <v>36</v>
+      </c>
+      <c r="G585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H585" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J585" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K585" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N585" s="4" t="s">
+        <v>4534</v>
+      </c>
+      <c r="O585" s="4" t="s">
+        <v>4535</v>
+      </c>
+      <c r="P585" s="4" t="s">
+        <v>4536</v>
+      </c>
+      <c r="Q585" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R585" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S585" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T585" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W585" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="586" spans="1:23">
+      <c r="A586" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B586" s="4">
+        <v>8</v>
+      </c>
+      <c r="C586" s="4" t="s">
+        <v>4537</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>4538</v>
+      </c>
+      <c r="E586" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F586" s="4">
+        <v>50</v>
+      </c>
+      <c r="G586" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H586" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I586" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J586" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K586" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L586" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M586" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N586" s="4" t="s">
+        <v>4539</v>
+      </c>
+      <c r="O586" s="4" t="s">
+        <v>4540</v>
+      </c>
+      <c r="P586" s="4" t="s">
+        <v>4541</v>
+      </c>
+      <c r="Q586" s="4" t="s">
+        <v>4542</v>
+      </c>
+      <c r="R586" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S586" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T586" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U586" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V586" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W586" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="587" spans="1:23">
+      <c r="A587" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B587" s="4">
+        <v>9</v>
+      </c>
+      <c r="C587" s="4" t="s">
+        <v>4482</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>4483</v>
+      </c>
+      <c r="E587" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F587" s="4">
+        <v>50</v>
+      </c>
+      <c r="G587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H587" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K587" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N587" s="4" t="s">
+        <v>4543</v>
+      </c>
+      <c r="O587" s="4" t="s">
+        <v>4544</v>
+      </c>
+      <c r="P587" s="4" t="s">
+        <v>4545</v>
+      </c>
+      <c r="Q587" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="R587" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S587" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T587" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U587" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W587" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="588" spans="1:23">
+      <c r="A588" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B588" s="4">
+        <v>10</v>
+      </c>
+      <c r="C588" s="4" t="s">
+        <v>4487</v>
+      </c>
+      <c r="D588" s="4" t="s">
+        <v>4488</v>
+      </c>
+      <c r="E588" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F588" s="4">
+        <v>36</v>
+      </c>
+      <c r="G588" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H588" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I588" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J588" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K588" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L588" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M588" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N588" s="4" t="s">
+        <v>4546</v>
+      </c>
+      <c r="O588" s="4" t="s">
+        <v>4547</v>
+      </c>
+      <c r="P588" s="4" t="s">
+        <v>4548</v>
+      </c>
+      <c r="Q588" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R588" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S588" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T588" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U588" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V588" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W588" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="589" spans="1:23">
+      <c r="A589" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B589" s="4">
+        <v>11</v>
+      </c>
+      <c r="C589" s="4" t="s">
+        <v>4549</v>
+      </c>
+      <c r="D589" s="4" t="s">
+        <v>4550</v>
+      </c>
+      <c r="E589" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F589" s="4">
+        <v>500</v>
+      </c>
+      <c r="G589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H589" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K589" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N589" s="4" t="s">
+        <v>4551</v>
+      </c>
+      <c r="O589" s="4" t="s">
+        <v>4552</v>
+      </c>
+      <c r="P589" s="4" t="s">
+        <v>4553</v>
+      </c>
+      <c r="Q589" s="4" t="s">
+        <v>4554</v>
+      </c>
+      <c r="R589" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S589" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U589" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V589" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W589" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="590" spans="1:23">
+      <c r="A590" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B590" s="4">
+        <v>12</v>
+      </c>
+      <c r="C590" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D590" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E590" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F590" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G590" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K590" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M590" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N590" s="4" t="s">
+        <v>4555</v>
+      </c>
+      <c r="O590" s="4" t="s">
+        <v>4556</v>
+      </c>
+      <c r="P590" s="4" t="s">
+        <v>4557</v>
+      </c>
+      <c r="Q590" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R590" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U590" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V590" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W590" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="591" spans="1:23">
+      <c r="A591" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B591" s="4">
+        <v>13</v>
+      </c>
+      <c r="C591" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D591" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E591" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F591" s="4">
+        <v>36</v>
+      </c>
+      <c r="G591" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H591" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I591" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J591" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K591" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L591" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M591" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N591" s="4" t="s">
+        <v>4558</v>
+      </c>
+      <c r="O591" s="4" t="s">
+        <v>4559</v>
+      </c>
+      <c r="P591" s="4" t="s">
+        <v>4560</v>
+      </c>
+      <c r="Q591" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R591" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S591" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T591" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U591" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V591" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W591" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="592" spans="1:23">
+      <c r="A592" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B592" s="4">
+        <v>14</v>
+      </c>
+      <c r="C592" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D592" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E592" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F592" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G592" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K592" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M592" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N592" s="4" t="s">
+        <v>4561</v>
+      </c>
+      <c r="O592" s="4" t="s">
+        <v>4562</v>
+      </c>
+      <c r="P592" s="4" t="s">
+        <v>4563</v>
+      </c>
+      <c r="Q592" s="4">
+        <v>1</v>
+      </c>
+      <c r="R592" s="4">
+        <v>1</v>
+      </c>
+      <c r="S592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U592" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V592" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W592" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -65921,7 +69306,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FF8F3C-B975-44A1-AEC1-A0B924B73AFA}">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="28.28515625" style="4" customWidth="1"/>
@@ -68590,6 +71975,296 @@
       </c>
       <c r="I96" s="4" t="s">
         <v>3928</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>4598</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>4599</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>4600</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>4601</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>4602</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>4603</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>4604</v>
+      </c>
+      <c r="F98" s="4">
+        <v>2</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>4605</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>4606</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>4607</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>4608</v>
+      </c>
+      <c r="F99" s="4">
+        <v>3</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>4610</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>4611</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>4612</v>
+      </c>
+      <c r="F100" s="4">
+        <v>4</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>4614</v>
+      </c>
+      <c r="F101" s="4">
+        <v>1</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>4616</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>4617</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>4618</v>
+      </c>
+      <c r="F102" s="4">
+        <v>2</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>4619</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>4620</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>4621</v>
+      </c>
+      <c r="F103" s="4">
+        <v>3</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>4623</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>4624</v>
+      </c>
+      <c r="F104" s="4">
+        <v>4</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>4626</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>4627</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>4628</v>
+      </c>
+      <c r="F105" s="4">
+        <v>5</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>4629</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="4" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>4630</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>4631</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>4632</v>
+      </c>
+      <c r="F106" s="4">
+        <v>6</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>4633</v>
       </c>
     </row>
   </sheetData>

--- a/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
+++ b/docs/domain/Memgine_Physical_Data_Model_catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MynikaTech\memgine\docs\domain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E648539-C542-4F56-B93B-FFAA79B83836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354F09F5-5A12-44DB-88BA-14394BAE67E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="11" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="13" xr2:uid="{AA28BC4D-8219-43B9-8C16-6977709D904A}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity Catalogue" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18252" uniqueCount="4635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18546" uniqueCount="4690">
   <si>
     <t>Domain</t>
   </si>
@@ -13949,6 +13949,171 @@
   </si>
   <si>
     <t>QR_CODE</t>
+  </si>
+  <si>
+    <t>QRACQATTR</t>
+  </si>
+  <si>
+    <t>QR Acquisition</t>
+  </si>
+  <si>
+    <t>QR Membership Acquisition Attribution</t>
+  </si>
+  <si>
+    <t>qr_membership_acquisition_attributions</t>
+  </si>
+  <si>
+    <t>Links a successful business-membership QR scan to the membership subscription created from that acquisition journey.</t>
+  </si>
+  <si>
+    <t>qr_membership_acquisition_attribution_id</t>
+  </si>
+  <si>
+    <t>Attributed At</t>
+  </si>
+  <si>
+    <t>Relationship entity connecting a qualifying QR scan to the resulting membership subscription without modifying QR Scan History.</t>
+  </si>
+  <si>
+    <t>QR Membership Acquisition Attribution Identifier</t>
+  </si>
+  <si>
+    <t>Uniquely identifies the acquisition attribution record.</t>
+  </si>
+  <si>
+    <t>System-generated identifier for the attribution record.</t>
+  </si>
+  <si>
+    <t>Represents the relationship between a QR scan and the resulting membership subscription.</t>
+  </si>
+  <si>
+    <t>Identifies the QR scan that generated the acquisition journey.</t>
+  </si>
+  <si>
+    <t>References the source QR Scan History record.</t>
+  </si>
+  <si>
+    <t>Links the membership acquisition attribution to the immutable QR scan event.</t>
+  </si>
+  <si>
+    <t>Identifies the membership subscription created from the QR acquisition journey.</t>
+  </si>
+  <si>
+    <t>References the resulting membership subscription.</t>
+  </si>
+  <si>
+    <t>Links the QR scan to the membership purchased from that journey.</t>
+  </si>
+  <si>
+    <t>Identifies the organization associated with the acquisition.</t>
+  </si>
+  <si>
+    <t>References the organization owning the QR and membership.</t>
+  </si>
+  <si>
+    <t>Preserves tenant context for attribution reporting.</t>
+  </si>
+  <si>
+    <t>Identifies the membership product acquired.</t>
+  </si>
+  <si>
+    <t>References the membership product associated with the subscription plan.</t>
+  </si>
+  <si>
+    <t>Supports membership-product-level acquisition analytics.</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>Identifies the customer associated with the attributed acquisition when known.</t>
+  </si>
+  <si>
+    <t>References the customer associated with the organization user.</t>
+  </si>
+  <si>
+    <t>Supports customer-level QR acquisition analytics.</t>
+  </si>
+  <si>
+    <t>attributed_at</t>
+  </si>
+  <si>
+    <t>Records when the QR scan was attributed to the subscription.</t>
+  </si>
+  <si>
+    <t>Timestamp when attribution was created.</t>
+  </si>
+  <si>
+    <t>Records the point at which the scan-to-subscription relationship was established.</t>
+  </si>
+  <si>
+    <t>Timestamp when the attribution record was created.</t>
+  </si>
+  <si>
+    <t>Identifies the user or system that created the attribution.</t>
+  </si>
+  <si>
+    <t>References the creating user when available.</t>
+  </si>
+  <si>
+    <t>Organization has QR Membership Acquisition Attributions</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Each acquisition attribution belongs to one organization.</t>
+  </si>
+  <si>
+    <t>Scan History has Acquisition Attribution</t>
+  </si>
+  <si>
+    <t>1:0..1</t>
+  </si>
+  <si>
+    <t>A QR scan may result in zero or one membership acquisition attribution.</t>
+  </si>
+  <si>
+    <t>Subscription has QR Acquisition Attribution</t>
+  </si>
+  <si>
+    <t>A membership subscription may have zero or one QR acquisition attribution.</t>
+  </si>
+  <si>
+    <t>Membership Product has QR Acquisition Attributions</t>
+  </si>
+  <si>
+    <t>Identifies the membership product acquired through the QR journey.</t>
+  </si>
+  <si>
+    <t>QR Code has Scan History</t>
+  </si>
+  <si>
+    <t>Each QR scan history record references the QR Code that was scanned.</t>
+  </si>
+  <si>
+    <t>QR Code has QR Code Type</t>
+  </si>
+  <si>
+    <t>Identifies the journey type configured for the QR Code.</t>
+  </si>
+  <si>
+    <t>REL095</t>
+  </si>
+  <si>
+    <t>REL096</t>
+  </si>
+  <si>
+    <t>REL097</t>
+  </si>
+  <si>
+    <t>REL098</t>
+  </si>
+  <si>
+    <t>REL099</t>
+  </si>
+  <si>
+    <t>REL100</t>
   </si>
 </sst>
 </file>
@@ -14180,7 +14345,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q51" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3841114F-D1EC-49B1-850B-590431E39412}" name="Table2" displayName="Table2" ref="A1:Q52" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FEF6275C-74E6-4563-BFF3-6461E4A3D8DA}" name="Entity Code" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{67FE23FD-539D-4023-BA73-D2A0B84718BF}" name="Domain" dataDxfId="15"/>
@@ -14501,7 +14666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4659496D-1A4F-4BC3-BD65-377E70E6B8BE}">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -17206,6 +17371,59 @@
         <v>4460</v>
       </c>
     </row>
+    <row r="52" spans="1:17" ht="60">
+      <c r="A52" s="4" t="s">
+        <v>4635</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>4636</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>4638</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>4639</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>4640</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>4641</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>4642</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -20781,7 +20999,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85B9BC7-C8C8-4E3E-A0EF-02B9554CEAE5}">
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -23703,7 +23921,7 @@
         <v>4431</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" ht="30">
       <c r="A84" s="4" t="s">
         <v>4564</v>
       </c>
@@ -23808,7 +24026,7 @@
         <v>4571</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" ht="30">
       <c r="A87" s="4" t="s">
         <v>4572</v>
       </c>
@@ -23948,7 +24166,7 @@
         <v>4583</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" ht="30">
       <c r="A91" s="4" t="s">
         <v>4584</v>
       </c>
@@ -24018,7 +24236,7 @@
         <v>4588</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" ht="30">
       <c r="A93" s="4" t="s">
         <v>4589</v>
       </c>
@@ -24053,7 +24271,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" ht="30">
       <c r="A94" s="4" t="s">
         <v>4592</v>
       </c>
@@ -24088,7 +24306,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" ht="30">
       <c r="A95" s="4" t="s">
         <v>4595</v>
       </c>
@@ -24121,6 +24339,216 @@
       </c>
       <c r="K95" s="4" t="s">
         <v>4597</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="45">
+      <c r="A96" s="4" t="s">
+        <v>4684</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>4670</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>4672</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="30">
+      <c r="A97" s="4" t="s">
+        <v>4685</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>4673</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>4444</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>4674</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="30">
+      <c r="A98" s="4" t="s">
+        <v>4686</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>4676</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>4674</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>4677</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="30">
+      <c r="A99" s="4" t="s">
+        <v>4687</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>4678</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="30">
+      <c r="A100" s="4" t="s">
+        <v>4688</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>4680</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>4437</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>4681</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="4" t="s">
+        <v>4689</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>4434</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>4682</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>4671</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>4451</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>4683</v>
       </c>
     </row>
   </sheetData>
@@ -28178,7 +28606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21F442-9136-4C15-8BA3-92E07332B93A}">
-  <dimension ref="A1:W592"/>
+  <dimension ref="A1:W602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="4" customWidth="1"/>
@@ -66934,7 +67362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="563" spans="1:23">
+    <row r="563" spans="1:23" ht="30">
       <c r="A563" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67005,7 +67433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="564" spans="1:23">
+    <row r="564" spans="1:23" ht="30">
       <c r="A564" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67076,7 +67504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="565" spans="1:23">
+    <row r="565" spans="1:23" ht="45">
       <c r="A565" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67147,7 +67575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="566" spans="1:23">
+    <row r="566" spans="1:23" ht="60">
       <c r="A566" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67218,7 +67646,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="567" spans="1:23">
+    <row r="567" spans="1:23" ht="45">
       <c r="A567" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67289,7 +67717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="568" spans="1:23">
+    <row r="568" spans="1:23" ht="45">
       <c r="A568" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67360,7 +67788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="569" spans="1:23">
+    <row r="569" spans="1:23" ht="45">
       <c r="A569" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67431,7 +67859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="570" spans="1:23">
+    <row r="570" spans="1:23" ht="45">
       <c r="A570" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67502,7 +67930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="571" spans="1:23">
+    <row r="571" spans="1:23" ht="45">
       <c r="A571" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67573,7 +68001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="572" spans="1:23">
+    <row r="572" spans="1:23" ht="30">
       <c r="A572" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67644,7 +68072,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="573" spans="1:23">
+    <row r="573" spans="1:23" ht="30">
       <c r="A573" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67715,7 +68143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="574" spans="1:23">
+    <row r="574" spans="1:23" ht="30">
       <c r="A574" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67786,7 +68214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="575" spans="1:23">
+    <row r="575" spans="1:23" ht="30">
       <c r="A575" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67857,7 +68285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="576" spans="1:23">
+    <row r="576" spans="1:23" ht="30">
       <c r="A576" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67928,7 +68356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="577" spans="1:23">
+    <row r="577" spans="1:23" ht="30">
       <c r="A577" s="4" t="s">
         <v>4434</v>
       </c>
@@ -67999,7 +68427,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="578" spans="1:23">
+    <row r="578" spans="1:23" ht="30">
       <c r="A578" s="4" t="s">
         <v>4434</v>
       </c>
@@ -68070,7 +68498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="579" spans="1:23">
+    <row r="579" spans="1:23" ht="30">
       <c r="A579" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68141,7 +68569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="580" spans="1:23">
+    <row r="580" spans="1:23" ht="30">
       <c r="A580" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68212,7 +68640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="581" spans="1:23">
+    <row r="581" spans="1:23" ht="45">
       <c r="A581" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68283,7 +68711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="582" spans="1:23">
+    <row r="582" spans="1:23" ht="30">
       <c r="A582" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68354,7 +68782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="583" spans="1:23">
+    <row r="583" spans="1:23" ht="30">
       <c r="A583" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68425,7 +68853,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="584" spans="1:23">
+    <row r="584" spans="1:23" ht="30">
       <c r="A584" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68496,7 +68924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="585" spans="1:23">
+    <row r="585" spans="1:23" ht="45">
       <c r="A585" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68567,7 +68995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="586" spans="1:23">
+    <row r="586" spans="1:23" ht="45">
       <c r="A586" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68638,7 +69066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="587" spans="1:23">
+    <row r="587" spans="1:23" ht="30">
       <c r="A587" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68709,7 +69137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="588" spans="1:23">
+    <row r="588" spans="1:23" ht="30">
       <c r="A588" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68780,7 +69208,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="589" spans="1:23">
+    <row r="589" spans="1:23" ht="45">
       <c r="A589" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68851,7 +69279,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="590" spans="1:23">
+    <row r="590" spans="1:23" ht="30">
       <c r="A590" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68922,7 +69350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="591" spans="1:23">
+    <row r="591" spans="1:23" ht="45">
       <c r="A591" s="4" t="s">
         <v>4441</v>
       </c>
@@ -68993,7 +69421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="592" spans="1:23">
+    <row r="592" spans="1:23" ht="30">
       <c r="A592" s="4" t="s">
         <v>4441</v>
       </c>
@@ -69061,6 +69489,716 @@
         <v>6</v>
       </c>
       <c r="W592" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="593" spans="1:23">
+      <c r="A593" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B593" s="4">
+        <v>1</v>
+      </c>
+      <c r="C593" s="4" t="s">
+        <v>4643</v>
+      </c>
+      <c r="D593" s="4" t="s">
+        <v>4640</v>
+      </c>
+      <c r="E593" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F593" s="4">
+        <v>36</v>
+      </c>
+      <c r="G593" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H593" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I593" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J593" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K593" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L593" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M593" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N593" s="4" t="s">
+        <v>4644</v>
+      </c>
+      <c r="O593" s="4" t="s">
+        <v>4645</v>
+      </c>
+      <c r="P593" s="4" t="s">
+        <v>4646</v>
+      </c>
+      <c r="Q593" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R593" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="S593" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T593" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U593" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V593" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W593" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="594" spans="1:23">
+      <c r="A594" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B594" s="4">
+        <v>2</v>
+      </c>
+      <c r="C594" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="D594" s="4" t="s">
+        <v>4444</v>
+      </c>
+      <c r="E594" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F594" s="4">
+        <v>36</v>
+      </c>
+      <c r="G594" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H594" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I594" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J594" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K594" s="4" t="s">
+        <v>4441</v>
+      </c>
+      <c r="L594" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M594" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N594" s="4" t="s">
+        <v>4647</v>
+      </c>
+      <c r="O594" s="4" t="s">
+        <v>4648</v>
+      </c>
+      <c r="P594" s="4" t="s">
+        <v>4649</v>
+      </c>
+      <c r="Q594" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R594" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S594" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T594" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U594" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V594" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W594" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="595" spans="1:23">
+      <c r="A595" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B595" s="4">
+        <v>3</v>
+      </c>
+      <c r="C595" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D595" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E595" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F595" s="4">
+        <v>36</v>
+      </c>
+      <c r="G595" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H595" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I595" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J595" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K595" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="L595" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M595" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N595" s="4" t="s">
+        <v>4650</v>
+      </c>
+      <c r="O595" s="4" t="s">
+        <v>4651</v>
+      </c>
+      <c r="P595" s="4" t="s">
+        <v>4652</v>
+      </c>
+      <c r="Q595" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R595" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S595" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T595" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U595" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V595" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W595" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="596" spans="1:23">
+      <c r="A596" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B596" s="4">
+        <v>4</v>
+      </c>
+      <c r="C596" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D596" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E596" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F596" s="4">
+        <v>36</v>
+      </c>
+      <c r="G596" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H596" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I596" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J596" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K596" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L596" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M596" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N596" s="4" t="s">
+        <v>4653</v>
+      </c>
+      <c r="O596" s="4" t="s">
+        <v>4654</v>
+      </c>
+      <c r="P596" s="4" t="s">
+        <v>4655</v>
+      </c>
+      <c r="Q596" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R596" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S596" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T596" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U596" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V596" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W596" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="597" spans="1:23">
+      <c r="A597" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B597" s="4">
+        <v>5</v>
+      </c>
+      <c r="C597" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D597" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E597" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F597" s="4">
+        <v>36</v>
+      </c>
+      <c r="G597" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H597" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I597" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J597" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K597" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L597" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M597" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N597" s="4" t="s">
+        <v>4656</v>
+      </c>
+      <c r="O597" s="4" t="s">
+        <v>4657</v>
+      </c>
+      <c r="P597" s="4" t="s">
+        <v>4658</v>
+      </c>
+      <c r="Q597" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R597" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S597" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T597" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U597" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V597" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W597" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="598" spans="1:23">
+      <c r="A598" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B598" s="4">
+        <v>6</v>
+      </c>
+      <c r="C598" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D598" s="4" t="s">
+        <v>4659</v>
+      </c>
+      <c r="E598" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F598" s="4">
+        <v>36</v>
+      </c>
+      <c r="G598" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H598" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I598" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J598" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K598" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L598" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M598" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N598" s="4" t="s">
+        <v>4660</v>
+      </c>
+      <c r="O598" s="4" t="s">
+        <v>4661</v>
+      </c>
+      <c r="P598" s="4" t="s">
+        <v>4662</v>
+      </c>
+      <c r="Q598" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R598" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S598" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T598" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U598" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V598" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="W598" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="599" spans="1:23">
+      <c r="A599" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B599" s="4">
+        <v>7</v>
+      </c>
+      <c r="C599" s="4" t="s">
+        <v>4641</v>
+      </c>
+      <c r="D599" s="4" t="s">
+        <v>4663</v>
+      </c>
+      <c r="E599" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F599" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G599" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H599" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I599" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J599" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K599" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L599" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M599" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N599" s="4" t="s">
+        <v>4664</v>
+      </c>
+      <c r="O599" s="4" t="s">
+        <v>4665</v>
+      </c>
+      <c r="P599" s="4" t="s">
+        <v>4666</v>
+      </c>
+      <c r="Q599" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R599" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S599" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T599" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U599" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V599" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W599" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="600" spans="1:23">
+      <c r="A600" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B600" s="4">
+        <v>8</v>
+      </c>
+      <c r="C600" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D600" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E600" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F600" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G600" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K600" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M600" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N600" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="O600" s="4" t="s">
+        <v>4667</v>
+      </c>
+      <c r="P600" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q600" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R600" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U600" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V600" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W600" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="601" spans="1:23">
+      <c r="A601" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B601" s="4">
+        <v>9</v>
+      </c>
+      <c r="C601" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D601" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E601" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F601" s="4">
+        <v>36</v>
+      </c>
+      <c r="G601" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H601" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I601" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J601" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K601" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L601" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M601" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N601" s="4" t="s">
+        <v>4668</v>
+      </c>
+      <c r="O601" s="4" t="s">
+        <v>4669</v>
+      </c>
+      <c r="P601" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q601" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="R601" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S601" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="T601" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="U601" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V601" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W601" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="602" spans="1:23">
+      <c r="A602" s="4" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B602" s="4">
+        <v>10</v>
+      </c>
+      <c r="C602" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D602" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E602" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F602" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G602" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K602" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="L602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M602" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N602" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="O602" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="P602" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="Q602" s="4">
+        <v>1</v>
+      </c>
+      <c r="R602" s="4">
+        <v>1</v>
+      </c>
+      <c r="S602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U602" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V602" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W602" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -71977,7 +73115,7 @@
         <v>3928</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" ht="90">
       <c r="A97" s="4" t="s">
         <v>4448</v>
       </c>
@@ -72006,7 +73144,7 @@
         <v>4601</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" ht="60">
       <c r="A98" s="4" t="s">
         <v>4448</v>
       </c>
@@ -72035,7 +73173,7 @@
         <v>4605</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" ht="75">
       <c r="A99" s="4" t="s">
         <v>4448</v>
       </c>
@@ -72064,7 +73202,7 @@
         <v>4609</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" ht="75">
       <c r="A100" s="4" t="s">
         <v>4448</v>
       </c>
@@ -72093,7 +73231,7 @@
         <v>4613</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" ht="30">
       <c r="A101" s="4" t="s">
         <v>4455</v>
       </c>
@@ -72122,7 +73260,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" ht="30">
       <c r="A102" s="4" t="s">
         <v>4455</v>
       </c>
@@ -72151,7 +73289,7 @@
         <v>4619</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" ht="60">
       <c r="A103" s="4" t="s">
         <v>4455</v>
       </c>
@@ -72180,7 +73318,7 @@
         <v>4622</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" ht="30">
       <c r="A104" s="4" t="s">
         <v>4455</v>
       </c>
@@ -72209,7 +73347,7 @@
         <v>4625</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" ht="75">
       <c r="A105" s="4" t="s">
         <v>4455</v>
       </c>
@@ -72238,7 +73376,7 @@
         <v>4629</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" ht="75">
       <c r="A106" s="4" t="s">
         <v>4455</v>
       </c>
